--- a/public/data/List_Team_Region.xlsx
+++ b/public/data/List_Team_Region.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muham\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7768B6AB-0CE5-4F90-96F2-7064F204EF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9088B6B0-BA65-4C94-9BFB-186DA718DD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2205" windowWidth="21600" windowHeight="11340" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="636">
   <si>
     <t>JAMBI</t>
   </si>
@@ -80,9 +80,6 @@
     <t>SBS-MERANTI.JAYA-MA5801-OLT-01</t>
   </si>
   <si>
-    <t>All OLT Muara Bulian</t>
-  </si>
-  <si>
     <t>SBS-PAYOSELINCAH.ATAS-HW.MA5801-OLT-02</t>
   </si>
   <si>
@@ -158,12 +155,6 @@
     <t>SBS-MENDALO-MA5801-OLT-01</t>
   </si>
   <si>
-    <t>ALL OLT Sarolangun</t>
-  </si>
-  <si>
-    <t>Mampun Baru</t>
-  </si>
-  <si>
     <t>SBS-MUARA.TEMBESI-HW.MA5801-OLT-01</t>
   </si>
   <si>
@@ -203,9 +194,6 @@
     <t>SBS-TEGAL.ARUM-HW.MA5801-OLT-01</t>
   </si>
   <si>
-    <t>Telanai Pura,</t>
-  </si>
-  <si>
     <t>SBS-TANJUNG.BENUANG-RC-OLT-01</t>
   </si>
   <si>
@@ -311,9 +299,6 @@
     <t>SERPO JAMBI KOTA</t>
   </si>
   <si>
-    <t>SERPO BUNGO2</t>
-  </si>
-  <si>
     <t>SERPO SAROLANGUN</t>
   </si>
   <si>
@@ -332,24 +317,12 @@
     <t xml:space="preserve">SERPO KUALA TUNGKAL </t>
   </si>
   <si>
-    <t>bungo</t>
-  </si>
-  <si>
-    <t>ALL OLT Muara Bungo</t>
-  </si>
-  <si>
     <t xml:space="preserve">  SBS-MUARA.BULIAN-FH.AN6001-G16-OLT-01</t>
   </si>
   <si>
-    <t xml:space="preserve">  SBS-SUNGAI.PENUH-HW.MA5801-OLT-03</t>
-  </si>
-  <si>
     <t>SBS-KUALA.TUNGKAL-RC-OLT-01</t>
   </si>
   <si>
-    <t>tebo</t>
-  </si>
-  <si>
     <t>SBS-PASAR.BUNGO-HW.MA5801-OLT-02</t>
   </si>
   <si>
@@ -371,31 +344,12 @@
     <t>SBS-AURDURI.BAGANPETE-RC-OLT-01</t>
   </si>
   <si>
-    <t>SBS-RIMBO.TENGAH-HW.MA5801-OLT-01</t>
-  </si>
-  <si>
-    <t>w</t>
-  </si>
-  <si>
-    <t>Merangin</t>
-  </si>
-  <si>
     <t>SBS-BATIN.TIGA-RC-OLT-01</t>
   </si>
   <si>
-    <t>sidodadi</t>
-  </si>
-  <si>
     <t xml:space="preserve">  SBS-TELANAI.PURA-HW.MA5801-OLT-01</t>
   </si>
   <si>
-    <t>SBS-SUNGAI.ULAK-HW.MA5801-OLT-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A
-</t>
-  </si>
-  <si>
     <t>SBS-PEMATANG.GAJAH-HW.MA5801-OLT-01</t>
   </si>
   <si>
@@ -570,36 +524,15 @@
     <t>SBS-KALIREJO-HW.MA5801-OLT-01</t>
   </si>
   <si>
-    <t>ALL OLT KOTA AGUNG</t>
-  </si>
-  <si>
-    <t>ALL OLT BANDAR JAYA</t>
-  </si>
-  <si>
     <t>SBS-TANJUNG.SENANG-HW.MA5801-OLT-01</t>
   </si>
   <si>
     <t>SBS-PAGELARAN-MA5801-OLT-01</t>
   </si>
   <si>
-    <t>ALL OLT GISTING</t>
-  </si>
-  <si>
-    <t>ALL OLT LEMPUYANG BANDAR</t>
-  </si>
-  <si>
     <t>SBS-SUKABUMI-HW.MA5801-OLT-01</t>
   </si>
   <si>
-    <t>ALL OLT PRINGSEWU</t>
-  </si>
-  <si>
-    <t>ALL OLT TALANG PADANG</t>
-  </si>
-  <si>
-    <t>GNSA</t>
-  </si>
-  <si>
     <t xml:space="preserve">SBS-BRANTI-HW.MA5801-OLT-01 </t>
   </si>
   <si>
@@ -642,9 +575,6 @@
     <t>SBS-KARANG.ANYAR-HW.MA5801-OLT-01</t>
   </si>
   <si>
-    <t>KARANG ANYAR</t>
-  </si>
-  <si>
     <t>wahyu</t>
   </si>
   <si>
@@ -714,18 +644,12 @@
     <t>SBS-KOTA.BUMI-HW.MA5801-OLT-02</t>
   </si>
   <si>
-    <t>Bandar Jaya</t>
-  </si>
-  <si>
     <t>SBS-SRIBAWONO-HW.MA5801-OLT-02</t>
   </si>
   <si>
     <t>SBS-LEMPUYANG.BANDAR-HW.MA5801-OLT-01</t>
   </si>
   <si>
-    <t>OLT DOWN JUGA SAMA</t>
-  </si>
-  <si>
     <t xml:space="preserve"> SBS-TELUK.BETUNG-HW.MA5801-OLT-01</t>
   </si>
   <si>
@@ -744,9 +668,6 @@
     <t>SBS-PEKALONGAN-HW.MA5801-OLT-01</t>
   </si>
   <si>
-    <t>ALL METRO</t>
-  </si>
-  <si>
     <t>SEMANGAT</t>
   </si>
   <si>
@@ -1392,9 +1313,6 @@
     <t>SBS-KAUR-RAISECOM-OLT-01</t>
   </si>
   <si>
-    <t>SBS-CURUP-HW.MA5801-OLT-04</t>
-  </si>
-  <si>
     <t>SBS-MANNA-RC-OLT-02</t>
   </si>
   <si>
@@ -1605,12 +1523,6 @@
     <t>SERPO MUKO-MUKO</t>
   </si>
   <si>
-    <t>SERPO MUKO-MUKO2</t>
-  </si>
-  <si>
-    <t>SERPO MUKO-MUKO3</t>
-  </si>
-  <si>
     <t>SBS-ARGA.MAKMUR-HW.MA5801-OLT-02</t>
   </si>
   <si>
@@ -1620,9 +1532,6 @@
     <t>Simbika</t>
   </si>
   <si>
-    <t>BABEL</t>
-  </si>
-  <si>
     <t>RITEL BABEL</t>
   </si>
   <si>
@@ -1647,9 +1556,6 @@
     <t>TTM TOBOALI</t>
   </si>
   <si>
-    <t xml:space="preserve"> SBS-CABANG.BANGKA-AN6001.G16-OLT-01</t>
-  </si>
-  <si>
     <t>SBS-SUNGAI.LIAT-HW.MA5801-OLT-01</t>
   </si>
   <si>
@@ -1668,9 +1574,6 @@
     <t>SBS-TOBOALI-MA5801-OLT-01</t>
   </si>
   <si>
-    <t xml:space="preserve"> SBS-KERABUT-HW.MA5801-OLT-01</t>
-  </si>
-  <si>
     <t>SBS-BUKIT.BETUNG-HW.MA5801-OLT-01</t>
   </si>
   <si>
@@ -1713,18 +1616,12 @@
     <t>SBS-TELEK-HW.MA5801-OLT-01</t>
   </si>
   <si>
-    <t>wilayah</t>
-  </si>
-  <si>
     <t>SBS-SINARJAYA-HW.MA5801-OLT-01</t>
   </si>
   <si>
     <t>SBS-AIR.KETEKOK-HW.MA5801-OLT-01</t>
   </si>
   <si>
-    <t>SBS-MISLAK-HW.MA5801-OLT-02</t>
-  </si>
-  <si>
     <t>SBS-SADAI-RC-OLT-01</t>
   </si>
   <si>
@@ -1767,9 +1664,6 @@
     <t>SBS-SHELTER.TANJUNG.PANDAN-AN6001.G16-OLT-01</t>
   </si>
   <si>
-    <t>parit tiga</t>
-  </si>
-  <si>
     <t>SBS-LUBUK.BESAR-HW.MA5801-OLT-01</t>
   </si>
   <si>
@@ -1791,9 +1685,6 @@
     <t>SBS-SUKAL-HW.MA5801-OLT-01</t>
   </si>
   <si>
-    <t>UIW Babel</t>
-  </si>
-  <si>
     <t>SBS-BATU.RUSA-HW.MA5801-OLT-01</t>
   </si>
   <si>
@@ -1857,9 +1748,6 @@
     <t>FEEDER BABEL</t>
   </si>
   <si>
-    <t>SERPO KOBA (Tarapti)</t>
-  </si>
-  <si>
     <t>SERPO PANGKAL PINANG</t>
   </si>
   <si>
@@ -1890,9 +1778,6 @@
     <t>SBS-PLTD.MANGGAR-AN6001.G16-OLT-01</t>
   </si>
   <si>
-    <t>seputih</t>
-  </si>
-  <si>
     <t>SBS-SUNGAI.LIAT.3-RC-OLT-01</t>
   </si>
   <si>
@@ -1905,33 +1790,18 @@
     <t>SBS-AIR.NANGKA-HW.MA5801-OLT-01</t>
   </si>
   <si>
-    <t>SBS-TANJUNG.NIUR-RC-OLT-01</t>
-  </si>
-  <si>
     <t>SBS-GANTUNG-HW.MA5801-OLT-01</t>
   </si>
   <si>
-    <t>UP 3 Bangka (OLT DOWN)</t>
-  </si>
-  <si>
     <t>SBS-PULAU.LEPAR-RC-OLT-01</t>
   </si>
   <si>
-    <t>Muntok (OLT DOWN)</t>
-  </si>
-  <si>
     <t>SBS-MENTIGI-RC-OLT-01</t>
   </si>
   <si>
-    <t>Teluk Limau (OLT DOWN)</t>
-  </si>
-  <si>
     <t>SBS-TANJUNG.PANDAN-HW.MA5801-OLT-04</t>
   </si>
   <si>
-    <t>UIW Babel (OLT DOWN)</t>
-  </si>
-  <si>
     <t>SBS-KAYU.ARANG-RC-OLT-01</t>
   </si>
   <si>
@@ -1944,15 +1814,9 @@
     <t>SBS-SIMPANG.RIMBA-HW.MA5801-OLT-01</t>
   </si>
   <si>
-    <t>Tuatunu (OLT DOWN)</t>
-  </si>
-  <si>
     <t>SBS-TEMPILANG-HW.MA5801-OLT-01</t>
   </si>
   <si>
-    <t>SBS-TIANG.TARA-RC-OLT-01</t>
-  </si>
-  <si>
     <t>SBS-DALIL-RC-OLT-01</t>
   </si>
   <si>
@@ -1965,10 +1829,121 @@
     <t>SBS-PANGKAL.NIUR-FH.AN6001.G16-OLT-01</t>
   </si>
   <si>
-    <t>BALUNIJUK</t>
-  </si>
-  <si>
     <t>Tarapti</t>
+  </si>
+  <si>
+    <t>SBS-TELANAI.PURA-HW.MA5801-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-SAROLANGUN-HW.MA5801-OLT-02</t>
+  </si>
+  <si>
+    <t>SBS-PELAWAN-HW.MA5801-OLT-02</t>
+  </si>
+  <si>
+    <t>SBS-SINGKUT.3-HW.MA5801-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-SINGKUT.4-HW.MA5801-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-SINGKUT.7-HW.MA5801-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-MERANGIN2-RC-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-MUARA.BULIAN-FH.AN6001-G16-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-PASAR.BUNGO-RC-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-SUNGAI.PENUH-RC-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-AIR.HANGAT.TIMUR-HW.MA5801-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-SUNGAI.PENUH-HW.MA5801-OLT-02</t>
+  </si>
+  <si>
+    <t>SBS-SUNGAI.PENUH-HW.MA5801-OLT-03</t>
+  </si>
+  <si>
+    <t>SBS-PRINGSEWU-MA5801-OLT-02</t>
+  </si>
+  <si>
+    <t>SBS-PRINGSEWU-HW.MA5801-OLT-03</t>
+  </si>
+  <si>
+    <t>SBS-GISTING-MA5801-OLT-02</t>
+  </si>
+  <si>
+    <t>SBS-TALANG.PADANG-RC-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-TALANG.PADANG-HW.MA5801-OLT-03</t>
+  </si>
+  <si>
+    <t>SBS-BANDAR.JAYA-HW.MA5801-OLT-02</t>
+  </si>
+  <si>
+    <t>SBS-BANDAR.JAYA-HW.MA5801-OLT-03</t>
+  </si>
+  <si>
+    <t>SBS-UP3.METRO-RC-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-METRO-FH.AN6001.G16-OLT-02</t>
+  </si>
+  <si>
+    <t>SBS-METRO.TIMUR-HW.MA5801-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-METRO.KOTA-HW.MA5801-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-METRO.UTARA-HW.MA5801-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-METRO.PUSAT-HW.MA5801-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-METRO.BARAT-HW.MA5801-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-METRO.SELATAN-HW.MA5801-OLT-01</t>
+  </si>
+  <si>
+    <t>SERPO PEKALONGAN</t>
+  </si>
+  <si>
+    <t>SERPO KAUR</t>
+  </si>
+  <si>
+    <t>SBS-CABANG.BANGKA-AN6001.G16-OLT-02</t>
+  </si>
+  <si>
+    <t>SBS-SUNGAI.LIAT.2-HW.MA5801-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-T.PANDAN.3-RC-OLT-1</t>
+  </si>
+  <si>
+    <t>SBS-MUNTOK-MA5801-OLT-02</t>
+  </si>
+  <si>
+    <t>SBS-TELUK-LIMAU-RC-OLT-02</t>
+  </si>
+  <si>
+    <t>SBS-TOBOALI-MA5801-OLT-02</t>
+  </si>
+  <si>
+    <t>SBS-TJ.NIUR-RC-OLT-01</t>
+  </si>
+  <si>
+    <t>BANGKA BELITUNG</t>
   </si>
 </sst>
 </file>
@@ -2207,17 +2182,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2267,11 +2233,50 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2503,7 +2508,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}" name="Table919" displayName="Table919" ref="B3:H22" totalsRowShown="0" headerRowDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}" name="Table919" displayName="Table919" ref="B3:H22" totalsRowShown="0" headerRowDxfId="14">
   <autoFilter ref="B3:H22" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{1E18F602-B85E-4C85-8C34-8684E3651598}" name="INTERNAL JAMBI"/>
@@ -2519,7 +2524,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}" name="Table27" displayName="Table27" ref="B130:T147" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}" name="Table27" displayName="Table27" ref="B130:T147" totalsRowShown="0" headerRowDxfId="3">
   <autoFilter ref="B130:T147" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{F8A4E442-73AD-4EB9-BB0D-D55E87DA1888}" name="SERPO PALEMBANG KOTA"/>
@@ -2547,26 +2552,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57681EA6-18EF-4E05-B178-44A6E049B133}" name="Table1020" displayName="Table1020" ref="B26:K44" totalsRowShown="0" headerRowDxfId="10">
-  <autoFilter ref="B26:K44" xr:uid="{57681EA6-18EF-4E05-B178-44A6E049B133}"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57681EA6-18EF-4E05-B178-44A6E049B133}" name="Table1020" displayName="Table1020" ref="B26:J44" totalsRowShown="0" headerRowDxfId="13">
+  <autoFilter ref="B26:J44" xr:uid="{57681EA6-18EF-4E05-B178-44A6E049B133}"/>
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{A8602C42-C67C-43B1-B2C0-728995582D93}" name="SERPO BUNGO"/>
     <tableColumn id="2" xr3:uid="{619A7501-DACA-4455-8C0A-1CD6591C8FA5}" name="SERPO PAYOSELINCAH"/>
     <tableColumn id="3" xr3:uid="{E1FD6AAE-454C-4AEB-AE78-3D7DE2FD86CD}" name="SERPO JAMBI KOTA"/>
-    <tableColumn id="4" xr3:uid="{8C7936D5-21B6-4BC7-B145-A4B7FE39A1B9}" name="SERPO BUNGO2"/>
-    <tableColumn id="5" xr3:uid="{B0DF24BD-707B-477E-9292-33344AF6BE5C}" name="SERPO SAROLANGUN"/>
-    <tableColumn id="6" xr3:uid="{915D1D23-08B2-4174-9624-B5C4DC7CEDC6}" name="SERPO MUARA BULIAN"/>
-    <tableColumn id="7" xr3:uid="{212A932D-9B54-42B8-ABA9-E3869505C618}" name="SERPO BANGKO"/>
-    <tableColumn id="8" xr3:uid="{94B0E65E-2D30-4D05-B639-D4F5446CA52A}" name="SERPO SUNGAI PENUH"/>
-    <tableColumn id="9" xr3:uid="{FFB1E37C-CA89-4405-AD62-CF629F6847D8}" name="SERPO TEBO"/>
-    <tableColumn id="10" xr3:uid="{84D0B178-F454-41C3-B9F6-B0D8CA6CC010}" name="SERPO KUALA TUNGKAL "/>
+    <tableColumn id="4" xr3:uid="{8C7936D5-21B6-4BC7-B145-A4B7FE39A1B9}" name="SERPO SAROLANGUN"/>
+    <tableColumn id="5" xr3:uid="{B0DF24BD-707B-477E-9292-33344AF6BE5C}" name="SERPO MUARA BULIAN"/>
+    <tableColumn id="6" xr3:uid="{915D1D23-08B2-4174-9624-B5C4DC7CEDC6}" name="SERPO BANGKO"/>
+    <tableColumn id="7" xr3:uid="{212A932D-9B54-42B8-ABA9-E3869505C618}" name="SERPO SUNGAI PENUH"/>
+    <tableColumn id="8" xr3:uid="{94B0E65E-2D30-4D05-B639-D4F5446CA52A}" name="SERPO TEBO"/>
+    <tableColumn id="9" xr3:uid="{FFB1E37C-CA89-4405-AD62-CF629F6847D8}" name="SERPO KUALA TUNGKAL "/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C6FB933F-6103-42DE-BAEC-03E0FCFEB76C}" name="Table1121" displayName="Table1121" ref="B50:G78" totalsRowShown="0" headerRowDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C6FB933F-6103-42DE-BAEC-03E0FCFEB76C}" name="Table1121" displayName="Table1121" ref="B50:G78" totalsRowShown="0" headerRowDxfId="12">
   <autoFilter ref="B50:G78" xr:uid="{C6FB933F-6103-42DE-BAEC-03E0FCFEB76C}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{DCC806F7-D168-48B2-B03E-CCE7FD87EEA9}" name="SIB PESAWARAN"/>
@@ -2581,7 +2585,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6E2D26AE-ECD5-48A4-AC1D-1B4180A6F140}" name="Table1222" displayName="Table1222" ref="B82:J104" totalsRowShown="0" headerRowDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6E2D26AE-ECD5-48A4-AC1D-1B4180A6F140}" name="Table1222" displayName="Table1222" ref="B82:J104" totalsRowShown="0" headerRowDxfId="11">
   <autoFilter ref="B82:J104" xr:uid="{6E2D26AE-ECD5-48A4-AC1D-1B4180A6F140}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{060484FA-EE1E-4DC8-9A74-A60AA9B20548}" name="SERPO TEGINENENG_x0009__x0009_"/>
@@ -2599,7 +2603,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}" name="Table1323" displayName="Table1323" ref="B110:O127" totalsRowShown="0" headerRowDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}" name="Table1323" displayName="Table1323" ref="B110:O127" totalsRowShown="0" headerRowDxfId="10">
   <autoFilter ref="B110:O127" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{6FB6563D-399C-4506-8AF0-A312347E4888}" name="REG7 PALEMBANG 1"/>
@@ -2622,7 +2626,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}" name="Table1424" displayName="Table1424" ref="B152:I176" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="4" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}" name="Table1424" displayName="Table1424" ref="B152:I176" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7">
   <autoFilter ref="B152:I176" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{9BFFF82B-4674-404E-AC18-7772CF16890E}" name="GSP BENGKULU 1"/>
@@ -2639,23 +2643,23 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}" name="Table1525" displayName="Table1525" ref="B180:H210" totalsRowShown="0" headerRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}" name="Table1525" displayName="Table1525" ref="B180:H210" totalsRowShown="0" headerRowDxfId="6">
   <autoFilter ref="B180:H210" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{ACEB90AF-9CBB-4605-8377-2CF0EF299650}" name="SERPO SUKAMERINDU"/>
     <tableColumn id="2" xr3:uid="{351154A5-2DE7-411B-9044-B8641069B0BF}" name="SERPO BENGKULU KOTA"/>
     <tableColumn id="3" xr3:uid="{2D38274A-547B-4312-8D99-F58A44BF772F}" name="SERPO ARGA MAKMUR"/>
     <tableColumn id="4" xr3:uid="{A2545D3E-8190-44A6-8858-E9BEBEE6A78F}" name="SERPO MANNA"/>
-    <tableColumn id="5" xr3:uid="{E2E796D3-E5D5-48C0-A581-FC37CEF86CF8}" name="SERPO MUKO-MUKO"/>
-    <tableColumn id="6" xr3:uid="{8D02523D-F371-4D30-BD5B-523DFBE391C4}" name="SERPO MUKO-MUKO2"/>
-    <tableColumn id="7" xr3:uid="{F61B377D-5E04-42DF-B815-83A2C21A1209}" name="SERPO MUKO-MUKO3"/>
+    <tableColumn id="5" xr3:uid="{E2E796D3-E5D5-48C0-A581-FC37CEF86CF8}" name="SERPO PEKALONGAN"/>
+    <tableColumn id="6" xr3:uid="{8D02523D-F371-4D30-BD5B-523DFBE391C4}" name="SERPO MUKO-MUKO"/>
+    <tableColumn id="7" xr3:uid="{F61B377D-5E04-42DF-B815-83A2C21A1209}" name="SERPO KAUR"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}" name="Table1626" displayName="Table1626" ref="B215:H237" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}" name="Table1626" displayName="Table1626" ref="B215:H237" totalsRowShown="0" headerRowDxfId="5">
   <autoFilter ref="B215:H237" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D0B3A41D-F35E-4B89-AC56-18717B9B04E5}" name="BANGKA REG 7"/>
@@ -2671,16 +2675,15 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}" name="Table1727" displayName="Table1727" ref="B240:H260" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="B240:H260" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{97E25E83-847F-4991-A885-21D98063A2DB}" name="SERPO KOBA (Tarapti)"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}" name="Table1727" displayName="Table1727" ref="B240:G261" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="B240:G261" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{97E25E83-847F-4991-A885-21D98063A2DB}" name="SERPO KOBA"/>
     <tableColumn id="2" xr3:uid="{0AB964B5-883A-49C8-8DDA-C8EE93753519}" name="SERPO PANGKAL PINANG"/>
-    <tableColumn id="3" xr3:uid="{B1949157-6036-480A-8565-B43E67A7DC9E}" name="SERPO KOBA"/>
-    <tableColumn id="4" xr3:uid="{16ED9F1D-5BCA-48A2-8AE8-C95A6A70432A}" name="SERPO KELAPA"/>
-    <tableColumn id="5" xr3:uid="{CB6B9ED9-8C7C-40AB-9A3B-399FB8E1F2EC}" name="SERPO MANGGAR "/>
-    <tableColumn id="6" xr3:uid="{443B6D8A-EFC6-44D0-920E-2D26100E9F12}" name="SERPO BELITUNG"/>
-    <tableColumn id="7" xr3:uid="{722CEF2B-205F-4159-A478-ED91DC24EC64}" name="SERPO SUNGAI LIAT"/>
+    <tableColumn id="3" xr3:uid="{B1949157-6036-480A-8565-B43E67A7DC9E}" name="SERPO KELAPA"/>
+    <tableColumn id="4" xr3:uid="{16ED9F1D-5BCA-48A2-8AE8-C95A6A70432A}" name="SERPO MANGGAR "/>
+    <tableColumn id="5" xr3:uid="{CB6B9ED9-8C7C-40AB-9A3B-399FB8E1F2EC}" name="SERPO BELITUNG"/>
+    <tableColumn id="6" xr3:uid="{443B6D8A-EFC6-44D0-920E-2D26100E9F12}" name="SERPO SUNGAI LIAT"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3003,7 +3006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D0AF9EF-6686-405D-9473-604A5805FA6C}">
-  <dimension ref="A1:T260"/>
+  <dimension ref="A1:T262"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34.140625" customWidth="1"/>
@@ -3036,45 +3039,45 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-    </row>
-    <row r="3" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+    </row>
+    <row r="3" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3089,3773 +3092,3817 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
+        <v>605</v>
+      </c>
+      <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>16</v>
-      </c>
-      <c r="H4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
+        <v>599</v>
+      </c>
+      <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>21</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>22</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>23</v>
-      </c>
-      <c r="H5" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
+        <v>604</v>
+      </c>
+      <c r="E6" t="s">
         <v>27</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>28</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>29</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>30</v>
-      </c>
-      <c r="H6" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>600</v>
       </c>
       <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
         <v>34</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>35</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>36</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>37</v>
-      </c>
-      <c r="H7" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
         <v>39</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F8" t="s">
         <v>40</v>
       </c>
-      <c r="D8" t="s">
+      <c r="G8" t="s">
         <v>41</v>
       </c>
-      <c r="E8" t="s">
+      <c r="H8" t="s">
         <v>42</v>
-      </c>
-      <c r="F8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>601</v>
+      </c>
+      <c r="D9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" t="s">
         <v>46</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H9" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>602</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" t="s">
         <v>50</v>
       </c>
-      <c r="D10" t="s">
+      <c r="H10" t="s">
         <v>51</v>
-      </c>
-      <c r="F10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
+        <v>598</v>
+      </c>
+      <c r="C11" t="s">
+        <v>603</v>
+      </c>
+      <c r="D11" t="s">
         <v>55</v>
       </c>
-      <c r="D11" t="s">
-        <v>56</v>
-      </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
         <v>58</v>
       </c>
-      <c r="D12" t="s">
-        <v>59</v>
-      </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F20" t="s">
+      <c r="C23" s="4" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D21" t="s">
+      <c r="D23" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D22" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="E23" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="F23" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="G23" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="H23" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="28"/>
+      <c r="R25" s="28"/>
+      <c r="S25" s="28"/>
+      <c r="T25" s="28"/>
+    </row>
+    <row r="26" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
-      <c r="R25" s="7"/>
-      <c r="S25" s="7"/>
-      <c r="T25" s="7"/>
-    </row>
-    <row r="26" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" s="8" t="s">
+      <c r="F26" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="G26" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="H26" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="I26" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="J26" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>98</v>
+        <v>606</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E27" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="H27" t="s">
-        <v>13</v>
+        <v>607</v>
       </c>
       <c r="I27" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="J27" t="s">
-        <v>24</v>
-      </c>
-      <c r="K27" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E28" t="s">
-        <v>104</v>
+        <v>599</v>
       </c>
       <c r="F28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" t="s">
         <v>19</v>
       </c>
-      <c r="G28" t="s">
-        <v>21</v>
-      </c>
       <c r="H28" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I28" t="s">
-        <v>105</v>
-      </c>
-      <c r="J28" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E29" t="s">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="F29" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" t="s">
+        <v>604</v>
+      </c>
+      <c r="H29" t="s">
+        <v>608</v>
+      </c>
+      <c r="I29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" t="s">
+        <v>101</v>
+      </c>
+      <c r="E30" t="s">
+        <v>600</v>
+      </c>
+      <c r="F30" t="s">
+        <v>34</v>
+      </c>
+      <c r="G30" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" t="s">
+        <v>36</v>
+      </c>
+      <c r="I30" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" t="s">
+        <v>39</v>
+      </c>
+      <c r="G31" t="s">
         <v>33</v>
       </c>
-      <c r="G29" t="s">
-        <v>28</v>
-      </c>
-      <c r="H29" t="s">
-        <v>27</v>
-      </c>
-      <c r="I29" t="s">
-        <v>109</v>
-      </c>
-      <c r="J29" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C30" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30" t="s">
-        <v>110</v>
-      </c>
-      <c r="E30" t="s">
-        <v>111</v>
-      </c>
-      <c r="F30" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" t="s">
-        <v>35</v>
-      </c>
-      <c r="H30" t="s">
-        <v>34</v>
-      </c>
-      <c r="I30" t="s">
-        <v>37</v>
-      </c>
-      <c r="J30" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="C31" t="s">
-        <v>63</v>
-      </c>
-      <c r="D31" t="s">
-        <v>39</v>
-      </c>
-      <c r="E31" t="s">
-        <v>106</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
+        <v>50</v>
+      </c>
+      <c r="I31" t="s">
         <v>42</v>
-      </c>
-      <c r="H31" t="s">
-        <v>113</v>
-      </c>
-      <c r="I31" t="s">
-        <v>23</v>
-      </c>
-      <c r="J31" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E32" t="s">
-        <v>114</v>
+        <v>601</v>
+      </c>
+      <c r="G32" t="s">
+        <v>48</v>
       </c>
       <c r="H32" t="s">
-        <v>13</v>
+        <v>609</v>
       </c>
       <c r="I32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" t="s">
+        <v>602</v>
+      </c>
+      <c r="G33" t="s">
+        <v>52</v>
+      </c>
+      <c r="H33" t="s">
+        <v>610</v>
+      </c>
+      <c r="I33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" t="s">
+        <v>603</v>
+      </c>
+      <c r="G34" t="s">
+        <v>55</v>
+      </c>
+      <c r="H34" t="s">
+        <v>29</v>
+      </c>
+      <c r="I34" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" t="s">
+        <v>73</v>
+      </c>
+      <c r="E35" t="s">
+        <v>25</v>
+      </c>
+      <c r="G35" t="s">
+        <v>58</v>
+      </c>
+      <c r="H35" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>56</v>
+      </c>
+      <c r="D36" t="s">
+        <v>31</v>
+      </c>
+      <c r="G36" t="s">
+        <v>60</v>
+      </c>
+      <c r="H36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37" t="s">
+        <v>104</v>
+      </c>
+      <c r="G37" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G38" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
         <v>44</v>
       </c>
-      <c r="J32" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C33" t="s">
-        <v>71</v>
-      </c>
-      <c r="D33" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33" t="s">
-        <v>115</v>
-      </c>
-      <c r="H33" t="s">
-        <v>51</v>
-      </c>
-      <c r="I33" t="s">
-        <v>30</v>
-      </c>
-      <c r="J33" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C34" t="s">
-        <v>61</v>
-      </c>
-      <c r="D34" t="s">
-        <v>116</v>
-      </c>
-      <c r="H34" t="s">
-        <v>56</v>
-      </c>
-      <c r="J34" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C35" t="s">
-        <v>73</v>
-      </c>
-      <c r="D35" t="s">
-        <v>77</v>
-      </c>
-      <c r="H35" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C36" t="s">
-        <v>60</v>
-      </c>
-      <c r="D36" t="s">
-        <v>32</v>
-      </c>
-      <c r="E36" t="s">
-        <v>118</v>
-      </c>
-      <c r="H36" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C37" t="s">
+      <c r="G40" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
         <v>65</v>
       </c>
-      <c r="D37" t="s">
-        <v>119</v>
-      </c>
-      <c r="H37" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D38" t="s">
-        <v>36</v>
-      </c>
-      <c r="H38" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C39" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" t="s">
-        <v>18</v>
-      </c>
-      <c r="H39" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C40" t="s">
-        <v>47</v>
-      </c>
-      <c r="H40" t="s">
+      <c r="G41" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H41" t="s">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G42" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H42" t="s">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G43" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H43" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H44" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="J45" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="K45" s="9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
+      <c r="B49" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="26"/>
+      <c r="J49" s="26"/>
+      <c r="K49" s="26"/>
+      <c r="L49" s="26"/>
+      <c r="M49" s="26"/>
+      <c r="N49" s="26"/>
+    </row>
+    <row r="50" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>128</v>
+      <c r="B50" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C51" t="s">
-        <v>130</v>
+        <v>120</v>
+      </c>
+      <c r="D51" t="s">
+        <v>206</v>
       </c>
       <c r="E51" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F51" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="G51" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C52" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D52" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="E52" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="F52" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G52" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C53" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D53" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="E53" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="F53" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="G53" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="C54" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D54" t="s">
-        <v>148</v>
+        <v>613</v>
       </c>
       <c r="E54" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="F54" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="G54" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C55" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D55" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="E55" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="F55" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="G55" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C56" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D56" t="s">
-        <v>160</v>
+        <v>614</v>
       </c>
       <c r="E56" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="F56" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="G56" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C57" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="D57" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="F57" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="G57" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C58" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="D58" t="s">
-        <v>169</v>
+        <v>615</v>
       </c>
       <c r="F58" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G58" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C59" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="D59" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="F59" t="s">
-        <v>174</v>
+        <v>123</v>
       </c>
       <c r="G59" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C60" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="D60" t="s">
-        <v>177</v>
+        <v>139</v>
       </c>
       <c r="F60" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="G60" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C61" t="s">
-        <v>180</v>
+        <v>115</v>
       </c>
       <c r="D61" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="F61" t="s">
-        <v>182</v>
+        <v>117</v>
       </c>
       <c r="G61" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C62" t="s">
-        <v>184</v>
+        <v>611</v>
       </c>
       <c r="D62" t="s">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="F62" t="s">
-        <v>186</v>
+        <v>616</v>
       </c>
       <c r="G62" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C63" t="s">
+        <v>612</v>
+      </c>
       <c r="D63" t="s">
-        <v>188</v>
+        <v>154</v>
+      </c>
+      <c r="F63" t="s">
+        <v>617</v>
       </c>
       <c r="G63" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G64" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G65" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G66" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G67" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G68" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G69" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G70" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G71" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G72" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G73" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G74" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G75" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G76" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G77" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G78" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>206</v>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B81" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="7"/>
-      <c r="J81" s="7"/>
-      <c r="K81" s="7"/>
-      <c r="L81" s="7"/>
-      <c r="M81" s="7"/>
-      <c r="N81" s="7"/>
-      <c r="O81" s="7"/>
-      <c r="P81" s="7"/>
-      <c r="Q81" s="7"/>
-      <c r="R81" s="7"/>
-      <c r="S81" s="7"/>
-      <c r="T81" s="7"/>
-    </row>
-    <row r="82" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="8" t="s">
+      <c r="B81" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="C81" s="27"/>
+      <c r="D81" s="27"/>
+      <c r="E81" s="27"/>
+      <c r="F81" s="27"/>
+      <c r="G81" s="27"/>
+      <c r="H81" s="27"/>
+      <c r="I81" s="28"/>
+      <c r="J81" s="28"/>
+      <c r="K81" s="28"/>
+      <c r="L81" s="28"/>
+      <c r="M81" s="28"/>
+      <c r="N81" s="28"/>
+      <c r="O81" s="28"/>
+      <c r="P81" s="28"/>
+      <c r="Q81" s="28"/>
+      <c r="R81" s="28"/>
+      <c r="S81" s="28"/>
+      <c r="T81" s="28"/>
+    </row>
+    <row r="82" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B82" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="E82" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="F82" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="G82" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="H82" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="I82" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="J82" s="9" t="s">
-        <v>216</v>
+      <c r="B82" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="J82" s="6" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
+        <v>141</v>
+      </c>
+      <c r="C83" t="s">
         <v>156</v>
       </c>
-      <c r="C83" t="s">
-        <v>171</v>
-      </c>
       <c r="D83" t="s">
+        <v>173</v>
+      </c>
+      <c r="E83" t="s">
+        <v>114</v>
+      </c>
+      <c r="F83" t="s">
+        <v>194</v>
+      </c>
+      <c r="G83" t="s">
         <v>195</v>
       </c>
-      <c r="E83" t="s">
-        <v>129</v>
-      </c>
-      <c r="F83" t="s">
-        <v>217</v>
-      </c>
-      <c r="G83" t="s">
-        <v>218</v>
-      </c>
       <c r="H83" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="I83" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="J83" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
+        <v>155</v>
+      </c>
+      <c r="C84" t="s">
+        <v>152</v>
+      </c>
+      <c r="D84" t="s">
         <v>170</v>
       </c>
-      <c r="C84" t="s">
-        <v>167</v>
-      </c>
-      <c r="D84" t="s">
-        <v>192</v>
-      </c>
       <c r="E84" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="F84" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="G84" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="H84" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>225</v>
+        <v>117</v>
       </c>
       <c r="C85" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D85" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="E85" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="G85" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>166</v>
+        <v>616</v>
       </c>
       <c r="C86" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D86" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="E86" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="G86" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="C87" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="D87" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="E87" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="G87" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>228</v>
+        <v>123</v>
       </c>
       <c r="C88" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D88" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="E88" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="G88" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>144</v>
+        <v>617</v>
       </c>
       <c r="C89" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="D89" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="E89" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="G89" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="C90" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D90" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="E90" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>232</v>
+        <v>129</v>
       </c>
       <c r="C91" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="E91" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C92" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="E92" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>234</v>
+        <v>135</v>
       </c>
       <c r="C93" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="E93" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>162</v>
+        <v>209</v>
       </c>
       <c r="C94" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="E94" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>235</v>
+        <v>147</v>
       </c>
       <c r="C95" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="E95" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>618</v>
+      </c>
+      <c r="C96" t="s">
+        <v>162</v>
+      </c>
       <c r="E96" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
+        <v>619</v>
+      </c>
       <c r="E97" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B98" t="s">
+        <v>620</v>
+      </c>
       <c r="E98" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>621</v>
+      </c>
       <c r="E99" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
+        <v>622</v>
+      </c>
       <c r="E100" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B101" t="s">
+        <v>623</v>
+      </c>
       <c r="E101" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>624</v>
+      </c>
       <c r="E102" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
+        <v>625</v>
+      </c>
       <c r="E103" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B104" t="s">
+        <v>207</v>
+      </c>
       <c r="E104" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B105" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="C105" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="D105" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="E105" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="F105" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="G105" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="I105" s="9" t="s">
-        <v>238</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="I105" s="6" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B109" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
-      <c r="F109" s="3"/>
-      <c r="G109" s="3"/>
-      <c r="H109" s="3"/>
-      <c r="I109" s="3"/>
-      <c r="J109" s="3"/>
-      <c r="K109" s="3"/>
-      <c r="L109" s="3"/>
-      <c r="M109" s="3"/>
-      <c r="N109" s="3"/>
-    </row>
-    <row r="110" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="4" t="s">
+      <c r="B109" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="C109" s="26"/>
+      <c r="D109" s="26"/>
+      <c r="E109" s="26"/>
+      <c r="F109" s="26"/>
+      <c r="G109" s="26"/>
+      <c r="H109" s="26"/>
+      <c r="I109" s="26"/>
+      <c r="J109" s="26"/>
+      <c r="K109" s="26"/>
+      <c r="L109" s="26"/>
+      <c r="M109" s="26"/>
+      <c r="N109" s="26"/>
+    </row>
+    <row r="110" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B110" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="D110" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="E110" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="F110" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="G110" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="H110" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I110" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="J110" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="K110" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="L110" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="M110" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="N110" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="O110" s="4" t="s">
-        <v>254</v>
+      <c r="B110" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="J110" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="K110" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="L110" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="M110" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="N110" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="O110" s="3" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="C111" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="D111" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="E111" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="F111" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="G111" t="s">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="H111" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="I111" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="J111" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="K111" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="L111" t="s">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="M111" t="s">
-        <v>266</v>
+        <v>240</v>
       </c>
       <c r="N111" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="O111" t="s">
-        <v>268</v>
+        <v>242</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="C112" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="D112" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="E112" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="F112" t="s">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="G112" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
       <c r="H112" t="s">
-        <v>275</v>
+        <v>249</v>
       </c>
       <c r="I112" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="J112" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="K112" t="s">
-        <v>277</v>
+        <v>251</v>
       </c>
       <c r="L112" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="M112" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="N112" t="s">
-        <v>280</v>
+        <v>254</v>
       </c>
       <c r="O112" t="s">
-        <v>281</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="C113" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="D113" t="s">
-        <v>284</v>
+        <v>258</v>
       </c>
       <c r="E113" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="F113" t="s">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="G113" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="I113" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="J113" t="s">
-        <v>289</v>
+        <v>263</v>
       </c>
       <c r="K113" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="L113" t="s">
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="M113" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="N113" t="s">
-        <v>293</v>
+        <v>267</v>
       </c>
       <c r="O113" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="C114" t="s">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="D114" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E114" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="F114" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="G114" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="I114" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="J114" t="s">
-        <v>301</v>
+        <v>275</v>
       </c>
       <c r="K114" t="s">
-        <v>302</v>
+        <v>276</v>
       </c>
       <c r="L114" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="M114" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="N114" t="s">
-        <v>305</v>
+        <v>279</v>
       </c>
       <c r="O114" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>307</v>
+        <v>281</v>
       </c>
       <c r="C115" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="D115" t="s">
-        <v>309</v>
+        <v>283</v>
       </c>
       <c r="E115" t="s">
-        <v>310</v>
+        <v>284</v>
       </c>
       <c r="F115" t="s">
-        <v>311</v>
+        <v>285</v>
       </c>
       <c r="G115" t="s">
-        <v>312</v>
+        <v>286</v>
       </c>
       <c r="I115" t="s">
-        <v>313</v>
+        <v>287</v>
       </c>
       <c r="J115" t="s">
-        <v>314</v>
+        <v>288</v>
       </c>
       <c r="K115" t="s">
-        <v>315</v>
+        <v>289</v>
       </c>
       <c r="L115" t="s">
-        <v>316</v>
+        <v>290</v>
       </c>
       <c r="M115" t="s">
-        <v>317</v>
+        <v>291</v>
       </c>
       <c r="O115" t="s">
-        <v>318</v>
+        <v>292</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>319</v>
+        <v>293</v>
       </c>
       <c r="C116" t="s">
-        <v>320</v>
+        <v>294</v>
       </c>
       <c r="D116" t="s">
-        <v>321</v>
+        <v>295</v>
       </c>
       <c r="E116" t="s">
-        <v>322</v>
+        <v>296</v>
       </c>
       <c r="G116" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
       <c r="I116" t="s">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="J116" t="s">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="K116" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
       <c r="L116" t="s">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="O116" t="s">
-        <v>328</v>
+        <v>302</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>329</v>
+        <v>303</v>
       </c>
       <c r="C117" t="s">
-        <v>330</v>
+        <v>304</v>
       </c>
       <c r="D117" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="E117" t="s">
-        <v>332</v>
+        <v>306</v>
       </c>
       <c r="I117" t="s">
-        <v>333</v>
+        <v>307</v>
       </c>
       <c r="J117" t="s">
-        <v>334</v>
+        <v>308</v>
       </c>
       <c r="K117" t="s">
-        <v>335</v>
+        <v>309</v>
       </c>
       <c r="L117" t="s">
-        <v>336</v>
+        <v>310</v>
       </c>
       <c r="O117" t="s">
-        <v>337</v>
+        <v>311</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>338</v>
+        <v>312</v>
       </c>
       <c r="C118" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="D118" t="s">
-        <v>340</v>
+        <v>314</v>
       </c>
       <c r="E118" t="s">
-        <v>341</v>
+        <v>315</v>
       </c>
       <c r="I118" t="s">
-        <v>342</v>
+        <v>316</v>
+      </c>
+      <c r="J118" t="s">
+        <v>372</v>
       </c>
       <c r="K118" t="s">
-        <v>343</v>
+        <v>317</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>344</v>
+        <v>318</v>
       </c>
       <c r="C119" t="s">
-        <v>345</v>
+        <v>319</v>
       </c>
       <c r="D119" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="E119" t="s">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="K119" t="s">
-        <v>348</v>
+        <v>322</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>349</v>
+        <v>323</v>
       </c>
       <c r="C120" t="s">
-        <v>350</v>
+        <v>324</v>
       </c>
       <c r="D120" t="s">
-        <v>351</v>
+        <v>325</v>
       </c>
       <c r="K120" t="s">
-        <v>352</v>
+        <v>326</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C121" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="K121" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="K122" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K123" t="s">
-        <v>358</v>
+        <v>332</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K124" t="s">
-        <v>359</v>
+        <v>333</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K125" t="s">
-        <v>360</v>
+        <v>334</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K126" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="127" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="D127" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="E127" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="F127" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="G127" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H127" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I127" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="J127" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="K127" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="L127" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="M127" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="N127" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="O127" s="5" t="s">
-        <v>373</v>
+        <v>335</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I127" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="J127" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="K127" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="L127" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="M127" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="N127" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="O127" s="4" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="129" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B129" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="C129" s="6"/>
-      <c r="D129" s="6"/>
-      <c r="E129" s="6"/>
-      <c r="F129" s="6"/>
-      <c r="G129" s="6"/>
-      <c r="H129" s="6"/>
-      <c r="I129" s="7"/>
-      <c r="J129" s="7"/>
-      <c r="K129" s="7"/>
-      <c r="L129" s="7"/>
-      <c r="M129" s="7"/>
-      <c r="N129" s="7"/>
-      <c r="O129" s="7"/>
-      <c r="P129" s="7"/>
-      <c r="Q129" s="7"/>
-      <c r="R129" s="7"/>
-      <c r="S129" s="7"/>
-      <c r="T129" s="7"/>
-    </row>
-    <row r="130" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="8" t="s">
+      <c r="B129" s="27" t="s">
+        <v>348</v>
+      </c>
+      <c r="C129" s="27"/>
+      <c r="D129" s="27"/>
+      <c r="E129" s="27"/>
+      <c r="F129" s="27"/>
+      <c r="G129" s="27"/>
+      <c r="H129" s="27"/>
+      <c r="I129" s="28"/>
+      <c r="J129" s="28"/>
+      <c r="K129" s="28"/>
+      <c r="L129" s="28"/>
+      <c r="M129" s="28"/>
+      <c r="N129" s="28"/>
+      <c r="O129" s="28"/>
+      <c r="P129" s="28"/>
+      <c r="Q129" s="28"/>
+      <c r="R129" s="28"/>
+      <c r="S129" s="28"/>
+      <c r="T129" s="28"/>
+    </row>
+    <row r="130" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B130" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="C130" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="D130" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="E130" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="F130" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="G130" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="H130" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="I130" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="J130" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="K130" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="L130" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="M130" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="N130" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="O130" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="P130" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="Q130" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="R130" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="S130" s="8" t="s">
-        <v>392</v>
-      </c>
-      <c r="T130" s="8" t="s">
-        <v>393</v>
+      <c r="B130" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="F130" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="H130" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="I130" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="J130" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="K130" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="L130" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="M130" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="N130" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="O130" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="P130" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q130" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="R130" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="S130" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="T130" s="5" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="131" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>315</v>
+        <v>289</v>
       </c>
       <c r="C131" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="D131" t="s">
-        <v>266</v>
+        <v>240</v>
       </c>
       <c r="E131" t="s">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="F131" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="G131" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="H131" t="s">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="I131" t="s">
-        <v>395</v>
+        <v>369</v>
       </c>
       <c r="J131" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="K131" t="s">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="L131" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
       <c r="M131" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
       <c r="N131" t="s">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="O131" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="P131" t="s">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="Q131" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="R131" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="S131" t="s">
-        <v>277</v>
+        <v>251</v>
       </c>
       <c r="T131" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
     </row>
     <row r="132" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="C132" t="s">
-        <v>280</v>
+        <v>254</v>
       </c>
       <c r="D132" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="E132" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="F132" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="G132" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="I132" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
       <c r="J132" t="s">
-        <v>312</v>
+        <v>286</v>
       </c>
       <c r="K132" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="L132" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="N132" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
       <c r="O132" t="s">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="P132" t="s">
-        <v>337</v>
+        <v>311</v>
       </c>
       <c r="Q132" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="R132" t="s">
-        <v>319</v>
+        <v>293</v>
       </c>
       <c r="S132" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="T132" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
     </row>
     <row r="133" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="C133" t="s">
-        <v>293</v>
+        <v>267</v>
       </c>
       <c r="D133" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="E133" t="s">
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="F133" t="s">
-        <v>289</v>
+        <v>263</v>
       </c>
       <c r="G133" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="I133" t="s">
-        <v>402</v>
+        <v>376</v>
       </c>
       <c r="J133" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
       <c r="K133" t="s">
-        <v>403</v>
+        <v>377</v>
       </c>
       <c r="N133" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="O133" t="s">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="Q133" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="R133" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="S133" t="s">
-        <v>302</v>
+        <v>276</v>
       </c>
       <c r="T133" t="s">
-        <v>284</v>
+        <v>258</v>
       </c>
     </row>
     <row r="134" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="C134" t="s">
-        <v>305</v>
+        <v>279</v>
       </c>
       <c r="D134" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="E134" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="F134" t="s">
-        <v>301</v>
+        <v>275</v>
       </c>
       <c r="G134" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="O134" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="Q134" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="R134" t="s">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="S134" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="T134" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
     </row>
     <row r="135" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C135" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="D135" t="s">
-        <v>317</v>
+        <v>291</v>
       </c>
       <c r="E135" t="s">
-        <v>316</v>
+        <v>290</v>
       </c>
       <c r="F135" t="s">
-        <v>314</v>
+        <v>288</v>
       </c>
       <c r="G135" t="s">
-        <v>313</v>
+        <v>287</v>
       </c>
       <c r="O135" t="s">
-        <v>311</v>
+        <v>285</v>
       </c>
       <c r="Q135" t="s">
-        <v>310</v>
+        <v>284</v>
       </c>
       <c r="R135" t="s">
-        <v>329</v>
+        <v>303</v>
       </c>
       <c r="S135" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
       <c r="T135" t="s">
-        <v>309</v>
+        <v>283</v>
       </c>
     </row>
     <row r="136" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="C136" t="s">
-        <v>275</v>
+        <v>249</v>
       </c>
       <c r="D136" t="s">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="E136" t="s">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="F136" t="s">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="G136" t="s">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="Q136" t="s">
-        <v>322</v>
+        <v>296</v>
       </c>
       <c r="R136" t="s">
-        <v>338</v>
+        <v>312</v>
       </c>
       <c r="S136" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="T136" t="s">
-        <v>321</v>
+        <v>295</v>
       </c>
     </row>
     <row r="137" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
-        <v>405</v>
+        <v>379</v>
       </c>
       <c r="D137" t="s">
-        <v>281</v>
+        <v>255</v>
       </c>
       <c r="E137" t="s">
-        <v>336</v>
+        <v>310</v>
       </c>
       <c r="F137" t="s">
-        <v>334</v>
+        <v>308</v>
       </c>
       <c r="G137" t="s">
-        <v>333</v>
+        <v>307</v>
       </c>
       <c r="Q137" t="s">
-        <v>332</v>
+        <v>306</v>
       </c>
       <c r="R137" t="s">
-        <v>349</v>
+        <v>323</v>
       </c>
       <c r="S137" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="T137" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
     </row>
     <row r="138" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
-        <v>307</v>
+        <v>281</v>
       </c>
       <c r="D138" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="G138" t="s">
-        <v>342</v>
+        <v>316</v>
       </c>
       <c r="Q138" t="s">
-        <v>341</v>
+        <v>315</v>
       </c>
       <c r="R138" t="s">
-        <v>344</v>
+        <v>318</v>
       </c>
       <c r="S138" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="T138" t="s">
-        <v>340</v>
+        <v>314</v>
       </c>
     </row>
     <row r="139" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
-        <v>348</v>
+        <v>322</v>
       </c>
       <c r="D139" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
       <c r="Q139" t="s">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="R139" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="S139" t="s">
-        <v>320</v>
+        <v>294</v>
       </c>
       <c r="T139" t="s">
-        <v>351</v>
+        <v>325</v>
       </c>
     </row>
     <row r="140" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="D140" t="s">
-        <v>318</v>
+        <v>292</v>
       </c>
       <c r="R140" t="s">
-        <v>345</v>
+        <v>319</v>
       </c>
       <c r="S140" t="s">
-        <v>330</v>
+        <v>304</v>
       </c>
     </row>
     <row r="141" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="R141" t="s">
-        <v>350</v>
+        <v>324</v>
       </c>
       <c r="S141" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
     </row>
     <row r="142" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
     </row>
     <row r="143" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
-        <v>358</v>
+        <v>332</v>
       </c>
     </row>
     <row r="144" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
-        <v>359</v>
+        <v>333</v>
       </c>
     </row>
     <row r="145" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
-        <v>360</v>
+        <v>334</v>
       </c>
     </row>
     <row r="146" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="147" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B147" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="C147" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="D147" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="E147" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="F147" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="G147" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="I147" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="J147" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="K147" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="L147" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="M147" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="N147" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="O147" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="P147" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="Q147" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="R147" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="S147" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="T147" s="9" t="s">
-        <v>406</v>
+        <v>335</v>
+      </c>
+    </row>
+    <row r="147" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="G147" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H147" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="I147" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="J147" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="K147" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="L147" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="M147" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="N147" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="O147" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="P147" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q147" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="R147" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="S147" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="T147" s="6" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="150" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A150" s="10" t="s">
-        <v>408</v>
+      <c r="A150" s="7" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="151" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B151" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="C151" s="3"/>
-      <c r="D151" s="3"/>
-      <c r="E151" s="3"/>
-      <c r="F151" s="3"/>
-      <c r="G151" s="3"/>
-      <c r="H151" s="3"/>
-      <c r="I151" s="3"/>
-      <c r="J151" s="3"/>
-      <c r="K151" s="3"/>
-      <c r="L151" s="3"/>
-      <c r="M151" s="3"/>
-      <c r="N151" s="3"/>
-    </row>
-    <row r="152" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="4" t="s">
+      <c r="B151" s="26" t="s">
+        <v>383</v>
+      </c>
+      <c r="C151" s="26"/>
+      <c r="D151" s="26"/>
+      <c r="E151" s="26"/>
+      <c r="F151" s="26"/>
+      <c r="G151" s="26"/>
+      <c r="H151" s="26"/>
+      <c r="I151" s="26"/>
+      <c r="J151" s="26"/>
+      <c r="K151" s="26"/>
+      <c r="L151" s="26"/>
+      <c r="M151" s="26"/>
+      <c r="N151" s="26"/>
+    </row>
+    <row r="152" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B152" s="11" t="s">
-        <v>410</v>
-      </c>
-      <c r="C152" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="D152" s="11" t="s">
-        <v>412</v>
-      </c>
-      <c r="E152" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="F152" s="13" t="s">
-        <v>414</v>
-      </c>
-      <c r="G152" s="14" t="s">
-        <v>415</v>
-      </c>
-      <c r="H152" s="14" t="s">
-        <v>416</v>
-      </c>
-      <c r="I152" s="14" t="s">
-        <v>417</v>
+      <c r="B152" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="E152" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="F152" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="G152" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="H152" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="I152" s="11" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="153" spans="1:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="B153" s="16" t="s">
-        <v>418</v>
+      <c r="B153" s="13" t="s">
+        <v>392</v>
       </c>
       <c r="C153" t="s">
-        <v>419</v>
+        <v>393</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="E153" t="s">
-        <v>421</v>
-      </c>
-      <c r="F153" s="17" t="s">
-        <v>422</v>
+        <v>395</v>
+      </c>
+      <c r="F153" s="14" t="s">
+        <v>396</v>
       </c>
       <c r="G153" t="s">
-        <v>423</v>
-      </c>
-      <c r="H153" s="18" t="s">
-        <v>424</v>
-      </c>
-      <c r="I153" s="19" t="s">
-        <v>425</v>
+        <v>397</v>
+      </c>
+      <c r="H153" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="I153" s="16" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="154" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="C154" t="s">
-        <v>427</v>
+        <v>401</v>
       </c>
       <c r="D154" t="s">
-        <v>428</v>
+        <v>402</v>
       </c>
       <c r="E154" t="s">
+        <v>395</v>
+      </c>
+      <c r="F154" t="s">
+        <v>410</v>
+      </c>
+      <c r="G154" t="s">
+        <v>403</v>
+      </c>
+      <c r="H154" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="I154" s="16" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="155" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B155" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="C155" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="D155" t="s">
+        <v>408</v>
+      </c>
+      <c r="E155" t="s">
+        <v>409</v>
+      </c>
+      <c r="F155" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="G155" t="s">
+        <v>411</v>
+      </c>
+      <c r="H155" t="s">
+        <v>412</v>
+      </c>
+      <c r="I155" s="18" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B156" t="s">
+        <v>414</v>
+      </c>
+      <c r="C156" t="s">
+        <v>415</v>
+      </c>
+      <c r="D156" t="s">
+        <v>416</v>
+      </c>
+      <c r="E156" t="s">
+        <v>417</v>
+      </c>
+      <c r="F156" s="14" t="s">
+        <v>468</v>
+      </c>
+      <c r="G156" t="s">
+        <v>419</v>
+      </c>
+      <c r="H156" t="s">
+        <v>420</v>
+      </c>
+      <c r="I156" s="16" t="s">
         <v>421</v>
-      </c>
-      <c r="F154" t="s">
-        <v>234</v>
-      </c>
-      <c r="G154" t="s">
-        <v>429</v>
-      </c>
-      <c r="H154" s="18" t="s">
-        <v>430</v>
-      </c>
-      <c r="I154" s="19" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="155" spans="1:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="B155" s="20" t="s">
-        <v>432</v>
-      </c>
-      <c r="C155" s="20" t="s">
-        <v>433</v>
-      </c>
-      <c r="D155" t="s">
-        <v>434</v>
-      </c>
-      <c r="E155" t="s">
-        <v>435</v>
-      </c>
-      <c r="F155" s="17" t="s">
-        <v>436</v>
-      </c>
-      <c r="G155" t="s">
-        <v>437</v>
-      </c>
-      <c r="H155" t="s">
-        <v>438</v>
-      </c>
-      <c r="I155" s="21" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="156" spans="1:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="B156" t="s">
-        <v>440</v>
-      </c>
-      <c r="C156" t="s">
-        <v>441</v>
-      </c>
-      <c r="D156" t="s">
-        <v>442</v>
-      </c>
-      <c r="E156" t="s">
-        <v>443</v>
-      </c>
-      <c r="F156" s="17" t="s">
-        <v>444</v>
-      </c>
-      <c r="G156" t="s">
-        <v>445</v>
-      </c>
-      <c r="H156" t="s">
-        <v>446</v>
-      </c>
-      <c r="I156" s="19" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="157" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
-        <v>448</v>
+        <v>422</v>
       </c>
       <c r="C157" t="s">
-        <v>449</v>
+        <v>423</v>
       </c>
       <c r="E157" t="s">
-        <v>450</v>
+        <v>424</v>
       </c>
       <c r="F157" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="G157" t="s">
-        <v>452</v>
+        <v>425</v>
       </c>
       <c r="H157" t="s">
-        <v>453</v>
-      </c>
-      <c r="I157" s="19" t="s">
-        <v>454</v>
+        <v>426</v>
+      </c>
+      <c r="I157" s="16" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="158" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
-        <v>455</v>
+        <v>428</v>
       </c>
       <c r="C158" t="s">
-        <v>456</v>
+        <v>429</v>
       </c>
       <c r="E158" t="s">
-        <v>457</v>
+        <v>430</v>
       </c>
       <c r="F158" t="s">
-        <v>458</v>
-      </c>
-      <c r="G158" s="22"/>
+        <v>396</v>
+      </c>
+      <c r="G158" s="19"/>
       <c r="H158" t="s">
-        <v>459</v>
-      </c>
-      <c r="I158" s="19" t="s">
-        <v>460</v>
+        <v>432</v>
+      </c>
+      <c r="I158" s="16" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="159" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
-        <v>461</v>
+        <v>434</v>
       </c>
       <c r="C159" t="s">
-        <v>462</v>
+        <v>435</v>
       </c>
       <c r="E159" t="s">
-        <v>463</v>
+        <v>436</v>
       </c>
       <c r="F159" t="s">
-        <v>464</v>
+        <v>410</v>
       </c>
       <c r="H159" t="s">
-        <v>465</v>
-      </c>
-      <c r="I159" s="23" t="s">
-        <v>466</v>
+        <v>438</v>
+      </c>
+      <c r="I159" s="20" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="160" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="C160" t="s">
-        <v>467</v>
+        <v>440</v>
       </c>
       <c r="E160" t="s">
-        <v>468</v>
+        <v>441</v>
       </c>
       <c r="F160" t="s">
-        <v>469</v>
-      </c>
-      <c r="I160" s="23" t="s">
-        <v>470</v>
+        <v>475</v>
+      </c>
+      <c r="I160" s="20" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="161" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
-        <v>471</v>
+        <v>444</v>
       </c>
       <c r="C161" t="s">
-        <v>472</v>
+        <v>445</v>
       </c>
       <c r="E161" t="s">
-        <v>473</v>
+        <v>446</v>
       </c>
       <c r="F161" t="s">
-        <v>474</v>
-      </c>
-      <c r="I161" s="19" t="s">
-        <v>475</v>
+        <v>418</v>
+      </c>
+      <c r="I161" s="16" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="162" spans="2:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B162" s="17" t="s">
-        <v>476</v>
+      <c r="B162" s="14" t="s">
+        <v>449</v>
       </c>
       <c r="C162" t="s">
-        <v>477</v>
+        <v>450</v>
       </c>
       <c r="E162" t="s">
-        <v>478</v>
+        <v>451</v>
       </c>
       <c r="F162" t="s">
-        <v>479</v>
-      </c>
-      <c r="I162" s="19" t="s">
-        <v>480</v>
+        <v>431</v>
+      </c>
+      <c r="I162" s="16" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="163" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B163" t="s">
-        <v>481</v>
+        <v>454</v>
       </c>
       <c r="C163" t="s">
-        <v>462</v>
+        <v>435</v>
       </c>
       <c r="F163" t="s">
-        <v>482</v>
-      </c>
-      <c r="I163" s="19" t="s">
-        <v>483</v>
+        <v>437</v>
+      </c>
+      <c r="I163" s="16" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="164" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B164" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="C164" t="s">
-        <v>484</v>
+        <v>457</v>
       </c>
       <c r="F164" t="s">
-        <v>485</v>
-      </c>
-      <c r="I164" s="19" t="s">
-        <v>486</v>
+        <v>442</v>
+      </c>
+      <c r="I164" s="16" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="165" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B165" t="s">
-        <v>487</v>
+        <v>460</v>
       </c>
       <c r="C165" t="s">
-        <v>488</v>
+        <v>461</v>
       </c>
       <c r="F165" t="s">
-        <v>489</v>
+        <v>447</v>
       </c>
     </row>
     <row r="166" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B166" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
       <c r="C166" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="F166" t="s">
-        <v>492</v>
+        <v>452</v>
       </c>
     </row>
     <row r="167" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B167" t="s">
-        <v>493</v>
+        <v>466</v>
       </c>
       <c r="C167" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="F167" t="s">
-        <v>495</v>
+        <v>455</v>
       </c>
     </row>
     <row r="168" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B168" t="s">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="C168" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="F168" t="s">
-        <v>497</v>
+        <v>458</v>
       </c>
     </row>
     <row r="169" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B169" t="s">
-        <v>498</v>
+        <v>471</v>
       </c>
       <c r="C169" t="s">
-        <v>499</v>
+        <v>472</v>
       </c>
       <c r="F169" t="s">
-        <v>422</v>
+        <v>462</v>
       </c>
     </row>
     <row r="170" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B170" t="s">
-        <v>500</v>
-      </c>
-      <c r="C170" s="24" t="s">
-        <v>501</v>
+        <v>473</v>
+      </c>
+      <c r="C170" s="21" t="s">
+        <v>474</v>
       </c>
       <c r="F170" t="s">
-        <v>436</v>
+        <v>465</v>
       </c>
     </row>
     <row r="171" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B171" t="s">
-        <v>448</v>
-      </c>
-      <c r="F171" t="s">
-        <v>502</v>
+        <v>422</v>
       </c>
     </row>
     <row r="172" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B172" t="s">
-        <v>503</v>
-      </c>
-      <c r="F172" t="s">
-        <v>444</v>
+        <v>476</v>
       </c>
     </row>
     <row r="173" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B173" t="s">
-        <v>504</v>
+        <v>477</v>
       </c>
     </row>
     <row r="174" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
-        <v>505</v>
+        <v>478</v>
       </c>
     </row>
     <row r="175" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B175" t="s">
-        <v>506</v>
+        <v>479</v>
       </c>
     </row>
     <row r="176" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B176" s="25" t="s">
-        <v>507</v>
+      <c r="B176" s="22" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="177" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A177" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B177" s="26" t="s">
-        <v>508</v>
-      </c>
-      <c r="C177" s="26" t="s">
-        <v>509</v>
-      </c>
-      <c r="D177" s="26" t="s">
-        <v>510</v>
-      </c>
-      <c r="E177" s="27" t="s">
-        <v>511</v>
-      </c>
-      <c r="F177" s="28" t="s">
-        <v>512</v>
-      </c>
-      <c r="G177" s="26" t="s">
-        <v>513</v>
-      </c>
-      <c r="H177" s="26" t="s">
-        <v>514</v>
-      </c>
-      <c r="I177" s="26" t="s">
-        <v>515</v>
+      <c r="A177" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B177" s="23" t="s">
+        <v>481</v>
+      </c>
+      <c r="C177" s="23" t="s">
+        <v>482</v>
+      </c>
+      <c r="D177" s="23" t="s">
+        <v>483</v>
+      </c>
+      <c r="E177" s="24" t="s">
+        <v>484</v>
+      </c>
+      <c r="F177" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="G177" s="23" t="s">
+        <v>486</v>
+      </c>
+      <c r="H177" s="23" t="s">
+        <v>487</v>
+      </c>
+      <c r="I177" s="23" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="179" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B179" s="6" t="s">
-        <v>516</v>
-      </c>
-      <c r="C179" s="6"/>
-      <c r="D179" s="6"/>
-      <c r="E179" s="6"/>
-      <c r="F179" s="6"/>
-      <c r="G179" s="6"/>
-      <c r="H179" s="6"/>
-      <c r="I179" s="7"/>
-      <c r="J179" s="7"/>
-      <c r="K179" s="7"/>
-      <c r="L179" s="7"/>
-      <c r="M179" s="7"/>
-      <c r="N179" s="7"/>
-      <c r="O179" s="7"/>
-      <c r="P179" s="7"/>
-      <c r="Q179" s="7"/>
-      <c r="R179" s="7"/>
-      <c r="S179" s="7"/>
-      <c r="T179" s="7"/>
-    </row>
-    <row r="180" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="8" t="s">
+      <c r="B179" s="27" t="s">
+        <v>489</v>
+      </c>
+      <c r="C179" s="27"/>
+      <c r="D179" s="27"/>
+      <c r="E179" s="27"/>
+      <c r="F179" s="27"/>
+      <c r="G179" s="27"/>
+      <c r="H179" s="27"/>
+      <c r="I179" s="28"/>
+      <c r="J179" s="28"/>
+      <c r="K179" s="28"/>
+      <c r="L179" s="28"/>
+      <c r="M179" s="28"/>
+      <c r="N179" s="28"/>
+      <c r="O179" s="28"/>
+      <c r="P179" s="28"/>
+      <c r="Q179" s="28"/>
+      <c r="R179" s="28"/>
+      <c r="S179" s="28"/>
+      <c r="T179" s="28"/>
+    </row>
+    <row r="180" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B180" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="C180" s="8" t="s">
-        <v>518</v>
-      </c>
-      <c r="D180" s="8" t="s">
-        <v>519</v>
-      </c>
-      <c r="E180" s="8" t="s">
-        <v>520</v>
-      </c>
-      <c r="F180" s="8" t="s">
-        <v>521</v>
-      </c>
-      <c r="G180" s="8" t="s">
-        <v>522</v>
-      </c>
-      <c r="H180" s="8" t="s">
-        <v>523</v>
+      <c r="B180" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="D180" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="E180" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="F180" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="G180" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="H180" s="5" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="181" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B181" t="s">
-        <v>419</v>
+        <v>393</v>
       </c>
       <c r="C181" t="s">
-        <v>418</v>
+        <v>392</v>
       </c>
       <c r="D181" t="s">
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="E181" t="s">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="F181" t="s">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="G181" t="s">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="H181" t="s">
-        <v>443</v>
+        <v>417</v>
       </c>
     </row>
     <row r="182" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B182" t="s">
-        <v>427</v>
+        <v>401</v>
       </c>
       <c r="C182" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="D182" t="s">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="E182" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="F182" t="s">
-        <v>495</v>
+        <v>468</v>
       </c>
       <c r="G182" t="s">
+        <v>404</v>
+      </c>
+      <c r="H182" t="s">
         <v>430</v>
-      </c>
-      <c r="H182" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="183" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B183" t="s">
-        <v>433</v>
+        <v>407</v>
       </c>
       <c r="C183" t="s">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="D183" t="s">
-        <v>524</v>
+        <v>495</v>
       </c>
       <c r="E183" t="s">
-        <v>429</v>
+        <v>403</v>
       </c>
       <c r="F183" t="s">
-        <v>428</v>
+        <v>402</v>
       </c>
       <c r="G183" t="s">
-        <v>424</v>
+        <v>398</v>
       </c>
     </row>
     <row r="184" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B184" t="s">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="C184" t="s">
-        <v>448</v>
+        <v>422</v>
       </c>
       <c r="E184" t="s">
-        <v>525</v>
+        <v>496</v>
       </c>
     </row>
     <row r="185" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B185" t="s">
-        <v>449</v>
+        <v>423</v>
       </c>
       <c r="C185" t="s">
-        <v>455</v>
+        <v>428</v>
       </c>
     </row>
     <row r="186" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B186" t="s">
-        <v>456</v>
+        <v>429</v>
       </c>
       <c r="C186" t="s">
-        <v>461</v>
+        <v>434</v>
       </c>
     </row>
     <row r="187" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B187" t="s">
-        <v>462</v>
+        <v>435</v>
       </c>
       <c r="C187" t="s">
-        <v>471</v>
+        <v>444</v>
       </c>
     </row>
     <row r="188" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B188" t="s">
-        <v>467</v>
+        <v>440</v>
       </c>
       <c r="C188" t="s">
-        <v>493</v>
+        <v>466</v>
       </c>
     </row>
     <row r="189" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
-        <v>472</v>
+        <v>445</v>
       </c>
       <c r="C189" t="s">
-        <v>440</v>
+        <v>414</v>
       </c>
     </row>
     <row r="190" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B190" t="s">
-        <v>477</v>
+        <v>450</v>
       </c>
       <c r="C190" t="s">
-        <v>498</v>
+        <v>471</v>
       </c>
     </row>
     <row r="191" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B191" t="s">
-        <v>462</v>
+        <v>435</v>
       </c>
       <c r="C191" t="s">
-        <v>500</v>
+        <v>473</v>
       </c>
     </row>
     <row r="192" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B192" t="s">
-        <v>484</v>
+        <v>457</v>
       </c>
       <c r="C192" t="s">
-        <v>448</v>
+        <v>422</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B193" t="s">
-        <v>499</v>
+        <v>472</v>
       </c>
       <c r="C193" t="s">
-        <v>503</v>
+        <v>476</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B194" t="s">
-        <v>488</v>
+        <v>461</v>
       </c>
       <c r="C194" t="s">
-        <v>504</v>
+        <v>477</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B195" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="C195" t="s">
-        <v>505</v>
+        <v>478</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B196" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="C196" t="s">
-        <v>506</v>
+        <v>479</v>
       </c>
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B197" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="C197" t="s">
-        <v>507</v>
+        <v>480</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B198" t="s">
-        <v>501</v>
+        <v>474</v>
       </c>
       <c r="C198" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B199" t="s">
-        <v>476</v>
+        <v>449</v>
       </c>
       <c r="C199" t="s">
-        <v>431</v>
+        <v>405</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
-        <v>481</v>
+        <v>454</v>
       </c>
       <c r="C200" t="s">
-        <v>439</v>
+        <v>413</v>
       </c>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B201" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="C201" t="s">
-        <v>447</v>
+        <v>421</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B202" t="s">
-        <v>487</v>
+        <v>460</v>
       </c>
       <c r="C202" t="s">
-        <v>454</v>
+        <v>427</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B203" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
       <c r="C203" t="s">
-        <v>460</v>
+        <v>433</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B204" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="C204" t="s">
-        <v>466</v>
+        <v>439</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C205" t="s">
-        <v>470</v>
+        <v>443</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C206" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C207" t="s">
-        <v>480</v>
+        <v>453</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C208" t="s">
-        <v>483</v>
+        <v>456</v>
       </c>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C209" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="210" spans="1:14" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B210" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="C210" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="D210" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="E210" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="F210" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="G210" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="H210" s="9" t="s">
-        <v>526</v>
+        <v>459</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="C210" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="D210" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="E210" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="F210" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="G210" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="H210" s="6" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A213" s="10" t="s">
-        <v>527</v>
+      <c r="A213" s="7" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B214" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="C214" s="3"/>
-      <c r="D214" s="3"/>
-      <c r="E214" s="3"/>
-      <c r="F214" s="3"/>
-      <c r="G214" s="3"/>
-      <c r="H214" s="3"/>
-      <c r="I214" s="3"/>
-      <c r="J214" s="3"/>
-      <c r="K214" s="3"/>
-      <c r="L214" s="3"/>
-      <c r="M214" s="3"/>
-      <c r="N214" s="3"/>
-    </row>
-    <row r="215" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="4" t="s">
+      <c r="B214" s="26" t="s">
+        <v>498</v>
+      </c>
+      <c r="C214" s="26"/>
+      <c r="D214" s="26"/>
+      <c r="E214" s="26"/>
+      <c r="F214" s="26"/>
+      <c r="G214" s="26"/>
+      <c r="H214" s="26"/>
+      <c r="I214" s="26"/>
+      <c r="J214" s="26"/>
+      <c r="K214" s="26"/>
+      <c r="L214" s="26"/>
+      <c r="M214" s="26"/>
+      <c r="N214" s="26"/>
+    </row>
+    <row r="215" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A215" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B215" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="C215" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="D215" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="E215" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="F215" s="4" t="s">
-        <v>533</v>
-      </c>
-      <c r="G215" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="H215" s="4" t="s">
-        <v>535</v>
+      <c r="B215" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="H215" s="3" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B216" t="s">
-        <v>536</v>
+        <v>558</v>
       </c>
       <c r="C216" t="s">
-        <v>537</v>
+        <v>512</v>
       </c>
       <c r="D216" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E216" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="F216" t="s">
-        <v>540</v>
+        <v>509</v>
       </c>
       <c r="G216" t="s">
-        <v>541</v>
+        <v>510</v>
       </c>
       <c r="H216" t="s">
-        <v>542</v>
+        <v>516</v>
       </c>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B217" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C217" t="s">
-        <v>544</v>
+        <v>518</v>
       </c>
       <c r="D217" t="s">
-        <v>545</v>
+        <v>507</v>
       </c>
       <c r="E217" t="s">
-        <v>546</v>
+        <v>508</v>
       </c>
       <c r="G217" t="s">
-        <v>547</v>
+        <v>515</v>
       </c>
       <c r="H217" t="s">
-        <v>548</v>
+        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B218" t="s">
-        <v>549</v>
+        <v>628</v>
       </c>
       <c r="C218" t="s">
-        <v>550</v>
+        <v>522</v>
       </c>
       <c r="D218" t="s">
-        <v>109</v>
+        <v>630</v>
       </c>
       <c r="E218" t="s">
-        <v>551</v>
+        <v>631</v>
       </c>
       <c r="H218" t="s">
-        <v>552</v>
+        <v>525</v>
       </c>
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B219" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C219" t="s">
-        <v>554</v>
+        <v>526</v>
       </c>
       <c r="D219" t="s">
-        <v>555</v>
+        <v>587</v>
       </c>
       <c r="E219" t="s">
-        <v>556</v>
+        <v>632</v>
       </c>
       <c r="H219" t="s">
-        <v>557</v>
+        <v>528</v>
       </c>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B220" t="s">
-        <v>558</v>
+        <v>521</v>
       </c>
       <c r="C220" t="s">
-        <v>559</v>
+        <v>530</v>
       </c>
       <c r="D220" t="s">
-        <v>560</v>
+        <v>513</v>
       </c>
       <c r="E220" t="s">
-        <v>561</v>
+        <v>519</v>
       </c>
       <c r="H220" t="s">
-        <v>562</v>
+        <v>533</v>
       </c>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B221" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C221" t="s">
-        <v>564</v>
+        <v>535</v>
       </c>
       <c r="D221" t="s">
-        <v>565</v>
+        <v>100</v>
       </c>
       <c r="E221" t="s">
-        <v>566</v>
+        <v>592</v>
       </c>
       <c r="H221" t="s">
-        <v>567</v>
+        <v>538</v>
       </c>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B222" t="s">
-        <v>568</v>
+        <v>534</v>
       </c>
       <c r="C222" t="s">
-        <v>569</v>
+        <v>540</v>
       </c>
       <c r="D222" t="s">
-        <v>570</v>
+        <v>523</v>
       </c>
       <c r="E222" t="s">
-        <v>571</v>
+        <v>532</v>
       </c>
       <c r="H222" t="s">
-        <v>572</v>
+        <v>542</v>
       </c>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B223" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C223" t="s">
-        <v>574</v>
+        <v>544</v>
       </c>
       <c r="D223" t="s">
-        <v>575</v>
+        <v>531</v>
       </c>
       <c r="E223" t="s">
-        <v>576</v>
+        <v>537</v>
       </c>
       <c r="H223" t="s">
-        <v>577</v>
+        <v>511</v>
       </c>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B224" t="s">
-        <v>578</v>
+        <v>553</v>
       </c>
       <c r="C224" t="s">
-        <v>579</v>
+        <v>547</v>
+      </c>
+      <c r="D224" t="s">
+        <v>536</v>
       </c>
       <c r="E224" t="s">
-        <v>580</v>
+        <v>552</v>
+      </c>
+      <c r="H224" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="225" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B225" t="s">
-        <v>581</v>
+        <v>551</v>
       </c>
       <c r="C225" t="s">
-        <v>582</v>
+        <v>549</v>
+      </c>
+      <c r="D225" t="s">
+        <v>527</v>
       </c>
       <c r="E225" t="s">
-        <v>583</v>
+        <v>524</v>
+      </c>
+      <c r="H225" t="s">
+        <v>633</v>
       </c>
     </row>
     <row r="226" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B226" t="s">
-        <v>584</v>
+        <v>539</v>
       </c>
       <c r="C226" t="s">
-        <v>585</v>
+        <v>544</v>
       </c>
       <c r="E226" t="s">
-        <v>586</v>
+        <v>545</v>
       </c>
     </row>
     <row r="227" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B227" t="s">
-        <v>587</v>
+        <v>561</v>
       </c>
       <c r="C227" t="s">
-        <v>579</v>
+        <v>506</v>
       </c>
       <c r="E227" t="s">
-        <v>588</v>
+        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B228" t="s">
-        <v>589</v>
+        <v>529</v>
+      </c>
+      <c r="C228" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="229" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B229" t="s">
-        <v>590</v>
+        <v>557</v>
+      </c>
+      <c r="C229" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="230" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B230" t="s">
-        <v>591</v>
+        <v>554</v>
       </c>
     </row>
     <row r="231" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B231" t="s">
-        <v>592</v>
+        <v>543</v>
       </c>
     </row>
     <row r="232" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B232" t="s">
-        <v>593</v>
+        <v>555</v>
       </c>
     </row>
     <row r="233" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B233" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B234" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="235" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B235" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B236" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="237" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B237" s="5" t="s">
-        <v>598</v>
-      </c>
-      <c r="C237" s="5" t="s">
-        <v>599</v>
-      </c>
-      <c r="D237" s="5" t="s">
-        <v>600</v>
-      </c>
-      <c r="E237" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="F237" s="5" t="s">
-        <v>602</v>
-      </c>
-      <c r="G237" s="5" t="s">
-        <v>603</v>
-      </c>
-      <c r="H237" s="5" t="s">
-        <v>604</v>
+        <v>517</v>
+      </c>
+    </row>
+    <row r="237" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="D237" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="E237" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="F237" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="G237" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="H237" s="4" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="239" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B239" s="6" t="s">
-        <v>605</v>
-      </c>
-      <c r="C239" s="6"/>
-      <c r="D239" s="6"/>
-      <c r="E239" s="6"/>
-      <c r="F239" s="6"/>
-      <c r="G239" s="6"/>
-      <c r="H239" s="6"/>
-      <c r="I239" s="7"/>
-      <c r="J239" s="7"/>
-      <c r="K239" s="7"/>
-      <c r="L239" s="7"/>
-      <c r="M239" s="7"/>
-      <c r="N239" s="7"/>
-      <c r="O239" s="7"/>
-      <c r="P239" s="7"/>
-      <c r="Q239" s="7"/>
-      <c r="R239" s="7"/>
-      <c r="S239" s="7"/>
-      <c r="T239" s="7"/>
-    </row>
-    <row r="240" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="8" t="s">
+      <c r="B239" s="27" t="s">
+        <v>569</v>
+      </c>
+      <c r="C239" s="27"/>
+      <c r="D239" s="27"/>
+      <c r="E239" s="27"/>
+      <c r="F239" s="27"/>
+      <c r="G239" s="27"/>
+      <c r="H239" s="27"/>
+      <c r="I239" s="28"/>
+      <c r="J239" s="28"/>
+      <c r="K239" s="28"/>
+      <c r="L239" s="28"/>
+      <c r="M239" s="28"/>
+      <c r="N239" s="28"/>
+      <c r="O239" s="28"/>
+      <c r="P239" s="28"/>
+      <c r="Q239" s="28"/>
+      <c r="R239" s="28"/>
+      <c r="S239" s="28"/>
+      <c r="T239" s="28"/>
+    </row>
+    <row r="240" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A240" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B240" s="8" t="s">
-        <v>606</v>
-      </c>
-      <c r="C240" s="8" t="s">
-        <v>607</v>
-      </c>
-      <c r="D240" s="8" t="s">
-        <v>608</v>
-      </c>
-      <c r="E240" s="8" t="s">
-        <v>609</v>
-      </c>
-      <c r="F240" s="8" t="s">
-        <v>610</v>
-      </c>
-      <c r="G240" s="8" t="s">
-        <v>611</v>
-      </c>
-      <c r="H240" s="8" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="241" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B240" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="D240" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="E240" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="F240" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="G240" s="5" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="241" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B241" t="s">
+        <v>577</v>
+      </c>
+      <c r="C241" t="s">
+        <v>558</v>
+      </c>
+      <c r="D241" t="s">
+        <v>550</v>
+      </c>
+      <c r="E241" t="s">
+        <v>579</v>
+      </c>
+      <c r="F241" t="s">
+        <v>541</v>
+      </c>
+      <c r="G241" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="242" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B242" t="s">
+        <v>520</v>
+      </c>
+      <c r="C242" t="s">
+        <v>546</v>
+      </c>
+      <c r="D242" t="s">
+        <v>581</v>
+      </c>
+      <c r="E242" t="s">
+        <v>582</v>
+      </c>
+      <c r="F242" t="s">
+        <v>507</v>
+      </c>
+      <c r="G242" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="243" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B243" t="s">
         <v>542</v>
       </c>
-      <c r="C241" t="s">
-        <v>613</v>
-      </c>
-      <c r="D241" t="s">
-        <v>614</v>
-      </c>
-      <c r="E241" t="s">
-        <v>615</v>
-      </c>
-      <c r="F241" t="s">
-        <v>616</v>
-      </c>
-      <c r="G241" t="s">
-        <v>617</v>
-      </c>
-      <c r="H241" t="s">
+      <c r="C243" t="s">
+        <v>628</v>
+      </c>
+      <c r="D243" t="s">
+        <v>508</v>
+      </c>
+      <c r="E243" t="s">
+        <v>584</v>
+      </c>
+      <c r="F243" t="s">
+        <v>630</v>
+      </c>
+      <c r="G243" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="244" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B244" t="s">
+        <v>585</v>
+      </c>
+      <c r="C244" t="s">
+        <v>556</v>
+      </c>
+      <c r="D244" t="s">
+        <v>578</v>
+      </c>
+      <c r="F244" t="s">
+        <v>587</v>
+      </c>
+      <c r="G244" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="245" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B245" t="s">
+        <v>538</v>
+      </c>
+      <c r="C245" t="s">
+        <v>521</v>
+      </c>
+      <c r="D245" t="s">
+        <v>631</v>
+      </c>
+      <c r="F245" t="s">
+        <v>586</v>
+      </c>
+      <c r="G245" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="242" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B242" t="s">
-        <v>548</v>
-      </c>
-      <c r="C242" t="s">
-        <v>618</v>
-      </c>
-      <c r="D242" t="s">
-        <v>552</v>
-      </c>
-      <c r="E242" t="s">
-        <v>619</v>
-      </c>
-      <c r="F242" t="s">
-        <v>620</v>
-      </c>
-      <c r="G242" t="s">
-        <v>621</v>
-      </c>
-      <c r="H242" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="243" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B243" t="s">
-        <v>557</v>
-      </c>
-      <c r="C243" t="s">
-        <v>595</v>
-      </c>
-      <c r="D243" t="s">
-        <v>577</v>
-      </c>
-      <c r="E243" t="s">
-        <v>622</v>
-      </c>
-      <c r="F243" t="s">
-        <v>623</v>
-      </c>
-      <c r="G243" t="s">
-        <v>555</v>
-      </c>
-      <c r="H243" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="244" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B244" t="s">
-        <v>552</v>
-      </c>
-      <c r="C244" t="s">
-        <v>624</v>
-      </c>
-      <c r="D244" t="s">
-        <v>625</v>
-      </c>
-      <c r="E244" t="s">
-        <v>626</v>
-      </c>
-      <c r="G244" t="s">
-        <v>627</v>
-      </c>
-      <c r="H244" t="s">
+    <row r="246" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B246" t="s">
+        <v>560</v>
+      </c>
+      <c r="C246" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="245" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C245" t="s">
-        <v>553</v>
-      </c>
-      <c r="D245" t="s">
-        <v>572</v>
-      </c>
-      <c r="E245" t="s">
-        <v>628</v>
-      </c>
-      <c r="G245" t="s">
-        <v>629</v>
-      </c>
-      <c r="H245" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="246" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B246" t="s">
-        <v>567</v>
-      </c>
-      <c r="C246" t="s">
-        <v>630</v>
-      </c>
       <c r="D246" t="s">
-        <v>596</v>
-      </c>
-      <c r="E246" t="s">
-        <v>631</v>
+        <v>588</v>
+      </c>
+      <c r="F246" t="s">
+        <v>513</v>
       </c>
       <c r="G246" t="s">
-        <v>565</v>
-      </c>
-      <c r="H246" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="247" spans="2:8" x14ac:dyDescent="0.25">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="247" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B247" t="s">
-        <v>629</v>
+        <v>589</v>
       </c>
       <c r="C247" t="s">
-        <v>568</v>
+        <v>534</v>
       </c>
       <c r="D247" t="s">
         <v>632</v>
       </c>
-      <c r="E247" t="s">
-        <v>633</v>
+      <c r="F247" t="s">
+        <v>100</v>
       </c>
       <c r="G247" t="s">
-        <v>109</v>
-      </c>
-      <c r="H247" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="248" spans="2:8" x14ac:dyDescent="0.25">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="248" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B248" t="s">
-        <v>634</v>
+        <v>591</v>
       </c>
       <c r="C248" t="s">
-        <v>635</v>
+        <v>576</v>
       </c>
       <c r="D248" t="s">
         <v>634</v>
       </c>
-      <c r="E248" t="s">
-        <v>636</v>
-      </c>
-      <c r="H248" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="249" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F248" t="s">
+        <v>523</v>
+      </c>
+      <c r="G248" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="249" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B249" t="s">
+        <v>514</v>
+      </c>
       <c r="C249" t="s">
-        <v>573</v>
+        <v>553</v>
       </c>
       <c r="D249" t="s">
-        <v>546</v>
-      </c>
-      <c r="E249" t="s">
-        <v>556</v>
-      </c>
-      <c r="H249" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="250" spans="2:8" x14ac:dyDescent="0.25">
+        <v>596</v>
+      </c>
+      <c r="F249" t="s">
+        <v>583</v>
+      </c>
+      <c r="G249" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="250" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B250" t="s">
+        <v>528</v>
+      </c>
       <c r="C250" t="s">
-        <v>581</v>
+        <v>551</v>
       </c>
       <c r="D250" t="s">
-        <v>562</v>
-      </c>
-      <c r="E250" t="s">
-        <v>637</v>
-      </c>
-      <c r="H250" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="251" spans="2:8" x14ac:dyDescent="0.25">
+        <v>590</v>
+      </c>
+      <c r="F250" t="s">
+        <v>531</v>
+      </c>
+      <c r="G250" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="251" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B251" t="s">
+        <v>594</v>
+      </c>
       <c r="C251" t="s">
+        <v>539</v>
+      </c>
+      <c r="D251" t="s">
+        <v>519</v>
+      </c>
+      <c r="F251" t="s">
+        <v>536</v>
+      </c>
+      <c r="G251" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="252" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B252" t="s">
+        <v>525</v>
+      </c>
+      <c r="C252" t="s">
+        <v>561</v>
+      </c>
+      <c r="D252" t="s">
         <v>592</v>
       </c>
-      <c r="D251" t="s">
-        <v>639</v>
-      </c>
-      <c r="E251" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="252" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C252" t="s">
-        <v>564</v>
-      </c>
-      <c r="D252" t="s">
+      <c r="F252" t="s">
+        <v>527</v>
+      </c>
+      <c r="G252" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="253" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B253" t="s">
+        <v>516</v>
+      </c>
+      <c r="C253" t="s">
+        <v>529</v>
+      </c>
+      <c r="D253" t="s">
+        <v>532</v>
+      </c>
+      <c r="G253" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="254" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C254" t="s">
         <v>557</v>
       </c>
-      <c r="E252" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="253" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C253" t="s">
-        <v>563</v>
-      </c>
-      <c r="D253" t="s">
-        <v>548</v>
-      </c>
-      <c r="E253" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="254" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C254" t="s">
-        <v>597</v>
-      </c>
-      <c r="E254" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="255" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D254" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="255" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C255" t="s">
         <v>554</v>
       </c>
-      <c r="E255" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="256" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D255" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="256" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C256" t="s">
-        <v>591</v>
-      </c>
-      <c r="E256" t="s">
-        <v>641</v>
+        <v>543</v>
+      </c>
+      <c r="D256" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C257" t="s">
-        <v>642</v>
-      </c>
-      <c r="E257" t="s">
-        <v>580</v>
+        <v>555</v>
+      </c>
+      <c r="D257" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E258" t="s">
-        <v>571</v>
+      <c r="C258" t="s">
+        <v>517</v>
+      </c>
+      <c r="D258" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E259" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="260" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A260" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B260" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="C260" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="D260" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="E260" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="F260" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="G260" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="H260" s="9" t="s">
-        <v>643</v>
+      <c r="D259" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D260" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D261" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A262" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B262" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="C262" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="D262" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E262" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="F262" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="G262" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="H262" s="6" t="s">
+        <v>597</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/List_Team_Region.xlsx
+++ b/public/data/List_Team_Region.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muham\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9088B6B0-BA65-4C94-9BFB-186DA718DD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4446C9E-D804-4C9F-B0A4-4BBBC3DB01CE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
+    <workbookView xWindow="2130" yWindow="2670" windowWidth="21600" windowHeight="11295" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,12 +23,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="636">
   <si>
     <t>JAMBI</t>
   </si>
@@ -1950,7 +1945,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2246,37 +2241,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <font>
         <strike val="0"/>
@@ -2508,7 +2473,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}" name="Table919" displayName="Table919" ref="B3:H22" totalsRowShown="0" headerRowDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}" name="Table919" displayName="Table919" ref="B3:H22" totalsRowShown="0" headerRowDxfId="11">
   <autoFilter ref="B3:H22" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{1E18F602-B85E-4C85-8C34-8684E3651598}" name="INTERNAL JAMBI"/>
@@ -2524,7 +2489,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}" name="Table27" displayName="Table27" ref="B130:T147" totalsRowShown="0" headerRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}" name="Table27" displayName="Table27" ref="B130:T147" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="B130:T147" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{F8A4E442-73AD-4EB9-BB0D-D55E87DA1888}" name="SERPO PALEMBANG KOTA"/>
@@ -2552,7 +2517,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57681EA6-18EF-4E05-B178-44A6E049B133}" name="Table1020" displayName="Table1020" ref="B26:J44" totalsRowShown="0" headerRowDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57681EA6-18EF-4E05-B178-44A6E049B133}" name="Table1020" displayName="Table1020" ref="B26:J44" totalsRowShown="0" headerRowDxfId="10">
   <autoFilter ref="B26:J44" xr:uid="{57681EA6-18EF-4E05-B178-44A6E049B133}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{A8602C42-C67C-43B1-B2C0-728995582D93}" name="SERPO BUNGO"/>
@@ -2570,7 +2535,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C6FB933F-6103-42DE-BAEC-03E0FCFEB76C}" name="Table1121" displayName="Table1121" ref="B50:G78" totalsRowShown="0" headerRowDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C6FB933F-6103-42DE-BAEC-03E0FCFEB76C}" name="Table1121" displayName="Table1121" ref="B50:G78" totalsRowShown="0" headerRowDxfId="9">
   <autoFilter ref="B50:G78" xr:uid="{C6FB933F-6103-42DE-BAEC-03E0FCFEB76C}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{DCC806F7-D168-48B2-B03E-CCE7FD87EEA9}" name="SIB PESAWARAN"/>
@@ -2585,7 +2550,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6E2D26AE-ECD5-48A4-AC1D-1B4180A6F140}" name="Table1222" displayName="Table1222" ref="B82:J104" totalsRowShown="0" headerRowDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6E2D26AE-ECD5-48A4-AC1D-1B4180A6F140}" name="Table1222" displayName="Table1222" ref="B82:J104" totalsRowShown="0" headerRowDxfId="8">
   <autoFilter ref="B82:J104" xr:uid="{6E2D26AE-ECD5-48A4-AC1D-1B4180A6F140}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{060484FA-EE1E-4DC8-9A74-A60AA9B20548}" name="SERPO TEGINENENG_x0009__x0009_"/>
@@ -2603,7 +2568,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}" name="Table1323" displayName="Table1323" ref="B110:O127" totalsRowShown="0" headerRowDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}" name="Table1323" displayName="Table1323" ref="B110:O127" totalsRowShown="0" headerRowDxfId="7">
   <autoFilter ref="B110:O127" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{6FB6563D-399C-4506-8AF0-A312347E4888}" name="REG7 PALEMBANG 1"/>
@@ -2626,7 +2591,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}" name="Table1424" displayName="Table1424" ref="B152:I176" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}" name="Table1424" displayName="Table1424" ref="B152:I176" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
   <autoFilter ref="B152:I176" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{9BFFF82B-4674-404E-AC18-7772CF16890E}" name="GSP BENGKULU 1"/>
@@ -2643,7 +2608,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}" name="Table1525" displayName="Table1525" ref="B180:H210" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}" name="Table1525" displayName="Table1525" ref="B180:H210" totalsRowShown="0" headerRowDxfId="3">
   <autoFilter ref="B180:H210" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{ACEB90AF-9CBB-4605-8377-2CF0EF299650}" name="SERPO SUKAMERINDU"/>
@@ -2659,7 +2624,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}" name="Table1626" displayName="Table1626" ref="B215:H237" totalsRowShown="0" headerRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}" name="Table1626" displayName="Table1626" ref="B215:H237" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="B215:H237" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D0B3A41D-F35E-4B89-AC56-18717B9B04E5}" name="BANGKA REG 7"/>
@@ -2675,7 +2640,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}" name="Table1727" displayName="Table1727" ref="B240:G261" totalsRowShown="0" headerRowDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}" name="Table1727" displayName="Table1727" ref="B240:G261" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="B240:G261" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{97E25E83-847F-4991-A885-21D98063A2DB}" name="SERPO KOBA"/>
@@ -3007,35 +2972,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D0AF9EF-6686-405D-9473-604A5805FA6C}">
   <dimension ref="A1:T262"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="34.140625" customWidth="1"/>
+    <col min="2" max="2" width="34.125" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="27.7109375" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" customWidth="1"/>
-    <col min="6" max="6" width="27.5703125" customWidth="1"/>
-    <col min="7" max="7" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="27.75" customWidth="1"/>
+    <col min="5" max="5" width="26.625" customWidth="1"/>
+    <col min="6" max="6" width="27.625" customWidth="1"/>
+    <col min="7" max="7" width="22.875" customWidth="1"/>
     <col min="8" max="8" width="27" customWidth="1"/>
-    <col min="9" max="9" width="21.85546875" customWidth="1"/>
-    <col min="10" max="10" width="27.140625" customWidth="1"/>
-    <col min="11" max="11" width="24.7109375" customWidth="1"/>
-    <col min="12" max="12" width="27.5703125" customWidth="1"/>
-    <col min="13" max="13" width="21.85546875" customWidth="1"/>
+    <col min="9" max="9" width="21.875" customWidth="1"/>
+    <col min="10" max="10" width="27.125" customWidth="1"/>
+    <col min="11" max="11" width="24.75" customWidth="1"/>
+    <col min="12" max="12" width="27.625" customWidth="1"/>
+    <col min="13" max="13" width="21.875" customWidth="1"/>
     <col min="14" max="14" width="28" customWidth="1"/>
-    <col min="15" max="15" width="25.7109375" customWidth="1"/>
-    <col min="16" max="16" width="20.85546875" customWidth="1"/>
-    <col min="17" max="17" width="23.85546875" customWidth="1"/>
-    <col min="18" max="18" width="22.28515625" customWidth="1"/>
-    <col min="19" max="19" width="28.140625" customWidth="1"/>
-    <col min="20" max="20" width="27.28515625" customWidth="1"/>
+    <col min="15" max="15" width="25.75" customWidth="1"/>
+    <col min="16" max="16" width="20.875" customWidth="1"/>
+    <col min="17" max="17" width="23.875" customWidth="1"/>
+    <col min="18" max="18" width="22.25" customWidth="1"/>
+    <col min="19" max="19" width="28.125" customWidth="1"/>
+    <col min="20" max="20" width="27.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -3055,7 +3020,7 @@
       <c r="M2" s="26"/>
       <c r="N2" s="26"/>
     </row>
-    <row r="3" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" s="3" customFormat="1">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -3081,7 +3046,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14">
       <c r="B4" t="s">
         <v>11</v>
       </c>
@@ -3104,7 +3069,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14">
       <c r="B5" t="s">
         <v>17</v>
       </c>
@@ -3127,7 +3092,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14">
       <c r="B6" t="s">
         <v>24</v>
       </c>
@@ -3150,7 +3115,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14">
       <c r="B7" t="s">
         <v>31</v>
       </c>
@@ -3173,7 +3138,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14">
       <c r="B8" t="s">
         <v>38</v>
       </c>
@@ -3196,7 +3161,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14">
       <c r="B9" t="s">
         <v>43</v>
       </c>
@@ -3216,7 +3181,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14">
       <c r="B10" t="s">
         <v>47</v>
       </c>
@@ -3236,7 +3201,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14">
       <c r="B11" t="s">
         <v>598</v>
       </c>
@@ -3250,7 +3215,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14">
       <c r="B12" t="s">
         <v>54</v>
       </c>
@@ -3264,7 +3229,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14">
       <c r="B13" t="s">
         <v>57</v>
       </c>
@@ -3275,7 +3240,10 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14">
+      <c r="B14" t="s">
+        <v>101</v>
+      </c>
       <c r="D14" t="s">
         <v>62</v>
       </c>
@@ -3283,7 +3251,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14">
       <c r="D15" t="s">
         <v>64</v>
       </c>
@@ -3291,7 +3259,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14">
       <c r="D16" t="s">
         <v>66</v>
       </c>
@@ -3299,7 +3267,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20">
       <c r="D17" t="s">
         <v>68</v>
       </c>
@@ -3307,7 +3275,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20">
       <c r="D18" t="s">
         <v>70</v>
       </c>
@@ -3315,7 +3283,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20">
       <c r="D19" t="s">
         <v>72</v>
       </c>
@@ -3323,7 +3291,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20">
       <c r="D20" t="s">
         <v>74</v>
       </c>
@@ -3331,7 +3299,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" s="4" customFormat="1">
       <c r="A23" s="4" t="s">
         <v>75</v>
       </c>
@@ -3357,7 +3325,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="15">
       <c r="A25" s="2" t="s">
         <v>1</v>
       </c>
@@ -3383,7 +3351,7 @@
       <c r="S25" s="28"/>
       <c r="T25" s="28"/>
     </row>
-    <row r="26" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" s="5" customFormat="1">
       <c r="A26" s="5" t="s">
         <v>3</v>
       </c>
@@ -3415,7 +3383,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20">
       <c r="B27" t="s">
         <v>606</v>
       </c>
@@ -3444,7 +3412,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20">
       <c r="B28" t="s">
         <v>99</v>
       </c>
@@ -3470,7 +3438,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20">
       <c r="B29" t="s">
         <v>95</v>
       </c>
@@ -3496,7 +3464,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20">
       <c r="B30" t="s">
         <v>97</v>
       </c>
@@ -3522,7 +3490,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20">
       <c r="B31" t="s">
         <v>102</v>
       </c>
@@ -3548,7 +3516,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20">
       <c r="C32" t="s">
         <v>40</v>
       </c>
@@ -3568,7 +3536,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10">
       <c r="C33" t="s">
         <v>67</v>
       </c>
@@ -3588,7 +3556,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10">
       <c r="C34" t="s">
         <v>57</v>
       </c>
@@ -3608,7 +3576,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10">
       <c r="C35" t="s">
         <v>69</v>
       </c>
@@ -3625,7 +3593,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10">
       <c r="C36" t="s">
         <v>56</v>
       </c>
@@ -3639,7 +3607,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10">
       <c r="C37" t="s">
         <v>61</v>
       </c>
@@ -3650,7 +3618,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10">
       <c r="C38" t="s">
         <v>53</v>
       </c>
@@ -3661,7 +3629,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10">
       <c r="C39" t="s">
         <v>21</v>
       </c>
@@ -3669,7 +3637,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10">
       <c r="C40" t="s">
         <v>44</v>
       </c>
@@ -3677,7 +3645,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10">
       <c r="C41" t="s">
         <v>65</v>
       </c>
@@ -3685,17 +3653,17 @@
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10">
       <c r="G42" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10">
       <c r="G43" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="45" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" s="6" customFormat="1">
       <c r="A45" s="6" t="s">
         <v>75</v>
       </c>
@@ -3727,12 +3695,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="15">
       <c r="A48" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14">
       <c r="A49" s="2" t="s">
         <v>1</v>
       </c>
@@ -3752,7 +3720,7 @@
       <c r="M49" s="26"/>
       <c r="N49" s="26"/>
     </row>
-    <row r="50" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" s="3" customFormat="1">
       <c r="A50" s="3" t="s">
         <v>3</v>
       </c>
@@ -3775,7 +3743,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14">
       <c r="B51" t="s">
         <v>114</v>
       </c>
@@ -3795,7 +3763,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14">
       <c r="B52" t="s">
         <v>119</v>
       </c>
@@ -3815,7 +3783,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14">
       <c r="B53" t="s">
         <v>125</v>
       </c>
@@ -3835,7 +3803,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14">
       <c r="B54" t="s">
         <v>131</v>
       </c>
@@ -3855,7 +3823,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14">
       <c r="B55" t="s">
         <v>137</v>
       </c>
@@ -3875,7 +3843,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14">
       <c r="B56" t="s">
         <v>143</v>
       </c>
@@ -3895,7 +3863,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14">
       <c r="C57" t="s">
         <v>153</v>
       </c>
@@ -3909,7 +3877,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14">
       <c r="C58" t="s">
         <v>157</v>
       </c>
@@ -3923,7 +3891,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14">
       <c r="C59" t="s">
         <v>161</v>
       </c>
@@ -3937,7 +3905,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14">
       <c r="C60" t="s">
         <v>163</v>
       </c>
@@ -3951,7 +3919,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14">
       <c r="C61" t="s">
         <v>115</v>
       </c>
@@ -3965,7 +3933,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14">
       <c r="C62" t="s">
         <v>611</v>
       </c>
@@ -3979,7 +3947,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14">
       <c r="C63" t="s">
         <v>612</v>
       </c>
@@ -3993,77 +3961,77 @@
         <v>167</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14">
       <c r="G64" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7">
       <c r="G65" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7">
       <c r="G66" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7">
       <c r="G67" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7">
       <c r="G68" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7">
       <c r="G69" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7">
       <c r="G70" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7">
       <c r="G71" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7">
       <c r="G72" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7">
       <c r="G73" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7">
       <c r="G74" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7">
       <c r="G75" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7">
       <c r="G76" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7">
       <c r="G77" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="79" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" s="4" customFormat="1">
       <c r="A79" s="4" t="s">
         <v>75</v>
       </c>
@@ -4086,7 +4054,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="15">
       <c r="A81" s="2" t="s">
         <v>1</v>
       </c>
@@ -4112,7 +4080,7 @@
       <c r="S81" s="28"/>
       <c r="T81" s="28"/>
     </row>
-    <row r="82" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" s="6" customFormat="1">
       <c r="A82" s="5" t="s">
         <v>3</v>
       </c>
@@ -4144,7 +4112,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20">
       <c r="B83" t="s">
         <v>141</v>
       </c>
@@ -4173,7 +4141,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20">
       <c r="B84" t="s">
         <v>155</v>
       </c>
@@ -4196,7 +4164,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20">
       <c r="B85" t="s">
         <v>117</v>
       </c>
@@ -4213,7 +4181,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20">
       <c r="B86" t="s">
         <v>616</v>
       </c>
@@ -4230,7 +4198,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20">
       <c r="B87" t="s">
         <v>203</v>
       </c>
@@ -4247,7 +4215,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20">
       <c r="B88" t="s">
         <v>123</v>
       </c>
@@ -4264,7 +4232,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20">
       <c r="B89" t="s">
         <v>617</v>
       </c>
@@ -4281,7 +4249,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20">
       <c r="B90" t="s">
         <v>151</v>
       </c>
@@ -4295,7 +4263,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20">
       <c r="B91" t="s">
         <v>129</v>
       </c>
@@ -4306,7 +4274,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20">
       <c r="B92" t="s">
         <v>159</v>
       </c>
@@ -4317,7 +4285,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20">
       <c r="B93" t="s">
         <v>135</v>
       </c>
@@ -4328,7 +4296,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20">
       <c r="B94" t="s">
         <v>209</v>
       </c>
@@ -4339,7 +4307,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20">
       <c r="B95" t="s">
         <v>147</v>
       </c>
@@ -4350,7 +4318,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20">
       <c r="B96" t="s">
         <v>618</v>
       </c>
@@ -4361,7 +4329,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15">
       <c r="B97" t="s">
         <v>619</v>
       </c>
@@ -4369,7 +4337,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15">
       <c r="B98" t="s">
         <v>620</v>
       </c>
@@ -4377,7 +4345,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15">
       <c r="B99" t="s">
         <v>621</v>
       </c>
@@ -4385,7 +4353,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15">
       <c r="B100" t="s">
         <v>622</v>
       </c>
@@ -4393,7 +4361,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15">
       <c r="B101" t="s">
         <v>623</v>
       </c>
@@ -4401,7 +4369,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15">
       <c r="B102" t="s">
         <v>624</v>
       </c>
@@ -4409,7 +4377,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15">
       <c r="B103" t="s">
         <v>625</v>
       </c>
@@ -4417,7 +4385,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15">
       <c r="B104" t="s">
         <v>207</v>
       </c>
@@ -4425,7 +4393,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="105" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" s="6" customFormat="1">
       <c r="A105" s="6" t="s">
         <v>75</v>
       </c>
@@ -4454,12 +4422,12 @@
         <v>212</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" ht="15">
       <c r="A108" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15">
       <c r="A109" s="2" t="s">
         <v>1</v>
       </c>
@@ -4479,7 +4447,7 @@
       <c r="M109" s="26"/>
       <c r="N109" s="26"/>
     </row>
-    <row r="110" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" s="3" customFormat="1">
       <c r="A110" s="3" t="s">
         <v>3</v>
       </c>
@@ -4526,7 +4494,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15">
       <c r="B111" t="s">
         <v>229</v>
       </c>
@@ -4570,7 +4538,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15">
       <c r="B112" t="s">
         <v>243</v>
       </c>
@@ -4614,7 +4582,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15">
       <c r="B113" t="s">
         <v>256</v>
       </c>
@@ -4655,7 +4623,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15">
       <c r="B114" t="s">
         <v>269</v>
       </c>
@@ -4696,7 +4664,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15">
       <c r="B115" t="s">
         <v>281</v>
       </c>
@@ -4734,7 +4702,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15">
       <c r="B116" t="s">
         <v>293</v>
       </c>
@@ -4766,7 +4734,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15">
       <c r="B117" t="s">
         <v>303</v>
       </c>
@@ -4795,7 +4763,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15">
       <c r="B118" t="s">
         <v>312</v>
       </c>
@@ -4818,7 +4786,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15">
       <c r="B119" t="s">
         <v>318</v>
       </c>
@@ -4835,7 +4803,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15">
       <c r="B120" t="s">
         <v>323</v>
       </c>
@@ -4849,7 +4817,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15">
       <c r="B121" t="s">
         <v>327</v>
       </c>
@@ -4860,7 +4828,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15">
       <c r="B122" t="s">
         <v>330</v>
       </c>
@@ -4868,27 +4836,27 @@
         <v>331</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15">
       <c r="K123" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15">
       <c r="K124" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15">
       <c r="K125" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15">
       <c r="K126" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="127" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" s="4" customFormat="1">
       <c r="A127" s="4" t="s">
         <v>75</v>
       </c>
@@ -4935,7 +4903,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:20" ht="15">
       <c r="A129" s="2" t="s">
         <v>1</v>
       </c>
@@ -4961,7 +4929,7 @@
       <c r="S129" s="28"/>
       <c r="T129" s="28"/>
     </row>
-    <row r="130" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:20" s="5" customFormat="1">
       <c r="A130" s="5" t="s">
         <v>3</v>
       </c>
@@ -5023,7 +4991,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:20">
       <c r="B131" t="s">
         <v>289</v>
       </c>
@@ -5082,7 +5050,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:20">
       <c r="B132" t="s">
         <v>229</v>
       </c>
@@ -5135,7 +5103,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:20">
       <c r="B133" t="s">
         <v>243</v>
       </c>
@@ -5182,7 +5150,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:20">
       <c r="B134" t="s">
         <v>256</v>
       </c>
@@ -5217,7 +5185,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:20">
       <c r="B135" t="s">
         <v>327</v>
       </c>
@@ -5252,7 +5220,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:20">
       <c r="B136" t="s">
         <v>378</v>
       </c>
@@ -5284,7 +5252,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:20">
       <c r="B137" t="s">
         <v>379</v>
       </c>
@@ -5313,7 +5281,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:20">
       <c r="B138" t="s">
         <v>281</v>
       </c>
@@ -5336,7 +5304,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:20">
       <c r="B139" t="s">
         <v>322</v>
       </c>
@@ -5356,7 +5324,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:20">
       <c r="B140" t="s">
         <v>326</v>
       </c>
@@ -5370,7 +5338,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:20">
       <c r="B141" t="s">
         <v>330</v>
       </c>
@@ -5381,32 +5349,32 @@
         <v>313</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:20">
       <c r="B142" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:20">
       <c r="B143" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:20">
       <c r="B144" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:20">
       <c r="B145" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:20">
       <c r="B146" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="147" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:20" s="6" customFormat="1">
       <c r="A147" s="6" t="s">
         <v>75</v>
       </c>
@@ -5468,12 +5436,12 @@
         <v>380</v>
       </c>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:20" ht="15">
       <c r="A150" s="7" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:20">
       <c r="A151" s="2" t="s">
         <v>1</v>
       </c>
@@ -5493,7 +5461,7 @@
       <c r="M151" s="26"/>
       <c r="N151" s="26"/>
     </row>
-    <row r="152" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:20" s="12" customFormat="1" ht="15">
       <c r="A152" s="3" t="s">
         <v>3</v>
       </c>
@@ -5522,7 +5490,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="153" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:20" ht="28.5">
       <c r="B153" s="13" t="s">
         <v>392</v>
       </c>
@@ -5548,7 +5516,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:20">
       <c r="B154" t="s">
         <v>400</v>
       </c>
@@ -5574,7 +5542,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="155" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:20" ht="28.5">
       <c r="B155" s="17" t="s">
         <v>406</v>
       </c>
@@ -5600,7 +5568,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:20">
       <c r="B156" t="s">
         <v>414</v>
       </c>
@@ -5626,7 +5594,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:20">
       <c r="B157" t="s">
         <v>422</v>
       </c>
@@ -5649,7 +5617,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:20" ht="15">
       <c r="B158" t="s">
         <v>428</v>
       </c>
@@ -5670,7 +5638,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:20">
       <c r="B159" t="s">
         <v>434</v>
       </c>
@@ -5690,7 +5658,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:20">
       <c r="B160" t="s">
         <v>400</v>
       </c>
@@ -5707,7 +5675,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="161" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:9">
       <c r="B161" t="s">
         <v>444</v>
       </c>
@@ -5724,7 +5692,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="162" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:9" ht="28.5">
       <c r="B162" s="14" t="s">
         <v>449</v>
       </c>
@@ -5741,7 +5709,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="163" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:9">
       <c r="B163" t="s">
         <v>454</v>
       </c>
@@ -5755,7 +5723,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="164" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:9">
       <c r="B164" t="s">
         <v>400</v>
       </c>
@@ -5769,7 +5737,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="165" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:9">
       <c r="B165" t="s">
         <v>460</v>
       </c>
@@ -5780,7 +5748,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="166" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:9">
       <c r="B166" t="s">
         <v>463</v>
       </c>
@@ -5791,7 +5759,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="167" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:9">
       <c r="B167" t="s">
         <v>466</v>
       </c>
@@ -5802,7 +5770,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="168" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:9">
       <c r="B168" t="s">
         <v>414</v>
       </c>
@@ -5813,7 +5781,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="169" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:9">
       <c r="B169" t="s">
         <v>471</v>
       </c>
@@ -5824,7 +5792,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="170" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:9" ht="15">
       <c r="B170" t="s">
         <v>473</v>
       </c>
@@ -5835,37 +5803,37 @@
         <v>465</v>
       </c>
     </row>
-    <row r="171" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:9">
       <c r="B171" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="172" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:9">
       <c r="B172" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="173" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:9">
       <c r="B173" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="174" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:9">
       <c r="B174" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="175" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:9">
       <c r="B175" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="176" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:9">
       <c r="B176" s="22" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:20" ht="15">
       <c r="A177" s="4" t="s">
         <v>75</v>
       </c>
@@ -5894,7 +5862,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:20" ht="15">
       <c r="A179" s="2" t="s">
         <v>1</v>
       </c>
@@ -5920,7 +5888,7 @@
       <c r="S179" s="28"/>
       <c r="T179" s="28"/>
     </row>
-    <row r="180" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:20" s="5" customFormat="1">
       <c r="A180" s="5" t="s">
         <v>3</v>
       </c>
@@ -5946,7 +5914,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:20">
       <c r="B181" t="s">
         <v>393</v>
       </c>
@@ -5969,7 +5937,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:20">
       <c r="B182" t="s">
         <v>401</v>
       </c>
@@ -5992,7 +5960,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:20">
       <c r="B183" t="s">
         <v>407</v>
       </c>
@@ -6012,7 +5980,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:20">
       <c r="B184" t="s">
         <v>415</v>
       </c>
@@ -6023,7 +5991,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:20">
       <c r="B185" t="s">
         <v>423</v>
       </c>
@@ -6031,7 +5999,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:20">
       <c r="B186" t="s">
         <v>429</v>
       </c>
@@ -6039,7 +6007,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:20">
       <c r="B187" t="s">
         <v>435</v>
       </c>
@@ -6047,7 +6015,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:20">
       <c r="B188" t="s">
         <v>440</v>
       </c>
@@ -6055,7 +6023,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:20">
       <c r="B189" t="s">
         <v>445</v>
       </c>
@@ -6063,7 +6031,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:20">
       <c r="B190" t="s">
         <v>450</v>
       </c>
@@ -6071,7 +6039,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:20">
       <c r="B191" t="s">
         <v>435</v>
       </c>
@@ -6079,7 +6047,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:20">
       <c r="B192" t="s">
         <v>457</v>
       </c>
@@ -6087,7 +6055,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="193" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:3">
       <c r="B193" t="s">
         <v>472</v>
       </c>
@@ -6095,7 +6063,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="194" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:3">
       <c r="B194" t="s">
         <v>461</v>
       </c>
@@ -6103,7 +6071,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="195" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:3">
       <c r="B195" t="s">
         <v>464</v>
       </c>
@@ -6111,7 +6079,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="196" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:3">
       <c r="B196" t="s">
         <v>467</v>
       </c>
@@ -6119,7 +6087,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="197" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:3">
       <c r="B197" t="s">
         <v>469</v>
       </c>
@@ -6127,7 +6095,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="198" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:3">
       <c r="B198" t="s">
         <v>474</v>
       </c>
@@ -6135,7 +6103,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="199" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:3">
       <c r="B199" t="s">
         <v>449</v>
       </c>
@@ -6143,7 +6111,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="200" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:3">
       <c r="B200" t="s">
         <v>454</v>
       </c>
@@ -6151,7 +6119,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="201" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:3">
       <c r="B201" t="s">
         <v>400</v>
       </c>
@@ -6159,7 +6127,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="202" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:3">
       <c r="B202" t="s">
         <v>460</v>
       </c>
@@ -6167,7 +6135,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="203" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:3">
       <c r="B203" t="s">
         <v>463</v>
       </c>
@@ -6175,7 +6143,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="204" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:3">
       <c r="B204" t="s">
         <v>400</v>
       </c>
@@ -6183,32 +6151,32 @@
         <v>439</v>
       </c>
     </row>
-    <row r="205" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:3">
       <c r="C205" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="206" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:3">
       <c r="C206" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="207" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:3">
       <c r="C207" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="208" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:3">
       <c r="C208" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:14">
       <c r="C209" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="210" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:14" s="6" customFormat="1">
       <c r="A210" s="6" t="s">
         <v>75</v>
       </c>
@@ -6234,12 +6202,12 @@
         <v>497</v>
       </c>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:14" ht="15">
       <c r="A213" s="7" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:14">
       <c r="A214" s="2" t="s">
         <v>1</v>
       </c>
@@ -6259,7 +6227,7 @@
       <c r="M214" s="26"/>
       <c r="N214" s="26"/>
     </row>
-    <row r="215" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:14" s="3" customFormat="1">
       <c r="A215" s="3" t="s">
         <v>3</v>
       </c>
@@ -6285,7 +6253,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:14">
       <c r="B216" t="s">
         <v>558</v>
       </c>
@@ -6308,7 +6276,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:14">
       <c r="B217" t="s">
         <v>546</v>
       </c>
@@ -6328,7 +6296,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:14">
       <c r="B218" t="s">
         <v>628</v>
       </c>
@@ -6345,7 +6313,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:14">
       <c r="B219" t="s">
         <v>556</v>
       </c>
@@ -6362,7 +6330,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:14">
       <c r="B220" t="s">
         <v>521</v>
       </c>
@@ -6379,7 +6347,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:14">
       <c r="B221" t="s">
         <v>559</v>
       </c>
@@ -6396,7 +6364,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:14">
       <c r="B222" t="s">
         <v>534</v>
       </c>
@@ -6413,7 +6381,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:14">
       <c r="B223" t="s">
         <v>576</v>
       </c>
@@ -6430,7 +6398,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:14">
       <c r="B224" t="s">
         <v>553</v>
       </c>
@@ -6447,7 +6415,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:20">
       <c r="B225" t="s">
         <v>551</v>
       </c>
@@ -6464,7 +6432,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:20">
       <c r="B226" t="s">
         <v>539</v>
       </c>
@@ -6475,7 +6443,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:20">
       <c r="B227" t="s">
         <v>561</v>
       </c>
@@ -6486,7 +6454,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:20">
       <c r="B228" t="s">
         <v>529</v>
       </c>
@@ -6494,7 +6462,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:20">
       <c r="B229" t="s">
         <v>557</v>
       </c>
@@ -6502,27 +6470,27 @@
         <v>580</v>
       </c>
     </row>
-    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:20">
       <c r="B230" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:20">
       <c r="B231" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:20">
       <c r="B232" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:20">
       <c r="B233" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="237" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:20" s="4" customFormat="1">
       <c r="A237" s="4" t="s">
         <v>75</v>
       </c>
@@ -6548,7 +6516,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:20" ht="15">
       <c r="A239" s="2" t="s">
         <v>1</v>
       </c>
@@ -6574,7 +6542,7 @@
       <c r="S239" s="28"/>
       <c r="T239" s="28"/>
     </row>
-    <row r="240" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:20" s="5" customFormat="1">
       <c r="A240" s="5" t="s">
         <v>3</v>
       </c>
@@ -6597,7 +6565,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="241" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:7">
       <c r="B241" t="s">
         <v>577</v>
       </c>
@@ -6617,7 +6585,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="242" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:7">
       <c r="B242" t="s">
         <v>520</v>
       </c>
@@ -6637,7 +6605,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="243" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:7">
       <c r="B243" t="s">
         <v>542</v>
       </c>
@@ -6657,7 +6625,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="244" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:7">
       <c r="B244" t="s">
         <v>585</v>
       </c>
@@ -6674,7 +6642,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="245" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:7">
       <c r="B245" t="s">
         <v>538</v>
       </c>
@@ -6691,7 +6659,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="246" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:7">
       <c r="B246" t="s">
         <v>560</v>
       </c>
@@ -6708,7 +6676,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="247" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:7">
       <c r="B247" t="s">
         <v>589</v>
       </c>
@@ -6725,7 +6693,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="248" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:7">
       <c r="B248" t="s">
         <v>591</v>
       </c>
@@ -6742,7 +6710,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="249" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:7">
       <c r="B249" t="s">
         <v>514</v>
       </c>
@@ -6759,7 +6727,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="250" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:7">
       <c r="B250" t="s">
         <v>528</v>
       </c>
@@ -6776,7 +6744,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="251" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:7">
       <c r="B251" t="s">
         <v>594</v>
       </c>
@@ -6793,7 +6761,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="252" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:7">
       <c r="B252" t="s">
         <v>525</v>
       </c>
@@ -6810,7 +6778,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="253" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:7">
       <c r="B253" t="s">
         <v>516</v>
       </c>
@@ -6824,7 +6792,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="254" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:7">
       <c r="C254" t="s">
         <v>557</v>
       </c>
@@ -6832,7 +6800,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="255" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:7">
       <c r="C255" t="s">
         <v>554</v>
       </c>
@@ -6840,7 +6808,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="256" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:7">
       <c r="C256" t="s">
         <v>543</v>
       </c>
@@ -6848,7 +6816,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8">
       <c r="C257" t="s">
         <v>555</v>
       </c>
@@ -6856,7 +6824,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8">
       <c r="C258" t="s">
         <v>517</v>
       </c>
@@ -6864,22 +6832,22 @@
         <v>524</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8">
       <c r="D259" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8">
       <c r="D260" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8">
       <c r="D261" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="262" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" s="6" customFormat="1">
       <c r="A262" s="6" t="s">
         <v>75</v>
       </c>

--- a/public/data/List_Team_Region.xlsx
+++ b/public/data/List_Team_Region.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yoss Work\App Retail SBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4446C9E-D804-4C9F-B0A4-4BBBC3DB01CE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D7CD8D-9BAB-4A90-AC53-C18325A28E72}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2130" yWindow="2670" windowWidth="21600" windowHeight="11295" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
+    <workbookView xWindow="1470" yWindow="2175" windowWidth="21600" windowHeight="11295" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="643">
   <si>
     <t>JAMBI</t>
   </si>
@@ -261,9 +261,6 @@
     <t>Nama Tim</t>
   </si>
   <si>
-    <t>NOC RETAIL</t>
-  </si>
-  <si>
     <t>Ferdi</t>
   </si>
   <si>
@@ -582,9 +579,6 @@
     <t>Dery</t>
   </si>
   <si>
-    <t xml:space="preserve">LPGBDL-SIB-MTR06-RENDY </t>
-  </si>
-  <si>
     <t>FEEDER LAMPUNG</t>
   </si>
   <si>
@@ -669,9 +663,6 @@
     <t xml:space="preserve">SEMANGAT	</t>
   </si>
   <si>
-    <t>Semangat</t>
-  </si>
-  <si>
     <t>SUMATERA SELATAN</t>
   </si>
   <si>
@@ -1939,6 +1930,36 @@
   </si>
   <si>
     <t>BANGKA BELITUNG</t>
+  </si>
+  <si>
+    <t>SBS-CURUP-HW.MA5801-OLT-04</t>
+  </si>
+  <si>
+    <t>SBS-CURUP-RC-OLT-03</t>
+  </si>
+  <si>
+    <t>SBS-ARGA.MAKMUR-HW.MA5801-OLT-03</t>
+  </si>
+  <si>
+    <t>SBS-ARGA.MAKMUR-RC-OLT-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBS-RIMBO.TENGAH-HW.MA5801-OLT-01 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBS-KURAU-MA5801-OLT-01 </t>
+  </si>
+  <si>
+    <t>SBS-KOBA-RC-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-TIANG.TARA-RC-OLT-01</t>
+  </si>
+  <si>
+    <t>PLN Icon Plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENDY </t>
   </si>
 </sst>
 </file>
@@ -2173,7 +2194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2237,11 +2258,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
     <dxf>
       <font>
         <strike val="0"/>
@@ -2259,6 +2281,16 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2473,7 +2505,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}" name="Table919" displayName="Table919" ref="B3:H22" totalsRowShown="0" headerRowDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}" name="Table919" displayName="Table919" ref="B3:H22" totalsRowShown="0" headerRowDxfId="12">
   <autoFilter ref="B3:H22" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{1E18F602-B85E-4C85-8C34-8684E3651598}" name="INTERNAL JAMBI"/>
@@ -2489,7 +2521,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}" name="Table27" displayName="Table27" ref="B130:T147" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}" name="Table27" displayName="Table27" ref="B130:T147" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="B130:T147" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{F8A4E442-73AD-4EB9-BB0D-D55E87DA1888}" name="SERPO PALEMBANG KOTA"/>
@@ -2517,7 +2549,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57681EA6-18EF-4E05-B178-44A6E049B133}" name="Table1020" displayName="Table1020" ref="B26:J44" totalsRowShown="0" headerRowDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57681EA6-18EF-4E05-B178-44A6E049B133}" name="Table1020" displayName="Table1020" ref="B26:J44" totalsRowShown="0" headerRowDxfId="11">
   <autoFilter ref="B26:J44" xr:uid="{57681EA6-18EF-4E05-B178-44A6E049B133}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{A8602C42-C67C-43B1-B2C0-728995582D93}" name="SERPO BUNGO"/>
@@ -2535,7 +2567,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C6FB933F-6103-42DE-BAEC-03E0FCFEB76C}" name="Table1121" displayName="Table1121" ref="B50:G78" totalsRowShown="0" headerRowDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C6FB933F-6103-42DE-BAEC-03E0FCFEB76C}" name="Table1121" displayName="Table1121" ref="B50:G78" totalsRowShown="0" headerRowDxfId="10">
   <autoFilter ref="B50:G78" xr:uid="{C6FB933F-6103-42DE-BAEC-03E0FCFEB76C}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{DCC806F7-D168-48B2-B03E-CCE7FD87EEA9}" name="SIB PESAWARAN"/>
@@ -2550,7 +2582,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6E2D26AE-ECD5-48A4-AC1D-1B4180A6F140}" name="Table1222" displayName="Table1222" ref="B82:J104" totalsRowShown="0" headerRowDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6E2D26AE-ECD5-48A4-AC1D-1B4180A6F140}" name="Table1222" displayName="Table1222" ref="B82:J104" totalsRowShown="0" headerRowDxfId="9">
   <autoFilter ref="B82:J104" xr:uid="{6E2D26AE-ECD5-48A4-AC1D-1B4180A6F140}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{060484FA-EE1E-4DC8-9A74-A60AA9B20548}" name="SERPO TEGINENENG_x0009__x0009_"/>
@@ -2568,7 +2600,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}" name="Table1323" displayName="Table1323" ref="B110:O127" totalsRowShown="0" headerRowDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}" name="Table1323" displayName="Table1323" ref="B110:O127" totalsRowShown="0" headerRowDxfId="8">
   <autoFilter ref="B110:O127" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{6FB6563D-399C-4506-8AF0-A312347E4888}" name="REG7 PALEMBANG 1"/>
@@ -2591,7 +2623,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}" name="Table1424" displayName="Table1424" ref="B152:I176" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}" name="Table1424" displayName="Table1424" ref="B152:I176" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
   <autoFilter ref="B152:I176" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{9BFFF82B-4674-404E-AC18-7772CF16890E}" name="GSP BENGKULU 1"/>
@@ -2608,7 +2640,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}" name="Table1525" displayName="Table1525" ref="B180:H210" totalsRowShown="0" headerRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}" name="Table1525" displayName="Table1525" ref="B180:H210" totalsRowShown="0" headerRowDxfId="4">
   <autoFilter ref="B180:H210" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{ACEB90AF-9CBB-4605-8377-2CF0EF299650}" name="SERPO SUKAMERINDU"/>
@@ -2624,7 +2656,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}" name="Table1626" displayName="Table1626" ref="B215:H237" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}" name="Table1626" displayName="Table1626" ref="B215:H237" totalsRowShown="0" headerRowDxfId="3">
   <autoFilter ref="B215:H237" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{D0B3A41D-F35E-4B89-AC56-18717B9B04E5}" name="BANGKA REG 7"/>
@@ -2640,8 +2672,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}" name="Table1727" displayName="Table1727" ref="B240:G261" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="B240:G261" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}" name="Table1727" displayName="Table1727" ref="B240:G262" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="B240:G262" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{97E25E83-847F-4991-A885-21D98063A2DB}" name="SERPO KOBA"/>
     <tableColumn id="2" xr3:uid="{0AB964B5-883A-49C8-8DDA-C8EE93753519}" name="SERPO PANGKAL PINANG"/>
@@ -2971,7 +3003,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D0AF9EF-6686-405D-9473-604A5805FA6C}">
-  <dimension ref="A1:T262"/>
+  <dimension ref="A1:T263"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="34.125" customWidth="1"/>
@@ -3057,7 +3089,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
@@ -3074,7 +3106,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -3100,7 +3132,7 @@
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E6" t="s">
         <v>27</v>
@@ -3120,7 +3152,7 @@
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -3166,7 +3198,7 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D9" t="s">
         <v>48</v>
@@ -3186,7 +3218,7 @@
         <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D10" t="s">
         <v>52</v>
@@ -3203,10 +3235,10 @@
     </row>
     <row r="11" spans="1:14">
       <c r="B11" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C11" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D11" t="s">
         <v>55</v>
@@ -3242,7 +3274,7 @@
     </row>
     <row r="14" spans="1:14">
       <c r="B14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
         <v>62</v>
@@ -3304,25 +3336,25 @@
         <v>75</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="E23" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="F23" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="G23" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="H23" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="15">
@@ -3330,7 +3362,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C25" s="27"/>
       <c r="D25" s="27"/>
@@ -3356,36 +3388,36 @@
         <v>3</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="F26" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="H26" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="I26" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="I26" s="5" t="s">
+      <c r="J26" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:20">
       <c r="B27" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C27" t="s">
         <v>63</v>
@@ -3397,24 +3429,24 @@
         <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="I27" t="s">
         <v>16</v>
       </c>
       <c r="J27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:20">
       <c r="B28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
         <v>49</v>
@@ -3423,7 +3455,7 @@
         <v>47</v>
       </c>
       <c r="E28" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -3440,10 +3472,10 @@
     </row>
     <row r="29" spans="1:20">
       <c r="B29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D29" t="s">
         <v>24</v>
@@ -3455,10 +3487,10 @@
         <v>27</v>
       </c>
       <c r="G29" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="H29" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="I29" t="s">
         <v>30</v>
@@ -3466,16 +3498,16 @@
     </row>
     <row r="30" spans="1:20">
       <c r="B30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
         <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E30" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="F30" t="s">
         <v>34</v>
@@ -3487,12 +3519,12 @@
         <v>36</v>
       </c>
       <c r="I30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:20">
       <c r="B31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
         <v>59</v>
@@ -3517,6 +3549,9 @@
       </c>
     </row>
     <row r="32" spans="1:20">
+      <c r="B32" t="s">
+        <v>637</v>
+      </c>
       <c r="C32" t="s">
         <v>40</v>
       </c>
@@ -3524,13 +3559,13 @@
         <v>26</v>
       </c>
       <c r="E32" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="G32" t="s">
         <v>48</v>
       </c>
       <c r="H32" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="I32" t="s">
         <v>46</v>
@@ -3544,13 +3579,13 @@
         <v>28</v>
       </c>
       <c r="E33" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="G33" t="s">
         <v>52</v>
       </c>
       <c r="H33" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="I33" t="s">
         <v>51</v>
@@ -3561,10 +3596,10 @@
         <v>57</v>
       </c>
       <c r="D34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E34" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="G34" t="s">
         <v>55</v>
@@ -3612,7 +3647,7 @@
         <v>61</v>
       </c>
       <c r="D37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G37" t="s">
         <v>62</v>
@@ -3668,36 +3703,36 @@
         <v>75</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15">
       <c r="A48" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -3705,7 +3740,7 @@
         <v>1</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C49" s="26"/>
       <c r="D49" s="26"/>
@@ -3725,310 +3760,310 @@
         <v>3</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="E50" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="F50" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="G50" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="B51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C51" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D51" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E51" t="s">
+        <v>115</v>
+      </c>
+      <c r="F51" t="s">
         <v>116</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>117</v>
-      </c>
-      <c r="G51" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="B52" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C52" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E52" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F52" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G52" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="B53" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C53" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D53" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E53" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G53" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="B54" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C54" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D54" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="E54" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F54" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="55" spans="1:14">
       <c r="B55" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C55" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D55" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E55" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F55" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G55" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="B56" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C56" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D56" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E56" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F56" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G56" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="57" spans="1:14">
       <c r="C57" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D57" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F57" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G57" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58" spans="1:14">
       <c r="C58" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D58" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="F58" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G58" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" spans="1:14">
       <c r="C59" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D59" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F59" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G59" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:14">
       <c r="C60" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D60" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F60" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G60" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="C61" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D61" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F61" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G61" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="62" spans="1:14">
       <c r="C62" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="D62" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F62" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="C63" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D63" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F63" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="G63" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="64" spans="1:14">
       <c r="G64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="G65" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="G66" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="G67" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="G68" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="G69" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="G70" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="G71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="G72" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="G73" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="G74" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="G75" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="G76" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="G77" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="79" spans="1:7" s="4" customFormat="1">
@@ -4036,22 +4071,22 @@
         <v>75</v>
       </c>
       <c r="B79" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="D79" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="E79" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="F79" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="E79" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="G79" s="4" t="s">
-        <v>183</v>
+        <v>642</v>
       </c>
     </row>
     <row r="81" spans="1:20" ht="15">
@@ -4059,7 +4094,7 @@
         <v>1</v>
       </c>
       <c r="B81" s="27" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C81" s="27"/>
       <c r="D81" s="27"/>
@@ -4085,312 +4120,312 @@
         <v>3</v>
       </c>
       <c r="B82" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D82" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C82" s="6" t="s">
+      <c r="E82" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="D82" s="6" t="s">
+      <c r="F82" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="E82" s="6" t="s">
+      <c r="G82" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="F82" s="6" t="s">
+      <c r="H82" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="G82" s="6" t="s">
+      <c r="I82" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="H82" s="6" t="s">
+      <c r="J82" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="I82" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="J82" s="6" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="83" spans="1:20">
       <c r="B83" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C83" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D83" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E83" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F83" t="s">
+        <v>192</v>
+      </c>
+      <c r="G83" t="s">
+        <v>193</v>
+      </c>
+      <c r="H83" t="s">
         <v>194</v>
       </c>
-      <c r="G83" t="s">
+      <c r="I83" t="s">
         <v>195</v>
       </c>
-      <c r="H83" t="s">
+      <c r="J83" t="s">
         <v>196</v>
-      </c>
-      <c r="I83" t="s">
-        <v>197</v>
-      </c>
-      <c r="J83" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:20">
       <c r="B84" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C84" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D84" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E84" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F84" t="s">
+        <v>197</v>
+      </c>
+      <c r="G84" t="s">
+        <v>198</v>
+      </c>
+      <c r="H84" t="s">
         <v>199</v>
-      </c>
-      <c r="G84" t="s">
-        <v>200</v>
-      </c>
-      <c r="H84" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="85" spans="1:20">
       <c r="B85" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C85" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D85" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E85" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G85" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="86" spans="1:20">
       <c r="B86" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C86" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D86" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E86" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G86" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="87" spans="1:20">
       <c r="B87" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C87" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D87" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E87" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G87" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="88" spans="1:20">
       <c r="B88" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C88" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D88" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E88" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G88" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="89" spans="1:20">
       <c r="B89" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C89" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D89" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E89" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G89" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="90" spans="1:20">
       <c r="B90" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C90" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D90" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E90" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="91" spans="1:20">
       <c r="B91" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C91" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E91" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="92" spans="1:20">
       <c r="B92" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C92" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E92" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="93" spans="1:20">
       <c r="B93" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C93" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E93" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="94" spans="1:20">
       <c r="B94" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C94" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E94" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="95" spans="1:20">
       <c r="B95" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C95" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E95" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="96" spans="1:20">
       <c r="B96" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C96" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E96" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="97" spans="1:15">
       <c r="B97" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E97" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="98" spans="1:15">
       <c r="B98" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="E98" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="99" spans="1:15">
       <c r="B99" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="E99" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="100" spans="1:15">
       <c r="B100" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="E100" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="101" spans="1:15">
       <c r="B101" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E101" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="102" spans="1:15">
       <c r="B102" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="E102" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="103" spans="1:15">
       <c r="B103" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="E103" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="104" spans="1:15">
       <c r="B104" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E104" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="105" spans="1:15" s="6" customFormat="1">
@@ -4398,33 +4433,36 @@
         <v>75</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
+      </c>
+      <c r="J105" s="6" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="108" spans="1:15" ht="15">
       <c r="A108" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="109" spans="1:15">
@@ -4432,7 +4470,7 @@
         <v>1</v>
       </c>
       <c r="B109" s="26" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C109" s="26"/>
       <c r="D109" s="26"/>
@@ -4452,408 +4490,408 @@
         <v>3</v>
       </c>
       <c r="B110" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E110" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="F110" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D110" s="3" t="s">
+      <c r="G110" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="E110" s="3" t="s">
+      <c r="H110" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="F110" s="3" t="s">
+      <c r="I110" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="G110" s="3" t="s">
+      <c r="J110" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="H110" s="3" t="s">
+      <c r="K110" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="I110" s="3" t="s">
+      <c r="L110" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="J110" s="3" t="s">
+      <c r="M110" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="K110" s="3" t="s">
+      <c r="N110" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="L110" s="3" t="s">
+      <c r="O110" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="M110" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="N110" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="O110" s="3" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="111" spans="1:15">
       <c r="B111" t="s">
+        <v>226</v>
+      </c>
+      <c r="C111" t="s">
+        <v>227</v>
+      </c>
+      <c r="D111" t="s">
+        <v>228</v>
+      </c>
+      <c r="E111" t="s">
         <v>229</v>
       </c>
-      <c r="C111" t="s">
+      <c r="F111" t="s">
         <v>230</v>
       </c>
-      <c r="D111" t="s">
+      <c r="G111" t="s">
         <v>231</v>
       </c>
-      <c r="E111" t="s">
+      <c r="H111" t="s">
         <v>232</v>
       </c>
-      <c r="F111" t="s">
+      <c r="I111" t="s">
         <v>233</v>
       </c>
-      <c r="G111" t="s">
+      <c r="J111" t="s">
         <v>234</v>
       </c>
-      <c r="H111" t="s">
+      <c r="K111" t="s">
         <v>235</v>
       </c>
-      <c r="I111" t="s">
+      <c r="L111" t="s">
         <v>236</v>
       </c>
-      <c r="J111" t="s">
+      <c r="M111" t="s">
         <v>237</v>
       </c>
-      <c r="K111" t="s">
+      <c r="N111" t="s">
         <v>238</v>
       </c>
-      <c r="L111" t="s">
+      <c r="O111" t="s">
         <v>239</v>
-      </c>
-      <c r="M111" t="s">
-        <v>240</v>
-      </c>
-      <c r="N111" t="s">
-        <v>241</v>
-      </c>
-      <c r="O111" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="112" spans="1:15">
       <c r="B112" t="s">
+        <v>240</v>
+      </c>
+      <c r="C112" t="s">
+        <v>241</v>
+      </c>
+      <c r="D112" t="s">
+        <v>242</v>
+      </c>
+      <c r="E112" t="s">
         <v>243</v>
       </c>
-      <c r="C112" t="s">
+      <c r="F112" t="s">
         <v>244</v>
       </c>
-      <c r="D112" t="s">
+      <c r="G112" t="s">
         <v>245</v>
       </c>
-      <c r="E112" t="s">
+      <c r="H112" t="s">
         <v>246</v>
       </c>
-      <c r="F112" t="s">
+      <c r="I112" t="s">
         <v>247</v>
       </c>
-      <c r="G112" t="s">
+      <c r="J112" t="s">
+        <v>234</v>
+      </c>
+      <c r="K112" t="s">
         <v>248</v>
       </c>
-      <c r="H112" t="s">
+      <c r="L112" t="s">
         <v>249</v>
       </c>
-      <c r="I112" t="s">
+      <c r="M112" t="s">
         <v>250</v>
       </c>
-      <c r="J112" t="s">
-        <v>237</v>
-      </c>
-      <c r="K112" t="s">
+      <c r="N112" t="s">
         <v>251</v>
       </c>
-      <c r="L112" t="s">
+      <c r="O112" t="s">
         <v>252</v>
-      </c>
-      <c r="M112" t="s">
-        <v>253</v>
-      </c>
-      <c r="N112" t="s">
-        <v>254</v>
-      </c>
-      <c r="O112" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="113" spans="1:15">
       <c r="B113" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" t="s">
+        <v>254</v>
+      </c>
+      <c r="D113" t="s">
+        <v>255</v>
+      </c>
+      <c r="E113" t="s">
         <v>256</v>
       </c>
-      <c r="C113" t="s">
+      <c r="F113" t="s">
         <v>257</v>
       </c>
-      <c r="D113" t="s">
+      <c r="G113" t="s">
         <v>258</v>
       </c>
-      <c r="E113" t="s">
+      <c r="I113" t="s">
         <v>259</v>
       </c>
-      <c r="F113" t="s">
+      <c r="J113" t="s">
         <v>260</v>
       </c>
-      <c r="G113" t="s">
+      <c r="K113" t="s">
         <v>261</v>
       </c>
-      <c r="I113" t="s">
+      <c r="L113" t="s">
         <v>262</v>
       </c>
-      <c r="J113" t="s">
+      <c r="M113" t="s">
         <v>263</v>
       </c>
-      <c r="K113" t="s">
+      <c r="N113" t="s">
         <v>264</v>
       </c>
-      <c r="L113" t="s">
+      <c r="O113" t="s">
         <v>265</v>
-      </c>
-      <c r="M113" t="s">
-        <v>266</v>
-      </c>
-      <c r="N113" t="s">
-        <v>267</v>
-      </c>
-      <c r="O113" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="114" spans="1:15">
       <c r="B114" t="s">
+        <v>266</v>
+      </c>
+      <c r="C114" t="s">
+        <v>267</v>
+      </c>
+      <c r="D114" t="s">
+        <v>95</v>
+      </c>
+      <c r="E114" t="s">
+        <v>268</v>
+      </c>
+      <c r="F114" t="s">
         <v>269</v>
       </c>
-      <c r="C114" t="s">
+      <c r="G114" t="s">
         <v>270</v>
       </c>
-      <c r="D114" t="s">
-        <v>96</v>
-      </c>
-      <c r="E114" t="s">
+      <c r="I114" t="s">
         <v>271</v>
       </c>
-      <c r="F114" t="s">
+      <c r="J114" t="s">
         <v>272</v>
       </c>
-      <c r="G114" t="s">
+      <c r="K114" t="s">
         <v>273</v>
       </c>
-      <c r="I114" t="s">
+      <c r="L114" t="s">
         <v>274</v>
       </c>
-      <c r="J114" t="s">
+      <c r="M114" t="s">
         <v>275</v>
       </c>
-      <c r="K114" t="s">
+      <c r="N114" t="s">
         <v>276</v>
       </c>
-      <c r="L114" t="s">
+      <c r="O114" t="s">
         <v>277</v>
-      </c>
-      <c r="M114" t="s">
-        <v>278</v>
-      </c>
-      <c r="N114" t="s">
-        <v>279</v>
-      </c>
-      <c r="O114" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="115" spans="1:15">
       <c r="B115" t="s">
+        <v>278</v>
+      </c>
+      <c r="C115" t="s">
+        <v>279</v>
+      </c>
+      <c r="D115" t="s">
+        <v>280</v>
+      </c>
+      <c r="E115" t="s">
         <v>281</v>
       </c>
-      <c r="C115" t="s">
+      <c r="F115" t="s">
         <v>282</v>
       </c>
-      <c r="D115" t="s">
+      <c r="G115" t="s">
         <v>283</v>
       </c>
-      <c r="E115" t="s">
+      <c r="I115" t="s">
         <v>284</v>
       </c>
-      <c r="F115" t="s">
+      <c r="J115" t="s">
         <v>285</v>
       </c>
-      <c r="G115" t="s">
+      <c r="K115" t="s">
         <v>286</v>
       </c>
-      <c r="I115" t="s">
+      <c r="L115" t="s">
         <v>287</v>
       </c>
-      <c r="J115" t="s">
+      <c r="M115" t="s">
         <v>288</v>
       </c>
-      <c r="K115" t="s">
+      <c r="O115" t="s">
         <v>289</v>
-      </c>
-      <c r="L115" t="s">
-        <v>290</v>
-      </c>
-      <c r="M115" t="s">
-        <v>291</v>
-      </c>
-      <c r="O115" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="116" spans="1:15">
       <c r="B116" t="s">
+        <v>290</v>
+      </c>
+      <c r="C116" t="s">
+        <v>291</v>
+      </c>
+      <c r="D116" t="s">
+        <v>292</v>
+      </c>
+      <c r="E116" t="s">
         <v>293</v>
       </c>
-      <c r="C116" t="s">
+      <c r="G116" t="s">
         <v>294</v>
       </c>
-      <c r="D116" t="s">
+      <c r="I116" t="s">
         <v>295</v>
       </c>
-      <c r="E116" t="s">
+      <c r="J116" t="s">
         <v>296</v>
       </c>
-      <c r="G116" t="s">
+      <c r="K116" t="s">
         <v>297</v>
       </c>
-      <c r="I116" t="s">
+      <c r="L116" t="s">
         <v>298</v>
       </c>
-      <c r="J116" t="s">
+      <c r="O116" t="s">
         <v>299</v>
-      </c>
-      <c r="K116" t="s">
-        <v>300</v>
-      </c>
-      <c r="L116" t="s">
-        <v>301</v>
-      </c>
-      <c r="O116" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="117" spans="1:15">
       <c r="B117" t="s">
+        <v>300</v>
+      </c>
+      <c r="C117" t="s">
+        <v>301</v>
+      </c>
+      <c r="D117" t="s">
+        <v>302</v>
+      </c>
+      <c r="E117" t="s">
         <v>303</v>
       </c>
-      <c r="C117" t="s">
+      <c r="I117" t="s">
         <v>304</v>
       </c>
-      <c r="D117" t="s">
+      <c r="J117" t="s">
         <v>305</v>
       </c>
-      <c r="E117" t="s">
+      <c r="K117" t="s">
         <v>306</v>
       </c>
-      <c r="I117" t="s">
+      <c r="L117" t="s">
         <v>307</v>
       </c>
-      <c r="J117" t="s">
+      <c r="O117" t="s">
         <v>308</v>
-      </c>
-      <c r="K117" t="s">
-        <v>309</v>
-      </c>
-      <c r="L117" t="s">
-        <v>310</v>
-      </c>
-      <c r="O117" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="118" spans="1:15">
       <c r="B118" t="s">
+        <v>309</v>
+      </c>
+      <c r="C118" t="s">
+        <v>310</v>
+      </c>
+      <c r="D118" t="s">
+        <v>311</v>
+      </c>
+      <c r="E118" t="s">
         <v>312</v>
       </c>
-      <c r="C118" t="s">
+      <c r="I118" t="s">
         <v>313</v>
       </c>
-      <c r="D118" t="s">
+      <c r="J118" t="s">
+        <v>369</v>
+      </c>
+      <c r="K118" t="s">
         <v>314</v>
-      </c>
-      <c r="E118" t="s">
-        <v>315</v>
-      </c>
-      <c r="I118" t="s">
-        <v>316</v>
-      </c>
-      <c r="J118" t="s">
-        <v>372</v>
-      </c>
-      <c r="K118" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="119" spans="1:15">
       <c r="B119" t="s">
+        <v>315</v>
+      </c>
+      <c r="C119" t="s">
+        <v>316</v>
+      </c>
+      <c r="D119" t="s">
+        <v>317</v>
+      </c>
+      <c r="E119" t="s">
         <v>318</v>
       </c>
-      <c r="C119" t="s">
+      <c r="K119" t="s">
         <v>319</v>
-      </c>
-      <c r="D119" t="s">
-        <v>320</v>
-      </c>
-      <c r="E119" t="s">
-        <v>321</v>
-      </c>
-      <c r="K119" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="120" spans="1:15">
       <c r="B120" t="s">
+        <v>320</v>
+      </c>
+      <c r="C120" t="s">
+        <v>321</v>
+      </c>
+      <c r="D120" t="s">
+        <v>322</v>
+      </c>
+      <c r="K120" t="s">
         <v>323</v>
-      </c>
-      <c r="C120" t="s">
-        <v>324</v>
-      </c>
-      <c r="D120" t="s">
-        <v>325</v>
-      </c>
-      <c r="K120" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="121" spans="1:15">
       <c r="B121" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C121" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="K121" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="122" spans="1:15">
       <c r="B122" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="K122" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="123" spans="1:15">
       <c r="K123" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="124" spans="1:15">
       <c r="K124" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="125" spans="1:15">
       <c r="K125" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="126" spans="1:15">
       <c r="K126" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="127" spans="1:15" s="4" customFormat="1">
@@ -4861,46 +4899,46 @@
         <v>75</v>
       </c>
       <c r="B127" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="E127" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="C127" s="4" t="s">
+      <c r="F127" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="D127" s="4" t="s">
+      <c r="G127" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="I127" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="E127" s="4" t="s">
+      <c r="J127" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="F127" s="4" t="s">
+      <c r="K127" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="G127" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="I127" s="4" t="s">
+      <c r="L127" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="J127" s="4" t="s">
+      <c r="M127" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="K127" s="4" t="s">
+      <c r="N127" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="L127" s="4" t="s">
+      <c r="O127" s="4" t="s">
         <v>344</v>
-      </c>
-      <c r="M127" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="N127" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="O127" s="4" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="129" spans="1:20" ht="15">
@@ -4908,7 +4946,7 @@
         <v>1</v>
       </c>
       <c r="B129" s="27" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C129" s="27"/>
       <c r="D129" s="27"/>
@@ -4934,444 +4972,444 @@
         <v>3</v>
       </c>
       <c r="B130" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="E130" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="C130" s="5" t="s">
+      <c r="F130" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="D130" s="5" t="s">
+      <c r="G130" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="E130" s="5" t="s">
+      <c r="H130" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="F130" s="5" t="s">
+      <c r="I130" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="G130" s="5" t="s">
+      <c r="J130" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="H130" s="5" t="s">
+      <c r="K130" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="I130" s="5" t="s">
+      <c r="L130" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="J130" s="5" t="s">
+      <c r="M130" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="K130" s="5" t="s">
+      <c r="N130" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="L130" s="5" t="s">
+      <c r="O130" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="M130" s="5" t="s">
+      <c r="P130" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="N130" s="5" t="s">
+      <c r="Q130" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="O130" s="5" t="s">
+      <c r="R130" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="P130" s="5" t="s">
+      <c r="S130" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="Q130" s="5" t="s">
+      <c r="T130" s="5" t="s">
         <v>364</v>
-      </c>
-      <c r="R130" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="S130" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="T130" s="5" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="131" spans="1:20">
       <c r="B131" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C131" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D131" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E131" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F131" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G131" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="H131" t="s">
+        <v>365</v>
+      </c>
+      <c r="I131" t="s">
+        <v>366</v>
+      </c>
+      <c r="J131" t="s">
+        <v>270</v>
+      </c>
+      <c r="K131" t="s">
+        <v>367</v>
+      </c>
+      <c r="L131" t="s">
         <v>368</v>
       </c>
-      <c r="I131" t="s">
-        <v>369</v>
-      </c>
-      <c r="J131" t="s">
-        <v>273</v>
-      </c>
-      <c r="K131" t="s">
-        <v>370</v>
-      </c>
-      <c r="L131" t="s">
-        <v>371</v>
-      </c>
       <c r="M131" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="N131" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O131" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P131" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Q131" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="R131" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="S131" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="T131" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="132" spans="1:20">
       <c r="B132" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C132" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D132" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E132" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F132" t="s">
+        <v>369</v>
+      </c>
+      <c r="G132" t="s">
+        <v>247</v>
+      </c>
+      <c r="I132" t="s">
+        <v>370</v>
+      </c>
+      <c r="J132" t="s">
+        <v>283</v>
+      </c>
+      <c r="K132" t="s">
+        <v>371</v>
+      </c>
+      <c r="L132" t="s">
         <v>372</v>
       </c>
-      <c r="G132" t="s">
-        <v>250</v>
-      </c>
-      <c r="I132" t="s">
-        <v>373</v>
-      </c>
-      <c r="J132" t="s">
-        <v>286</v>
-      </c>
-      <c r="K132" t="s">
-        <v>374</v>
-      </c>
-      <c r="L132" t="s">
-        <v>375</v>
-      </c>
       <c r="N132" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O132" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P132" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="Q132" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="R132" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="S132" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="T132" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="133" spans="1:20">
       <c r="B133" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C133" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E133" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F133" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G133" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="I133" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="J133" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="K133" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="N133" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="O133" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="Q133" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="R133" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="S133" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="T133" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="134" spans="1:20">
       <c r="B134" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C134" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D134" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E134" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F134" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G134" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="O134" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q134" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="R134" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="S134" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="T134" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="135" spans="1:20">
       <c r="B135" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C135" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D135" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E135" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F135" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G135" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="O135" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="Q135" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="R135" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="S135" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="T135" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="136" spans="1:20">
       <c r="B136" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C136" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D136" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E136" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F136" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G136" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Q136" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="R136" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="S136" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="T136" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="137" spans="1:20">
       <c r="B137" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D137" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E137" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F137" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G137" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="Q137" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="R137" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="S137" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="T137" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="138" spans="1:20">
       <c r="B138" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D138" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G138" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="Q138" t="s">
+        <v>312</v>
+      </c>
+      <c r="R138" t="s">
         <v>315</v>
       </c>
-      <c r="R138" t="s">
-        <v>318</v>
-      </c>
       <c r="S138" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="T138" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="139" spans="1:20">
       <c r="B139" t="s">
+        <v>319</v>
+      </c>
+      <c r="D139" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>318</v>
+      </c>
+      <c r="R139" t="s">
+        <v>325</v>
+      </c>
+      <c r="S139" t="s">
+        <v>291</v>
+      </c>
+      <c r="T139" t="s">
         <v>322</v>
-      </c>
-      <c r="D139" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q139" t="s">
-        <v>321</v>
-      </c>
-      <c r="R139" t="s">
-        <v>328</v>
-      </c>
-      <c r="S139" t="s">
-        <v>294</v>
-      </c>
-      <c r="T139" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="140" spans="1:20">
       <c r="B140" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D140" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="R140" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="S140" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="141" spans="1:20">
       <c r="B141" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="R141" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="S141" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="142" spans="1:20">
       <c r="B142" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="143" spans="1:20">
       <c r="B143" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="144" spans="1:20">
       <c r="B144" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="145" spans="1:20">
       <c r="B145" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="146" spans="1:20">
       <c r="B146" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="147" spans="1:20" s="6" customFormat="1">
@@ -5379,66 +5417,66 @@
         <v>75</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="G147" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H147" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="J147" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="K147" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="L147" s="6" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="M147" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="N147" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="O147" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="P147" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="Q147" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="R147" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="S147" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="T147" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="150" spans="1:20" ht="15">
       <c r="A150" s="7" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="151" spans="1:20">
@@ -5446,7 +5484,7 @@
         <v>1</v>
       </c>
       <c r="B151" s="26" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C151" s="26"/>
       <c r="D151" s="26"/>
@@ -5466,371 +5504,371 @@
         <v>3</v>
       </c>
       <c r="B152" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="E152" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="C152" s="8" t="s">
+      <c r="F152" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="D152" s="8" t="s">
+      <c r="G152" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="E152" s="9" t="s">
+      <c r="H152" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="F152" s="10" t="s">
+      <c r="I152" s="11" t="s">
         <v>388</v>
-      </c>
-      <c r="G152" s="11" t="s">
-        <v>389</v>
-      </c>
-      <c r="H152" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="I152" s="11" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="153" spans="1:20" ht="28.5">
       <c r="B153" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="C153" t="s">
+        <v>390</v>
+      </c>
+      <c r="D153" t="s">
+        <v>391</v>
+      </c>
+      <c r="E153" t="s">
         <v>392</v>
       </c>
-      <c r="C153" t="s">
+      <c r="F153" s="14" t="s">
         <v>393</v>
       </c>
-      <c r="D153" t="s">
+      <c r="G153" t="s">
         <v>394</v>
       </c>
-      <c r="E153" t="s">
+      <c r="H153" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="F153" s="14" t="s">
+      <c r="I153" s="16" t="s">
         <v>396</v>
-      </c>
-      <c r="G153" t="s">
-        <v>397</v>
-      </c>
-      <c r="H153" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="I153" s="16" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="154" spans="1:20">
       <c r="B154" t="s">
+        <v>397</v>
+      </c>
+      <c r="C154" t="s">
+        <v>398</v>
+      </c>
+      <c r="D154" t="s">
+        <v>399</v>
+      </c>
+      <c r="E154" t="s">
+        <v>392</v>
+      </c>
+      <c r="F154" t="s">
+        <v>407</v>
+      </c>
+      <c r="G154" t="s">
         <v>400</v>
       </c>
-      <c r="C154" t="s">
+      <c r="H154" s="15" t="s">
         <v>401</v>
       </c>
-      <c r="D154" t="s">
+      <c r="I154" s="16" t="s">
         <v>402</v>
-      </c>
-      <c r="E154" t="s">
-        <v>395</v>
-      </c>
-      <c r="F154" t="s">
-        <v>410</v>
-      </c>
-      <c r="G154" t="s">
-        <v>403</v>
-      </c>
-      <c r="H154" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="I154" s="16" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="155" spans="1:20" ht="28.5">
       <c r="B155" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="C155" s="17" t="s">
+        <v>404</v>
+      </c>
+      <c r="D155" t="s">
+        <v>405</v>
+      </c>
+      <c r="E155" t="s">
         <v>406</v>
       </c>
-      <c r="C155" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="D155" t="s">
+      <c r="F155" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="G155" t="s">
         <v>408</v>
       </c>
-      <c r="E155" t="s">
+      <c r="H155" t="s">
         <v>409</v>
       </c>
-      <c r="F155" s="14" t="s">
-        <v>418</v>
-      </c>
-      <c r="G155" t="s">
-        <v>411</v>
-      </c>
-      <c r="H155" t="s">
-        <v>412</v>
-      </c>
       <c r="I155" s="18" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="156" spans="1:20">
       <c r="B156" t="s">
+        <v>411</v>
+      </c>
+      <c r="C156" t="s">
+        <v>412</v>
+      </c>
+      <c r="D156" t="s">
+        <v>413</v>
+      </c>
+      <c r="E156" t="s">
         <v>414</v>
       </c>
-      <c r="C156" t="s">
-        <v>415</v>
-      </c>
-      <c r="D156" t="s">
+      <c r="F156" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="G156" t="s">
         <v>416</v>
       </c>
-      <c r="E156" t="s">
+      <c r="H156" t="s">
         <v>417</v>
       </c>
-      <c r="F156" s="14" t="s">
-        <v>468</v>
-      </c>
-      <c r="G156" t="s">
-        <v>419</v>
-      </c>
-      <c r="H156" t="s">
-        <v>420</v>
-      </c>
       <c r="I156" s="16" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="157" spans="1:20">
       <c r="B157" t="s">
+        <v>419</v>
+      </c>
+      <c r="C157" t="s">
+        <v>420</v>
+      </c>
+      <c r="E157" t="s">
+        <v>421</v>
+      </c>
+      <c r="F157" t="s">
+        <v>467</v>
+      </c>
+      <c r="G157" t="s">
         <v>422</v>
       </c>
-      <c r="C157" t="s">
+      <c r="H157" t="s">
         <v>423</v>
       </c>
-      <c r="E157" t="s">
+      <c r="I157" s="16" t="s">
         <v>424</v>
-      </c>
-      <c r="F157" t="s">
-        <v>470</v>
-      </c>
-      <c r="G157" t="s">
-        <v>425</v>
-      </c>
-      <c r="H157" t="s">
-        <v>426</v>
-      </c>
-      <c r="I157" s="16" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="158" spans="1:20" ht="15">
       <c r="B158" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C158" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E158" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F158" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="G158" s="19"/>
       <c r="H158" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="I158" s="16" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="159" spans="1:20">
       <c r="B159" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C159" t="s">
+        <v>432</v>
+      </c>
+      <c r="E159" t="s">
+        <v>433</v>
+      </c>
+      <c r="F159" t="s">
+        <v>407</v>
+      </c>
+      <c r="H159" t="s">
         <v>435</v>
       </c>
-      <c r="E159" t="s">
+      <c r="I159" s="20" t="s">
         <v>436</v>
-      </c>
-      <c r="F159" t="s">
-        <v>410</v>
-      </c>
-      <c r="H159" t="s">
-        <v>438</v>
-      </c>
-      <c r="I159" s="20" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="160" spans="1:20">
       <c r="B160" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C160" t="s">
+        <v>437</v>
+      </c>
+      <c r="E160" t="s">
+        <v>438</v>
+      </c>
+      <c r="F160" t="s">
+        <v>472</v>
+      </c>
+      <c r="I160" s="20" t="s">
         <v>440</v>
-      </c>
-      <c r="E160" t="s">
-        <v>441</v>
-      </c>
-      <c r="F160" t="s">
-        <v>475</v>
-      </c>
-      <c r="I160" s="20" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="161" spans="2:9">
       <c r="B161" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C161" t="s">
+        <v>442</v>
+      </c>
+      <c r="E161" t="s">
+        <v>443</v>
+      </c>
+      <c r="F161" t="s">
+        <v>415</v>
+      </c>
+      <c r="I161" s="16" t="s">
         <v>445</v>
-      </c>
-      <c r="E161" t="s">
-        <v>446</v>
-      </c>
-      <c r="F161" t="s">
-        <v>418</v>
-      </c>
-      <c r="I161" s="16" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="162" spans="2:9" ht="28.5">
       <c r="B162" s="14" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C162" t="s">
+        <v>447</v>
+      </c>
+      <c r="E162" t="s">
+        <v>448</v>
+      </c>
+      <c r="F162" t="s">
+        <v>428</v>
+      </c>
+      <c r="I162" s="16" t="s">
         <v>450</v>
-      </c>
-      <c r="E162" t="s">
-        <v>451</v>
-      </c>
-      <c r="F162" t="s">
-        <v>431</v>
-      </c>
-      <c r="I162" s="16" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="163" spans="2:9">
       <c r="B163" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C163" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F163" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="I163" s="16" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="164" spans="2:9">
       <c r="B164" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C164" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F164" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="I164" s="16" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="165" spans="2:9">
       <c r="B165" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C165" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F165" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="166" spans="2:9">
       <c r="B166" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C166" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F166" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="167" spans="2:9">
       <c r="B167" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C167" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F167" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="168" spans="2:9">
       <c r="B168" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C168" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F168" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="169" spans="2:9">
       <c r="B169" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C169" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F169" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="170" spans="2:9" ht="15">
       <c r="B170" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C170" s="21" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="F170" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="171" spans="2:9">
       <c r="B171" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="172" spans="2:9">
       <c r="B172" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="173" spans="2:9">
       <c r="B173" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="174" spans="2:9">
       <c r="B174" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="175" spans="2:9">
       <c r="B175" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="176" spans="2:9">
       <c r="B176" s="22" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="177" spans="1:20" ht="15">
@@ -5838,28 +5876,28 @@
         <v>75</v>
       </c>
       <c r="B177" s="23" t="s">
+        <v>478</v>
+      </c>
+      <c r="C177" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="D177" s="23" t="s">
+        <v>480</v>
+      </c>
+      <c r="E177" s="24" t="s">
         <v>481</v>
       </c>
-      <c r="C177" s="23" t="s">
+      <c r="F177" s="25" t="s">
         <v>482</v>
       </c>
-      <c r="D177" s="23" t="s">
+      <c r="G177" s="23" t="s">
         <v>483</v>
       </c>
-      <c r="E177" s="24" t="s">
+      <c r="H177" s="23" t="s">
         <v>484</v>
       </c>
-      <c r="F177" s="25" t="s">
+      <c r="I177" s="23" t="s">
         <v>485</v>
-      </c>
-      <c r="G177" s="23" t="s">
-        <v>486</v>
-      </c>
-      <c r="H177" s="23" t="s">
-        <v>487</v>
-      </c>
-      <c r="I177" s="23" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="179" spans="1:20" ht="15">
@@ -5867,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="B179" s="27" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C179" s="27"/>
       <c r="D179" s="27"/>
@@ -5893,287 +5931,383 @@
         <v>3</v>
       </c>
       <c r="B180" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="D180" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="E180" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="C180" s="5" t="s">
+      <c r="F180" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="G180" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="D180" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="E180" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="F180" s="5" t="s">
-        <v>626</v>
-      </c>
-      <c r="G180" s="5" t="s">
-        <v>494</v>
-      </c>
       <c r="H180" s="5" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="181" spans="1:20">
       <c r="B181" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C181" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D181" t="s">
+        <v>391</v>
+      </c>
+      <c r="E181" t="s">
         <v>394</v>
       </c>
-      <c r="E181" t="s">
-        <v>397</v>
-      </c>
       <c r="F181" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="G181" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H181" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="182" spans="1:20">
       <c r="B182" t="s">
+        <v>398</v>
+      </c>
+      <c r="C182" t="s">
+        <v>403</v>
+      </c>
+      <c r="D182" t="s">
+        <v>405</v>
+      </c>
+      <c r="E182" t="s">
+        <v>408</v>
+      </c>
+      <c r="F182" t="s">
+        <v>465</v>
+      </c>
+      <c r="G182" t="s">
         <v>401</v>
       </c>
-      <c r="C182" t="s">
-        <v>406</v>
-      </c>
-      <c r="D182" t="s">
-        <v>408</v>
-      </c>
-      <c r="E182" t="s">
-        <v>411</v>
-      </c>
-      <c r="F182" t="s">
-        <v>468</v>
-      </c>
-      <c r="G182" t="s">
-        <v>404</v>
-      </c>
       <c r="H182" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="183" spans="1:20">
       <c r="B183" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C183" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D183" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E183" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="F183" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="G183" t="s">
-        <v>398</v>
+        <v>395</v>
+      </c>
+      <c r="H183" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="184" spans="1:20">
       <c r="B184" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C184" t="s">
-        <v>422</v>
+        <v>419</v>
+      </c>
+      <c r="D184" t="s">
+        <v>635</v>
       </c>
       <c r="E184" t="s">
-        <v>496</v>
+        <v>493</v>
+      </c>
+      <c r="F184" t="s">
+        <v>633</v>
+      </c>
+      <c r="G184" t="s">
+        <v>409</v>
+      </c>
+      <c r="H184" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="185" spans="1:20">
       <c r="B185" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C185" t="s">
-        <v>428</v>
+        <v>425</v>
+      </c>
+      <c r="D185" t="s">
+        <v>636</v>
+      </c>
+      <c r="E185" t="s">
+        <v>422</v>
+      </c>
+      <c r="F185" t="s">
+        <v>434</v>
+      </c>
+      <c r="G185" t="s">
+        <v>417</v>
+      </c>
+      <c r="H185" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="186" spans="1:20">
       <c r="B186" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C186" t="s">
-        <v>434</v>
+        <v>431</v>
+      </c>
+      <c r="D186" t="s">
+        <v>413</v>
+      </c>
+      <c r="E186" t="s">
+        <v>420</v>
+      </c>
+      <c r="F186" t="s">
+        <v>439</v>
+      </c>
+      <c r="G186" t="s">
+        <v>423</v>
+      </c>
+      <c r="H186" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="187" spans="1:20">
       <c r="B187" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C187" t="s">
+        <v>441</v>
+      </c>
+      <c r="F187" t="s">
         <v>444</v>
+      </c>
+      <c r="G187" t="s">
+        <v>429</v>
+      </c>
+      <c r="H187" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="188" spans="1:20">
       <c r="B188" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C188" t="s">
-        <v>466</v>
+        <v>463</v>
+      </c>
+      <c r="F188" t="s">
+        <v>449</v>
+      </c>
+      <c r="H188" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="189" spans="1:20">
       <c r="B189" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C189" t="s">
-        <v>414</v>
+        <v>411</v>
+      </c>
+      <c r="F189" t="s">
+        <v>452</v>
+      </c>
+      <c r="H189" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="190" spans="1:20">
       <c r="B190" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C190" t="s">
-        <v>471</v>
+        <v>468</v>
+      </c>
+      <c r="F190" t="s">
+        <v>455</v>
+      </c>
+      <c r="H190" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="191" spans="1:20">
       <c r="B191" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C191" t="s">
-        <v>473</v>
+        <v>470</v>
+      </c>
+      <c r="F191" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="192" spans="1:20">
       <c r="B192" t="s">
+        <v>454</v>
+      </c>
+      <c r="C192" t="s">
+        <v>419</v>
+      </c>
+      <c r="F192" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="193" spans="2:6">
+      <c r="B193" t="s">
+        <v>469</v>
+      </c>
+      <c r="C193" t="s">
+        <v>473</v>
+      </c>
+      <c r="F193" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="194" spans="2:6">
+      <c r="B194" t="s">
+        <v>458</v>
+      </c>
+      <c r="C194" t="s">
+        <v>474</v>
+      </c>
+      <c r="F194" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="195" spans="2:6">
+      <c r="B195" t="s">
+        <v>461</v>
+      </c>
+      <c r="C195" t="s">
+        <v>475</v>
+      </c>
+      <c r="F195" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="196" spans="2:6">
+      <c r="B196" t="s">
+        <v>464</v>
+      </c>
+      <c r="C196" t="s">
+        <v>476</v>
+      </c>
+      <c r="F196" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="197" spans="2:6">
+      <c r="B197" t="s">
+        <v>466</v>
+      </c>
+      <c r="C197" t="s">
+        <v>477</v>
+      </c>
+      <c r="F197" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="198" spans="2:6">
+      <c r="B198" t="s">
+        <v>471</v>
+      </c>
+      <c r="C198" t="s">
+        <v>413</v>
+      </c>
+      <c r="F198" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="199" spans="2:6">
+      <c r="B199" t="s">
+        <v>446</v>
+      </c>
+      <c r="C199" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="200" spans="2:6">
+      <c r="B200" t="s">
+        <v>451</v>
+      </c>
+      <c r="C200" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="201" spans="2:6">
+      <c r="B201" t="s">
+        <v>397</v>
+      </c>
+      <c r="C201" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="202" spans="2:6">
+      <c r="B202" t="s">
         <v>457</v>
       </c>
-      <c r="C192" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="193" spans="2:3">
-      <c r="B193" t="s">
-        <v>472</v>
-      </c>
-      <c r="C193" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="194" spans="2:3">
-      <c r="B194" t="s">
-        <v>461</v>
-      </c>
-      <c r="C194" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="195" spans="2:3">
-      <c r="B195" t="s">
-        <v>464</v>
-      </c>
-      <c r="C195" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="196" spans="2:3">
-      <c r="B196" t="s">
-        <v>467</v>
-      </c>
-      <c r="C196" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="197" spans="2:3">
-      <c r="B197" t="s">
-        <v>469</v>
-      </c>
-      <c r="C197" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="198" spans="2:3">
-      <c r="B198" t="s">
-        <v>474</v>
-      </c>
-      <c r="C198" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="199" spans="2:3">
-      <c r="B199" t="s">
-        <v>449</v>
-      </c>
-      <c r="C199" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="200" spans="2:3">
-      <c r="B200" t="s">
-        <v>454</v>
-      </c>
-      <c r="C200" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="201" spans="2:3">
-      <c r="B201" t="s">
-        <v>400</v>
-      </c>
-      <c r="C201" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="202" spans="2:3">
-      <c r="B202" t="s">
+      <c r="C202" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="203" spans="2:6">
+      <c r="B203" t="s">
         <v>460</v>
       </c>
-      <c r="C202" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="203" spans="2:3">
-      <c r="B203" t="s">
-        <v>463</v>
-      </c>
       <c r="C203" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="204" spans="2:3">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="204" spans="2:6">
       <c r="B204" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C204" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="205" spans="2:3">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="205" spans="2:6">
       <c r="C205" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="206" spans="2:3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="206" spans="2:6">
       <c r="C206" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="207" spans="2:3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="207" spans="2:6">
       <c r="C207" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="208" spans="2:6">
+      <c r="C208" t="s">
         <v>453</v>
-      </c>
-    </row>
-    <row r="208" spans="2:3">
-      <c r="C208" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="209" spans="1:14">
       <c r="C209" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="210" spans="1:14" s="6" customFormat="1">
@@ -6181,30 +6315,30 @@
         <v>75</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="213" spans="1:14" ht="15">
       <c r="A213" s="7" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="214" spans="1:14">
@@ -6212,7 +6346,7 @@
         <v>1</v>
       </c>
       <c r="B214" s="26" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C214" s="26"/>
       <c r="D214" s="26"/>
@@ -6232,262 +6366,271 @@
         <v>3</v>
       </c>
       <c r="B215" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="E215" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="C215" s="3" t="s">
+      <c r="F215" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="D215" s="3" t="s">
+      <c r="G215" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="E215" s="3" t="s">
+      <c r="H215" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="F215" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="G215" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="H215" s="3" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="216" spans="1:14">
+    </row>
+    <row r="216" spans="1:14" ht="15">
       <c r="B216" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C216" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D216" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="E216" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F216" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="G216" t="s">
-        <v>510</v>
-      </c>
-      <c r="H216" t="s">
-        <v>516</v>
+        <v>507</v>
+      </c>
+      <c r="H216" s="21" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="217" spans="1:14">
       <c r="B217" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C217" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D217" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E217" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="G217" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="H217" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="218" spans="1:14">
       <c r="B218" t="s">
+        <v>625</v>
+      </c>
+      <c r="C218" t="s">
+        <v>519</v>
+      </c>
+      <c r="D218" t="s">
+        <v>627</v>
+      </c>
+      <c r="E218" t="s">
         <v>628</v>
       </c>
-      <c r="C218" t="s">
+      <c r="H218" t="s">
         <v>522</v>
-      </c>
-      <c r="D218" t="s">
-        <v>630</v>
-      </c>
-      <c r="E218" t="s">
-        <v>631</v>
-      </c>
-      <c r="H218" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="219" spans="1:14">
       <c r="B219" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C219" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D219" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E219" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="H219" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="220" spans="1:14">
       <c r="B220" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C220" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D220" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E220" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="H220" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="221" spans="1:14">
       <c r="B221" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C221" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D221" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E221" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="H221" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="222" spans="1:14">
       <c r="B222" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C222" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D222" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E222" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="H222" t="s">
-        <v>542</v>
+        <v>508</v>
       </c>
     </row>
     <row r="223" spans="1:14">
       <c r="B223" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C223" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D223" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E223" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="H223" t="s">
-        <v>511</v>
+        <v>591</v>
       </c>
     </row>
     <row r="224" spans="1:14">
       <c r="B224" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C224" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D224" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="E224" t="s">
-        <v>552</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="F224" s="29"/>
       <c r="H224" t="s">
-        <v>594</v>
+        <v>630</v>
       </c>
     </row>
     <row r="225" spans="1:20">
       <c r="B225" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C225" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D225" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E225" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="H225" t="s">
-        <v>633</v>
+        <v>582</v>
       </c>
     </row>
     <row r="226" spans="1:20">
       <c r="B226" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C226" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E226" t="s">
-        <v>545</v>
+        <v>542</v>
+      </c>
+      <c r="H226" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="227" spans="1:20">
       <c r="B227" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C227" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E227" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="228" spans="1:20">
       <c r="B228" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C228" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="229" spans="1:20">
       <c r="B229" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C229" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="230" spans="1:20">
       <c r="B230" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="231" spans="1:20">
       <c r="B231" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="232" spans="1:20">
       <c r="B232" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="233" spans="1:20">
       <c r="B233" t="s">
-        <v>517</v>
+        <v>514</v>
+      </c>
+    </row>
+    <row r="234" spans="1:20">
+      <c r="B234" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="237" spans="1:20" s="4" customFormat="1">
@@ -6495,25 +6638,25 @@
         <v>75</v>
       </c>
       <c r="B237" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="D237" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="E237" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="C237" s="4" t="s">
+      <c r="F237" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="D237" s="4" t="s">
+      <c r="G237" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="E237" s="4" t="s">
+      <c r="H237" s="4" t="s">
         <v>565</v>
-      </c>
-      <c r="F237" s="4" t="s">
-        <v>566</v>
-      </c>
-      <c r="G237" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="H237" s="4" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="239" spans="1:20" ht="15">
@@ -6521,7 +6664,7 @@
         <v>1</v>
       </c>
       <c r="B239" s="27" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C239" s="27"/>
       <c r="D239" s="27"/>
@@ -6547,330 +6690,344 @@
         <v>3</v>
       </c>
       <c r="B240" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="D240" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="E240" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="F240" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="C240" s="5" t="s">
-        <v>570</v>
-      </c>
-      <c r="D240" s="5" t="s">
+      <c r="G240" s="5" t="s">
         <v>572</v>
-      </c>
-      <c r="E240" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="F240" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="G240" s="5" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="241" spans="2:7">
       <c r="B241" t="s">
-        <v>577</v>
+        <v>557</v>
       </c>
       <c r="C241" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D241" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E241" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="F241" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="G241" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="242" spans="2:7">
       <c r="B242" t="s">
-        <v>520</v>
+        <v>639</v>
       </c>
       <c r="C242" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D242" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E242" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="F242" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="G242" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="243" spans="2:7">
       <c r="B243" t="s">
-        <v>542</v>
+        <v>508</v>
       </c>
       <c r="C243" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="D243" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E243" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="F243" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="G243" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="244" spans="2:7">
       <c r="B244" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="C244" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D244" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="F244" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="G244" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="245" spans="2:7">
       <c r="B245" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="C245" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D245" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="F245" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="G245" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="246" spans="2:7">
       <c r="B246" t="s">
-        <v>560</v>
+        <v>630</v>
       </c>
       <c r="C246" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D246" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="F246" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="G246" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="247" spans="2:7">
       <c r="B247" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C247" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D247" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F247" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G247" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="248" spans="2:7">
       <c r="B248" t="s">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="C248" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D248" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F248" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="G248" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="249" spans="2:7">
       <c r="B249" t="s">
-        <v>514</v>
+        <v>539</v>
       </c>
       <c r="C249" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D249" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="F249" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="G249" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="250" spans="2:7">
       <c r="B250" t="s">
+        <v>586</v>
+      </c>
+      <c r="C250" t="s">
+        <v>548</v>
+      </c>
+      <c r="D250" t="s">
+        <v>587</v>
+      </c>
+      <c r="F250" t="s">
         <v>528</v>
       </c>
-      <c r="C250" t="s">
-        <v>551</v>
-      </c>
-      <c r="D250" t="s">
-        <v>590</v>
-      </c>
-      <c r="F250" t="s">
-        <v>531</v>
-      </c>
       <c r="G250" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="251" spans="2:7">
       <c r="B251" t="s">
-        <v>594</v>
+        <v>517</v>
       </c>
       <c r="C251" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D251" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="F251" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="G251" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="252" spans="2:7">
       <c r="B252" t="s">
-        <v>525</v>
+        <v>511</v>
       </c>
       <c r="C252" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D252" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="F252" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="G252" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="253" spans="2:7">
       <c r="B253" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C253" t="s">
+        <v>526</v>
+      </c>
+      <c r="D253" t="s">
         <v>529</v>
       </c>
-      <c r="D253" t="s">
-        <v>532</v>
-      </c>
       <c r="G253" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="254" spans="2:7">
+      <c r="B254" t="s">
+        <v>522</v>
+      </c>
+      <c r="C254" t="s">
+        <v>554</v>
+      </c>
+      <c r="D254" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="255" spans="2:7">
+      <c r="B255" t="s">
+        <v>582</v>
+      </c>
+      <c r="C255" t="s">
+        <v>551</v>
+      </c>
+      <c r="D255" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="256" spans="2:7">
+      <c r="B256" t="s">
+        <v>530</v>
+      </c>
+      <c r="C256" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="254" spans="2:7">
-      <c r="C254" t="s">
-        <v>557</v>
-      </c>
-      <c r="D254" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="255" spans="2:7">
-      <c r="C255" t="s">
-        <v>554</v>
-      </c>
-      <c r="D255" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="256" spans="2:7">
-      <c r="C256" t="s">
-        <v>543</v>
-      </c>
       <c r="D256" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="257" spans="1:8">
       <c r="C257" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D257" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="258" spans="1:8">
       <c r="C258" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D258" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="259" spans="1:8">
       <c r="D259" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="260" spans="1:8">
       <c r="D260" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="261" spans="1:8">
       <c r="D261" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="262" spans="1:8" s="6" customFormat="1">
-      <c r="A262" s="6" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8">
+      <c r="D262" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" s="6" customFormat="1">
+      <c r="A263" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B262" s="6" t="s">
-        <v>597</v>
-      </c>
-      <c r="C262" s="6" t="s">
-        <v>597</v>
-      </c>
-      <c r="D262" s="6" t="s">
-        <v>597</v>
-      </c>
-      <c r="E262" s="6" t="s">
-        <v>597</v>
-      </c>
-      <c r="F262" s="6" t="s">
-        <v>597</v>
-      </c>
-      <c r="G262" s="6" t="s">
-        <v>597</v>
-      </c>
-      <c r="H262" s="6" t="s">
-        <v>597</v>
+      <c r="B263" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="C263" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="D263" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="E263" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="F263" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="G263" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="H263" s="6" t="s">
+        <v>594</v>
       </c>
     </row>
   </sheetData>
@@ -6886,6 +7043,11 @@
     <mergeCell ref="B109:N109"/>
     <mergeCell ref="B129:T129"/>
   </mergeCells>
+  <conditionalFormatting sqref="H217:H226">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="SBS-GADUNG-HW.MA5801-OLT-01">
+      <formula>NOT(ISERROR(SEARCH("SBS-GADUNG-HW.MA5801-OLT-01",H217)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="10">
     <tablePart r:id="rId1"/>

--- a/public/data/List_Team_Region.xlsx
+++ b/public/data/List_Team_Region.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yoss Work\App Retail SBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D7CD8D-9BAB-4A90-AC53-C18325A28E72}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C84BC07-672B-464C-93B4-E2CACA749FD0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="2175" windowWidth="21600" windowHeight="11295" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
+    <workbookView xWindow="-135" yWindow="2010" windowWidth="21600" windowHeight="12240" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="642">
   <si>
     <t>JAMBI</t>
   </si>
@@ -1932,12 +1932,6 @@
     <t>BANGKA BELITUNG</t>
   </si>
   <si>
-    <t>SBS-CURUP-HW.MA5801-OLT-04</t>
-  </si>
-  <si>
-    <t>SBS-CURUP-RC-OLT-03</t>
-  </si>
-  <si>
     <t>SBS-ARGA.MAKMUR-HW.MA5801-OLT-03</t>
   </si>
   <si>
@@ -1960,6 +1954,9 @@
   </si>
   <si>
     <t xml:space="preserve">RENDY </t>
+  </si>
+  <si>
+    <t>SBS-NUSA.INDAH-RC-OLT-02</t>
   </si>
 </sst>
 </file>
@@ -2040,7 +2037,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2077,8 +2074,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -2190,11 +2193,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2249,6 +2263,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2258,12 +2273,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="13">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2281,16 +2307,6 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2521,7 +2537,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}" name="Table27" displayName="Table27" ref="B130:T147" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}" name="Table27" displayName="Table27" ref="B130:T147" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="B130:T147" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{F8A4E442-73AD-4EB9-BB0D-D55E87DA1888}" name="SERPO PALEMBANG KOTA"/>
@@ -2672,8 +2688,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}" name="Table1727" displayName="Table1727" ref="B240:G262" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="B240:G262" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}" name="Table1727" displayName="Table1727" ref="B240:G263" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="B240:G263" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{97E25E83-847F-4991-A885-21D98063A2DB}" name="SERPO KOBA"/>
     <tableColumn id="2" xr3:uid="{0AB964B5-883A-49C8-8DDA-C8EE93753519}" name="SERPO PANGKAL PINANG"/>
@@ -3003,7 +3019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D0AF9EF-6686-405D-9473-604A5805FA6C}">
-  <dimension ref="A1:T263"/>
+  <dimension ref="A1:T264"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="34.125" customWidth="1"/>
@@ -3036,21 +3052,21 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
     </row>
     <row r="3" spans="1:14" s="3" customFormat="1">
       <c r="A3" s="3" t="s">
@@ -3336,7 +3352,7 @@
         <v>75</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>76</v>
@@ -3361,27 +3377,27 @@
       <c r="A25" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="28"/>
-      <c r="P25" s="28"/>
-      <c r="Q25" s="28"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="29"/>
     </row>
     <row r="26" spans="1:20" s="5" customFormat="1">
       <c r="A26" s="5" t="s">
@@ -3550,7 +3566,7 @@
     </row>
     <row r="32" spans="1:20">
       <c r="B32" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C32" t="s">
         <v>40</v>
@@ -3739,21 +3755,21 @@
       <c r="A49" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="26" t="s">
+      <c r="B49" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
-      <c r="H49" s="26"/>
-      <c r="I49" s="26"/>
-      <c r="J49" s="26"/>
-      <c r="K49" s="26"/>
-      <c r="L49" s="26"/>
-      <c r="M49" s="26"/>
-      <c r="N49" s="26"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="27"/>
+      <c r="I49" s="27"/>
+      <c r="J49" s="27"/>
+      <c r="K49" s="27"/>
+      <c r="L49" s="27"/>
+      <c r="M49" s="27"/>
+      <c r="N49" s="27"/>
     </row>
     <row r="50" spans="1:14" s="3" customFormat="1">
       <c r="A50" s="3" t="s">
@@ -3905,6 +3921,9 @@
       <c r="D57" t="s">
         <v>126</v>
       </c>
+      <c r="E57" t="s">
+        <v>200</v>
+      </c>
       <c r="F57" t="s">
         <v>154</v>
       </c>
@@ -4080,40 +4099,40 @@
         <v>180</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>181</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="81" spans="1:20" ht="15">
       <c r="A81" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B81" s="27" t="s">
+      <c r="B81" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="C81" s="27"/>
-      <c r="D81" s="27"/>
-      <c r="E81" s="27"/>
-      <c r="F81" s="27"/>
-      <c r="G81" s="27"/>
-      <c r="H81" s="27"/>
-      <c r="I81" s="28"/>
-      <c r="J81" s="28"/>
-      <c r="K81" s="28"/>
-      <c r="L81" s="28"/>
-      <c r="M81" s="28"/>
-      <c r="N81" s="28"/>
-      <c r="O81" s="28"/>
-      <c r="P81" s="28"/>
-      <c r="Q81" s="28"/>
-      <c r="R81" s="28"/>
-      <c r="S81" s="28"/>
-      <c r="T81" s="28"/>
+      <c r="C81" s="28"/>
+      <c r="D81" s="28"/>
+      <c r="E81" s="28"/>
+      <c r="F81" s="28"/>
+      <c r="G81" s="28"/>
+      <c r="H81" s="28"/>
+      <c r="I81" s="29"/>
+      <c r="J81" s="29"/>
+      <c r="K81" s="29"/>
+      <c r="L81" s="29"/>
+      <c r="M81" s="29"/>
+      <c r="N81" s="29"/>
+      <c r="O81" s="29"/>
+      <c r="P81" s="29"/>
+      <c r="Q81" s="29"/>
+      <c r="R81" s="29"/>
+      <c r="S81" s="29"/>
+      <c r="T81" s="29"/>
     </row>
     <row r="82" spans="1:20" s="6" customFormat="1">
       <c r="A82" s="5" t="s">
@@ -4457,7 +4476,7 @@
         <v>209</v>
       </c>
       <c r="J105" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="108" spans="1:15" ht="15">
@@ -4469,21 +4488,21 @@
       <c r="A109" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B109" s="26" t="s">
+      <c r="B109" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="C109" s="26"/>
-      <c r="D109" s="26"/>
-      <c r="E109" s="26"/>
-      <c r="F109" s="26"/>
-      <c r="G109" s="26"/>
-      <c r="H109" s="26"/>
-      <c r="I109" s="26"/>
-      <c r="J109" s="26"/>
-      <c r="K109" s="26"/>
-      <c r="L109" s="26"/>
-      <c r="M109" s="26"/>
-      <c r="N109" s="26"/>
+      <c r="C109" s="27"/>
+      <c r="D109" s="27"/>
+      <c r="E109" s="27"/>
+      <c r="F109" s="27"/>
+      <c r="G109" s="27"/>
+      <c r="H109" s="27"/>
+      <c r="I109" s="27"/>
+      <c r="J109" s="27"/>
+      <c r="K109" s="27"/>
+      <c r="L109" s="27"/>
+      <c r="M109" s="27"/>
+      <c r="N109" s="27"/>
     </row>
     <row r="110" spans="1:15" s="3" customFormat="1">
       <c r="A110" s="3" t="s">
@@ -4914,10 +4933,10 @@
         <v>337</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="I127" s="4" t="s">
         <v>338</v>
@@ -4945,27 +4964,27 @@
       <c r="A129" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B129" s="27" t="s">
+      <c r="B129" s="28" t="s">
         <v>345</v>
       </c>
-      <c r="C129" s="27"/>
-      <c r="D129" s="27"/>
-      <c r="E129" s="27"/>
-      <c r="F129" s="27"/>
-      <c r="G129" s="27"/>
-      <c r="H129" s="27"/>
-      <c r="I129" s="28"/>
-      <c r="J129" s="28"/>
-      <c r="K129" s="28"/>
-      <c r="L129" s="28"/>
-      <c r="M129" s="28"/>
-      <c r="N129" s="28"/>
-      <c r="O129" s="28"/>
-      <c r="P129" s="28"/>
-      <c r="Q129" s="28"/>
-      <c r="R129" s="28"/>
-      <c r="S129" s="28"/>
-      <c r="T129" s="28"/>
+      <c r="C129" s="28"/>
+      <c r="D129" s="28"/>
+      <c r="E129" s="28"/>
+      <c r="F129" s="28"/>
+      <c r="G129" s="28"/>
+      <c r="H129" s="28"/>
+      <c r="I129" s="29"/>
+      <c r="J129" s="29"/>
+      <c r="K129" s="29"/>
+      <c r="L129" s="29"/>
+      <c r="M129" s="29"/>
+      <c r="N129" s="29"/>
+      <c r="O129" s="29"/>
+      <c r="P129" s="29"/>
+      <c r="Q129" s="29"/>
+      <c r="R129" s="29"/>
+      <c r="S129" s="29"/>
+      <c r="T129" s="29"/>
     </row>
     <row r="130" spans="1:20" s="5" customFormat="1">
       <c r="A130" s="5" t="s">
@@ -5483,21 +5502,21 @@
       <c r="A151" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B151" s="26" t="s">
+      <c r="B151" s="27" t="s">
         <v>380</v>
       </c>
-      <c r="C151" s="26"/>
-      <c r="D151" s="26"/>
-      <c r="E151" s="26"/>
-      <c r="F151" s="26"/>
-      <c r="G151" s="26"/>
-      <c r="H151" s="26"/>
-      <c r="I151" s="26"/>
-      <c r="J151" s="26"/>
-      <c r="K151" s="26"/>
-      <c r="L151" s="26"/>
-      <c r="M151" s="26"/>
-      <c r="N151" s="26"/>
+      <c r="C151" s="27"/>
+      <c r="D151" s="27"/>
+      <c r="E151" s="27"/>
+      <c r="F151" s="27"/>
+      <c r="G151" s="27"/>
+      <c r="H151" s="27"/>
+      <c r="I151" s="27"/>
+      <c r="J151" s="27"/>
+      <c r="K151" s="27"/>
+      <c r="L151" s="27"/>
+      <c r="M151" s="27"/>
+      <c r="N151" s="27"/>
     </row>
     <row r="152" spans="1:20" s="12" customFormat="1" ht="15">
       <c r="A152" s="3" t="s">
@@ -5845,11 +5864,17 @@
       <c r="B171" t="s">
         <v>419</v>
       </c>
+      <c r="C171" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="172" spans="2:9">
       <c r="B172" t="s">
         <v>473</v>
       </c>
+      <c r="C172" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="173" spans="2:9">
       <c r="B173" t="s">
@@ -5904,27 +5929,27 @@
       <c r="A179" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B179" s="27" t="s">
+      <c r="B179" s="28" t="s">
         <v>486</v>
       </c>
-      <c r="C179" s="27"/>
-      <c r="D179" s="27"/>
-      <c r="E179" s="27"/>
-      <c r="F179" s="27"/>
-      <c r="G179" s="27"/>
-      <c r="H179" s="27"/>
-      <c r="I179" s="28"/>
-      <c r="J179" s="28"/>
-      <c r="K179" s="28"/>
-      <c r="L179" s="28"/>
-      <c r="M179" s="28"/>
-      <c r="N179" s="28"/>
-      <c r="O179" s="28"/>
-      <c r="P179" s="28"/>
-      <c r="Q179" s="28"/>
-      <c r="R179" s="28"/>
-      <c r="S179" s="28"/>
-      <c r="T179" s="28"/>
+      <c r="C179" s="28"/>
+      <c r="D179" s="28"/>
+      <c r="E179" s="28"/>
+      <c r="F179" s="28"/>
+      <c r="G179" s="28"/>
+      <c r="H179" s="28"/>
+      <c r="I179" s="29"/>
+      <c r="J179" s="29"/>
+      <c r="K179" s="29"/>
+      <c r="L179" s="29"/>
+      <c r="M179" s="29"/>
+      <c r="N179" s="29"/>
+      <c r="O179" s="29"/>
+      <c r="P179" s="29"/>
+      <c r="Q179" s="29"/>
+      <c r="R179" s="29"/>
+      <c r="S179" s="29"/>
+      <c r="T179" s="29"/>
     </row>
     <row r="180" spans="1:20" s="5" customFormat="1">
       <c r="A180" s="5" t="s">
@@ -5966,10 +5991,10 @@
         <v>394</v>
       </c>
       <c r="F181" t="s">
-        <v>428</v>
+        <v>393</v>
       </c>
       <c r="G181" t="s">
-        <v>435</v>
+        <v>401</v>
       </c>
       <c r="H181" t="s">
         <v>414</v>
@@ -5989,10 +6014,10 @@
         <v>408</v>
       </c>
       <c r="F182" t="s">
-        <v>465</v>
+        <v>407</v>
       </c>
       <c r="G182" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="H182" t="s">
         <v>427</v>
@@ -6012,10 +6037,10 @@
         <v>400</v>
       </c>
       <c r="F183" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="G183" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="H183" t="s">
         <v>392</v>
@@ -6029,16 +6054,16 @@
         <v>419</v>
       </c>
       <c r="D184" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E184" t="s">
         <v>493</v>
       </c>
       <c r="F184" t="s">
-        <v>633</v>
+        <v>465</v>
       </c>
       <c r="G184" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="H184" t="s">
         <v>406</v>
@@ -6052,16 +6077,16 @@
         <v>425</v>
       </c>
       <c r="D185" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="E185" t="s">
         <v>422</v>
       </c>
       <c r="F185" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="G185" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="H185" t="s">
         <v>416</v>
@@ -6081,10 +6106,10 @@
         <v>420</v>
       </c>
       <c r="F186" t="s">
-        <v>439</v>
+        <v>393</v>
       </c>
       <c r="G186" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="H186" t="s">
         <v>421</v>
@@ -6098,13 +6123,13 @@
         <v>441</v>
       </c>
       <c r="F187" t="s">
-        <v>444</v>
+        <v>407</v>
       </c>
       <c r="G187" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="H187" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="188" spans="1:20">
@@ -6115,10 +6140,10 @@
         <v>463</v>
       </c>
       <c r="F188" t="s">
-        <v>449</v>
+        <v>472</v>
       </c>
       <c r="H188" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="189" spans="1:20">
@@ -6129,10 +6154,10 @@
         <v>411</v>
       </c>
       <c r="F189" t="s">
-        <v>452</v>
+        <v>415</v>
       </c>
       <c r="H189" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
     </row>
     <row r="190" spans="1:20">
@@ -6143,7 +6168,7 @@
         <v>468</v>
       </c>
       <c r="F190" t="s">
-        <v>455</v>
+        <v>428</v>
       </c>
       <c r="H190" t="s">
         <v>448</v>
@@ -6157,7 +6182,7 @@
         <v>470</v>
       </c>
       <c r="F191" t="s">
-        <v>459</v>
+        <v>434</v>
       </c>
     </row>
     <row r="192" spans="1:20">
@@ -6168,7 +6193,7 @@
         <v>419</v>
       </c>
       <c r="F192" t="s">
-        <v>462</v>
+        <v>439</v>
       </c>
     </row>
     <row r="193" spans="2:6">
@@ -6179,7 +6204,7 @@
         <v>473</v>
       </c>
       <c r="F193" t="s">
-        <v>634</v>
+        <v>444</v>
       </c>
     </row>
     <row r="194" spans="2:6">
@@ -6190,7 +6215,7 @@
         <v>474</v>
       </c>
       <c r="F194" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
     </row>
     <row r="195" spans="2:6">
@@ -6201,7 +6226,7 @@
         <v>475</v>
       </c>
       <c r="F195" t="s">
-        <v>393</v>
+        <v>452</v>
       </c>
     </row>
     <row r="196" spans="2:6">
@@ -6212,7 +6237,7 @@
         <v>476</v>
       </c>
       <c r="F196" t="s">
-        <v>407</v>
+        <v>455</v>
       </c>
     </row>
     <row r="197" spans="2:6">
@@ -6223,7 +6248,7 @@
         <v>477</v>
       </c>
       <c r="F197" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
     </row>
     <row r="198" spans="2:6">
@@ -6234,7 +6259,7 @@
         <v>413</v>
       </c>
       <c r="F198" t="s">
-        <v>415</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="2:6">
@@ -6244,6 +6269,9 @@
       <c r="C199" t="s">
         <v>402</v>
       </c>
+      <c r="F199" t="s">
+        <v>399</v>
+      </c>
     </row>
     <row r="200" spans="2:6">
       <c r="B200" t="s">
@@ -6345,21 +6373,21 @@
       <c r="A214" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B214" s="26" t="s">
+      <c r="B214" s="27" t="s">
         <v>495</v>
       </c>
-      <c r="C214" s="26"/>
-      <c r="D214" s="26"/>
-      <c r="E214" s="26"/>
-      <c r="F214" s="26"/>
-      <c r="G214" s="26"/>
-      <c r="H214" s="26"/>
-      <c r="I214" s="26"/>
-      <c r="J214" s="26"/>
-      <c r="K214" s="26"/>
-      <c r="L214" s="26"/>
-      <c r="M214" s="26"/>
-      <c r="N214" s="26"/>
+      <c r="C214" s="27"/>
+      <c r="D214" s="27"/>
+      <c r="E214" s="27"/>
+      <c r="F214" s="27"/>
+      <c r="G214" s="27"/>
+      <c r="H214" s="27"/>
+      <c r="I214" s="27"/>
+      <c r="J214" s="27"/>
+      <c r="K214" s="27"/>
+      <c r="L214" s="27"/>
+      <c r="M214" s="27"/>
+      <c r="N214" s="27"/>
     </row>
     <row r="215" spans="1:14" s="3" customFormat="1">
       <c r="A215" s="3" t="s">
@@ -6480,6 +6508,7 @@
       <c r="H220" t="s">
         <v>535</v>
       </c>
+      <c r="K220" s="31"/>
     </row>
     <row r="221" spans="1:14">
       <c r="B221" t="s">
@@ -6497,6 +6526,7 @@
       <c r="H221" t="s">
         <v>539</v>
       </c>
+      <c r="K221" s="30"/>
     </row>
     <row r="222" spans="1:14">
       <c r="B222" t="s">
@@ -6514,6 +6544,7 @@
       <c r="H222" t="s">
         <v>508</v>
       </c>
+      <c r="K222" s="31"/>
     </row>
     <row r="223" spans="1:14">
       <c r="B223" t="s">
@@ -6531,6 +6562,7 @@
       <c r="H223" t="s">
         <v>591</v>
       </c>
+      <c r="K223" s="30"/>
     </row>
     <row r="224" spans="1:14">
       <c r="B224" t="s">
@@ -6545,10 +6577,11 @@
       <c r="E224" t="s">
         <v>549</v>
       </c>
-      <c r="F224" s="29"/>
+      <c r="F224" s="26"/>
       <c r="H224" t="s">
         <v>630</v>
       </c>
+      <c r="K224" s="31"/>
     </row>
     <row r="225" spans="1:20">
       <c r="B225" t="s">
@@ -6566,6 +6599,7 @@
       <c r="H225" t="s">
         <v>582</v>
       </c>
+      <c r="K225" s="30"/>
     </row>
     <row r="226" spans="1:20">
       <c r="B226" t="s">
@@ -6580,6 +6614,7 @@
       <c r="H226" t="s">
         <v>530</v>
       </c>
+      <c r="K226" s="31"/>
     </row>
     <row r="227" spans="1:20">
       <c r="B227" t="s">
@@ -6591,6 +6626,7 @@
       <c r="E227" t="s">
         <v>545</v>
       </c>
+      <c r="K227" s="30"/>
     </row>
     <row r="228" spans="1:20">
       <c r="B228" t="s">
@@ -6599,6 +6635,7 @@
       <c r="C228" t="s">
         <v>626</v>
       </c>
+      <c r="K228" s="31"/>
     </row>
     <row r="229" spans="1:20">
       <c r="B229" t="s">
@@ -6607,16 +6644,19 @@
       <c r="C229" t="s">
         <v>577</v>
       </c>
+      <c r="K229" s="30"/>
     </row>
     <row r="230" spans="1:20">
       <c r="B230" t="s">
         <v>551</v>
       </c>
+      <c r="K230" s="31"/>
     </row>
     <row r="231" spans="1:20">
       <c r="B231" t="s">
         <v>540</v>
       </c>
+      <c r="K231" s="30"/>
     </row>
     <row r="232" spans="1:20">
       <c r="B232" t="s">
@@ -6630,7 +6670,7 @@
     </row>
     <row r="234" spans="1:20">
       <c r="B234" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="237" spans="1:20" s="4" customFormat="1">
@@ -6663,27 +6703,27 @@
       <c r="A239" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B239" s="27" t="s">
+      <c r="B239" s="28" t="s">
         <v>566</v>
       </c>
-      <c r="C239" s="27"/>
-      <c r="D239" s="27"/>
-      <c r="E239" s="27"/>
-      <c r="F239" s="27"/>
-      <c r="G239" s="27"/>
-      <c r="H239" s="27"/>
-      <c r="I239" s="28"/>
-      <c r="J239" s="28"/>
-      <c r="K239" s="28"/>
-      <c r="L239" s="28"/>
-      <c r="M239" s="28"/>
-      <c r="N239" s="28"/>
-      <c r="O239" s="28"/>
-      <c r="P239" s="28"/>
-      <c r="Q239" s="28"/>
-      <c r="R239" s="28"/>
-      <c r="S239" s="28"/>
-      <c r="T239" s="28"/>
+      <c r="C239" s="28"/>
+      <c r="D239" s="28"/>
+      <c r="E239" s="28"/>
+      <c r="F239" s="28"/>
+      <c r="G239" s="28"/>
+      <c r="H239" s="28"/>
+      <c r="I239" s="29"/>
+      <c r="J239" s="29"/>
+      <c r="K239" s="29"/>
+      <c r="L239" s="29"/>
+      <c r="M239" s="29"/>
+      <c r="N239" s="29"/>
+      <c r="O239" s="29"/>
+      <c r="P239" s="29"/>
+      <c r="Q239" s="29"/>
+      <c r="R239" s="29"/>
+      <c r="S239" s="29"/>
+      <c r="T239" s="29"/>
     </row>
     <row r="240" spans="1:20" s="5" customFormat="1">
       <c r="A240" s="5" t="s">
@@ -6730,7 +6770,7 @@
     </row>
     <row r="242" spans="2:7">
       <c r="B242" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C242" t="s">
         <v>543</v>
@@ -7001,32 +7041,37 @@
     </row>
     <row r="262" spans="1:8">
       <c r="D262" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="263" spans="1:8" s="6" customFormat="1">
-      <c r="A263" s="6" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8">
+      <c r="D263" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" s="6" customFormat="1">
+      <c r="A264" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B263" s="6" t="s">
+      <c r="B264" s="6" t="s">
         <v>594</v>
       </c>
-      <c r="C263" s="6" t="s">
+      <c r="C264" s="6" t="s">
         <v>594</v>
       </c>
-      <c r="D263" s="6" t="s">
+      <c r="D264" s="6" t="s">
         <v>594</v>
       </c>
-      <c r="E263" s="6" t="s">
+      <c r="E264" s="6" t="s">
         <v>594</v>
       </c>
-      <c r="F263" s="6" t="s">
+      <c r="F264" s="6" t="s">
         <v>594</v>
       </c>
-      <c r="G263" s="6" t="s">
+      <c r="G264" s="6" t="s">
         <v>594</v>
       </c>
-      <c r="H263" s="6" t="s">
+      <c r="H264" s="6" t="s">
         <v>594</v>
       </c>
     </row>
@@ -7044,7 +7089,7 @@
     <mergeCell ref="B129:T129"/>
   </mergeCells>
   <conditionalFormatting sqref="H217:H226">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="SBS-GADUNG-HW.MA5801-OLT-01">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="SBS-GADUNG-HW.MA5801-OLT-01">
       <formula>NOT(ISERROR(SEARCH("SBS-GADUNG-HW.MA5801-OLT-01",H217)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/public/data/List_Team_Region.xlsx
+++ b/public/data/List_Team_Region.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yoss Work\App Retail SBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C84BC07-672B-464C-93B4-E2CACA749FD0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A42B3E-90B3-49D5-A1AA-4892E24CCC76}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="2010" windowWidth="21600" windowHeight="12240" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
+    <workbookView xWindow="0" yWindow="2010" windowWidth="21600" windowHeight="12240" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="643">
   <si>
     <t>JAMBI</t>
   </si>
@@ -1957,6 +1957,9 @@
   </si>
   <si>
     <t>SBS-NUSA.INDAH-RC-OLT-02</t>
+  </si>
+  <si>
+    <t>SBS-BENTENG-RC-OLT-02</t>
   </si>
 </sst>
 </file>
@@ -2264,6 +2267,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2273,8 +2278,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3052,21 +3055,21 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
     </row>
     <row r="3" spans="1:14" s="3" customFormat="1">
       <c r="A3" s="3" t="s">
@@ -3377,27 +3380,27 @@
       <c r="A25" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="29"/>
-      <c r="M25" s="29"/>
-      <c r="N25" s="29"/>
-      <c r="O25" s="29"/>
-      <c r="P25" s="29"/>
-      <c r="Q25" s="29"/>
-      <c r="R25" s="29"/>
-      <c r="S25" s="29"/>
-      <c r="T25" s="29"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="31"/>
+      <c r="P25" s="31"/>
+      <c r="Q25" s="31"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="31"/>
+      <c r="T25" s="31"/>
     </row>
     <row r="26" spans="1:20" s="5" customFormat="1">
       <c r="A26" s="5" t="s">
@@ -3755,21 +3758,21 @@
       <c r="A49" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="27" t="s">
+      <c r="B49" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="27"/>
-      <c r="K49" s="27"/>
-      <c r="L49" s="27"/>
-      <c r="M49" s="27"/>
-      <c r="N49" s="27"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="29"/>
+      <c r="M49" s="29"/>
+      <c r="N49" s="29"/>
     </row>
     <row r="50" spans="1:14" s="3" customFormat="1">
       <c r="A50" s="3" t="s">
@@ -4112,27 +4115,27 @@
       <c r="A81" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B81" s="28" t="s">
+      <c r="B81" s="30" t="s">
         <v>182</v>
       </c>
-      <c r="C81" s="28"/>
-      <c r="D81" s="28"/>
-      <c r="E81" s="28"/>
-      <c r="F81" s="28"/>
-      <c r="G81" s="28"/>
-      <c r="H81" s="28"/>
-      <c r="I81" s="29"/>
-      <c r="J81" s="29"/>
-      <c r="K81" s="29"/>
-      <c r="L81" s="29"/>
-      <c r="M81" s="29"/>
-      <c r="N81" s="29"/>
-      <c r="O81" s="29"/>
-      <c r="P81" s="29"/>
-      <c r="Q81" s="29"/>
-      <c r="R81" s="29"/>
-      <c r="S81" s="29"/>
-      <c r="T81" s="29"/>
+      <c r="C81" s="30"/>
+      <c r="D81" s="30"/>
+      <c r="E81" s="30"/>
+      <c r="F81" s="30"/>
+      <c r="G81" s="30"/>
+      <c r="H81" s="30"/>
+      <c r="I81" s="31"/>
+      <c r="J81" s="31"/>
+      <c r="K81" s="31"/>
+      <c r="L81" s="31"/>
+      <c r="M81" s="31"/>
+      <c r="N81" s="31"/>
+      <c r="O81" s="31"/>
+      <c r="P81" s="31"/>
+      <c r="Q81" s="31"/>
+      <c r="R81" s="31"/>
+      <c r="S81" s="31"/>
+      <c r="T81" s="31"/>
     </row>
     <row r="82" spans="1:20" s="6" customFormat="1">
       <c r="A82" s="5" t="s">
@@ -4488,21 +4491,21 @@
       <c r="A109" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B109" s="27" t="s">
+      <c r="B109" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="C109" s="27"/>
-      <c r="D109" s="27"/>
-      <c r="E109" s="27"/>
-      <c r="F109" s="27"/>
-      <c r="G109" s="27"/>
-      <c r="H109" s="27"/>
-      <c r="I109" s="27"/>
-      <c r="J109" s="27"/>
-      <c r="K109" s="27"/>
-      <c r="L109" s="27"/>
-      <c r="M109" s="27"/>
-      <c r="N109" s="27"/>
+      <c r="C109" s="29"/>
+      <c r="D109" s="29"/>
+      <c r="E109" s="29"/>
+      <c r="F109" s="29"/>
+      <c r="G109" s="29"/>
+      <c r="H109" s="29"/>
+      <c r="I109" s="29"/>
+      <c r="J109" s="29"/>
+      <c r="K109" s="29"/>
+      <c r="L109" s="29"/>
+      <c r="M109" s="29"/>
+      <c r="N109" s="29"/>
     </row>
     <row r="110" spans="1:15" s="3" customFormat="1">
       <c r="A110" s="3" t="s">
@@ -4964,27 +4967,27 @@
       <c r="A129" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B129" s="28" t="s">
+      <c r="B129" s="30" t="s">
         <v>345</v>
       </c>
-      <c r="C129" s="28"/>
-      <c r="D129" s="28"/>
-      <c r="E129" s="28"/>
-      <c r="F129" s="28"/>
-      <c r="G129" s="28"/>
-      <c r="H129" s="28"/>
-      <c r="I129" s="29"/>
-      <c r="J129" s="29"/>
-      <c r="K129" s="29"/>
-      <c r="L129" s="29"/>
-      <c r="M129" s="29"/>
-      <c r="N129" s="29"/>
-      <c r="O129" s="29"/>
-      <c r="P129" s="29"/>
-      <c r="Q129" s="29"/>
-      <c r="R129" s="29"/>
-      <c r="S129" s="29"/>
-      <c r="T129" s="29"/>
+      <c r="C129" s="30"/>
+      <c r="D129" s="30"/>
+      <c r="E129" s="30"/>
+      <c r="F129" s="30"/>
+      <c r="G129" s="30"/>
+      <c r="H129" s="30"/>
+      <c r="I129" s="31"/>
+      <c r="J129" s="31"/>
+      <c r="K129" s="31"/>
+      <c r="L129" s="31"/>
+      <c r="M129" s="31"/>
+      <c r="N129" s="31"/>
+      <c r="O129" s="31"/>
+      <c r="P129" s="31"/>
+      <c r="Q129" s="31"/>
+      <c r="R129" s="31"/>
+      <c r="S129" s="31"/>
+      <c r="T129" s="31"/>
     </row>
     <row r="130" spans="1:20" s="5" customFormat="1">
       <c r="A130" s="5" t="s">
@@ -5502,21 +5505,21 @@
       <c r="A151" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B151" s="27" t="s">
+      <c r="B151" s="29" t="s">
         <v>380</v>
       </c>
-      <c r="C151" s="27"/>
-      <c r="D151" s="27"/>
-      <c r="E151" s="27"/>
-      <c r="F151" s="27"/>
-      <c r="G151" s="27"/>
-      <c r="H151" s="27"/>
-      <c r="I151" s="27"/>
-      <c r="J151" s="27"/>
-      <c r="K151" s="27"/>
-      <c r="L151" s="27"/>
-      <c r="M151" s="27"/>
-      <c r="N151" s="27"/>
+      <c r="C151" s="29"/>
+      <c r="D151" s="29"/>
+      <c r="E151" s="29"/>
+      <c r="F151" s="29"/>
+      <c r="G151" s="29"/>
+      <c r="H151" s="29"/>
+      <c r="I151" s="29"/>
+      <c r="J151" s="29"/>
+      <c r="K151" s="29"/>
+      <c r="L151" s="29"/>
+      <c r="M151" s="29"/>
+      <c r="N151" s="29"/>
     </row>
     <row r="152" spans="1:20" s="12" customFormat="1" ht="15">
       <c r="A152" s="3" t="s">
@@ -5804,6 +5807,9 @@
       <c r="F165" t="s">
         <v>444</v>
       </c>
+      <c r="I165" t="s">
+        <v>642</v>
+      </c>
     </row>
     <row r="166" spans="2:9">
       <c r="B166" t="s">
@@ -5929,27 +5935,27 @@
       <c r="A179" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B179" s="28" t="s">
+      <c r="B179" s="30" t="s">
         <v>486</v>
       </c>
-      <c r="C179" s="28"/>
-      <c r="D179" s="28"/>
-      <c r="E179" s="28"/>
-      <c r="F179" s="28"/>
-      <c r="G179" s="28"/>
-      <c r="H179" s="28"/>
-      <c r="I179" s="29"/>
-      <c r="J179" s="29"/>
-      <c r="K179" s="29"/>
-      <c r="L179" s="29"/>
-      <c r="M179" s="29"/>
-      <c r="N179" s="29"/>
-      <c r="O179" s="29"/>
-      <c r="P179" s="29"/>
-      <c r="Q179" s="29"/>
-      <c r="R179" s="29"/>
-      <c r="S179" s="29"/>
-      <c r="T179" s="29"/>
+      <c r="C179" s="30"/>
+      <c r="D179" s="30"/>
+      <c r="E179" s="30"/>
+      <c r="F179" s="30"/>
+      <c r="G179" s="30"/>
+      <c r="H179" s="30"/>
+      <c r="I179" s="31"/>
+      <c r="J179" s="31"/>
+      <c r="K179" s="31"/>
+      <c r="L179" s="31"/>
+      <c r="M179" s="31"/>
+      <c r="N179" s="31"/>
+      <c r="O179" s="31"/>
+      <c r="P179" s="31"/>
+      <c r="Q179" s="31"/>
+      <c r="R179" s="31"/>
+      <c r="S179" s="31"/>
+      <c r="T179" s="31"/>
     </row>
     <row r="180" spans="1:20" s="5" customFormat="1">
       <c r="A180" s="5" t="s">
@@ -6338,29 +6344,34 @@
         <v>456</v>
       </c>
     </row>
-    <row r="210" spans="1:14" s="6" customFormat="1">
-      <c r="A210" s="6" t="s">
+    <row r="210" spans="1:14">
+      <c r="C210" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" s="6" customFormat="1">
+      <c r="A211" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B210" s="6" t="s">
+      <c r="B211" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="C210" s="6" t="s">
+      <c r="C211" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="D210" s="6" t="s">
+      <c r="D211" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="E210" s="6" t="s">
+      <c r="E211" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="F210" s="6" t="s">
+      <c r="F211" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="G210" s="6" t="s">
+      <c r="G211" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="H210" s="6" t="s">
+      <c r="H211" s="6" t="s">
         <v>494</v>
       </c>
     </row>
@@ -6373,21 +6384,21 @@
       <c r="A214" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B214" s="27" t="s">
+      <c r="B214" s="29" t="s">
         <v>495</v>
       </c>
-      <c r="C214" s="27"/>
-      <c r="D214" s="27"/>
-      <c r="E214" s="27"/>
-      <c r="F214" s="27"/>
-      <c r="G214" s="27"/>
-      <c r="H214" s="27"/>
-      <c r="I214" s="27"/>
-      <c r="J214" s="27"/>
-      <c r="K214" s="27"/>
-      <c r="L214" s="27"/>
-      <c r="M214" s="27"/>
-      <c r="N214" s="27"/>
+      <c r="C214" s="29"/>
+      <c r="D214" s="29"/>
+      <c r="E214" s="29"/>
+      <c r="F214" s="29"/>
+      <c r="G214" s="29"/>
+      <c r="H214" s="29"/>
+      <c r="I214" s="29"/>
+      <c r="J214" s="29"/>
+      <c r="K214" s="29"/>
+      <c r="L214" s="29"/>
+      <c r="M214" s="29"/>
+      <c r="N214" s="29"/>
     </row>
     <row r="215" spans="1:14" s="3" customFormat="1">
       <c r="A215" s="3" t="s">
@@ -6508,7 +6519,7 @@
       <c r="H220" t="s">
         <v>535</v>
       </c>
-      <c r="K220" s="31"/>
+      <c r="K220" s="28"/>
     </row>
     <row r="221" spans="1:14">
       <c r="B221" t="s">
@@ -6526,7 +6537,7 @@
       <c r="H221" t="s">
         <v>539</v>
       </c>
-      <c r="K221" s="30"/>
+      <c r="K221" s="27"/>
     </row>
     <row r="222" spans="1:14">
       <c r="B222" t="s">
@@ -6544,7 +6555,7 @@
       <c r="H222" t="s">
         <v>508</v>
       </c>
-      <c r="K222" s="31"/>
+      <c r="K222" s="28"/>
     </row>
     <row r="223" spans="1:14">
       <c r="B223" t="s">
@@ -6562,7 +6573,7 @@
       <c r="H223" t="s">
         <v>591</v>
       </c>
-      <c r="K223" s="30"/>
+      <c r="K223" s="27"/>
     </row>
     <row r="224" spans="1:14">
       <c r="B224" t="s">
@@ -6581,7 +6592,7 @@
       <c r="H224" t="s">
         <v>630</v>
       </c>
-      <c r="K224" s="31"/>
+      <c r="K224" s="28"/>
     </row>
     <row r="225" spans="1:20">
       <c r="B225" t="s">
@@ -6599,7 +6610,7 @@
       <c r="H225" t="s">
         <v>582</v>
       </c>
-      <c r="K225" s="30"/>
+      <c r="K225" s="27"/>
     </row>
     <row r="226" spans="1:20">
       <c r="B226" t="s">
@@ -6614,7 +6625,7 @@
       <c r="H226" t="s">
         <v>530</v>
       </c>
-      <c r="K226" s="31"/>
+      <c r="K226" s="28"/>
     </row>
     <row r="227" spans="1:20">
       <c r="B227" t="s">
@@ -6626,7 +6637,7 @@
       <c r="E227" t="s">
         <v>545</v>
       </c>
-      <c r="K227" s="30"/>
+      <c r="K227" s="27"/>
     </row>
     <row r="228" spans="1:20">
       <c r="B228" t="s">
@@ -6635,7 +6646,7 @@
       <c r="C228" t="s">
         <v>626</v>
       </c>
-      <c r="K228" s="31"/>
+      <c r="K228" s="28"/>
     </row>
     <row r="229" spans="1:20">
       <c r="B229" t="s">
@@ -6644,19 +6655,19 @@
       <c r="C229" t="s">
         <v>577</v>
       </c>
-      <c r="K229" s="30"/>
+      <c r="K229" s="27"/>
     </row>
     <row r="230" spans="1:20">
       <c r="B230" t="s">
         <v>551</v>
       </c>
-      <c r="K230" s="31"/>
+      <c r="K230" s="28"/>
     </row>
     <row r="231" spans="1:20">
       <c r="B231" t="s">
         <v>540</v>
       </c>
-      <c r="K231" s="30"/>
+      <c r="K231" s="27"/>
     </row>
     <row r="232" spans="1:20">
       <c r="B232" t="s">
@@ -6703,27 +6714,27 @@
       <c r="A239" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B239" s="28" t="s">
+      <c r="B239" s="30" t="s">
         <v>566</v>
       </c>
-      <c r="C239" s="28"/>
-      <c r="D239" s="28"/>
-      <c r="E239" s="28"/>
-      <c r="F239" s="28"/>
-      <c r="G239" s="28"/>
-      <c r="H239" s="28"/>
-      <c r="I239" s="29"/>
-      <c r="J239" s="29"/>
-      <c r="K239" s="29"/>
-      <c r="L239" s="29"/>
-      <c r="M239" s="29"/>
-      <c r="N239" s="29"/>
-      <c r="O239" s="29"/>
-      <c r="P239" s="29"/>
-      <c r="Q239" s="29"/>
-      <c r="R239" s="29"/>
-      <c r="S239" s="29"/>
-      <c r="T239" s="29"/>
+      <c r="C239" s="30"/>
+      <c r="D239" s="30"/>
+      <c r="E239" s="30"/>
+      <c r="F239" s="30"/>
+      <c r="G239" s="30"/>
+      <c r="H239" s="30"/>
+      <c r="I239" s="31"/>
+      <c r="J239" s="31"/>
+      <c r="K239" s="31"/>
+      <c r="L239" s="31"/>
+      <c r="M239" s="31"/>
+      <c r="N239" s="31"/>
+      <c r="O239" s="31"/>
+      <c r="P239" s="31"/>
+      <c r="Q239" s="31"/>
+      <c r="R239" s="31"/>
+      <c r="S239" s="31"/>
+      <c r="T239" s="31"/>
     </row>
     <row r="240" spans="1:20" s="5" customFormat="1">
       <c r="A240" s="5" t="s">

--- a/public/data/List_Team_Region.xlsx
+++ b/public/data/List_Team_Region.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yoss Work\App Retail SBS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muham\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A42B3E-90B3-49D5-A1AA-4892E24CCC76}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7733EE0-F6B4-4E23-BDBA-9C5068BCF313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2010" windowWidth="21600" windowHeight="12240" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="647">
   <si>
     <t>JAMBI</t>
   </si>
@@ -339,9 +339,6 @@
     <t>SBS-BATIN.TIGA-RC-OLT-01</t>
   </si>
   <si>
-    <t xml:space="preserve">  SBS-TELANAI.PURA-HW.MA5801-OLT-01</t>
-  </si>
-  <si>
     <t>SBS-PEMATANG.GAJAH-HW.MA5801-OLT-01</t>
   </si>
   <si>
@@ -1960,13 +1957,28 @@
   </si>
   <si>
     <t>SBS-BENTENG-RC-OLT-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SBS-KEDAMAIAN-HW.MA5801-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-BENTENG-RC-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-BHMA.TANJUNG.RATU-FH.AN6001.G16-OLT-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SBS-BHMA.TANJUNG.GUNUNG-FH.AN6000.2-OLT-01</t>
+  </si>
+  <si>
+    <t>BHMA PANGKAL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2039,8 +2051,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Ui-Sans-Serif"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2068,12 +2086,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2211,7 +2223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2239,7 +2251,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2266,9 +2277,8 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2278,6 +2288,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2540,8 +2551,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}" name="Table27" displayName="Table27" ref="B130:T147" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="B130:T147" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}" name="Table27" displayName="Table27" ref="B132:T149" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="B132:T149" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{F8A4E442-73AD-4EB9-BB0D-D55E87DA1888}" name="SERPO PALEMBANG KOTA"/>
     <tableColumn id="2" xr3:uid="{FDE83478-980D-467C-B140-58C1B9CDE4FE}" name="SERPO LAHAT"/>
@@ -2601,8 +2612,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6E2D26AE-ECD5-48A4-AC1D-1B4180A6F140}" name="Table1222" displayName="Table1222" ref="B82:J104" totalsRowShown="0" headerRowDxfId="9">
-  <autoFilter ref="B82:J104" xr:uid="{6E2D26AE-ECD5-48A4-AC1D-1B4180A6F140}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6E2D26AE-ECD5-48A4-AC1D-1B4180A6F140}" name="Table1222" displayName="Table1222" ref="B82:J106" totalsRowShown="0" headerRowDxfId="9">
+  <autoFilter ref="B82:J106" xr:uid="{6E2D26AE-ECD5-48A4-AC1D-1B4180A6F140}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{060484FA-EE1E-4DC8-9A74-A60AA9B20548}" name="SERPO TEGINENENG_x0009__x0009_"/>
     <tableColumn id="2" xr3:uid="{6EF60155-EEC6-4684-8887-3DAB1F16BBBB}" name="SERPO SUTAMI"/>
@@ -2619,8 +2630,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}" name="Table1323" displayName="Table1323" ref="B110:O127" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="B110:O127" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}" name="Table1323" displayName="Table1323" ref="B112:O129" totalsRowShown="0" headerRowDxfId="8">
+  <autoFilter ref="B112:O129" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{6FB6563D-399C-4506-8AF0-A312347E4888}" name="REG7 PALEMBANG 1"/>
     <tableColumn id="2" xr3:uid="{211D6500-28BD-4C9B-A588-576FE1D6FE10}" name="REG7 PALEMBANG 2"/>
@@ -2642,8 +2653,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}" name="Table1424" displayName="Table1424" ref="B152:I176" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
-  <autoFilter ref="B152:I176" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}" name="Table1424" displayName="Table1424" ref="B154:I178" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
+  <autoFilter ref="B154:I178" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{9BFFF82B-4674-404E-AC18-7772CF16890E}" name="GSP BENGKULU 1"/>
     <tableColumn id="2" xr3:uid="{BF3EB892-4094-4FE7-B983-B0CEE975CE16}" name="GSP BENGKULU 2"/>
@@ -2659,8 +2670,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}" name="Table1525" displayName="Table1525" ref="B180:H210" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="B180:H210" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}" name="Table1525" displayName="Table1525" ref="B182:H212" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="B182:H212" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{ACEB90AF-9CBB-4605-8377-2CF0EF299650}" name="SERPO SUKAMERINDU"/>
     <tableColumn id="2" xr3:uid="{351154A5-2DE7-411B-9044-B8641069B0BF}" name="SERPO BENGKULU KOTA"/>
@@ -2675,9 +2686,9 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}" name="Table1626" displayName="Table1626" ref="B215:H237" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="B215:H237" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}" name="Table1626" displayName="Table1626" ref="B217:I239" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="B217:I239" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{D0B3A41D-F35E-4B89-AC56-18717B9B04E5}" name="BANGKA REG 7"/>
     <tableColumn id="2" xr3:uid="{9C59FCCC-409F-4148-A8DC-48E653CEBBAA}" name="TTM SUNGAI LIAT"/>
     <tableColumn id="3" xr3:uid="{4CDF479A-0135-4579-8D4B-1BB69ED4C181}" name=" SIB BELITUNG"/>
@@ -2685,14 +2696,15 @@
     <tableColumn id="5" xr3:uid="{92F8ACC0-68CF-4596-9266-1F4FB8A66AB4}" name="BHMA MUNTOK"/>
     <tableColumn id="6" xr3:uid="{0B0239C9-7A4F-43FF-9290-2802C7BC9FB4}" name="BHMA TOBOALI"/>
     <tableColumn id="7" xr3:uid="{8123CD65-4692-4D67-A2BA-221C76B9CCAB}" name="TTM TOBOALI"/>
+    <tableColumn id="8" xr3:uid="{C1E7F7E2-1144-4652-A426-F632A32DB3B4}" name="BHMA PANGKAL"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}" name="Table1727" displayName="Table1727" ref="B240:G263" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="B240:G263" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}" name="Table1727" displayName="Table1727" ref="B242:G265" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="B242:G265" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{97E25E83-847F-4991-A885-21D98063A2DB}" name="SERPO KOBA"/>
     <tableColumn id="2" xr3:uid="{0AB964B5-883A-49C8-8DDA-C8EE93753519}" name="SERPO PANGKAL PINANG"/>
@@ -3022,31 +3034,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D0AF9EF-6686-405D-9473-604A5805FA6C}">
-  <dimension ref="A1:T264"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:T266"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="34.125" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="27.75" customWidth="1"/>
-    <col min="5" max="5" width="26.625" customWidth="1"/>
-    <col min="6" max="6" width="27.625" customWidth="1"/>
-    <col min="7" max="7" width="22.875" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" customWidth="1"/>
+    <col min="5" max="5" width="26.5703125" customWidth="1"/>
+    <col min="6" max="6" width="27.5703125" customWidth="1"/>
+    <col min="7" max="7" width="22.85546875" customWidth="1"/>
     <col min="8" max="8" width="27" customWidth="1"/>
-    <col min="9" max="9" width="21.875" customWidth="1"/>
-    <col min="10" max="10" width="27.125" customWidth="1"/>
-    <col min="11" max="11" width="24.75" customWidth="1"/>
-    <col min="12" max="12" width="27.625" customWidth="1"/>
-    <col min="13" max="13" width="21.875" customWidth="1"/>
+    <col min="9" max="9" width="21.85546875" customWidth="1"/>
+    <col min="10" max="10" width="27.140625" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" customWidth="1"/>
+    <col min="12" max="12" width="27.5703125" customWidth="1"/>
+    <col min="13" max="13" width="21.85546875" customWidth="1"/>
     <col min="14" max="14" width="28" customWidth="1"/>
-    <col min="15" max="15" width="25.75" customWidth="1"/>
-    <col min="16" max="16" width="20.875" customWidth="1"/>
-    <col min="17" max="17" width="23.875" customWidth="1"/>
-    <col min="18" max="18" width="22.25" customWidth="1"/>
-    <col min="19" max="19" width="28.125" customWidth="1"/>
-    <col min="20" max="20" width="27.25" customWidth="1"/>
+    <col min="15" max="15" width="25.7109375" customWidth="1"/>
+    <col min="16" max="16" width="20.85546875" customWidth="1"/>
+    <col min="17" max="17" width="23.85546875" customWidth="1"/>
+    <col min="18" max="18" width="22.28515625" customWidth="1"/>
+    <col min="19" max="19" width="28.140625" customWidth="1"/>
+    <col min="20" max="20" width="27.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3055,21 +3067,21 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
     </row>
     <row r="3" spans="1:14" s="3" customFormat="1">
       <c r="A3" s="3" t="s">
@@ -3108,7 +3120,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
@@ -3125,7 +3137,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -3151,7 +3163,7 @@
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E6" t="s">
         <v>27</v>
@@ -3171,7 +3183,7 @@
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -3217,7 +3229,7 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D9" t="s">
         <v>48</v>
@@ -3237,7 +3249,7 @@
         <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D10" t="s">
         <v>52</v>
@@ -3254,16 +3266,19 @@
     </row>
     <row r="11" spans="1:14">
       <c r="B11" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C11" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D11" t="s">
         <v>55</v>
       </c>
       <c r="F11" t="s">
         <v>53</v>
+      </c>
+      <c r="G11" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -3279,6 +3294,9 @@
       <c r="F12" t="s">
         <v>56</v>
       </c>
+      <c r="G12" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="13" spans="1:14">
       <c r="B13" t="s">
@@ -3350,12 +3368,22 @@
         <v>73</v>
       </c>
     </row>
+    <row r="21" spans="1:20">
+      <c r="F21" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+    </row>
     <row r="23" spans="1:20" s="4" customFormat="1">
       <c r="A23" s="4" t="s">
         <v>75</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>76</v>
@@ -3376,31 +3404,31 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="15">
+    <row r="25" spans="1:20">
       <c r="A25" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="31"/>
-      <c r="O25" s="31"/>
-      <c r="P25" s="31"/>
-      <c r="Q25" s="31"/>
-      <c r="R25" s="31"/>
-      <c r="S25" s="31"/>
-      <c r="T25" s="31"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="29"/>
     </row>
     <row r="26" spans="1:20" s="5" customFormat="1">
       <c r="A26" s="5" t="s">
@@ -3436,7 +3464,7 @@
     </row>
     <row r="27" spans="1:20">
       <c r="B27" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C27" t="s">
         <v>63</v>
@@ -3454,7 +3482,7 @@
         <v>13</v>
       </c>
       <c r="H27" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I27" t="s">
         <v>16</v>
@@ -3474,7 +3502,7 @@
         <v>47</v>
       </c>
       <c r="E28" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -3506,10 +3534,10 @@
         <v>27</v>
       </c>
       <c r="G29" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H29" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I29" t="s">
         <v>30</v>
@@ -3526,7 +3554,7 @@
         <v>100</v>
       </c>
       <c r="E30" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F30" t="s">
         <v>34</v>
@@ -3569,22 +3597,22 @@
     </row>
     <row r="32" spans="1:20">
       <c r="B32" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C32" t="s">
         <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E32" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G32" t="s">
         <v>48</v>
       </c>
       <c r="H32" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I32" t="s">
         <v>46</v>
@@ -3595,16 +3623,16 @@
         <v>67</v>
       </c>
       <c r="D33" t="s">
-        <v>28</v>
+        <v>594</v>
       </c>
       <c r="E33" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G33" t="s">
         <v>52</v>
       </c>
       <c r="H33" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I33" t="s">
         <v>51</v>
@@ -3615,10 +3643,10 @@
         <v>57</v>
       </c>
       <c r="D34" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="E34" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G34" t="s">
         <v>55</v>
@@ -3635,7 +3663,7 @@
         <v>69</v>
       </c>
       <c r="D35" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="E35" t="s">
         <v>25</v>
@@ -3652,7 +3680,7 @@
         <v>56</v>
       </c>
       <c r="D36" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="G36" t="s">
         <v>60</v>
@@ -3666,7 +3694,7 @@
         <v>61</v>
       </c>
       <c r="D37" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="G37" t="s">
         <v>62</v>
@@ -3677,7 +3705,7 @@
         <v>53</v>
       </c>
       <c r="D38" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="G38" t="s">
         <v>64</v>
@@ -3687,6 +3715,9 @@
       <c r="C39" t="s">
         <v>21</v>
       </c>
+      <c r="D39" t="s">
+        <v>43</v>
+      </c>
       <c r="G39" t="s">
         <v>66</v>
       </c>
@@ -3722,370 +3753,370 @@
         <v>75</v>
       </c>
       <c r="B45" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="J45" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="15">
-      <c r="A48" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
+      <c r="B49" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C49" s="27"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="27"/>
+      <c r="I49" s="27"/>
+      <c r="J49" s="27"/>
+      <c r="K49" s="27"/>
+      <c r="L49" s="27"/>
+      <c r="M49" s="27"/>
+      <c r="N49" s="27"/>
     </row>
     <row r="50" spans="1:14" s="3" customFormat="1">
       <c r="A50" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="E50" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="F50" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="G50" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="B51" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C51" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D51" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E51" t="s">
+        <v>114</v>
+      </c>
+      <c r="F51" t="s">
         <v>115</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>116</v>
-      </c>
-      <c r="G51" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="B52" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C52" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D52" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E52" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F52" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G52" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="B53" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C53" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D53" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E53" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G53" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="B54" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C54" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D54" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E54" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F54" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G54" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55" spans="1:14">
       <c r="B55" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C55" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D55" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E55" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F55" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G55" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="B56" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C56" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D56" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E56" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F56" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G56" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:14">
       <c r="C57" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D57" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E57" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G57" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:14">
       <c r="C58" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D58" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F58" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G58" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="59" spans="1:14">
       <c r="C59" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D59" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F59" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G59" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="60" spans="1:14">
       <c r="C60" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D60" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F60" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G60" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="C61" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D61" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F61" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G61" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="62" spans="1:14">
       <c r="C62" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D62" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F62" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G62" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="C63" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D63" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F63" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G63" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="64" spans="1:14">
       <c r="G64" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="G65" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="G66" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="G67" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="G68" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="G69" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="G70" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="G71" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="G72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="G73" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="G74" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="G75" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="G76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="G77" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="79" spans="1:7" s="4" customFormat="1">
@@ -4093,2966 +4124,2974 @@
         <v>75</v>
       </c>
       <c r="B79" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="D79" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="E79" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="F79" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="E79" s="4" t="s">
+      <c r="G79" s="4" t="s">
         <v>639</v>
       </c>
-      <c r="F79" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20" ht="15">
+    </row>
+    <row r="81" spans="1:20">
       <c r="A81" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B81" s="30" t="s">
-        <v>182</v>
-      </c>
-      <c r="C81" s="30"/>
-      <c r="D81" s="30"/>
-      <c r="E81" s="30"/>
-      <c r="F81" s="30"/>
-      <c r="G81" s="30"/>
-      <c r="H81" s="30"/>
-      <c r="I81" s="31"/>
-      <c r="J81" s="31"/>
-      <c r="K81" s="31"/>
-      <c r="L81" s="31"/>
-      <c r="M81" s="31"/>
-      <c r="N81" s="31"/>
-      <c r="O81" s="31"/>
-      <c r="P81" s="31"/>
-      <c r="Q81" s="31"/>
-      <c r="R81" s="31"/>
-      <c r="S81" s="31"/>
-      <c r="T81" s="31"/>
+      <c r="B81" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="C81" s="28"/>
+      <c r="D81" s="28"/>
+      <c r="E81" s="28"/>
+      <c r="F81" s="28"/>
+      <c r="G81" s="28"/>
+      <c r="H81" s="28"/>
+      <c r="I81" s="29"/>
+      <c r="J81" s="29"/>
+      <c r="K81" s="29"/>
+      <c r="L81" s="29"/>
+      <c r="M81" s="29"/>
+      <c r="N81" s="29"/>
+      <c r="O81" s="29"/>
+      <c r="P81" s="29"/>
+      <c r="Q81" s="29"/>
+      <c r="R81" s="29"/>
+      <c r="S81" s="29"/>
+      <c r="T81" s="29"/>
     </row>
     <row r="82" spans="1:20" s="6" customFormat="1">
       <c r="A82" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B82" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C82" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C82" s="6" t="s">
+      <c r="D82" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D82" s="6" t="s">
+      <c r="E82" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="E82" s="6" t="s">
+      <c r="F82" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F82" s="6" t="s">
+      <c r="G82" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="G82" s="6" t="s">
+      <c r="H82" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="H82" s="6" t="s">
+      <c r="I82" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="I82" s="6" t="s">
+      <c r="J82" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="J82" s="6" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="83" spans="1:20">
       <c r="B83" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C83" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D83" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E83" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F83" t="s">
+        <v>191</v>
+      </c>
+      <c r="G83" t="s">
         <v>192</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
         <v>193</v>
       </c>
-      <c r="H83" t="s">
+      <c r="I83" t="s">
         <v>194</v>
       </c>
-      <c r="I83" t="s">
+      <c r="J83" t="s">
         <v>195</v>
-      </c>
-      <c r="J83" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="84" spans="1:20">
       <c r="B84" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C84" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D84" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E84" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F84" t="s">
+        <v>196</v>
+      </c>
+      <c r="G84" t="s">
         <v>197</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
         <v>198</v>
-      </c>
-      <c r="H84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:20">
       <c r="B85" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C85" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D85" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E85" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G85" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:20">
       <c r="B86" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C86" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D86" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E86" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G86" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="87" spans="1:20">
       <c r="B87" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C87" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D87" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E87" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G87" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="88" spans="1:20">
       <c r="B88" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C88" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D88" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E88" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G88" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="89" spans="1:20">
       <c r="B89" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C89" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D89" t="s">
+        <v>201</v>
+      </c>
+      <c r="E89" t="s">
         <v>202</v>
       </c>
-      <c r="E89" t="s">
-        <v>203</v>
-      </c>
       <c r="G89" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="90" spans="1:20">
       <c r="B90" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C90" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D90" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E90" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="91" spans="1:20">
       <c r="B91" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C91" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E91" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="92" spans="1:20">
       <c r="B92" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C92" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E92" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="93" spans="1:20">
       <c r="B93" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C93" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E93" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="94" spans="1:20">
       <c r="B94" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C94" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E94" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="95" spans="1:20">
       <c r="B95" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C95" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E95" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="96" spans="1:20">
       <c r="B96" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C96" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E96" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="97" spans="1:15">
       <c r="B97" t="s">
-        <v>616</v>
+        <v>615</v>
+      </c>
+      <c r="C97" t="s">
+        <v>642</v>
       </c>
       <c r="E97" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="98" spans="1:15">
       <c r="B98" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E98" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="99" spans="1:15">
       <c r="B99" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E99" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="100" spans="1:15">
       <c r="B100" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E100" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="101" spans="1:15">
       <c r="B101" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E101" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="102" spans="1:15">
       <c r="B102" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E102" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="103" spans="1:15">
       <c r="B103" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E103" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="104" spans="1:15">
-      <c r="B104" t="s">
-        <v>205</v>
-      </c>
       <c r="E104" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" s="6" customFormat="1">
-      <c r="A105" s="6" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
+      <c r="E105" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15">
+      <c r="B106" t="s">
+        <v>204</v>
+      </c>
+      <c r="E106" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" s="6" customFormat="1">
+      <c r="A107" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B105" s="6" t="s">
+      <c r="B107" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F107" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="C105" s="6" t="s">
+      <c r="G107" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D105" s="6" t="s">
+      <c r="H107" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="E105" s="6" t="s">
+      <c r="I107" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="F105" s="6" t="s">
+      <c r="J107" s="6" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
+      <c r="A110" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="G105" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="I105" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="J105" s="6" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" ht="15">
-      <c r="A108" s="1" t="s">
+    </row>
+    <row r="111" spans="1:15">
+      <c r="A111" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B111" s="27" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="109" spans="1:15">
-      <c r="A109" s="2" t="s">
+      <c r="C111" s="27"/>
+      <c r="D111" s="27"/>
+      <c r="E111" s="27"/>
+      <c r="F111" s="27"/>
+      <c r="G111" s="27"/>
+      <c r="H111" s="27"/>
+      <c r="I111" s="27"/>
+      <c r="J111" s="27"/>
+      <c r="K111" s="27"/>
+      <c r="L111" s="27"/>
+      <c r="M111" s="27"/>
+      <c r="N111" s="27"/>
+    </row>
+    <row r="112" spans="1:15" s="3" customFormat="1">
+      <c r="A112" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="J112" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="K112" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="L112" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="M112" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="N112" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="O112" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="113" spans="2:15">
+      <c r="B113" t="s">
+        <v>225</v>
+      </c>
+      <c r="C113" t="s">
+        <v>226</v>
+      </c>
+      <c r="D113" t="s">
+        <v>227</v>
+      </c>
+      <c r="E113" t="s">
+        <v>228</v>
+      </c>
+      <c r="F113" t="s">
+        <v>229</v>
+      </c>
+      <c r="G113" t="s">
+        <v>230</v>
+      </c>
+      <c r="H113" t="s">
+        <v>231</v>
+      </c>
+      <c r="I113" t="s">
+        <v>232</v>
+      </c>
+      <c r="J113" t="s">
+        <v>233</v>
+      </c>
+      <c r="K113" t="s">
+        <v>234</v>
+      </c>
+      <c r="L113" t="s">
+        <v>235</v>
+      </c>
+      <c r="M113" t="s">
+        <v>236</v>
+      </c>
+      <c r="N113" t="s">
+        <v>237</v>
+      </c>
+      <c r="O113" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="114" spans="2:15">
+      <c r="B114" t="s">
+        <v>239</v>
+      </c>
+      <c r="C114" t="s">
+        <v>240</v>
+      </c>
+      <c r="D114" t="s">
+        <v>241</v>
+      </c>
+      <c r="E114" t="s">
+        <v>242</v>
+      </c>
+      <c r="F114" t="s">
+        <v>243</v>
+      </c>
+      <c r="G114" t="s">
+        <v>244</v>
+      </c>
+      <c r="H114" t="s">
+        <v>245</v>
+      </c>
+      <c r="I114" t="s">
+        <v>246</v>
+      </c>
+      <c r="J114" t="s">
+        <v>233</v>
+      </c>
+      <c r="K114" t="s">
+        <v>247</v>
+      </c>
+      <c r="L114" t="s">
+        <v>248</v>
+      </c>
+      <c r="M114" t="s">
+        <v>249</v>
+      </c>
+      <c r="N114" t="s">
+        <v>250</v>
+      </c>
+      <c r="O114" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="115" spans="2:15">
+      <c r="B115" t="s">
+        <v>252</v>
+      </c>
+      <c r="C115" t="s">
+        <v>253</v>
+      </c>
+      <c r="D115" t="s">
+        <v>254</v>
+      </c>
+      <c r="E115" t="s">
+        <v>255</v>
+      </c>
+      <c r="F115" t="s">
+        <v>256</v>
+      </c>
+      <c r="G115" t="s">
+        <v>257</v>
+      </c>
+      <c r="I115" t="s">
+        <v>258</v>
+      </c>
+      <c r="J115" t="s">
+        <v>259</v>
+      </c>
+      <c r="K115" t="s">
+        <v>260</v>
+      </c>
+      <c r="L115" t="s">
+        <v>261</v>
+      </c>
+      <c r="M115" t="s">
+        <v>262</v>
+      </c>
+      <c r="N115" t="s">
+        <v>263</v>
+      </c>
+      <c r="O115" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="116" spans="2:15">
+      <c r="B116" t="s">
+        <v>265</v>
+      </c>
+      <c r="C116" t="s">
+        <v>266</v>
+      </c>
+      <c r="D116" t="s">
+        <v>95</v>
+      </c>
+      <c r="E116" t="s">
+        <v>267</v>
+      </c>
+      <c r="F116" t="s">
+        <v>268</v>
+      </c>
+      <c r="G116" t="s">
+        <v>269</v>
+      </c>
+      <c r="I116" t="s">
+        <v>270</v>
+      </c>
+      <c r="J116" t="s">
+        <v>271</v>
+      </c>
+      <c r="K116" t="s">
+        <v>272</v>
+      </c>
+      <c r="L116" t="s">
+        <v>273</v>
+      </c>
+      <c r="M116" t="s">
+        <v>274</v>
+      </c>
+      <c r="N116" t="s">
+        <v>275</v>
+      </c>
+      <c r="O116" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="117" spans="2:15">
+      <c r="B117" t="s">
+        <v>277</v>
+      </c>
+      <c r="C117" t="s">
+        <v>278</v>
+      </c>
+      <c r="D117" t="s">
+        <v>279</v>
+      </c>
+      <c r="E117" t="s">
+        <v>280</v>
+      </c>
+      <c r="F117" t="s">
+        <v>281</v>
+      </c>
+      <c r="G117" t="s">
+        <v>282</v>
+      </c>
+      <c r="I117" t="s">
+        <v>283</v>
+      </c>
+      <c r="J117" t="s">
+        <v>284</v>
+      </c>
+      <c r="K117" t="s">
+        <v>285</v>
+      </c>
+      <c r="L117" t="s">
+        <v>286</v>
+      </c>
+      <c r="M117" t="s">
+        <v>287</v>
+      </c>
+      <c r="O117" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="118" spans="2:15">
+      <c r="B118" t="s">
+        <v>289</v>
+      </c>
+      <c r="C118" t="s">
+        <v>290</v>
+      </c>
+      <c r="D118" t="s">
+        <v>291</v>
+      </c>
+      <c r="E118" t="s">
+        <v>292</v>
+      </c>
+      <c r="G118" t="s">
+        <v>293</v>
+      </c>
+      <c r="I118" t="s">
+        <v>294</v>
+      </c>
+      <c r="J118" t="s">
+        <v>295</v>
+      </c>
+      <c r="K118" t="s">
+        <v>296</v>
+      </c>
+      <c r="L118" t="s">
+        <v>297</v>
+      </c>
+      <c r="O118" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="119" spans="2:15">
+      <c r="B119" t="s">
+        <v>299</v>
+      </c>
+      <c r="C119" t="s">
+        <v>300</v>
+      </c>
+      <c r="D119" t="s">
+        <v>301</v>
+      </c>
+      <c r="E119" t="s">
+        <v>302</v>
+      </c>
+      <c r="I119" t="s">
+        <v>303</v>
+      </c>
+      <c r="J119" t="s">
+        <v>304</v>
+      </c>
+      <c r="K119" t="s">
+        <v>305</v>
+      </c>
+      <c r="L119" t="s">
+        <v>306</v>
+      </c>
+      <c r="O119" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="120" spans="2:15">
+      <c r="B120" t="s">
+        <v>308</v>
+      </c>
+      <c r="C120" t="s">
+        <v>309</v>
+      </c>
+      <c r="D120" t="s">
+        <v>310</v>
+      </c>
+      <c r="E120" t="s">
+        <v>311</v>
+      </c>
+      <c r="I120" t="s">
+        <v>312</v>
+      </c>
+      <c r="J120" t="s">
+        <v>368</v>
+      </c>
+      <c r="K120" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="121" spans="2:15">
+      <c r="B121" t="s">
+        <v>314</v>
+      </c>
+      <c r="C121" t="s">
+        <v>315</v>
+      </c>
+      <c r="D121" t="s">
+        <v>316</v>
+      </c>
+      <c r="E121" t="s">
+        <v>317</v>
+      </c>
+      <c r="K121" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="122" spans="2:15">
+      <c r="B122" t="s">
+        <v>319</v>
+      </c>
+      <c r="C122" t="s">
+        <v>320</v>
+      </c>
+      <c r="D122" t="s">
+        <v>321</v>
+      </c>
+      <c r="K122" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="123" spans="2:15">
+      <c r="B123" t="s">
+        <v>323</v>
+      </c>
+      <c r="C123" t="s">
+        <v>324</v>
+      </c>
+      <c r="K123" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="124" spans="2:15">
+      <c r="B124" t="s">
+        <v>326</v>
+      </c>
+      <c r="K124" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="125" spans="2:15">
+      <c r="K125" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="126" spans="2:15">
+      <c r="K126" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="127" spans="2:15">
+      <c r="K127" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="128" spans="2:15">
+      <c r="K128" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="129" spans="1:20" s="4" customFormat="1">
+      <c r="A129" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="G129" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="H129" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="I129" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="J129" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="K129" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="L129" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="M129" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="N129" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="O129" s="4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="131" spans="1:20">
+      <c r="A131" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B109" s="29" t="s">
-        <v>211</v>
-      </c>
-      <c r="C109" s="29"/>
-      <c r="D109" s="29"/>
-      <c r="E109" s="29"/>
-      <c r="F109" s="29"/>
-      <c r="G109" s="29"/>
-      <c r="H109" s="29"/>
-      <c r="I109" s="29"/>
-      <c r="J109" s="29"/>
-      <c r="K109" s="29"/>
-      <c r="L109" s="29"/>
-      <c r="M109" s="29"/>
-      <c r="N109" s="29"/>
-    </row>
-    <row r="110" spans="1:15" s="3" customFormat="1">
-      <c r="A110" s="3" t="s">
+      <c r="B131" s="28" t="s">
+        <v>344</v>
+      </c>
+      <c r="C131" s="28"/>
+      <c r="D131" s="28"/>
+      <c r="E131" s="28"/>
+      <c r="F131" s="28"/>
+      <c r="G131" s="28"/>
+      <c r="H131" s="28"/>
+      <c r="I131" s="29"/>
+      <c r="J131" s="29"/>
+      <c r="K131" s="29"/>
+      <c r="L131" s="29"/>
+      <c r="M131" s="29"/>
+      <c r="N131" s="29"/>
+      <c r="O131" s="29"/>
+      <c r="P131" s="29"/>
+      <c r="Q131" s="29"/>
+      <c r="R131" s="29"/>
+      <c r="S131" s="29"/>
+      <c r="T131" s="29"/>
+    </row>
+    <row r="132" spans="1:20" s="5" customFormat="1">
+      <c r="A132" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B110" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="H110" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="I110" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="J110" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="K110" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="L110" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="M110" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="N110" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="O110" s="3" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15">
-      <c r="B111" t="s">
-        <v>226</v>
-      </c>
-      <c r="C111" t="s">
-        <v>227</v>
-      </c>
-      <c r="D111" t="s">
-        <v>228</v>
-      </c>
-      <c r="E111" t="s">
-        <v>229</v>
-      </c>
-      <c r="F111" t="s">
-        <v>230</v>
-      </c>
-      <c r="G111" t="s">
-        <v>231</v>
-      </c>
-      <c r="H111" t="s">
-        <v>232</v>
-      </c>
-      <c r="I111" t="s">
-        <v>233</v>
-      </c>
-      <c r="J111" t="s">
-        <v>234</v>
-      </c>
-      <c r="K111" t="s">
-        <v>235</v>
-      </c>
-      <c r="L111" t="s">
-        <v>236</v>
-      </c>
-      <c r="M111" t="s">
-        <v>237</v>
-      </c>
-      <c r="N111" t="s">
-        <v>238</v>
-      </c>
-      <c r="O111" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15">
-      <c r="B112" t="s">
-        <v>240</v>
-      </c>
-      <c r="C112" t="s">
-        <v>241</v>
-      </c>
-      <c r="D112" t="s">
-        <v>242</v>
-      </c>
-      <c r="E112" t="s">
-        <v>243</v>
-      </c>
-      <c r="F112" t="s">
-        <v>244</v>
-      </c>
-      <c r="G112" t="s">
-        <v>245</v>
-      </c>
-      <c r="H112" t="s">
-        <v>246</v>
-      </c>
-      <c r="I112" t="s">
-        <v>247</v>
-      </c>
-      <c r="J112" t="s">
-        <v>234</v>
-      </c>
-      <c r="K112" t="s">
-        <v>248</v>
-      </c>
-      <c r="L112" t="s">
-        <v>249</v>
-      </c>
-      <c r="M112" t="s">
-        <v>250</v>
-      </c>
-      <c r="N112" t="s">
-        <v>251</v>
-      </c>
-      <c r="O112" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15">
-      <c r="B113" t="s">
-        <v>253</v>
-      </c>
-      <c r="C113" t="s">
-        <v>254</v>
-      </c>
-      <c r="D113" t="s">
-        <v>255</v>
-      </c>
-      <c r="E113" t="s">
-        <v>256</v>
-      </c>
-      <c r="F113" t="s">
-        <v>257</v>
-      </c>
-      <c r="G113" t="s">
-        <v>258</v>
-      </c>
-      <c r="I113" t="s">
-        <v>259</v>
-      </c>
-      <c r="J113" t="s">
-        <v>260</v>
-      </c>
-      <c r="K113" t="s">
-        <v>261</v>
-      </c>
-      <c r="L113" t="s">
-        <v>262</v>
-      </c>
-      <c r="M113" t="s">
-        <v>263</v>
-      </c>
-      <c r="N113" t="s">
-        <v>264</v>
-      </c>
-      <c r="O113" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15">
-      <c r="B114" t="s">
-        <v>266</v>
-      </c>
-      <c r="C114" t="s">
-        <v>267</v>
-      </c>
-      <c r="D114" t="s">
-        <v>95</v>
-      </c>
-      <c r="E114" t="s">
-        <v>268</v>
-      </c>
-      <c r="F114" t="s">
-        <v>269</v>
-      </c>
-      <c r="G114" t="s">
-        <v>270</v>
-      </c>
-      <c r="I114" t="s">
-        <v>271</v>
-      </c>
-      <c r="J114" t="s">
-        <v>272</v>
-      </c>
-      <c r="K114" t="s">
-        <v>273</v>
-      </c>
-      <c r="L114" t="s">
-        <v>274</v>
-      </c>
-      <c r="M114" t="s">
-        <v>275</v>
-      </c>
-      <c r="N114" t="s">
-        <v>276</v>
-      </c>
-      <c r="O114" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15">
-      <c r="B115" t="s">
-        <v>278</v>
-      </c>
-      <c r="C115" t="s">
-        <v>279</v>
-      </c>
-      <c r="D115" t="s">
-        <v>280</v>
-      </c>
-      <c r="E115" t="s">
-        <v>281</v>
-      </c>
-      <c r="F115" t="s">
-        <v>282</v>
-      </c>
-      <c r="G115" t="s">
-        <v>283</v>
-      </c>
-      <c r="I115" t="s">
-        <v>284</v>
-      </c>
-      <c r="J115" t="s">
-        <v>285</v>
-      </c>
-      <c r="K115" t="s">
-        <v>286</v>
-      </c>
-      <c r="L115" t="s">
-        <v>287</v>
-      </c>
-      <c r="M115" t="s">
-        <v>288</v>
-      </c>
-      <c r="O115" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15">
-      <c r="B116" t="s">
-        <v>290</v>
-      </c>
-      <c r="C116" t="s">
-        <v>291</v>
-      </c>
-      <c r="D116" t="s">
-        <v>292</v>
-      </c>
-      <c r="E116" t="s">
-        <v>293</v>
-      </c>
-      <c r="G116" t="s">
-        <v>294</v>
-      </c>
-      <c r="I116" t="s">
-        <v>295</v>
-      </c>
-      <c r="J116" t="s">
-        <v>296</v>
-      </c>
-      <c r="K116" t="s">
-        <v>297</v>
-      </c>
-      <c r="L116" t="s">
-        <v>298</v>
-      </c>
-      <c r="O116" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15">
-      <c r="B117" t="s">
-        <v>300</v>
-      </c>
-      <c r="C117" t="s">
-        <v>301</v>
-      </c>
-      <c r="D117" t="s">
-        <v>302</v>
-      </c>
-      <c r="E117" t="s">
-        <v>303</v>
-      </c>
-      <c r="I117" t="s">
-        <v>304</v>
-      </c>
-      <c r="J117" t="s">
-        <v>305</v>
-      </c>
-      <c r="K117" t="s">
-        <v>306</v>
-      </c>
-      <c r="L117" t="s">
-        <v>307</v>
-      </c>
-      <c r="O117" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15">
-      <c r="B118" t="s">
-        <v>309</v>
-      </c>
-      <c r="C118" t="s">
-        <v>310</v>
-      </c>
-      <c r="D118" t="s">
-        <v>311</v>
-      </c>
-      <c r="E118" t="s">
-        <v>312</v>
-      </c>
-      <c r="I118" t="s">
-        <v>313</v>
-      </c>
-      <c r="J118" t="s">
-        <v>369</v>
-      </c>
-      <c r="K118" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15">
-      <c r="B119" t="s">
-        <v>315</v>
-      </c>
-      <c r="C119" t="s">
-        <v>316</v>
-      </c>
-      <c r="D119" t="s">
-        <v>317</v>
-      </c>
-      <c r="E119" t="s">
-        <v>318</v>
-      </c>
-      <c r="K119" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15">
-      <c r="B120" t="s">
-        <v>320</v>
-      </c>
-      <c r="C120" t="s">
-        <v>321</v>
-      </c>
-      <c r="D120" t="s">
-        <v>322</v>
-      </c>
-      <c r="K120" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="121" spans="1:15">
-      <c r="B121" t="s">
-        <v>324</v>
-      </c>
-      <c r="C121" t="s">
-        <v>325</v>
-      </c>
-      <c r="K121" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15">
-      <c r="B122" t="s">
-        <v>327</v>
-      </c>
-      <c r="K122" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="123" spans="1:15">
-      <c r="K123" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="124" spans="1:15">
-      <c r="K124" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="125" spans="1:15">
-      <c r="K125" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="126" spans="1:15">
-      <c r="K126" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="127" spans="1:15" s="4" customFormat="1">
-      <c r="A127" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="E127" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="G127" s="4" t="s">
-        <v>639</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>639</v>
-      </c>
-      <c r="I127" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="J127" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="K127" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="L127" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="M127" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="N127" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="O127" s="4" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="129" spans="1:20" ht="15">
-      <c r="A129" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B129" s="30" t="s">
+      <c r="B132" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="C129" s="30"/>
-      <c r="D129" s="30"/>
-      <c r="E129" s="30"/>
-      <c r="F129" s="30"/>
-      <c r="G129" s="30"/>
-      <c r="H129" s="30"/>
-      <c r="I129" s="31"/>
-      <c r="J129" s="31"/>
-      <c r="K129" s="31"/>
-      <c r="L129" s="31"/>
-      <c r="M129" s="31"/>
-      <c r="N129" s="31"/>
-      <c r="O129" s="31"/>
-      <c r="P129" s="31"/>
-      <c r="Q129" s="31"/>
-      <c r="R129" s="31"/>
-      <c r="S129" s="31"/>
-      <c r="T129" s="31"/>
-    </row>
-    <row r="130" spans="1:20" s="5" customFormat="1">
-      <c r="A130" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B130" s="5" t="s">
+      <c r="C132" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="C130" s="5" t="s">
+      <c r="D132" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="D130" s="5" t="s">
+      <c r="E132" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="E130" s="5" t="s">
+      <c r="F132" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="F130" s="5" t="s">
+      <c r="G132" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="G130" s="5" t="s">
+      <c r="H132" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="H130" s="5" t="s">
+      <c r="I132" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="I130" s="5" t="s">
+      <c r="J132" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="J130" s="5" t="s">
+      <c r="K132" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="K130" s="5" t="s">
+      <c r="L132" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="L130" s="5" t="s">
+      <c r="M132" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="M130" s="5" t="s">
+      <c r="N132" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="N130" s="5" t="s">
+      <c r="O132" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="O130" s="5" t="s">
+      <c r="P132" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="P130" s="5" t="s">
+      <c r="Q132" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="Q130" s="5" t="s">
+      <c r="R132" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="R130" s="5" t="s">
+      <c r="S132" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="S130" s="5" t="s">
+      <c r="T132" s="5" t="s">
         <v>363</v>
-      </c>
-      <c r="T130" s="5" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="131" spans="1:20">
-      <c r="B131" t="s">
-        <v>286</v>
-      </c>
-      <c r="C131" t="s">
-        <v>238</v>
-      </c>
-      <c r="D131" t="s">
-        <v>237</v>
-      </c>
-      <c r="E131" t="s">
-        <v>236</v>
-      </c>
-      <c r="F131" t="s">
-        <v>234</v>
-      </c>
-      <c r="G131" t="s">
-        <v>233</v>
-      </c>
-      <c r="H131" t="s">
-        <v>365</v>
-      </c>
-      <c r="I131" t="s">
-        <v>366</v>
-      </c>
-      <c r="J131" t="s">
-        <v>270</v>
-      </c>
-      <c r="K131" t="s">
-        <v>367</v>
-      </c>
-      <c r="L131" t="s">
-        <v>368</v>
-      </c>
-      <c r="M131" t="s">
-        <v>326</v>
-      </c>
-      <c r="N131" t="s">
-        <v>231</v>
-      </c>
-      <c r="O131" t="s">
-        <v>230</v>
-      </c>
-      <c r="P131" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q131" t="s">
-        <v>229</v>
-      </c>
-      <c r="R131" t="s">
-        <v>266</v>
-      </c>
-      <c r="S131" t="s">
-        <v>248</v>
-      </c>
-      <c r="T131" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="132" spans="1:20">
-      <c r="B132" t="s">
-        <v>226</v>
-      </c>
-      <c r="C132" t="s">
-        <v>251</v>
-      </c>
-      <c r="D132" t="s">
-        <v>250</v>
-      </c>
-      <c r="E132" t="s">
-        <v>249</v>
-      </c>
-      <c r="F132" t="s">
-        <v>369</v>
-      </c>
-      <c r="G132" t="s">
-        <v>247</v>
-      </c>
-      <c r="I132" t="s">
-        <v>370</v>
-      </c>
-      <c r="J132" t="s">
-        <v>283</v>
-      </c>
-      <c r="K132" t="s">
-        <v>371</v>
-      </c>
-      <c r="L132" t="s">
-        <v>372</v>
-      </c>
-      <c r="N132" t="s">
-        <v>245</v>
-      </c>
-      <c r="O132" t="s">
-        <v>244</v>
-      </c>
-      <c r="P132" t="s">
-        <v>308</v>
-      </c>
-      <c r="Q132" t="s">
-        <v>243</v>
-      </c>
-      <c r="R132" t="s">
-        <v>290</v>
-      </c>
-      <c r="S132" t="s">
-        <v>261</v>
-      </c>
-      <c r="T132" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="133" spans="1:20">
       <c r="B133" t="s">
-        <v>240</v>
+        <v>285</v>
       </c>
       <c r="C133" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="D133" t="s">
-        <v>263</v>
+        <v>236</v>
       </c>
       <c r="E133" t="s">
-        <v>262</v>
+        <v>235</v>
       </c>
       <c r="F133" t="s">
-        <v>260</v>
+        <v>233</v>
       </c>
       <c r="G133" t="s">
-        <v>259</v>
+        <v>232</v>
+      </c>
+      <c r="H133" t="s">
+        <v>364</v>
       </c>
       <c r="I133" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J133" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="K133" t="s">
-        <v>374</v>
+        <v>366</v>
+      </c>
+      <c r="L133" t="s">
+        <v>367</v>
+      </c>
+      <c r="M133" t="s">
+        <v>325</v>
       </c>
       <c r="N133" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="O133" t="s">
-        <v>257</v>
+        <v>229</v>
+      </c>
+      <c r="P133" t="s">
+        <v>298</v>
       </c>
       <c r="Q133" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="R133" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="S133" t="s">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="T133" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="134" spans="1:20">
       <c r="B134" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="C134" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="D134" t="s">
-        <v>275</v>
+        <v>249</v>
       </c>
       <c r="E134" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
       <c r="F134" t="s">
-        <v>272</v>
+        <v>368</v>
       </c>
       <c r="G134" t="s">
-        <v>271</v>
+        <v>246</v>
+      </c>
+      <c r="I134" t="s">
+        <v>369</v>
+      </c>
+      <c r="J134" t="s">
+        <v>282</v>
+      </c>
+      <c r="K134" t="s">
+        <v>370</v>
+      </c>
+      <c r="L134" t="s">
+        <v>371</v>
+      </c>
+      <c r="N134" t="s">
+        <v>244</v>
       </c>
       <c r="O134" t="s">
-        <v>269</v>
+        <v>243</v>
+      </c>
+      <c r="P134" t="s">
+        <v>307</v>
       </c>
       <c r="Q134" t="s">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="R134" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="S134" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="T134" t="s">
-        <v>95</v>
+        <v>241</v>
       </c>
     </row>
     <row r="135" spans="1:20">
       <c r="B135" t="s">
-        <v>324</v>
+        <v>239</v>
       </c>
       <c r="C135" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="D135" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="E135" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="F135" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="G135" t="s">
-        <v>284</v>
+        <v>258</v>
+      </c>
+      <c r="I135" t="s">
+        <v>372</v>
+      </c>
+      <c r="J135" t="s">
+        <v>293</v>
+      </c>
+      <c r="K135" t="s">
+        <v>373</v>
+      </c>
+      <c r="N135" t="s">
+        <v>257</v>
       </c>
       <c r="O135" t="s">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="Q135" t="s">
-        <v>281</v>
+        <v>255</v>
       </c>
       <c r="R135" t="s">
-        <v>300</v>
+        <v>253</v>
       </c>
       <c r="S135" t="s">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="T135" t="s">
-        <v>280</v>
+        <v>254</v>
       </c>
     </row>
     <row r="136" spans="1:20">
       <c r="B136" t="s">
-        <v>375</v>
+        <v>252</v>
       </c>
       <c r="C136" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="D136" t="s">
-        <v>239</v>
+        <v>274</v>
       </c>
       <c r="E136" t="s">
-        <v>298</v>
+        <v>273</v>
       </c>
       <c r="F136" t="s">
-        <v>296</v>
+        <v>271</v>
       </c>
       <c r="G136" t="s">
-        <v>295</v>
+        <v>270</v>
+      </c>
+      <c r="O136" t="s">
+        <v>268</v>
       </c>
       <c r="Q136" t="s">
-        <v>293</v>
+        <v>267</v>
       </c>
       <c r="R136" t="s">
-        <v>309</v>
+        <v>266</v>
       </c>
       <c r="S136" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="T136" t="s">
-        <v>292</v>
+        <v>95</v>
       </c>
     </row>
     <row r="137" spans="1:20">
       <c r="B137" t="s">
-        <v>376</v>
+        <v>323</v>
+      </c>
+      <c r="C137" t="s">
+        <v>231</v>
       </c>
       <c r="D137" t="s">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="E137" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="F137" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="G137" t="s">
-        <v>304</v>
+        <v>283</v>
+      </c>
+      <c r="O137" t="s">
+        <v>281</v>
       </c>
       <c r="Q137" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="R137" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="S137" t="s">
-        <v>241</v>
+        <v>296</v>
       </c>
       <c r="T137" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
     </row>
     <row r="138" spans="1:20">
       <c r="B138" t="s">
-        <v>278</v>
+        <v>374</v>
+      </c>
+      <c r="C138" t="s">
+        <v>245</v>
       </c>
       <c r="D138" t="s">
-        <v>265</v>
+        <v>238</v>
+      </c>
+      <c r="E138" t="s">
+        <v>297</v>
+      </c>
+      <c r="F138" t="s">
+        <v>295</v>
       </c>
       <c r="G138" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="Q138" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="R138" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="S138" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="T138" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
     </row>
     <row r="139" spans="1:20">
       <c r="B139" t="s">
+        <v>375</v>
+      </c>
+      <c r="D139" t="s">
+        <v>251</v>
+      </c>
+      <c r="E139" t="s">
+        <v>306</v>
+      </c>
+      <c r="F139" t="s">
+        <v>304</v>
+      </c>
+      <c r="G139" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>302</v>
+      </c>
+      <c r="R139" t="s">
         <v>319</v>
       </c>
-      <c r="D139" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q139" t="s">
-        <v>318</v>
-      </c>
-      <c r="R139" t="s">
-        <v>325</v>
-      </c>
       <c r="S139" t="s">
-        <v>291</v>
+        <v>240</v>
       </c>
       <c r="T139" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
     </row>
     <row r="140" spans="1:20">
       <c r="B140" t="s">
-        <v>323</v>
+        <v>277</v>
       </c>
       <c r="D140" t="s">
-        <v>289</v>
+        <v>264</v>
+      </c>
+      <c r="G140" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>311</v>
       </c>
       <c r="R140" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="S140" t="s">
-        <v>301</v>
+        <v>278</v>
+      </c>
+      <c r="T140" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="141" spans="1:20">
       <c r="B141" t="s">
-        <v>327</v>
+        <v>318</v>
+      </c>
+      <c r="D141" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>317</v>
       </c>
       <c r="R141" t="s">
+        <v>324</v>
+      </c>
+      <c r="S141" t="s">
+        <v>290</v>
+      </c>
+      <c r="T141" t="s">
         <v>321</v>
-      </c>
-      <c r="S141" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="142" spans="1:20">
       <c r="B142" t="s">
-        <v>328</v>
+        <v>322</v>
+      </c>
+      <c r="D142" t="s">
+        <v>288</v>
+      </c>
+      <c r="R142" t="s">
+        <v>315</v>
+      </c>
+      <c r="S142" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="143" spans="1:20">
       <c r="B143" t="s">
-        <v>329</v>
+        <v>326</v>
+      </c>
+      <c r="R143" t="s">
+        <v>320</v>
+      </c>
+      <c r="S143" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="144" spans="1:20">
       <c r="B144" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="145" spans="1:20">
       <c r="B145" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="146" spans="1:20">
       <c r="B146" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="147" spans="1:20" s="6" customFormat="1">
-      <c r="A147" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="147" spans="1:20">
+      <c r="B147" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="148" spans="1:20">
+      <c r="B148" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="149" spans="1:20" s="6" customFormat="1">
+      <c r="A149" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B147" s="6" t="s">
+      <c r="B149" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F149" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="G149" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H149" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="I149" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="J149" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="K149" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="L149" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="C147" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="D147" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="E147" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="F147" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="G147" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="H147" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="I147" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="J147" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="K147" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="L147" s="6" t="s">
+      <c r="M149" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="N149" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="O149" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="P149" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q149" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="R149" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="S149" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="T149" s="6" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="152" spans="1:20">
+      <c r="A152" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="M147" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="N147" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="O147" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="P147" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="Q147" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="R147" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="S147" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="T147" s="6" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="150" spans="1:20" ht="15">
-      <c r="A150" s="7" t="s">
+    </row>
+    <row r="153" spans="1:20">
+      <c r="A153" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B153" s="27" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="151" spans="1:20">
-      <c r="A151" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B151" s="29" t="s">
+      <c r="C153" s="27"/>
+      <c r="D153" s="27"/>
+      <c r="E153" s="27"/>
+      <c r="F153" s="27"/>
+      <c r="G153" s="27"/>
+      <c r="H153" s="27"/>
+      <c r="I153" s="27"/>
+      <c r="J153" s="27"/>
+      <c r="K153" s="27"/>
+      <c r="L153" s="27"/>
+      <c r="M153" s="27"/>
+      <c r="N153" s="27"/>
+    </row>
+    <row r="154" spans="1:20" s="12" customFormat="1">
+      <c r="A154" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B154" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="C151" s="29"/>
-      <c r="D151" s="29"/>
-      <c r="E151" s="29"/>
-      <c r="F151" s="29"/>
-      <c r="G151" s="29"/>
-      <c r="H151" s="29"/>
-      <c r="I151" s="29"/>
-      <c r="J151" s="29"/>
-      <c r="K151" s="29"/>
-      <c r="L151" s="29"/>
-      <c r="M151" s="29"/>
-      <c r="N151" s="29"/>
-    </row>
-    <row r="152" spans="1:20" s="12" customFormat="1" ht="15">
-      <c r="A152" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B152" s="8" t="s">
+      <c r="C154" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="C152" s="8" t="s">
+      <c r="D154" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="D152" s="8" t="s">
+      <c r="E154" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="E152" s="9" t="s">
+      <c r="F154" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="F152" s="10" t="s">
+      <c r="G154" s="11" t="s">
         <v>385</v>
       </c>
-      <c r="G152" s="11" t="s">
+      <c r="H154" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="H152" s="11" t="s">
+      <c r="I154" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="I152" s="11" t="s">
+    </row>
+    <row r="155" spans="1:20" ht="30">
+      <c r="B155" s="13" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="153" spans="1:20" ht="28.5">
-      <c r="B153" s="13" t="s">
+      <c r="C155" t="s">
         <v>389</v>
       </c>
-      <c r="C153" t="s">
+      <c r="D155" t="s">
         <v>390</v>
       </c>
-      <c r="D153" t="s">
+      <c r="E155" t="s">
         <v>391</v>
       </c>
-      <c r="E153" t="s">
+      <c r="F155" s="14" t="s">
         <v>392</v>
       </c>
-      <c r="F153" s="14" t="s">
+      <c r="G155" t="s">
         <v>393</v>
       </c>
-      <c r="G153" t="s">
-        <v>394</v>
-      </c>
-      <c r="H153" s="15" t="s">
+      <c r="H155" t="s">
+        <v>408</v>
+      </c>
+      <c r="I155" s="15" t="s">
         <v>395</v>
-      </c>
-      <c r="I153" s="16" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="154" spans="1:20">
-      <c r="B154" t="s">
-        <v>397</v>
-      </c>
-      <c r="C154" t="s">
-        <v>398</v>
-      </c>
-      <c r="D154" t="s">
-        <v>399</v>
-      </c>
-      <c r="E154" t="s">
-        <v>392</v>
-      </c>
-      <c r="F154" t="s">
-        <v>407</v>
-      </c>
-      <c r="G154" t="s">
-        <v>400</v>
-      </c>
-      <c r="H154" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="I154" s="16" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="155" spans="1:20" ht="28.5">
-      <c r="B155" s="17" t="s">
-        <v>403</v>
-      </c>
-      <c r="C155" s="17" t="s">
-        <v>404</v>
-      </c>
-      <c r="D155" t="s">
-        <v>405</v>
-      </c>
-      <c r="E155" t="s">
-        <v>406</v>
-      </c>
-      <c r="F155" s="14" t="s">
-        <v>415</v>
-      </c>
-      <c r="G155" t="s">
-        <v>408</v>
-      </c>
-      <c r="H155" t="s">
-        <v>409</v>
-      </c>
-      <c r="I155" s="18" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="156" spans="1:20">
       <c r="B156" t="s">
+        <v>396</v>
+      </c>
+      <c r="C156" t="s">
+        <v>397</v>
+      </c>
+      <c r="D156" t="s">
+        <v>398</v>
+      </c>
+      <c r="E156" t="s">
+        <v>391</v>
+      </c>
+      <c r="F156" t="s">
+        <v>406</v>
+      </c>
+      <c r="G156" t="s">
+        <v>399</v>
+      </c>
+      <c r="H156" t="s">
+        <v>416</v>
+      </c>
+      <c r="I156" s="15" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="157" spans="1:20" ht="30">
+      <c r="B157" s="16" t="s">
+        <v>402</v>
+      </c>
+      <c r="C157" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="D157" t="s">
+        <v>404</v>
+      </c>
+      <c r="E157" t="s">
+        <v>405</v>
+      </c>
+      <c r="F157" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="G157" t="s">
+        <v>407</v>
+      </c>
+      <c r="H157" t="s">
+        <v>422</v>
+      </c>
+      <c r="I157" s="17" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="158" spans="1:20">
+      <c r="B158" t="s">
+        <v>410</v>
+      </c>
+      <c r="C158" t="s">
         <v>411</v>
       </c>
-      <c r="C156" t="s">
+      <c r="D158" t="s">
         <v>412</v>
       </c>
-      <c r="D156" t="s">
+      <c r="E158" t="s">
         <v>413</v>
       </c>
-      <c r="E156" t="s">
-        <v>414</v>
-      </c>
-      <c r="F156" s="14" t="s">
-        <v>465</v>
-      </c>
-      <c r="G156" t="s">
-        <v>416</v>
-      </c>
-      <c r="H156" t="s">
+      <c r="F158" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="G158" t="s">
+        <v>415</v>
+      </c>
+      <c r="H158" t="s">
+        <v>428</v>
+      </c>
+      <c r="I158" s="15" t="s">
         <v>417</v>
-      </c>
-      <c r="I156" s="16" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="157" spans="1:20">
-      <c r="B157" t="s">
-        <v>419</v>
-      </c>
-      <c r="C157" t="s">
-        <v>420</v>
-      </c>
-      <c r="E157" t="s">
-        <v>421</v>
-      </c>
-      <c r="F157" t="s">
-        <v>467</v>
-      </c>
-      <c r="G157" t="s">
-        <v>422</v>
-      </c>
-      <c r="H157" t="s">
-        <v>423</v>
-      </c>
-      <c r="I157" s="16" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="158" spans="1:20" ht="15">
-      <c r="B158" t="s">
-        <v>425</v>
-      </c>
-      <c r="C158" t="s">
-        <v>426</v>
-      </c>
-      <c r="E158" t="s">
-        <v>427</v>
-      </c>
-      <c r="F158" t="s">
-        <v>393</v>
-      </c>
-      <c r="G158" s="19"/>
-      <c r="H158" t="s">
-        <v>429</v>
-      </c>
-      <c r="I158" s="16" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="159" spans="1:20">
       <c r="B159" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="C159" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="E159" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="F159" t="s">
-        <v>407</v>
+        <v>466</v>
+      </c>
+      <c r="G159" t="s">
+        <v>421</v>
       </c>
       <c r="H159" t="s">
-        <v>435</v>
-      </c>
-      <c r="I159" s="20" t="s">
-        <v>436</v>
+        <v>434</v>
+      </c>
+      <c r="I159" s="15" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:20">
       <c r="B160" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="C160" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="E160" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="F160" t="s">
-        <v>472</v>
-      </c>
-      <c r="I160" s="20" t="s">
-        <v>440</v>
+        <v>392</v>
+      </c>
+      <c r="G160" s="18"/>
+      <c r="I160" s="15" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="161" spans="2:9">
       <c r="B161" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C161" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="E161" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="F161" t="s">
-        <v>415</v>
-      </c>
-      <c r="I161" s="16" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="162" spans="2:9" ht="28.5">
-      <c r="B162" s="14" t="s">
-        <v>446</v>
+        <v>406</v>
+      </c>
+      <c r="I161" s="19" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="162" spans="2:9">
+      <c r="B162" t="s">
+        <v>396</v>
       </c>
       <c r="C162" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="E162" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="F162" t="s">
-        <v>428</v>
-      </c>
-      <c r="I162" s="16" t="s">
-        <v>450</v>
+        <v>471</v>
+      </c>
+      <c r="I162" s="19" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="163" spans="2:9">
       <c r="B163" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="C163" t="s">
-        <v>432</v>
+        <v>441</v>
+      </c>
+      <c r="E163" t="s">
+        <v>442</v>
       </c>
       <c r="F163" t="s">
-        <v>434</v>
-      </c>
-      <c r="I163" s="16" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="164" spans="2:9">
-      <c r="B164" t="s">
-        <v>397</v>
+        <v>414</v>
+      </c>
+      <c r="I163" s="15" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="164" spans="2:9" ht="30">
+      <c r="B164" s="14" t="s">
+        <v>445</v>
       </c>
       <c r="C164" t="s">
-        <v>454</v>
+        <v>446</v>
+      </c>
+      <c r="E164" t="s">
+        <v>447</v>
       </c>
       <c r="F164" t="s">
-        <v>439</v>
-      </c>
-      <c r="I164" s="16" t="s">
-        <v>456</v>
+        <v>427</v>
+      </c>
+      <c r="I164" s="15" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="165" spans="2:9">
       <c r="B165" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="C165" t="s">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="F165" t="s">
-        <v>444</v>
-      </c>
-      <c r="I165" t="s">
-        <v>642</v>
+        <v>433</v>
+      </c>
+      <c r="I165" s="15" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="166" spans="2:9">
       <c r="B166" t="s">
-        <v>460</v>
+        <v>396</v>
       </c>
       <c r="C166" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F166" t="s">
-        <v>449</v>
+        <v>438</v>
+      </c>
+      <c r="I166" s="15" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="167" spans="2:9">
       <c r="B167" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="C167" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="F167" t="s">
-        <v>452</v>
+        <v>443</v>
+      </c>
+      <c r="I167" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="168" spans="2:9">
       <c r="B168" t="s">
-        <v>411</v>
+        <v>459</v>
       </c>
       <c r="C168" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="F168" t="s">
-        <v>455</v>
+        <v>448</v>
+      </c>
+      <c r="I168" s="30" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="169" spans="2:9">
       <c r="B169" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C169" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="F169" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="170" spans="2:9" ht="15">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="170" spans="2:9">
       <c r="B170" t="s">
-        <v>470</v>
-      </c>
-      <c r="C170" s="21" t="s">
-        <v>471</v>
+        <v>410</v>
+      </c>
+      <c r="C170" t="s">
+        <v>465</v>
       </c>
       <c r="F170" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="171" spans="2:9">
       <c r="B171" t="s">
-        <v>419</v>
+        <v>467</v>
       </c>
       <c r="C171" t="s">
-        <v>493</v>
+        <v>468</v>
+      </c>
+      <c r="F171" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="172" spans="2:9">
       <c r="B172" t="s">
-        <v>473</v>
-      </c>
-      <c r="C172" t="s">
-        <v>641</v>
+        <v>469</v>
+      </c>
+      <c r="C172" s="20" t="s">
+        <v>470</v>
+      </c>
+      <c r="F172" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="173" spans="2:9">
       <c r="B173" t="s">
-        <v>474</v>
+        <v>418</v>
+      </c>
+      <c r="C173" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="174" spans="2:9">
       <c r="B174" t="s">
-        <v>475</v>
+        <v>472</v>
+      </c>
+      <c r="C174" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="175" spans="2:9">
       <c r="B175" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="176" spans="2:9">
+      <c r="B176" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="177" spans="1:20">
+      <c r="B177" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="178" spans="1:20">
+      <c r="B178" s="21" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="176" spans="2:9">
-      <c r="B176" s="22" t="s">
+    <row r="179" spans="1:20">
+      <c r="A179" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B179" s="22" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="177" spans="1:20" ht="15">
-      <c r="A177" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B177" s="23" t="s">
+      <c r="C179" s="22" t="s">
         <v>478</v>
       </c>
-      <c r="C177" s="23" t="s">
+      <c r="D179" s="22" t="s">
         <v>479</v>
       </c>
-      <c r="D177" s="23" t="s">
+      <c r="E179" s="23" t="s">
         <v>480</v>
       </c>
-      <c r="E177" s="24" t="s">
+      <c r="F179" s="24" t="s">
         <v>481</v>
       </c>
-      <c r="F177" s="25" t="s">
+      <c r="G179" s="22" t="s">
         <v>482</v>
       </c>
-      <c r="G177" s="23" t="s">
+      <c r="H179" s="22" t="s">
         <v>483</v>
       </c>
-      <c r="H177" s="23" t="s">
+      <c r="I179" s="22" t="s">
         <v>484</v>
       </c>
-      <c r="I177" s="23" t="s">
+    </row>
+    <row r="181" spans="1:20">
+      <c r="A181" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B181" s="28" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="179" spans="1:20" ht="15">
-      <c r="A179" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B179" s="30" t="s">
+      <c r="C181" s="28"/>
+      <c r="D181" s="28"/>
+      <c r="E181" s="28"/>
+      <c r="F181" s="28"/>
+      <c r="G181" s="28"/>
+      <c r="H181" s="28"/>
+      <c r="I181" s="29"/>
+      <c r="J181" s="29"/>
+      <c r="K181" s="29"/>
+      <c r="L181" s="29"/>
+      <c r="M181" s="29"/>
+      <c r="N181" s="29"/>
+      <c r="O181" s="29"/>
+      <c r="P181" s="29"/>
+      <c r="Q181" s="29"/>
+      <c r="R181" s="29"/>
+      <c r="S181" s="29"/>
+      <c r="T181" s="29"/>
+    </row>
+    <row r="182" spans="1:20" s="5" customFormat="1">
+      <c r="A182" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B182" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="C179" s="30"/>
-      <c r="D179" s="30"/>
-      <c r="E179" s="30"/>
-      <c r="F179" s="30"/>
-      <c r="G179" s="30"/>
-      <c r="H179" s="30"/>
-      <c r="I179" s="31"/>
-      <c r="J179" s="31"/>
-      <c r="K179" s="31"/>
-      <c r="L179" s="31"/>
-      <c r="M179" s="31"/>
-      <c r="N179" s="31"/>
-      <c r="O179" s="31"/>
-      <c r="P179" s="31"/>
-      <c r="Q179" s="31"/>
-      <c r="R179" s="31"/>
-      <c r="S179" s="31"/>
-      <c r="T179" s="31"/>
-    </row>
-    <row r="180" spans="1:20" s="5" customFormat="1">
-      <c r="A180" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B180" s="5" t="s">
+      <c r="C182" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="C180" s="5" t="s">
+      <c r="D182" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="D180" s="5" t="s">
+      <c r="E182" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="E180" s="5" t="s">
+      <c r="F182" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="G182" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="F180" s="5" t="s">
+      <c r="H182" s="5" t="s">
         <v>623</v>
-      </c>
-      <c r="G180" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="H180" s="5" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="181" spans="1:20">
-      <c r="B181" t="s">
-        <v>390</v>
-      </c>
-      <c r="C181" t="s">
-        <v>389</v>
-      </c>
-      <c r="D181" t="s">
-        <v>391</v>
-      </c>
-      <c r="E181" t="s">
-        <v>394</v>
-      </c>
-      <c r="F181" t="s">
-        <v>393</v>
-      </c>
-      <c r="G181" t="s">
-        <v>401</v>
-      </c>
-      <c r="H181" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="182" spans="1:20">
-      <c r="B182" t="s">
-        <v>398</v>
-      </c>
-      <c r="C182" t="s">
-        <v>403</v>
-      </c>
-      <c r="D182" t="s">
-        <v>405</v>
-      </c>
-      <c r="E182" t="s">
-        <v>408</v>
-      </c>
-      <c r="F182" t="s">
-        <v>407</v>
-      </c>
-      <c r="G182" t="s">
-        <v>395</v>
-      </c>
-      <c r="H182" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="183" spans="1:20">
       <c r="B183" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="C183" t="s">
-        <v>411</v>
+        <v>388</v>
       </c>
       <c r="D183" t="s">
-        <v>492</v>
+        <v>390</v>
       </c>
       <c r="E183" t="s">
+        <v>393</v>
+      </c>
+      <c r="F183" t="s">
+        <v>392</v>
+      </c>
+      <c r="G183" t="s">
         <v>400</v>
       </c>
-      <c r="F183" t="s">
-        <v>415</v>
-      </c>
-      <c r="G183" t="s">
-        <v>409</v>
-      </c>
       <c r="H183" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
     </row>
     <row r="184" spans="1:20">
       <c r="B184" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="C184" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="D184" t="s">
-        <v>634</v>
+        <v>404</v>
       </c>
       <c r="E184" t="s">
-        <v>493</v>
+        <v>407</v>
       </c>
       <c r="F184" t="s">
-        <v>465</v>
+        <v>406</v>
       </c>
       <c r="G184" t="s">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="H184" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
     </row>
     <row r="185" spans="1:20">
       <c r="B185" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="C185" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="D185" t="s">
-        <v>633</v>
+        <v>491</v>
       </c>
       <c r="E185" t="s">
-        <v>422</v>
+        <v>399</v>
       </c>
       <c r="F185" t="s">
-        <v>467</v>
+        <v>414</v>
       </c>
       <c r="G185" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="H185" t="s">
-        <v>416</v>
+        <v>391</v>
       </c>
     </row>
     <row r="186" spans="1:20">
       <c r="B186" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="C186" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="D186" t="s">
-        <v>413</v>
+        <v>633</v>
       </c>
       <c r="E186" t="s">
-        <v>420</v>
+        <v>492</v>
       </c>
       <c r="F186" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
       <c r="G186" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="H186" t="s">
-        <v>421</v>
+        <v>405</v>
       </c>
     </row>
     <row r="187" spans="1:20">
       <c r="B187" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="C187" t="s">
-        <v>441</v>
+        <v>424</v>
+      </c>
+      <c r="D187" t="s">
+        <v>632</v>
+      </c>
+      <c r="E187" t="s">
+        <v>421</v>
       </c>
       <c r="F187" t="s">
-        <v>407</v>
+        <v>466</v>
       </c>
       <c r="G187" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="H187" t="s">
-        <v>438</v>
+        <v>415</v>
       </c>
     </row>
     <row r="188" spans="1:20">
       <c r="B188" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="C188" t="s">
-        <v>463</v>
+        <v>430</v>
+      </c>
+      <c r="D188" t="s">
+        <v>412</v>
+      </c>
+      <c r="E188" t="s">
+        <v>419</v>
       </c>
       <c r="F188" t="s">
-        <v>472</v>
+        <v>392</v>
+      </c>
+      <c r="G188" t="s">
+        <v>428</v>
       </c>
       <c r="H188" t="s">
-        <v>443</v>
+        <v>420</v>
       </c>
     </row>
     <row r="189" spans="1:20">
       <c r="B189" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="C189" t="s">
-        <v>411</v>
+        <v>440</v>
       </c>
       <c r="F189" t="s">
-        <v>415</v>
+        <v>406</v>
+      </c>
+      <c r="G189" t="s">
+        <v>434</v>
       </c>
       <c r="H189" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="190" spans="1:20">
       <c r="B190" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="C190" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="F190" t="s">
-        <v>428</v>
+        <v>471</v>
       </c>
       <c r="H190" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
     </row>
     <row r="191" spans="1:20">
       <c r="B191" t="s">
+        <v>441</v>
+      </c>
+      <c r="C191" t="s">
+        <v>410</v>
+      </c>
+      <c r="F191" t="s">
+        <v>414</v>
+      </c>
+      <c r="H191" t="s">
         <v>432</v>
-      </c>
-      <c r="C191" t="s">
-        <v>470</v>
-      </c>
-      <c r="F191" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="192" spans="1:20">
       <c r="B192" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C192" t="s">
-        <v>419</v>
+        <v>467</v>
       </c>
       <c r="F192" t="s">
-        <v>439</v>
+        <v>427</v>
+      </c>
+      <c r="H192" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="193" spans="2:6">
       <c r="B193" t="s">
+        <v>431</v>
+      </c>
+      <c r="C193" t="s">
         <v>469</v>
       </c>
-      <c r="C193" t="s">
-        <v>473</v>
-      </c>
       <c r="F193" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
     </row>
     <row r="194" spans="2:6">
       <c r="B194" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C194" t="s">
-        <v>474</v>
+        <v>418</v>
       </c>
       <c r="F194" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
     </row>
     <row r="195" spans="2:6">
       <c r="B195" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="C195" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F195" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
     </row>
     <row r="196" spans="2:6">
       <c r="B196" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="C196" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F196" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
     </row>
     <row r="197" spans="2:6">
       <c r="B197" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C197" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F197" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
     </row>
     <row r="198" spans="2:6">
       <c r="B198" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C198" t="s">
-        <v>413</v>
+        <v>475</v>
       </c>
       <c r="F198" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="199" spans="2:6">
       <c r="B199" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="C199" t="s">
-        <v>402</v>
+        <v>476</v>
       </c>
       <c r="F199" t="s">
-        <v>399</v>
+        <v>458</v>
       </c>
     </row>
     <row r="200" spans="2:6">
       <c r="B200" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="C200" t="s">
-        <v>410</v>
+        <v>412</v>
+      </c>
+      <c r="F200" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="201" spans="2:6">
       <c r="B201" t="s">
-        <v>397</v>
+        <v>445</v>
       </c>
       <c r="C201" t="s">
-        <v>418</v>
+        <v>401</v>
+      </c>
+      <c r="F201" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="202" spans="2:6">
       <c r="B202" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="C202" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
     </row>
     <row r="203" spans="2:6">
       <c r="B203" t="s">
-        <v>460</v>
+        <v>396</v>
       </c>
       <c r="C203" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
     </row>
     <row r="204" spans="2:6">
       <c r="B204" t="s">
-        <v>397</v>
+        <v>456</v>
       </c>
       <c r="C204" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
     </row>
     <row r="205" spans="2:6">
+      <c r="B205" t="s">
+        <v>459</v>
+      </c>
       <c r="C205" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
     </row>
     <row r="206" spans="2:6">
+      <c r="B206" t="s">
+        <v>396</v>
+      </c>
       <c r="C206" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
     </row>
     <row r="207" spans="2:6">
       <c r="C207" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
     </row>
     <row r="208" spans="2:6">
       <c r="C208" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
     </row>
     <row r="209" spans="1:14">
       <c r="C209" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
     </row>
     <row r="210" spans="1:14">
       <c r="C210" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="211" spans="1:14" s="6" customFormat="1">
-      <c r="A211" s="6" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14">
+      <c r="C211" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14">
+      <c r="C212" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" s="6" customFormat="1">
+      <c r="A213" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B211" s="6" t="s">
+      <c r="B213" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="C213" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="D213" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="E213" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="F213" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="G213" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="H213" s="6" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14">
+      <c r="A215" s="7" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14">
+      <c r="A216" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B216" s="27" t="s">
         <v>494</v>
       </c>
-      <c r="C211" s="6" t="s">
-        <v>494</v>
-      </c>
-      <c r="D211" s="6" t="s">
-        <v>494</v>
-      </c>
-      <c r="E211" s="6" t="s">
-        <v>494</v>
-      </c>
-      <c r="F211" s="6" t="s">
-        <v>494</v>
-      </c>
-      <c r="G211" s="6" t="s">
-        <v>494</v>
-      </c>
-      <c r="H211" s="6" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="213" spans="1:14" ht="15">
-      <c r="A213" s="7" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="214" spans="1:14">
-      <c r="A214" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B214" s="29" t="s">
+      <c r="C216" s="27"/>
+      <c r="D216" s="27"/>
+      <c r="E216" s="27"/>
+      <c r="F216" s="27"/>
+      <c r="G216" s="27"/>
+      <c r="H216" s="27"/>
+      <c r="I216" s="27"/>
+      <c r="J216" s="27"/>
+      <c r="K216" s="27"/>
+      <c r="L216" s="27"/>
+      <c r="M216" s="27"/>
+      <c r="N216" s="27"/>
+    </row>
+    <row r="217" spans="1:14" s="3" customFormat="1">
+      <c r="A217" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B217" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="C214" s="29"/>
-      <c r="D214" s="29"/>
-      <c r="E214" s="29"/>
-      <c r="F214" s="29"/>
-      <c r="G214" s="29"/>
-      <c r="H214" s="29"/>
-      <c r="I214" s="29"/>
-      <c r="J214" s="29"/>
-      <c r="K214" s="29"/>
-      <c r="L214" s="29"/>
-      <c r="M214" s="29"/>
-      <c r="N214" s="29"/>
-    </row>
-    <row r="215" spans="1:14" s="3" customFormat="1">
-      <c r="A215" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B215" s="3" t="s">
+      <c r="C217" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="C215" s="3" t="s">
+      <c r="D217" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="D215" s="3" t="s">
+      <c r="E217" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="E215" s="3" t="s">
+      <c r="F217" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="F215" s="3" t="s">
+      <c r="G217" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="G215" s="3" t="s">
+      <c r="H217" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="H215" s="3" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="216" spans="1:14" ht="15">
-      <c r="B216" t="s">
-        <v>555</v>
-      </c>
-      <c r="C216" t="s">
-        <v>509</v>
-      </c>
-      <c r="D216" t="s">
-        <v>538</v>
-      </c>
-      <c r="E216" t="s">
-        <v>547</v>
-      </c>
-      <c r="F216" t="s">
-        <v>506</v>
-      </c>
-      <c r="G216" t="s">
-        <v>507</v>
-      </c>
-      <c r="H216" s="21" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="217" spans="1:14">
-      <c r="B217" t="s">
-        <v>543</v>
-      </c>
-      <c r="C217" t="s">
-        <v>515</v>
-      </c>
-      <c r="D217" t="s">
-        <v>504</v>
-      </c>
-      <c r="E217" t="s">
-        <v>505</v>
-      </c>
-      <c r="G217" t="s">
-        <v>512</v>
-      </c>
-      <c r="H217" t="s">
-        <v>517</v>
+      <c r="I217" s="3" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="218" spans="1:14">
       <c r="B218" t="s">
-        <v>625</v>
+        <v>554</v>
       </c>
       <c r="C218" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="D218" t="s">
-        <v>627</v>
+        <v>537</v>
       </c>
       <c r="E218" t="s">
-        <v>628</v>
-      </c>
-      <c r="H218" t="s">
-        <v>522</v>
+        <v>546</v>
+      </c>
+      <c r="F218" t="s">
+        <v>505</v>
+      </c>
+      <c r="G218" t="s">
+        <v>506</v>
+      </c>
+      <c r="H218" s="20" t="s">
+        <v>512</v>
+      </c>
+      <c r="I218" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="219" spans="1:14">
       <c r="B219" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="C219" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="D219" t="s">
-        <v>584</v>
+        <v>503</v>
       </c>
       <c r="E219" t="s">
-        <v>629</v>
+        <v>504</v>
+      </c>
+      <c r="G219" t="s">
+        <v>511</v>
       </c>
       <c r="H219" t="s">
-        <v>525</v>
+        <v>516</v>
+      </c>
+      <c r="I219" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="220" spans="1:14">
       <c r="B220" t="s">
+        <v>624</v>
+      </c>
+      <c r="C220" t="s">
         <v>518</v>
       </c>
-      <c r="C220" t="s">
-        <v>527</v>
-      </c>
       <c r="D220" t="s">
-        <v>510</v>
+        <v>626</v>
       </c>
       <c r="E220" t="s">
-        <v>516</v>
+        <v>627</v>
       </c>
       <c r="H220" t="s">
-        <v>535</v>
-      </c>
-      <c r="K220" s="28"/>
+        <v>521</v>
+      </c>
     </row>
     <row r="221" spans="1:14">
       <c r="B221" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C221" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="D221" t="s">
-        <v>99</v>
+        <v>583</v>
       </c>
       <c r="E221" t="s">
-        <v>589</v>
+        <v>628</v>
       </c>
       <c r="H221" t="s">
-        <v>539</v>
-      </c>
-      <c r="K221" s="27"/>
+        <v>524</v>
+      </c>
     </row>
     <row r="222" spans="1:14">
       <c r="B222" t="s">
-        <v>531</v>
+        <v>517</v>
       </c>
       <c r="C222" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="D222" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="E222" t="s">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="H222" t="s">
-        <v>508</v>
-      </c>
-      <c r="K222" s="28"/>
+        <v>534</v>
+      </c>
+      <c r="K222" s="26"/>
     </row>
     <row r="223" spans="1:14">
       <c r="B223" t="s">
-        <v>573</v>
+        <v>555</v>
       </c>
       <c r="C223" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="D223" t="s">
-        <v>528</v>
+        <v>99</v>
       </c>
       <c r="E223" t="s">
-        <v>534</v>
+        <v>588</v>
       </c>
       <c r="H223" t="s">
-        <v>591</v>
-      </c>
-      <c r="K223" s="27"/>
+        <v>538</v>
+      </c>
+      <c r="K223" s="25"/>
     </row>
     <row r="224" spans="1:14">
       <c r="B224" t="s">
+        <v>530</v>
+      </c>
+      <c r="C224" t="s">
+        <v>536</v>
+      </c>
+      <c r="D224" t="s">
+        <v>519</v>
+      </c>
+      <c r="E224" t="s">
+        <v>528</v>
+      </c>
+      <c r="H224" t="s">
+        <v>507</v>
+      </c>
+      <c r="K224" s="26"/>
+    </row>
+    <row r="225" spans="1:11">
+      <c r="B225" t="s">
+        <v>572</v>
+      </c>
+      <c r="C225" t="s">
+        <v>540</v>
+      </c>
+      <c r="D225" t="s">
+        <v>527</v>
+      </c>
+      <c r="E225" t="s">
+        <v>533</v>
+      </c>
+      <c r="H225" t="s">
+        <v>590</v>
+      </c>
+      <c r="K225" s="25"/>
+    </row>
+    <row r="226" spans="1:11">
+      <c r="B226" t="s">
+        <v>549</v>
+      </c>
+      <c r="C226" t="s">
+        <v>543</v>
+      </c>
+      <c r="D226" t="s">
+        <v>532</v>
+      </c>
+      <c r="E226" t="s">
+        <v>548</v>
+      </c>
+      <c r="H226" t="s">
+        <v>629</v>
+      </c>
+      <c r="K226" s="26"/>
+    </row>
+    <row r="227" spans="1:11">
+      <c r="B227" t="s">
+        <v>547</v>
+      </c>
+      <c r="C227" t="s">
+        <v>545</v>
+      </c>
+      <c r="D227" t="s">
+        <v>523</v>
+      </c>
+      <c r="E227" t="s">
+        <v>520</v>
+      </c>
+      <c r="H227" t="s">
+        <v>581</v>
+      </c>
+      <c r="K227" s="25"/>
+    </row>
+    <row r="228" spans="1:11">
+      <c r="B228" t="s">
+        <v>535</v>
+      </c>
+      <c r="C228" t="s">
+        <v>540</v>
+      </c>
+      <c r="E228" t="s">
+        <v>541</v>
+      </c>
+      <c r="H228" t="s">
+        <v>529</v>
+      </c>
+      <c r="K228" s="26"/>
+    </row>
+    <row r="229" spans="1:11">
+      <c r="B229" t="s">
+        <v>557</v>
+      </c>
+      <c r="C229" t="s">
+        <v>502</v>
+      </c>
+      <c r="E229" t="s">
+        <v>544</v>
+      </c>
+      <c r="K229" s="25"/>
+    </row>
+    <row r="230" spans="1:11">
+      <c r="B230" t="s">
+        <v>525</v>
+      </c>
+      <c r="C230" t="s">
+        <v>625</v>
+      </c>
+      <c r="K230" s="26"/>
+    </row>
+    <row r="231" spans="1:11">
+      <c r="B231" t="s">
+        <v>553</v>
+      </c>
+      <c r="C231" t="s">
+        <v>576</v>
+      </c>
+      <c r="K231" s="25"/>
+    </row>
+    <row r="232" spans="1:11">
+      <c r="B232" t="s">
         <v>550</v>
       </c>
-      <c r="C224" t="s">
-        <v>544</v>
-      </c>
-      <c r="D224" t="s">
+      <c r="K232" s="26"/>
+    </row>
+    <row r="233" spans="1:11">
+      <c r="B233" t="s">
+        <v>539</v>
+      </c>
+      <c r="K233" s="25"/>
+    </row>
+    <row r="234" spans="1:11">
+      <c r="B234" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11">
+      <c r="B235" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11">
+      <c r="B236" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" s="4" customFormat="1">
+      <c r="A239" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="D239" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="E239" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="F239" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="G239" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="H239" s="4" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="241" spans="1:20">
+      <c r="A241" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B241" s="28" t="s">
+        <v>565</v>
+      </c>
+      <c r="C241" s="28"/>
+      <c r="D241" s="28"/>
+      <c r="E241" s="28"/>
+      <c r="F241" s="28"/>
+      <c r="G241" s="28"/>
+      <c r="H241" s="28"/>
+      <c r="I241" s="29"/>
+      <c r="J241" s="29"/>
+      <c r="K241" s="29"/>
+      <c r="L241" s="29"/>
+      <c r="M241" s="29"/>
+      <c r="N241" s="29"/>
+      <c r="O241" s="29"/>
+      <c r="P241" s="29"/>
+      <c r="Q241" s="29"/>
+      <c r="R241" s="29"/>
+      <c r="S241" s="29"/>
+      <c r="T241" s="29"/>
+    </row>
+    <row r="242" spans="1:20" s="5" customFormat="1">
+      <c r="A242" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="C242" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="D242" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="E242" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="F242" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="G242" s="5" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="243" spans="1:20">
+      <c r="B243" t="s">
+        <v>556</v>
+      </c>
+      <c r="C243" t="s">
+        <v>554</v>
+      </c>
+      <c r="D243" t="s">
+        <v>546</v>
+      </c>
+      <c r="E243" t="s">
+        <v>575</v>
+      </c>
+      <c r="F243" t="s">
+        <v>537</v>
+      </c>
+      <c r="G243" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="244" spans="1:20">
+      <c r="B244" t="s">
+        <v>636</v>
+      </c>
+      <c r="C244" t="s">
+        <v>542</v>
+      </c>
+      <c r="D244" t="s">
+        <v>577</v>
+      </c>
+      <c r="E244" t="s">
+        <v>578</v>
+      </c>
+      <c r="F244" t="s">
+        <v>503</v>
+      </c>
+      <c r="G244" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="245" spans="1:20">
+      <c r="B245" t="s">
+        <v>507</v>
+      </c>
+      <c r="C245" t="s">
+        <v>624</v>
+      </c>
+      <c r="D245" t="s">
+        <v>504</v>
+      </c>
+      <c r="E245" t="s">
+        <v>580</v>
+      </c>
+      <c r="F245" t="s">
+        <v>626</v>
+      </c>
+      <c r="G245" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="246" spans="1:20">
+      <c r="B246" t="s">
+        <v>590</v>
+      </c>
+      <c r="C246" t="s">
+        <v>552</v>
+      </c>
+      <c r="D246" t="s">
+        <v>574</v>
+      </c>
+      <c r="F246" t="s">
+        <v>583</v>
+      </c>
+      <c r="G246" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="247" spans="1:20">
+      <c r="B247" t="s">
+        <v>524</v>
+      </c>
+      <c r="C247" t="s">
+        <v>517</v>
+      </c>
+      <c r="D247" t="s">
+        <v>627</v>
+      </c>
+      <c r="F247" t="s">
+        <v>582</v>
+      </c>
+      <c r="G247" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="248" spans="1:20">
+      <c r="B248" t="s">
+        <v>629</v>
+      </c>
+      <c r="C248" t="s">
+        <v>555</v>
+      </c>
+      <c r="D248" t="s">
+        <v>584</v>
+      </c>
+      <c r="F248" t="s">
+        <v>509</v>
+      </c>
+      <c r="G248" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="249" spans="1:20">
+      <c r="B249" t="s">
+        <v>587</v>
+      </c>
+      <c r="C249" t="s">
+        <v>530</v>
+      </c>
+      <c r="D249" t="s">
+        <v>628</v>
+      </c>
+      <c r="F249" t="s">
+        <v>99</v>
+      </c>
+      <c r="G249" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="250" spans="1:20">
+      <c r="B250" t="s">
+        <v>573</v>
+      </c>
+      <c r="C250" t="s">
+        <v>572</v>
+      </c>
+      <c r="D250" t="s">
+        <v>630</v>
+      </c>
+      <c r="F250" t="s">
+        <v>519</v>
+      </c>
+      <c r="G250" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="251" spans="1:20">
+      <c r="B251" t="s">
+        <v>538</v>
+      </c>
+      <c r="C251" t="s">
+        <v>549</v>
+      </c>
+      <c r="D251" t="s">
+        <v>592</v>
+      </c>
+      <c r="F251" t="s">
+        <v>579</v>
+      </c>
+      <c r="G251" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="252" spans="1:20">
+      <c r="B252" t="s">
+        <v>585</v>
+      </c>
+      <c r="C252" t="s">
+        <v>547</v>
+      </c>
+      <c r="D252" t="s">
+        <v>586</v>
+      </c>
+      <c r="F252" t="s">
+        <v>527</v>
+      </c>
+      <c r="G252" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="253" spans="1:20">
+      <c r="B253" t="s">
+        <v>516</v>
+      </c>
+      <c r="C253" t="s">
+        <v>535</v>
+      </c>
+      <c r="D253" t="s">
+        <v>515</v>
+      </c>
+      <c r="F253" t="s">
+        <v>532</v>
+      </c>
+      <c r="G253" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="254" spans="1:20">
+      <c r="B254" t="s">
+        <v>510</v>
+      </c>
+      <c r="C254" t="s">
+        <v>557</v>
+      </c>
+      <c r="D254" t="s">
+        <v>588</v>
+      </c>
+      <c r="F254" t="s">
+        <v>523</v>
+      </c>
+      <c r="G254" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="255" spans="1:20">
+      <c r="B255" t="s">
+        <v>512</v>
+      </c>
+      <c r="C255" t="s">
+        <v>525</v>
+      </c>
+      <c r="D255" t="s">
+        <v>528</v>
+      </c>
+      <c r="G255" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="256" spans="1:20">
+      <c r="B256" t="s">
+        <v>521</v>
+      </c>
+      <c r="C256" t="s">
+        <v>553</v>
+      </c>
+      <c r="D256" t="s">
         <v>533</v>
       </c>
-      <c r="E224" t="s">
-        <v>549</v>
-      </c>
-      <c r="F224" s="26"/>
-      <c r="H224" t="s">
-        <v>630</v>
-      </c>
-      <c r="K224" s="28"/>
-    </row>
-    <row r="225" spans="1:20">
-      <c r="B225" t="s">
+    </row>
+    <row r="257" spans="1:8">
+      <c r="B257" t="s">
+        <v>581</v>
+      </c>
+      <c r="C257" t="s">
+        <v>550</v>
+      </c>
+      <c r="D257" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8">
+      <c r="B258" t="s">
+        <v>529</v>
+      </c>
+      <c r="C258" t="s">
+        <v>539</v>
+      </c>
+      <c r="D258" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8">
+      <c r="C259" t="s">
+        <v>551</v>
+      </c>
+      <c r="D259" t="s">
         <v>548</v>
       </c>
-      <c r="C225" t="s">
-        <v>546</v>
-      </c>
-      <c r="D225" t="s">
-        <v>524</v>
-      </c>
-      <c r="E225" t="s">
-        <v>521</v>
-      </c>
-      <c r="H225" t="s">
-        <v>582</v>
-      </c>
-      <c r="K225" s="27"/>
-    </row>
-    <row r="226" spans="1:20">
-      <c r="B226" t="s">
-        <v>536</v>
-      </c>
-      <c r="C226" t="s">
-        <v>541</v>
-      </c>
-      <c r="E226" t="s">
-        <v>542</v>
-      </c>
-      <c r="H226" t="s">
-        <v>530</v>
-      </c>
-      <c r="K226" s="28"/>
-    </row>
-    <row r="227" spans="1:20">
-      <c r="B227" t="s">
-        <v>558</v>
-      </c>
-      <c r="C227" t="s">
-        <v>503</v>
-      </c>
-      <c r="E227" t="s">
-        <v>545</v>
-      </c>
-      <c r="K227" s="27"/>
-    </row>
-    <row r="228" spans="1:20">
-      <c r="B228" t="s">
-        <v>526</v>
-      </c>
-      <c r="C228" t="s">
-        <v>626</v>
-      </c>
-      <c r="K228" s="28"/>
-    </row>
-    <row r="229" spans="1:20">
-      <c r="B229" t="s">
-        <v>554</v>
-      </c>
-      <c r="C229" t="s">
-        <v>577</v>
-      </c>
-      <c r="K229" s="27"/>
-    </row>
-    <row r="230" spans="1:20">
-      <c r="B230" t="s">
-        <v>551</v>
-      </c>
-      <c r="K230" s="28"/>
-    </row>
-    <row r="231" spans="1:20">
-      <c r="B231" t="s">
-        <v>540</v>
-      </c>
-      <c r="K231" s="27"/>
-    </row>
-    <row r="232" spans="1:20">
-      <c r="B232" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="233" spans="1:20">
-      <c r="B233" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="234" spans="1:20">
-      <c r="B234" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="237" spans="1:20" s="4" customFormat="1">
-      <c r="A237" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B237" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="C237" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="D237" s="4" t="s">
-        <v>561</v>
-      </c>
-      <c r="E237" s="4" t="s">
-        <v>562</v>
-      </c>
-      <c r="F237" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="G237" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="H237" s="4" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="239" spans="1:20" ht="15">
-      <c r="A239" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B239" s="30" t="s">
-        <v>566</v>
-      </c>
-      <c r="C239" s="30"/>
-      <c r="D239" s="30"/>
-      <c r="E239" s="30"/>
-      <c r="F239" s="30"/>
-      <c r="G239" s="30"/>
-      <c r="H239" s="30"/>
-      <c r="I239" s="31"/>
-      <c r="J239" s="31"/>
-      <c r="K239" s="31"/>
-      <c r="L239" s="31"/>
-      <c r="M239" s="31"/>
-      <c r="N239" s="31"/>
-      <c r="O239" s="31"/>
-      <c r="P239" s="31"/>
-      <c r="Q239" s="31"/>
-      <c r="R239" s="31"/>
-      <c r="S239" s="31"/>
-      <c r="T239" s="31"/>
-    </row>
-    <row r="240" spans="1:20" s="5" customFormat="1">
-      <c r="A240" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B240" s="5" t="s">
-        <v>568</v>
-      </c>
-      <c r="C240" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="D240" s="5" t="s">
-        <v>569</v>
-      </c>
-      <c r="E240" s="5" t="s">
-        <v>570</v>
-      </c>
-      <c r="F240" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="G240" s="5" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="241" spans="2:7">
-      <c r="B241" t="s">
-        <v>557</v>
-      </c>
-      <c r="C241" t="s">
-        <v>555</v>
-      </c>
-      <c r="D241" t="s">
-        <v>547</v>
-      </c>
-      <c r="E241" t="s">
-        <v>576</v>
-      </c>
-      <c r="F241" t="s">
-        <v>538</v>
-      </c>
-      <c r="G241" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="242" spans="2:7">
-      <c r="B242" t="s">
-        <v>637</v>
-      </c>
-      <c r="C242" t="s">
-        <v>543</v>
-      </c>
-      <c r="D242" t="s">
-        <v>578</v>
-      </c>
-      <c r="E242" t="s">
-        <v>579</v>
-      </c>
-      <c r="F242" t="s">
-        <v>504</v>
-      </c>
-      <c r="G242" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="243" spans="2:7">
-      <c r="B243" t="s">
-        <v>508</v>
-      </c>
-      <c r="C243" t="s">
-        <v>625</v>
-      </c>
-      <c r="D243" t="s">
-        <v>505</v>
-      </c>
-      <c r="E243" t="s">
-        <v>581</v>
-      </c>
-      <c r="F243" t="s">
-        <v>627</v>
-      </c>
-      <c r="G243" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="244" spans="2:7">
-      <c r="B244" t="s">
-        <v>591</v>
-      </c>
-      <c r="C244" t="s">
-        <v>553</v>
-      </c>
-      <c r="D244" t="s">
-        <v>575</v>
-      </c>
-      <c r="F244" t="s">
-        <v>584</v>
-      </c>
-      <c r="G244" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="245" spans="2:7">
-      <c r="B245" t="s">
-        <v>525</v>
-      </c>
-      <c r="C245" t="s">
-        <v>518</v>
-      </c>
-      <c r="D245" t="s">
-        <v>628</v>
-      </c>
-      <c r="F245" t="s">
-        <v>583</v>
-      </c>
-      <c r="G245" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="246" spans="2:7">
-      <c r="B246" t="s">
-        <v>630</v>
-      </c>
-      <c r="C246" t="s">
-        <v>556</v>
-      </c>
-      <c r="D246" t="s">
-        <v>585</v>
-      </c>
-      <c r="F246" t="s">
-        <v>510</v>
-      </c>
-      <c r="G246" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="247" spans="2:7">
-      <c r="B247" t="s">
-        <v>588</v>
-      </c>
-      <c r="C247" t="s">
-        <v>531</v>
-      </c>
-      <c r="D247" t="s">
-        <v>629</v>
-      </c>
-      <c r="F247" t="s">
-        <v>99</v>
-      </c>
-      <c r="G247" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="248" spans="2:7">
-      <c r="B248" t="s">
-        <v>574</v>
-      </c>
-      <c r="C248" t="s">
-        <v>573</v>
-      </c>
-      <c r="D248" t="s">
-        <v>631</v>
-      </c>
-      <c r="F248" t="s">
+    </row>
+    <row r="260" spans="1:8">
+      <c r="C260" t="s">
+        <v>513</v>
+      </c>
+      <c r="D260" t="s">
         <v>520</v>
-      </c>
-      <c r="G248" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="249" spans="2:7">
-      <c r="B249" t="s">
-        <v>539</v>
-      </c>
-      <c r="C249" t="s">
-        <v>550</v>
-      </c>
-      <c r="D249" t="s">
-        <v>593</v>
-      </c>
-      <c r="F249" t="s">
-        <v>580</v>
-      </c>
-      <c r="G249" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="250" spans="2:7">
-      <c r="B250" t="s">
-        <v>586</v>
-      </c>
-      <c r="C250" t="s">
-        <v>548</v>
-      </c>
-      <c r="D250" t="s">
-        <v>587</v>
-      </c>
-      <c r="F250" t="s">
-        <v>528</v>
-      </c>
-      <c r="G250" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="251" spans="2:7">
-      <c r="B251" t="s">
-        <v>517</v>
-      </c>
-      <c r="C251" t="s">
-        <v>536</v>
-      </c>
-      <c r="D251" t="s">
-        <v>516</v>
-      </c>
-      <c r="F251" t="s">
-        <v>533</v>
-      </c>
-      <c r="G251" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="252" spans="2:7">
-      <c r="B252" t="s">
-        <v>511</v>
-      </c>
-      <c r="C252" t="s">
-        <v>558</v>
-      </c>
-      <c r="D252" t="s">
-        <v>589</v>
-      </c>
-      <c r="F252" t="s">
-        <v>524</v>
-      </c>
-      <c r="G252" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="253" spans="2:7">
-      <c r="B253" t="s">
-        <v>513</v>
-      </c>
-      <c r="C253" t="s">
-        <v>526</v>
-      </c>
-      <c r="D253" t="s">
-        <v>529</v>
-      </c>
-      <c r="G253" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="254" spans="2:7">
-      <c r="B254" t="s">
-        <v>522</v>
-      </c>
-      <c r="C254" t="s">
-        <v>554</v>
-      </c>
-      <c r="D254" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="255" spans="2:7">
-      <c r="B255" t="s">
-        <v>582</v>
-      </c>
-      <c r="C255" t="s">
-        <v>551</v>
-      </c>
-      <c r="D255" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="256" spans="2:7">
-      <c r="B256" t="s">
-        <v>530</v>
-      </c>
-      <c r="C256" t="s">
-        <v>540</v>
-      </c>
-      <c r="D256" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="257" spans="1:8">
-      <c r="C257" t="s">
-        <v>552</v>
-      </c>
-      <c r="D257" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="258" spans="1:8">
-      <c r="C258" t="s">
-        <v>514</v>
-      </c>
-      <c r="D258" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="259" spans="1:8">
-      <c r="D259" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="260" spans="1:8">
-      <c r="D260" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="261" spans="1:8">
       <c r="D261" t="s">
-        <v>590</v>
+        <v>541</v>
       </c>
     </row>
     <row r="262" spans="1:8">
       <c r="D262" t="s">
-        <v>638</v>
+        <v>544</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -7060,48 +7099,58 @@
         <v>589</v>
       </c>
     </row>
-    <row r="264" spans="1:8" s="6" customFormat="1">
-      <c r="A264" s="6" t="s">
+    <row r="264" spans="1:8">
+      <c r="D264" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8">
+      <c r="D265" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" s="6" customFormat="1">
+      <c r="A266" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B264" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="C264" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="D264" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="E264" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="F264" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="G264" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="H264" s="6" t="s">
-        <v>594</v>
+      <c r="B266" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="C266" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="D266" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="E266" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="F266" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="G266" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="H266" s="6" t="s">
+        <v>593</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B151:N151"/>
-    <mergeCell ref="B179:T179"/>
-    <mergeCell ref="B214:N214"/>
-    <mergeCell ref="B239:T239"/>
+    <mergeCell ref="B153:N153"/>
+    <mergeCell ref="B181:T181"/>
+    <mergeCell ref="B216:N216"/>
+    <mergeCell ref="B241:T241"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B25:T25"/>
     <mergeCell ref="B49:N49"/>
     <mergeCell ref="B81:T81"/>
-    <mergeCell ref="B109:N109"/>
-    <mergeCell ref="B129:T129"/>
+    <mergeCell ref="B111:N111"/>
+    <mergeCell ref="B131:T131"/>
   </mergeCells>
-  <conditionalFormatting sqref="H217:H226">
+  <conditionalFormatting sqref="H219:H228">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="SBS-GADUNG-HW.MA5801-OLT-01">
-      <formula>NOT(ISERROR(SEARCH("SBS-GADUNG-HW.MA5801-OLT-01",H217)))</formula>
+      <formula>NOT(ISERROR(SEARCH("SBS-GADUNG-HW.MA5801-OLT-01",H219)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/data/List_Team_Region.xlsx
+++ b/public/data/List_Team_Region.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muham\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7733EE0-F6B4-4E23-BDBA-9C5068BCF313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFEFE1CB-1FFD-4FCB-B0FD-306C528D8BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="649">
   <si>
     <t>JAMBI</t>
   </si>
@@ -1398,9 +1398,6 @@
     <t>SBS-CURUP-HW.MA5801-OLT-09</t>
   </si>
   <si>
-    <t>SBS-MUARABANGKAHULU-HW.MA5801-OLT-01</t>
-  </si>
-  <si>
     <t>SBS-KAMPUNG.MELAYU-HW.MA5801-OLT-03</t>
   </si>
   <si>
@@ -1972,6 +1969,15 @@
   </si>
   <si>
     <t>BHMA PANGKAL</t>
+  </si>
+  <si>
+    <t>SBS-MUARABANGKAHULU-MA5801-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-MUARABANGKAHULU-HW.MA5801-OLT-04</t>
+  </si>
+  <si>
+    <t>SBS-MUARABANGKAHULU-HW.MA5801-OLT-07</t>
   </si>
 </sst>
 </file>
@@ -2279,6 +2285,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2288,7 +2295,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2670,8 +2676,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}" name="Table1525" displayName="Table1525" ref="B182:H212" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="B182:H212" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}" name="Table1525" displayName="Table1525" ref="B182:H214" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="B182:H214" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{ACEB90AF-9CBB-4605-8377-2CF0EF299650}" name="SERPO SUKAMERINDU"/>
     <tableColumn id="2" xr3:uid="{351154A5-2DE7-411B-9044-B8641069B0BF}" name="SERPO BENGKULU KOTA"/>
@@ -2686,8 +2692,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}" name="Table1626" displayName="Table1626" ref="B217:I239" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="B217:I239" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}" name="Table1626" displayName="Table1626" ref="B219:I241" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="B219:I241" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{D0B3A41D-F35E-4B89-AC56-18717B9B04E5}" name="BANGKA REG 7"/>
     <tableColumn id="2" xr3:uid="{9C59FCCC-409F-4148-A8DC-48E653CEBBAA}" name="TTM SUNGAI LIAT"/>
@@ -2703,8 +2709,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}" name="Table1727" displayName="Table1727" ref="B242:G265" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="B242:G265" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}" name="Table1727" displayName="Table1727" ref="B244:G267" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="B244:G267" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{97E25E83-847F-4991-A885-21D98063A2DB}" name="SERPO KOBA"/>
     <tableColumn id="2" xr3:uid="{0AB964B5-883A-49C8-8DDA-C8EE93753519}" name="SERPO PANGKAL PINANG"/>
@@ -3034,7 +3040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D0AF9EF-6686-405D-9473-604A5805FA6C}">
-  <dimension ref="A1:T266"/>
+  <dimension ref="A1:T268"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="34.140625" customWidth="1"/>
@@ -3067,21 +3073,21 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
     </row>
     <row r="3" spans="1:14" s="3" customFormat="1">
       <c r="A3" s="3" t="s">
@@ -3120,7 +3126,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
@@ -3137,7 +3143,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -3163,7 +3169,7 @@
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E6" t="s">
         <v>27</v>
@@ -3183,7 +3189,7 @@
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -3229,7 +3235,7 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D9" t="s">
         <v>48</v>
@@ -3249,7 +3255,7 @@
         <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D10" t="s">
         <v>52</v>
@@ -3266,10 +3272,10 @@
     </row>
     <row r="11" spans="1:14">
       <c r="B11" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D11" t="s">
         <v>55</v>
@@ -3278,7 +3284,7 @@
         <v>53</v>
       </c>
       <c r="G11" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -3295,7 +3301,7 @@
         <v>56</v>
       </c>
       <c r="G12" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -3383,7 +3389,7 @@
         <v>75</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>76</v>
@@ -3408,27 +3414,27 @@
       <c r="A25" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="29"/>
-      <c r="M25" s="29"/>
-      <c r="N25" s="29"/>
-      <c r="O25" s="29"/>
-      <c r="P25" s="29"/>
-      <c r="Q25" s="29"/>
-      <c r="R25" s="29"/>
-      <c r="S25" s="29"/>
-      <c r="T25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
+      <c r="P25" s="30"/>
+      <c r="Q25" s="30"/>
+      <c r="R25" s="30"/>
+      <c r="S25" s="30"/>
+      <c r="T25" s="30"/>
     </row>
     <row r="26" spans="1:20" s="5" customFormat="1">
       <c r="A26" s="5" t="s">
@@ -3464,7 +3470,7 @@
     </row>
     <row r="27" spans="1:20">
       <c r="B27" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C27" t="s">
         <v>63</v>
@@ -3482,7 +3488,7 @@
         <v>13</v>
       </c>
       <c r="H27" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I27" t="s">
         <v>16</v>
@@ -3502,7 +3508,7 @@
         <v>47</v>
       </c>
       <c r="E28" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -3534,10 +3540,10 @@
         <v>27</v>
       </c>
       <c r="G29" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H29" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I29" t="s">
         <v>30</v>
@@ -3554,7 +3560,7 @@
         <v>100</v>
       </c>
       <c r="E30" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F30" t="s">
         <v>34</v>
@@ -3597,7 +3603,7 @@
     </row>
     <row r="32" spans="1:20">
       <c r="B32" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C32" t="s">
         <v>40</v>
@@ -3606,13 +3612,13 @@
         <v>28</v>
       </c>
       <c r="E32" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G32" t="s">
         <v>48</v>
       </c>
       <c r="H32" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I32" t="s">
         <v>46</v>
@@ -3623,16 +3629,16 @@
         <v>67</v>
       </c>
       <c r="D33" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E33" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G33" t="s">
         <v>52</v>
       </c>
       <c r="H33" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I33" t="s">
         <v>51</v>
@@ -3646,7 +3652,7 @@
         <v>73</v>
       </c>
       <c r="E34" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G34" t="s">
         <v>55</v>
@@ -3789,21 +3795,21 @@
       <c r="A49" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="27" t="s">
+      <c r="B49" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="27"/>
-      <c r="K49" s="27"/>
-      <c r="L49" s="27"/>
-      <c r="M49" s="27"/>
-      <c r="N49" s="27"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
+      <c r="K49" s="28"/>
+      <c r="L49" s="28"/>
+      <c r="M49" s="28"/>
+      <c r="N49" s="28"/>
     </row>
     <row r="50" spans="1:14" s="3" customFormat="1">
       <c r="A50" s="3" t="s">
@@ -3896,7 +3902,7 @@
         <v>136</v>
       </c>
       <c r="D54" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E54" t="s">
         <v>132</v>
@@ -3936,7 +3942,7 @@
         <v>147</v>
       </c>
       <c r="D56" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E56" t="s">
         <v>144</v>
@@ -3970,7 +3976,7 @@
         <v>155</v>
       </c>
       <c r="D58" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F58" t="s">
         <v>157</v>
@@ -4023,13 +4029,13 @@
     </row>
     <row r="62" spans="1:14">
       <c r="C62" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D62" t="s">
         <v>148</v>
       </c>
       <c r="F62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G62" t="s">
         <v>163</v>
@@ -4037,13 +4043,13 @@
     </row>
     <row r="63" spans="1:14">
       <c r="C63" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D63" t="s">
         <v>152</v>
       </c>
       <c r="F63" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G63" t="s">
         <v>165</v>
@@ -4133,40 +4139,40 @@
         <v>179</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>180</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="81" spans="1:20">
       <c r="A81" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B81" s="28" t="s">
+      <c r="B81" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="C81" s="28"/>
-      <c r="D81" s="28"/>
-      <c r="E81" s="28"/>
-      <c r="F81" s="28"/>
-      <c r="G81" s="28"/>
-      <c r="H81" s="28"/>
-      <c r="I81" s="29"/>
-      <c r="J81" s="29"/>
-      <c r="K81" s="29"/>
-      <c r="L81" s="29"/>
-      <c r="M81" s="29"/>
-      <c r="N81" s="29"/>
-      <c r="O81" s="29"/>
-      <c r="P81" s="29"/>
-      <c r="Q81" s="29"/>
-      <c r="R81" s="29"/>
-      <c r="S81" s="29"/>
-      <c r="T81" s="29"/>
+      <c r="C81" s="29"/>
+      <c r="D81" s="29"/>
+      <c r="E81" s="29"/>
+      <c r="F81" s="29"/>
+      <c r="G81" s="29"/>
+      <c r="H81" s="29"/>
+      <c r="I81" s="30"/>
+      <c r="J81" s="30"/>
+      <c r="K81" s="30"/>
+      <c r="L81" s="30"/>
+      <c r="M81" s="30"/>
+      <c r="N81" s="30"/>
+      <c r="O81" s="30"/>
+      <c r="P81" s="30"/>
+      <c r="Q81" s="30"/>
+      <c r="R81" s="30"/>
+      <c r="S81" s="30"/>
+      <c r="T81" s="30"/>
     </row>
     <row r="82" spans="1:20" s="6" customFormat="1">
       <c r="A82" s="5" t="s">
@@ -4271,7 +4277,7 @@
     </row>
     <row r="86" spans="1:20">
       <c r="B86" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C86" t="s">
         <v>140</v>
@@ -4322,7 +4328,7 @@
     </row>
     <row r="89" spans="1:20">
       <c r="B89" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C89" t="s">
         <v>134</v>
@@ -4408,7 +4414,7 @@
     </row>
     <row r="96" spans="1:20">
       <c r="B96" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C96" t="s">
         <v>160</v>
@@ -4419,10 +4425,10 @@
     </row>
     <row r="97" spans="1:15">
       <c r="B97" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C97" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E97" t="s">
         <v>143</v>
@@ -4430,7 +4436,7 @@
     </row>
     <row r="98" spans="1:15">
       <c r="B98" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E98" t="s">
         <v>118</v>
@@ -4438,7 +4444,7 @@
     </row>
     <row r="99" spans="1:15">
       <c r="B99" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E99" t="s">
         <v>136</v>
@@ -4446,7 +4452,7 @@
     </row>
     <row r="100" spans="1:15">
       <c r="B100" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E100" t="s">
         <v>142</v>
@@ -4454,7 +4460,7 @@
     </row>
     <row r="101" spans="1:15">
       <c r="B101" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E101" t="s">
         <v>152</v>
@@ -4462,7 +4468,7 @@
     </row>
     <row r="102" spans="1:15">
       <c r="B102" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E102" t="s">
         <v>117</v>
@@ -4470,7 +4476,7 @@
     </row>
     <row r="103" spans="1:15">
       <c r="B103" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E103" t="s">
         <v>148</v>
@@ -4478,7 +4484,7 @@
     </row>
     <row r="104" spans="1:15">
       <c r="E104" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="105" spans="1:15">
@@ -4523,7 +4529,7 @@
         <v>208</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="110" spans="1:15">
@@ -4535,21 +4541,21 @@
       <c r="A111" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B111" s="27" t="s">
+      <c r="B111" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="C111" s="27"/>
-      <c r="D111" s="27"/>
-      <c r="E111" s="27"/>
-      <c r="F111" s="27"/>
-      <c r="G111" s="27"/>
-      <c r="H111" s="27"/>
-      <c r="I111" s="27"/>
-      <c r="J111" s="27"/>
-      <c r="K111" s="27"/>
-      <c r="L111" s="27"/>
-      <c r="M111" s="27"/>
-      <c r="N111" s="27"/>
+      <c r="C111" s="28"/>
+      <c r="D111" s="28"/>
+      <c r="E111" s="28"/>
+      <c r="F111" s="28"/>
+      <c r="G111" s="28"/>
+      <c r="H111" s="28"/>
+      <c r="I111" s="28"/>
+      <c r="J111" s="28"/>
+      <c r="K111" s="28"/>
+      <c r="L111" s="28"/>
+      <c r="M111" s="28"/>
+      <c r="N111" s="28"/>
     </row>
     <row r="112" spans="1:15" s="3" customFormat="1">
       <c r="A112" s="3" t="s">
@@ -4980,10 +4986,10 @@
         <v>336</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="I129" s="4" t="s">
         <v>337</v>
@@ -5011,27 +5017,27 @@
       <c r="A131" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B131" s="28" t="s">
+      <c r="B131" s="29" t="s">
         <v>344</v>
       </c>
-      <c r="C131" s="28"/>
-      <c r="D131" s="28"/>
-      <c r="E131" s="28"/>
-      <c r="F131" s="28"/>
-      <c r="G131" s="28"/>
-      <c r="H131" s="28"/>
-      <c r="I131" s="29"/>
-      <c r="J131" s="29"/>
-      <c r="K131" s="29"/>
-      <c r="L131" s="29"/>
-      <c r="M131" s="29"/>
-      <c r="N131" s="29"/>
-      <c r="O131" s="29"/>
-      <c r="P131" s="29"/>
-      <c r="Q131" s="29"/>
-      <c r="R131" s="29"/>
-      <c r="S131" s="29"/>
-      <c r="T131" s="29"/>
+      <c r="C131" s="29"/>
+      <c r="D131" s="29"/>
+      <c r="E131" s="29"/>
+      <c r="F131" s="29"/>
+      <c r="G131" s="29"/>
+      <c r="H131" s="29"/>
+      <c r="I131" s="30"/>
+      <c r="J131" s="30"/>
+      <c r="K131" s="30"/>
+      <c r="L131" s="30"/>
+      <c r="M131" s="30"/>
+      <c r="N131" s="30"/>
+      <c r="O131" s="30"/>
+      <c r="P131" s="30"/>
+      <c r="Q131" s="30"/>
+      <c r="R131" s="30"/>
+      <c r="S131" s="30"/>
+      <c r="T131" s="30"/>
     </row>
     <row r="132" spans="1:20" s="5" customFormat="1">
       <c r="A132" s="5" t="s">
@@ -5549,21 +5555,21 @@
       <c r="A153" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B153" s="27" t="s">
+      <c r="B153" s="28" t="s">
         <v>379</v>
       </c>
-      <c r="C153" s="27"/>
-      <c r="D153" s="27"/>
-      <c r="E153" s="27"/>
-      <c r="F153" s="27"/>
-      <c r="G153" s="27"/>
-      <c r="H153" s="27"/>
-      <c r="I153" s="27"/>
-      <c r="J153" s="27"/>
-      <c r="K153" s="27"/>
-      <c r="L153" s="27"/>
-      <c r="M153" s="27"/>
-      <c r="N153" s="27"/>
+      <c r="C153" s="28"/>
+      <c r="D153" s="28"/>
+      <c r="E153" s="28"/>
+      <c r="F153" s="28"/>
+      <c r="G153" s="28"/>
+      <c r="H153" s="28"/>
+      <c r="I153" s="28"/>
+      <c r="J153" s="28"/>
+      <c r="K153" s="28"/>
+      <c r="L153" s="28"/>
+      <c r="M153" s="28"/>
+      <c r="N153" s="28"/>
     </row>
     <row r="154" spans="1:20" s="12" customFormat="1">
       <c r="A154" s="3" t="s">
@@ -5686,7 +5692,7 @@
         <v>413</v>
       </c>
       <c r="F158" s="14" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G158" t="s">
         <v>415</v>
@@ -5709,7 +5715,7 @@
         <v>420</v>
       </c>
       <c r="F159" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G159" t="s">
         <v>421</v>
@@ -5718,7 +5724,7 @@
         <v>434</v>
       </c>
       <c r="I159" s="15" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="160" spans="1:20">
@@ -5736,7 +5742,7 @@
       </c>
       <c r="G160" s="18"/>
       <c r="I160" s="15" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
     <row r="161" spans="2:9">
@@ -5753,7 +5759,7 @@
         <v>406</v>
       </c>
       <c r="I161" s="19" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="162" spans="2:9">
@@ -5767,10 +5773,10 @@
         <v>437</v>
       </c>
       <c r="F162" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I162" s="19" t="s">
-        <v>439</v>
+        <v>640</v>
       </c>
     </row>
     <row r="163" spans="2:9">
@@ -5787,7 +5793,7 @@
         <v>414</v>
       </c>
       <c r="I163" s="15" t="s">
-        <v>444</v>
+        <v>642</v>
       </c>
     </row>
     <row r="164" spans="2:9" ht="30">
@@ -5818,7 +5824,7 @@
         <v>433</v>
       </c>
       <c r="I165" s="15" t="s">
-        <v>452</v>
+        <v>646</v>
       </c>
     </row>
     <row r="166" spans="2:9">
@@ -5832,46 +5838,49 @@
         <v>438</v>
       </c>
       <c r="I166" s="15" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="167" spans="2:9">
       <c r="B167" t="s">
+        <v>455</v>
+      </c>
+      <c r="C167" t="s">
         <v>456</v>
-      </c>
-      <c r="C167" t="s">
-        <v>457</v>
       </c>
       <c r="F167" t="s">
         <v>443</v>
       </c>
       <c r="I167" t="s">
-        <v>641</v>
+        <v>423</v>
       </c>
     </row>
     <row r="168" spans="2:9">
       <c r="B168" t="s">
+        <v>458</v>
+      </c>
+      <c r="C168" t="s">
         <v>459</v>
-      </c>
-      <c r="C168" t="s">
-        <v>460</v>
       </c>
       <c r="F168" t="s">
         <v>448</v>
       </c>
-      <c r="I168" s="30" t="s">
-        <v>643</v>
+      <c r="I168" s="27" t="s">
+        <v>647</v>
       </c>
     </row>
     <row r="169" spans="2:9">
       <c r="B169" t="s">
+        <v>461</v>
+      </c>
+      <c r="C169" t="s">
         <v>462</v>
-      </c>
-      <c r="C169" t="s">
-        <v>463</v>
       </c>
       <c r="F169" t="s">
         <v>451</v>
+      </c>
+      <c r="I169" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="170" spans="2:9">
@@ -5879,32 +5888,35 @@
         <v>410</v>
       </c>
       <c r="C170" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F170" t="s">
         <v>454</v>
       </c>
+      <c r="I170" t="s">
+        <v>648</v>
+      </c>
     </row>
     <row r="171" spans="2:9">
       <c r="B171" t="s">
+        <v>466</v>
+      </c>
+      <c r="C171" t="s">
         <v>467</v>
       </c>
-      <c r="C171" t="s">
-        <v>468</v>
-      </c>
       <c r="F171" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="172" spans="2:9">
       <c r="B172" t="s">
+        <v>468</v>
+      </c>
+      <c r="C172" s="20" t="s">
         <v>469</v>
       </c>
-      <c r="C172" s="20" t="s">
-        <v>470</v>
-      </c>
       <c r="F172" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="173" spans="2:9">
@@ -5912,35 +5924,35 @@
         <v>418</v>
       </c>
       <c r="C173" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="174" spans="2:9">
       <c r="B174" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C174" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="175" spans="2:9">
       <c r="B175" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="176" spans="2:9">
       <c r="B176" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="177" spans="1:20">
       <c r="B177" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="178" spans="1:20">
       <c r="B178" s="21" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="179" spans="1:20">
@@ -5948,80 +5960,80 @@
         <v>75</v>
       </c>
       <c r="B179" s="22" t="s">
+        <v>476</v>
+      </c>
+      <c r="C179" s="22" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="22" t="s">
+      <c r="D179" s="22" t="s">
         <v>478</v>
       </c>
-      <c r="D179" s="22" t="s">
+      <c r="E179" s="23" t="s">
         <v>479</v>
       </c>
-      <c r="E179" s="23" t="s">
+      <c r="F179" s="24" t="s">
         <v>480</v>
       </c>
-      <c r="F179" s="24" t="s">
+      <c r="G179" s="22" t="s">
         <v>481</v>
       </c>
-      <c r="G179" s="22" t="s">
+      <c r="H179" s="22" t="s">
         <v>482</v>
       </c>
-      <c r="H179" s="22" t="s">
+      <c r="I179" s="22" t="s">
         <v>483</v>
-      </c>
-      <c r="I179" s="22" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="181" spans="1:20">
       <c r="A181" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B181" s="28" t="s">
-        <v>485</v>
-      </c>
-      <c r="C181" s="28"/>
-      <c r="D181" s="28"/>
-      <c r="E181" s="28"/>
-      <c r="F181" s="28"/>
-      <c r="G181" s="28"/>
-      <c r="H181" s="28"/>
-      <c r="I181" s="29"/>
-      <c r="J181" s="29"/>
-      <c r="K181" s="29"/>
-      <c r="L181" s="29"/>
-      <c r="M181" s="29"/>
-      <c r="N181" s="29"/>
-      <c r="O181" s="29"/>
-      <c r="P181" s="29"/>
-      <c r="Q181" s="29"/>
-      <c r="R181" s="29"/>
-      <c r="S181" s="29"/>
-      <c r="T181" s="29"/>
+      <c r="B181" s="29" t="s">
+        <v>484</v>
+      </c>
+      <c r="C181" s="29"/>
+      <c r="D181" s="29"/>
+      <c r="E181" s="29"/>
+      <c r="F181" s="29"/>
+      <c r="G181" s="29"/>
+      <c r="H181" s="29"/>
+      <c r="I181" s="30"/>
+      <c r="J181" s="30"/>
+      <c r="K181" s="30"/>
+      <c r="L181" s="30"/>
+      <c r="M181" s="30"/>
+      <c r="N181" s="30"/>
+      <c r="O181" s="30"/>
+      <c r="P181" s="30"/>
+      <c r="Q181" s="30"/>
+      <c r="R181" s="30"/>
+      <c r="S181" s="30"/>
+      <c r="T181" s="30"/>
     </row>
     <row r="182" spans="1:20" s="5" customFormat="1">
       <c r="A182" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B182" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="C182" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="C182" s="5" t="s">
+      <c r="D182" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="D182" s="5" t="s">
+      <c r="E182" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="E182" s="5" t="s">
+      <c r="F182" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="G182" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="F182" s="5" t="s">
+      <c r="H182" s="5" t="s">
         <v>622</v>
-      </c>
-      <c r="G182" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="H182" s="5" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="183" spans="1:20">
@@ -6078,7 +6090,7 @@
         <v>410</v>
       </c>
       <c r="D185" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E185" t="s">
         <v>399</v>
@@ -6101,13 +6113,13 @@
         <v>418</v>
       </c>
       <c r="D186" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E186" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F186" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G186" t="s">
         <v>416</v>
@@ -6124,13 +6136,13 @@
         <v>424</v>
       </c>
       <c r="D187" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E187" t="s">
         <v>421</v>
       </c>
       <c r="F187" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G187" t="s">
         <v>422</v>
@@ -6184,10 +6196,10 @@
         <v>436</v>
       </c>
       <c r="C190" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F190" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H190" t="s">
         <v>442</v>
@@ -6212,7 +6224,7 @@
         <v>446</v>
       </c>
       <c r="C192" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F192" t="s">
         <v>427</v>
@@ -6226,7 +6238,7 @@
         <v>431</v>
       </c>
       <c r="C193" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F193" t="s">
         <v>433</v>
@@ -6245,10 +6257,10 @@
     </row>
     <row r="195" spans="2:6">
       <c r="B195" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C195" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F195" t="s">
         <v>443</v>
@@ -6256,10 +6268,10 @@
     </row>
     <row r="196" spans="2:6">
       <c r="B196" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C196" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F196" t="s">
         <v>448</v>
@@ -6267,10 +6279,10 @@
     </row>
     <row r="197" spans="2:6">
       <c r="B197" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C197" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F197" t="s">
         <v>451</v>
@@ -6278,10 +6290,10 @@
     </row>
     <row r="198" spans="2:6">
       <c r="B198" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C198" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F198" t="s">
         <v>454</v>
@@ -6289,24 +6301,24 @@
     </row>
     <row r="199" spans="2:6">
       <c r="B199" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C199" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F199" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="200" spans="2:6">
       <c r="B200" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C200" t="s">
         <v>412</v>
       </c>
       <c r="F200" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="201" spans="2:6">
@@ -6338,18 +6350,18 @@
     </row>
     <row r="204" spans="2:6">
       <c r="B204" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C204" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="205" spans="2:6">
       <c r="B205" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C205" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
     <row r="206" spans="2:6">
@@ -6357,22 +6369,22 @@
         <v>396</v>
       </c>
       <c r="C206" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="207" spans="2:6">
       <c r="C207" t="s">
-        <v>439</v>
+        <v>640</v>
       </c>
     </row>
     <row r="208" spans="2:6">
       <c r="C208" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="209" spans="1:14">
       <c r="C209" t="s">
-        <v>449</v>
+        <v>646</v>
       </c>
     </row>
     <row r="210" spans="1:14">
@@ -6382,726 +6394,726 @@
     </row>
     <row r="211" spans="1:14">
       <c r="C211" t="s">
-        <v>455</v>
+        <v>423</v>
       </c>
     </row>
     <row r="212" spans="1:14">
       <c r="C212" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="213" spans="1:14" s="6" customFormat="1">
-      <c r="A213" s="6" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14">
+      <c r="C213" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14">
+      <c r="C214" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" s="6" customFormat="1">
+      <c r="A215" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B213" s="6" t="s">
+      <c r="B215" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="C215" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="D215" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="E215" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="F215" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="G215" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="H215" s="6" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14">
+      <c r="A217" s="7" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14">
+      <c r="A218" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B218" s="28" t="s">
         <v>493</v>
       </c>
-      <c r="C213" s="6" t="s">
-        <v>493</v>
-      </c>
-      <c r="D213" s="6" t="s">
-        <v>493</v>
-      </c>
-      <c r="E213" s="6" t="s">
-        <v>493</v>
-      </c>
-      <c r="F213" s="6" t="s">
-        <v>493</v>
-      </c>
-      <c r="G213" s="6" t="s">
-        <v>493</v>
-      </c>
-      <c r="H213" s="6" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="215" spans="1:14">
-      <c r="A215" s="7" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="216" spans="1:14">
-      <c r="A216" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B216" s="27" t="s">
+      <c r="C218" s="28"/>
+      <c r="D218" s="28"/>
+      <c r="E218" s="28"/>
+      <c r="F218" s="28"/>
+      <c r="G218" s="28"/>
+      <c r="H218" s="28"/>
+      <c r="I218" s="28"/>
+      <c r="J218" s="28"/>
+      <c r="K218" s="28"/>
+      <c r="L218" s="28"/>
+      <c r="M218" s="28"/>
+      <c r="N218" s="28"/>
+    </row>
+    <row r="219" spans="1:14" s="3" customFormat="1">
+      <c r="A219" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B219" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="C216" s="27"/>
-      <c r="D216" s="27"/>
-      <c r="E216" s="27"/>
-      <c r="F216" s="27"/>
-      <c r="G216" s="27"/>
-      <c r="H216" s="27"/>
-      <c r="I216" s="27"/>
-      <c r="J216" s="27"/>
-      <c r="K216" s="27"/>
-      <c r="L216" s="27"/>
-      <c r="M216" s="27"/>
-      <c r="N216" s="27"/>
-    </row>
-    <row r="217" spans="1:14" s="3" customFormat="1">
-      <c r="A217" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B217" s="3" t="s">
+      <c r="C219" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="C217" s="3" t="s">
+      <c r="D219" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="D217" s="3" t="s">
+      <c r="E219" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="E217" s="3" t="s">
+      <c r="F219" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="F217" s="3" t="s">
+      <c r="G219" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="G217" s="3" t="s">
+      <c r="H219" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="H217" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="I217" s="3" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="218" spans="1:14">
-      <c r="B218" t="s">
-        <v>554</v>
-      </c>
-      <c r="C218" t="s">
-        <v>508</v>
-      </c>
-      <c r="D218" t="s">
-        <v>537</v>
-      </c>
-      <c r="E218" t="s">
-        <v>546</v>
-      </c>
-      <c r="F218" t="s">
-        <v>505</v>
-      </c>
-      <c r="G218" t="s">
-        <v>506</v>
-      </c>
-      <c r="H218" s="20" t="s">
-        <v>512</v>
-      </c>
-      <c r="I218" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="219" spans="1:14">
-      <c r="B219" t="s">
-        <v>542</v>
-      </c>
-      <c r="C219" t="s">
-        <v>514</v>
-      </c>
-      <c r="D219" t="s">
-        <v>503</v>
-      </c>
-      <c r="E219" t="s">
-        <v>504</v>
-      </c>
-      <c r="G219" t="s">
-        <v>511</v>
-      </c>
-      <c r="H219" t="s">
-        <v>516</v>
-      </c>
-      <c r="I219" t="s">
+      <c r="I219" s="3" t="s">
         <v>645</v>
       </c>
     </row>
     <row r="220" spans="1:14">
       <c r="B220" t="s">
-        <v>624</v>
+        <v>553</v>
       </c>
       <c r="C220" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="D220" t="s">
-        <v>626</v>
+        <v>536</v>
       </c>
       <c r="E220" t="s">
-        <v>627</v>
-      </c>
-      <c r="H220" t="s">
-        <v>521</v>
+        <v>545</v>
+      </c>
+      <c r="F220" t="s">
+        <v>504</v>
+      </c>
+      <c r="G220" t="s">
+        <v>505</v>
+      </c>
+      <c r="H220" s="20" t="s">
+        <v>511</v>
+      </c>
+      <c r="I220" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="221" spans="1:14">
       <c r="B221" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="C221" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="D221" t="s">
-        <v>583</v>
+        <v>502</v>
       </c>
       <c r="E221" t="s">
-        <v>628</v>
+        <v>503</v>
+      </c>
+      <c r="G221" t="s">
+        <v>510</v>
       </c>
       <c r="H221" t="s">
-        <v>524</v>
+        <v>515</v>
+      </c>
+      <c r="I221" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="222" spans="1:14">
       <c r="B222" t="s">
+        <v>623</v>
+      </c>
+      <c r="C222" t="s">
         <v>517</v>
       </c>
-      <c r="C222" t="s">
-        <v>526</v>
-      </c>
       <c r="D222" t="s">
-        <v>509</v>
+        <v>625</v>
       </c>
       <c r="E222" t="s">
-        <v>515</v>
+        <v>626</v>
       </c>
       <c r="H222" t="s">
-        <v>534</v>
-      </c>
-      <c r="K222" s="26"/>
+        <v>520</v>
+      </c>
     </row>
     <row r="223" spans="1:14">
       <c r="B223" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C223" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="D223" t="s">
-        <v>99</v>
+        <v>582</v>
       </c>
       <c r="E223" t="s">
-        <v>588</v>
+        <v>627</v>
       </c>
       <c r="H223" t="s">
-        <v>538</v>
-      </c>
-      <c r="K223" s="25"/>
+        <v>523</v>
+      </c>
     </row>
     <row r="224" spans="1:14">
       <c r="B224" t="s">
+        <v>516</v>
+      </c>
+      <c r="C224" t="s">
+        <v>525</v>
+      </c>
+      <c r="D224" t="s">
+        <v>508</v>
+      </c>
+      <c r="E224" t="s">
+        <v>514</v>
+      </c>
+      <c r="H224" t="s">
+        <v>533</v>
+      </c>
+      <c r="K224" s="26"/>
+    </row>
+    <row r="225" spans="2:11">
+      <c r="B225" t="s">
+        <v>554</v>
+      </c>
+      <c r="C225" t="s">
         <v>530</v>
       </c>
-      <c r="C224" t="s">
-        <v>536</v>
-      </c>
-      <c r="D224" t="s">
+      <c r="D225" t="s">
+        <v>99</v>
+      </c>
+      <c r="E225" t="s">
+        <v>587</v>
+      </c>
+      <c r="H225" t="s">
+        <v>537</v>
+      </c>
+      <c r="K225" s="25"/>
+    </row>
+    <row r="226" spans="2:11">
+      <c r="B226" t="s">
+        <v>529</v>
+      </c>
+      <c r="C226" t="s">
+        <v>535</v>
+      </c>
+      <c r="D226" t="s">
+        <v>518</v>
+      </c>
+      <c r="E226" t="s">
+        <v>527</v>
+      </c>
+      <c r="H226" t="s">
+        <v>506</v>
+      </c>
+      <c r="K226" s="26"/>
+    </row>
+    <row r="227" spans="2:11">
+      <c r="B227" t="s">
+        <v>571</v>
+      </c>
+      <c r="C227" t="s">
+        <v>539</v>
+      </c>
+      <c r="D227" t="s">
+        <v>526</v>
+      </c>
+      <c r="E227" t="s">
+        <v>532</v>
+      </c>
+      <c r="H227" t="s">
+        <v>589</v>
+      </c>
+      <c r="K227" s="25"/>
+    </row>
+    <row r="228" spans="2:11">
+      <c r="B228" t="s">
+        <v>548</v>
+      </c>
+      <c r="C228" t="s">
+        <v>542</v>
+      </c>
+      <c r="D228" t="s">
+        <v>531</v>
+      </c>
+      <c r="E228" t="s">
+        <v>547</v>
+      </c>
+      <c r="H228" t="s">
+        <v>628</v>
+      </c>
+      <c r="K228" s="26"/>
+    </row>
+    <row r="229" spans="2:11">
+      <c r="B229" t="s">
+        <v>546</v>
+      </c>
+      <c r="C229" t="s">
+        <v>544</v>
+      </c>
+      <c r="D229" t="s">
+        <v>522</v>
+      </c>
+      <c r="E229" t="s">
         <v>519</v>
       </c>
-      <c r="E224" t="s">
+      <c r="H229" t="s">
+        <v>580</v>
+      </c>
+      <c r="K229" s="25"/>
+    </row>
+    <row r="230" spans="2:11">
+      <c r="B230" t="s">
+        <v>534</v>
+      </c>
+      <c r="C230" t="s">
+        <v>539</v>
+      </c>
+      <c r="E230" t="s">
+        <v>540</v>
+      </c>
+      <c r="H230" t="s">
         <v>528</v>
       </c>
-      <c r="H224" t="s">
-        <v>507</v>
-      </c>
-      <c r="K224" s="26"/>
-    </row>
-    <row r="225" spans="1:11">
-      <c r="B225" t="s">
-        <v>572</v>
-      </c>
-      <c r="C225" t="s">
-        <v>540</v>
-      </c>
-      <c r="D225" t="s">
-        <v>527</v>
-      </c>
-      <c r="E225" t="s">
-        <v>533</v>
-      </c>
-      <c r="H225" t="s">
-        <v>590</v>
-      </c>
-      <c r="K225" s="25"/>
-    </row>
-    <row r="226" spans="1:11">
-      <c r="B226" t="s">
+      <c r="K230" s="26"/>
+    </row>
+    <row r="231" spans="2:11">
+      <c r="B231" t="s">
+        <v>556</v>
+      </c>
+      <c r="C231" t="s">
+        <v>501</v>
+      </c>
+      <c r="E231" t="s">
+        <v>543</v>
+      </c>
+      <c r="K231" s="25"/>
+    </row>
+    <row r="232" spans="2:11">
+      <c r="B232" t="s">
+        <v>524</v>
+      </c>
+      <c r="C232" t="s">
+        <v>624</v>
+      </c>
+      <c r="K232" s="26"/>
+    </row>
+    <row r="233" spans="2:11">
+      <c r="B233" t="s">
+        <v>552</v>
+      </c>
+      <c r="C233" t="s">
+        <v>575</v>
+      </c>
+      <c r="K233" s="25"/>
+    </row>
+    <row r="234" spans="2:11">
+      <c r="B234" t="s">
         <v>549</v>
       </c>
-      <c r="C226" t="s">
-        <v>543</v>
-      </c>
-      <c r="D226" t="s">
-        <v>532</v>
-      </c>
-      <c r="E226" t="s">
-        <v>548</v>
-      </c>
-      <c r="H226" t="s">
-        <v>629</v>
-      </c>
-      <c r="K226" s="26"/>
-    </row>
-    <row r="227" spans="1:11">
-      <c r="B227" t="s">
-        <v>547</v>
-      </c>
-      <c r="C227" t="s">
-        <v>545</v>
-      </c>
-      <c r="D227" t="s">
-        <v>523</v>
-      </c>
-      <c r="E227" t="s">
-        <v>520</v>
-      </c>
-      <c r="H227" t="s">
-        <v>581</v>
-      </c>
-      <c r="K227" s="25"/>
-    </row>
-    <row r="228" spans="1:11">
-      <c r="B228" t="s">
-        <v>535</v>
-      </c>
-      <c r="C228" t="s">
-        <v>540</v>
-      </c>
-      <c r="E228" t="s">
-        <v>541</v>
-      </c>
-      <c r="H228" t="s">
-        <v>529</v>
-      </c>
-      <c r="K228" s="26"/>
-    </row>
-    <row r="229" spans="1:11">
-      <c r="B229" t="s">
+      <c r="K234" s="26"/>
+    </row>
+    <row r="235" spans="2:11">
+      <c r="B235" t="s">
+        <v>538</v>
+      </c>
+      <c r="K235" s="25"/>
+    </row>
+    <row r="236" spans="2:11">
+      <c r="B236" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="237" spans="2:11">
+      <c r="B237" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="238" spans="2:11">
+      <c r="B238" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="241" spans="1:20" s="4" customFormat="1">
+      <c r="A241" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B241" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="C229" t="s">
-        <v>502</v>
-      </c>
-      <c r="E229" t="s">
-        <v>544</v>
-      </c>
-      <c r="K229" s="25"/>
-    </row>
-    <row r="230" spans="1:11">
-      <c r="B230" t="s">
-        <v>525</v>
-      </c>
-      <c r="C230" t="s">
-        <v>625</v>
-      </c>
-      <c r="K230" s="26"/>
-    </row>
-    <row r="231" spans="1:11">
-      <c r="B231" t="s">
-        <v>553</v>
-      </c>
-      <c r="C231" t="s">
-        <v>576</v>
-      </c>
-      <c r="K231" s="25"/>
-    </row>
-    <row r="232" spans="1:11">
-      <c r="B232" t="s">
-        <v>550</v>
-      </c>
-      <c r="K232" s="26"/>
-    </row>
-    <row r="233" spans="1:11">
-      <c r="B233" t="s">
-        <v>539</v>
-      </c>
-      <c r="K233" s="25"/>
-    </row>
-    <row r="234" spans="1:11">
-      <c r="B234" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="235" spans="1:11">
-      <c r="B235" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="236" spans="1:11">
-      <c r="B236" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="239" spans="1:11" s="4" customFormat="1">
-      <c r="A239" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B239" s="4" t="s">
+      <c r="C241" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="C239" s="4" t="s">
+      <c r="D241" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="D239" s="4" t="s">
+      <c r="E241" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="E239" s="4" t="s">
+      <c r="F241" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="F239" s="4" t="s">
+      <c r="G241" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="G239" s="4" t="s">
+      <c r="H241" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="H239" s="4" t="s">
+    </row>
+    <row r="243" spans="1:20">
+      <c r="A243" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B243" s="29" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="241" spans="1:20">
-      <c r="A241" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B241" s="28" t="s">
+      <c r="C243" s="29"/>
+      <c r="D243" s="29"/>
+      <c r="E243" s="29"/>
+      <c r="F243" s="29"/>
+      <c r="G243" s="29"/>
+      <c r="H243" s="29"/>
+      <c r="I243" s="30"/>
+      <c r="J243" s="30"/>
+      <c r="K243" s="30"/>
+      <c r="L243" s="30"/>
+      <c r="M243" s="30"/>
+      <c r="N243" s="30"/>
+      <c r="O243" s="30"/>
+      <c r="P243" s="30"/>
+      <c r="Q243" s="30"/>
+      <c r="R243" s="30"/>
+      <c r="S243" s="30"/>
+      <c r="T243" s="30"/>
+    </row>
+    <row r="244" spans="1:20" s="5" customFormat="1">
+      <c r="A244" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="C244" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="C241" s="28"/>
-      <c r="D241" s="28"/>
-      <c r="E241" s="28"/>
-      <c r="F241" s="28"/>
-      <c r="G241" s="28"/>
-      <c r="H241" s="28"/>
-      <c r="I241" s="29"/>
-      <c r="J241" s="29"/>
-      <c r="K241" s="29"/>
-      <c r="L241" s="29"/>
-      <c r="M241" s="29"/>
-      <c r="N241" s="29"/>
-      <c r="O241" s="29"/>
-      <c r="P241" s="29"/>
-      <c r="Q241" s="29"/>
-      <c r="R241" s="29"/>
-      <c r="S241" s="29"/>
-      <c r="T241" s="29"/>
-    </row>
-    <row r="242" spans="1:20" s="5" customFormat="1">
-      <c r="A242" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B242" s="5" t="s">
+      <c r="D244" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="C242" s="5" t="s">
-        <v>566</v>
-      </c>
-      <c r="D242" s="5" t="s">
+      <c r="E244" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="E242" s="5" t="s">
+      <c r="F244" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="F242" s="5" t="s">
+      <c r="G244" s="5" t="s">
         <v>570</v>
-      </c>
-      <c r="G242" s="5" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="243" spans="1:20">
-      <c r="B243" t="s">
-        <v>556</v>
-      </c>
-      <c r="C243" t="s">
-        <v>554</v>
-      </c>
-      <c r="D243" t="s">
-        <v>546</v>
-      </c>
-      <c r="E243" t="s">
-        <v>575</v>
-      </c>
-      <c r="F243" t="s">
-        <v>537</v>
-      </c>
-      <c r="G243" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="244" spans="1:20">
-      <c r="B244" t="s">
-        <v>636</v>
-      </c>
-      <c r="C244" t="s">
-        <v>542</v>
-      </c>
-      <c r="D244" t="s">
-        <v>577</v>
-      </c>
-      <c r="E244" t="s">
-        <v>578</v>
-      </c>
-      <c r="F244" t="s">
-        <v>503</v>
-      </c>
-      <c r="G244" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="245" spans="1:20">
       <c r="B245" t="s">
+        <v>555</v>
+      </c>
+      <c r="C245" t="s">
+        <v>553</v>
+      </c>
+      <c r="D245" t="s">
+        <v>545</v>
+      </c>
+      <c r="E245" t="s">
+        <v>574</v>
+      </c>
+      <c r="F245" t="s">
+        <v>536</v>
+      </c>
+      <c r="G245" t="s">
         <v>507</v>
-      </c>
-      <c r="C245" t="s">
-        <v>624</v>
-      </c>
-      <c r="D245" t="s">
-        <v>504</v>
-      </c>
-      <c r="E245" t="s">
-        <v>580</v>
-      </c>
-      <c r="F245" t="s">
-        <v>626</v>
-      </c>
-      <c r="G245" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="246" spans="1:20">
       <c r="B246" t="s">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="C246" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="D246" t="s">
-        <v>574</v>
+        <v>576</v>
+      </c>
+      <c r="E246" t="s">
+        <v>577</v>
       </c>
       <c r="F246" t="s">
-        <v>583</v>
+        <v>502</v>
       </c>
       <c r="G246" t="s">
-        <v>514</v>
+        <v>542</v>
       </c>
     </row>
     <row r="247" spans="1:20">
       <c r="B247" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="C247" t="s">
-        <v>517</v>
+        <v>623</v>
       </c>
       <c r="D247" t="s">
-        <v>627</v>
+        <v>503</v>
+      </c>
+      <c r="E247" t="s">
+        <v>579</v>
       </c>
       <c r="F247" t="s">
-        <v>582</v>
+        <v>625</v>
       </c>
       <c r="G247" t="s">
-        <v>540</v>
+        <v>521</v>
       </c>
     </row>
     <row r="248" spans="1:20">
       <c r="B248" t="s">
-        <v>629</v>
+        <v>589</v>
       </c>
       <c r="C248" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="D248" t="s">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="F248" t="s">
-        <v>509</v>
+        <v>582</v>
       </c>
       <c r="G248" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:20">
       <c r="B249" t="s">
-        <v>587</v>
+        <v>523</v>
       </c>
       <c r="C249" t="s">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="D249" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="F249" t="s">
-        <v>99</v>
+        <v>581</v>
       </c>
       <c r="G249" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
     </row>
     <row r="250" spans="1:20">
       <c r="B250" t="s">
-        <v>573</v>
+        <v>628</v>
       </c>
       <c r="C250" t="s">
-        <v>572</v>
+        <v>554</v>
       </c>
       <c r="D250" t="s">
-        <v>630</v>
+        <v>583</v>
       </c>
       <c r="F250" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="G250" t="s">
-        <v>545</v>
+        <v>530</v>
       </c>
     </row>
     <row r="251" spans="1:20">
       <c r="B251" t="s">
-        <v>538</v>
+        <v>586</v>
       </c>
       <c r="C251" t="s">
-        <v>549</v>
+        <v>529</v>
       </c>
       <c r="D251" t="s">
-        <v>592</v>
+        <v>627</v>
       </c>
       <c r="F251" t="s">
-        <v>579</v>
+        <v>99</v>
       </c>
       <c r="G251" t="s">
-        <v>589</v>
+        <v>548</v>
       </c>
     </row>
     <row r="252" spans="1:20">
       <c r="B252" t="s">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="C252" t="s">
-        <v>547</v>
+        <v>571</v>
       </c>
       <c r="D252" t="s">
-        <v>586</v>
+        <v>629</v>
       </c>
       <c r="F252" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="G252" t="s">
-        <v>502</v>
+        <v>544</v>
       </c>
     </row>
     <row r="253" spans="1:20">
       <c r="B253" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="C253" t="s">
-        <v>535</v>
+        <v>548</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>591</v>
       </c>
       <c r="F253" t="s">
-        <v>532</v>
+        <v>578</v>
       </c>
       <c r="G253" t="s">
-        <v>625</v>
+        <v>588</v>
       </c>
     </row>
     <row r="254" spans="1:20">
       <c r="B254" t="s">
-        <v>510</v>
+        <v>584</v>
       </c>
       <c r="C254" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="D254" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="F254" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="G254" t="s">
-        <v>576</v>
+        <v>501</v>
       </c>
     </row>
     <row r="255" spans="1:20">
       <c r="B255" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C255" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="D255" t="s">
-        <v>528</v>
+        <v>514</v>
+      </c>
+      <c r="F255" t="s">
+        <v>531</v>
       </c>
       <c r="G255" t="s">
-        <v>536</v>
+        <v>624</v>
       </c>
     </row>
     <row r="256" spans="1:20">
       <c r="B256" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="C256" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D256" t="s">
-        <v>533</v>
+        <v>587</v>
+      </c>
+      <c r="F256" t="s">
+        <v>522</v>
+      </c>
+      <c r="G256" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="257" spans="1:8">
       <c r="B257" t="s">
-        <v>581</v>
+        <v>511</v>
       </c>
       <c r="C257" t="s">
-        <v>550</v>
+        <v>524</v>
       </c>
       <c r="D257" t="s">
-        <v>591</v>
+        <v>527</v>
+      </c>
+      <c r="G257" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="258" spans="1:8">
       <c r="B258" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="C258" t="s">
-        <v>539</v>
+        <v>552</v>
       </c>
       <c r="D258" t="s">
-        <v>508</v>
+        <v>532</v>
       </c>
     </row>
     <row r="259" spans="1:8">
+      <c r="B259" t="s">
+        <v>580</v>
+      </c>
       <c r="C259" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D259" t="s">
-        <v>548</v>
+        <v>590</v>
       </c>
     </row>
     <row r="260" spans="1:8">
+      <c r="B260" t="s">
+        <v>528</v>
+      </c>
       <c r="C260" t="s">
-        <v>513</v>
+        <v>538</v>
       </c>
       <c r="D260" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
     </row>
     <row r="261" spans="1:8">
+      <c r="C261" t="s">
+        <v>550</v>
+      </c>
       <c r="D261" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
     </row>
     <row r="262" spans="1:8">
+      <c r="C262" t="s">
+        <v>512</v>
+      </c>
       <c r="D262" t="s">
-        <v>544</v>
+        <v>519</v>
       </c>
     </row>
     <row r="263" spans="1:8">
       <c r="D263" t="s">
-        <v>589</v>
+        <v>540</v>
       </c>
     </row>
     <row r="264" spans="1:8">
       <c r="D264" t="s">
-        <v>637</v>
+        <v>543</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -7109,38 +7121,48 @@
         <v>588</v>
       </c>
     </row>
-    <row r="266" spans="1:8" s="6" customFormat="1">
-      <c r="A266" s="6" t="s">
+    <row r="266" spans="1:8">
+      <c r="D266" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8">
+      <c r="D267" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" s="6" customFormat="1">
+      <c r="A268" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B266" s="6" t="s">
-        <v>593</v>
-      </c>
-      <c r="C266" s="6" t="s">
-        <v>593</v>
-      </c>
-      <c r="D266" s="6" t="s">
-        <v>593</v>
-      </c>
-      <c r="E266" s="6" t="s">
-        <v>593</v>
-      </c>
-      <c r="F266" s="6" t="s">
-        <v>593</v>
-      </c>
-      <c r="G266" s="6" t="s">
-        <v>593</v>
-      </c>
-      <c r="H266" s="6" t="s">
-        <v>593</v>
+      <c r="B268" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="C268" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="D268" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="E268" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="F268" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="G268" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="H268" s="6" t="s">
+        <v>592</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="B153:N153"/>
     <mergeCell ref="B181:T181"/>
-    <mergeCell ref="B216:N216"/>
-    <mergeCell ref="B241:T241"/>
+    <mergeCell ref="B218:N218"/>
+    <mergeCell ref="B243:T243"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B25:T25"/>
     <mergeCell ref="B49:N49"/>
@@ -7148,9 +7170,9 @@
     <mergeCell ref="B111:N111"/>
     <mergeCell ref="B131:T131"/>
   </mergeCells>
-  <conditionalFormatting sqref="H219:H228">
+  <conditionalFormatting sqref="H221:H230">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="SBS-GADUNG-HW.MA5801-OLT-01">
-      <formula>NOT(ISERROR(SEARCH("SBS-GADUNG-HW.MA5801-OLT-01",H219)))</formula>
+      <formula>NOT(ISERROR(SEARCH("SBS-GADUNG-HW.MA5801-OLT-01",H221)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/data/List_Team_Region.xlsx
+++ b/public/data/List_Team_Region.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muham\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFEFE1CB-1FFD-4FCB-B0FD-306C528D8BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BCB72E-CDD4-486F-AF01-D5C1B79C9CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
+    <workbookView xWindow="1080" yWindow="1560" windowWidth="14460" windowHeight="7320" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="648">
   <si>
     <t>JAMBI</t>
   </si>
@@ -168,9 +168,6 @@
     <t>SBS-KOTA.KARANG-HW.MA5801-OLT-01</t>
   </si>
   <si>
-    <t xml:space="preserve">  SBS-SUNGAI.PENUH-HW.MA5801-OLT-01</t>
-  </si>
-  <si>
     <t>SBS-TEBO.TENGAH-HW.MA5801-OLT-01</t>
   </si>
   <si>
@@ -681,9 +678,6 @@
     <t>TTM INDRALAYA</t>
   </si>
   <si>
-    <t>IKR OKI</t>
-  </si>
-  <si>
     <t>FREELANCE SEMENDE</t>
   </si>
   <si>
@@ -1978,6 +1972,9 @@
   </si>
   <si>
     <t>SBS-MUARABANGKAHULU-HW.MA5801-OLT-07</t>
+  </si>
+  <si>
+    <t>SBS-SUNGAI.PENUH-HW.MA5801-OLT-01</t>
   </si>
 </sst>
 </file>
@@ -2557,8 +2554,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}" name="Table27" displayName="Table27" ref="B132:T149" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="B132:T149" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}" name="Table27" displayName="Table27" ref="B137:T154" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="B137:T154" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{F8A4E442-73AD-4EB9-BB0D-D55E87DA1888}" name="SERPO PALEMBANG KOTA"/>
     <tableColumn id="2" xr3:uid="{FDE83478-980D-467C-B140-58C1B9CDE4FE}" name="SERPO LAHAT"/>
@@ -2636,15 +2633,14 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}" name="Table1323" displayName="Table1323" ref="B112:O129" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="B112:O129" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}" name="Table1323" displayName="Table1323" ref="B112:N134" totalsRowShown="0" headerRowDxfId="8">
+  <autoFilter ref="B112:N134" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}"/>
+  <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{6FB6563D-399C-4506-8AF0-A312347E4888}" name="REG7 PALEMBANG 1"/>
     <tableColumn id="2" xr3:uid="{211D6500-28BD-4C9B-A588-576FE1D6FE10}" name="REG7 PALEMBANG 2"/>
     <tableColumn id="3" xr3:uid="{355E3A8F-21BA-4348-9564-2FAF305488B3}" name="REG7 PALEMBANG 3"/>
     <tableColumn id="4" xr3:uid="{070A17C8-52C6-4AF4-807C-E007D52A7DC6}" name="IKR OKU TIMUR"/>
     <tableColumn id="5" xr3:uid="{B35087CF-DE14-415A-9872-F1705541036A}" name="TTM INDRALAYA"/>
-    <tableColumn id="6" xr3:uid="{51CAB00F-EEF9-42DF-9518-87A4174E62E8}" name="IKR OKI"/>
     <tableColumn id="7" xr3:uid="{9ED06629-CF64-47B3-9390-70326979370E}" name="FREELANCE SEMENDE"/>
     <tableColumn id="8" xr3:uid="{E1884F1A-4DBF-4538-B943-F2B0885F20D9}" name="GSP LUBUK LINGGAU "/>
     <tableColumn id="9" xr3:uid="{AB7C9AAB-E771-4714-84C7-75EBAA4094CD}" name="GSP PRABU PANGKUL"/>
@@ -2659,8 +2655,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}" name="Table1424" displayName="Table1424" ref="B154:I178" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
-  <autoFilter ref="B154:I178" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}" name="Table1424" displayName="Table1424" ref="B159:I183" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
+  <autoFilter ref="B159:I183" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{9BFFF82B-4674-404E-AC18-7772CF16890E}" name="GSP BENGKULU 1"/>
     <tableColumn id="2" xr3:uid="{BF3EB892-4094-4FE7-B983-B0CEE975CE16}" name="GSP BENGKULU 2"/>
@@ -2676,8 +2672,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}" name="Table1525" displayName="Table1525" ref="B182:H214" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="B182:H214" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}" name="Table1525" displayName="Table1525" ref="B187:H219" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="B187:H219" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{ACEB90AF-9CBB-4605-8377-2CF0EF299650}" name="SERPO SUKAMERINDU"/>
     <tableColumn id="2" xr3:uid="{351154A5-2DE7-411B-9044-B8641069B0BF}" name="SERPO BENGKULU KOTA"/>
@@ -2692,8 +2688,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}" name="Table1626" displayName="Table1626" ref="B219:I241" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="B219:I241" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}" name="Table1626" displayName="Table1626" ref="B224:I246" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="B224:I246" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{D0B3A41D-F35E-4B89-AC56-18717B9B04E5}" name="BANGKA REG 7"/>
     <tableColumn id="2" xr3:uid="{9C59FCCC-409F-4148-A8DC-48E653CEBBAA}" name="TTM SUNGAI LIAT"/>
@@ -2709,8 +2705,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}" name="Table1727" displayName="Table1727" ref="B244:G267" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="B244:G267" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}" name="Table1727" displayName="Table1727" ref="B249:G272" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="B249:G272" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{97E25E83-847F-4991-A885-21D98063A2DB}" name="SERPO KOBA"/>
     <tableColumn id="2" xr3:uid="{0AB964B5-883A-49C8-8DDA-C8EE93753519}" name="SERPO PANGKAL PINANG"/>
@@ -3040,7 +3036,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D0AF9EF-6686-405D-9473-604A5805FA6C}">
-  <dimension ref="A1:T268"/>
+  <dimension ref="A1:T273"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="34.140625" customWidth="1"/>
@@ -3126,7 +3122,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
@@ -3143,7 +3139,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -3169,7 +3165,7 @@
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E6" t="s">
         <v>27</v>
@@ -3189,7 +3185,7 @@
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -3235,148 +3231,151 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F9" t="s">
         <v>44</v>
       </c>
       <c r="G9" t="s">
+        <v>647</v>
+      </c>
+      <c r="H9" t="s">
         <v>45</v>
-      </c>
-      <c r="H9" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="B10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" t="s">
         <v>49</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>50</v>
-      </c>
-      <c r="H10" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="B11" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C11" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G11" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="B12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
         <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="B13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>58</v>
+      </c>
+      <c r="G13" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="B14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="D15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="D16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:20">
       <c r="D17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:20">
       <c r="D18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:20">
       <c r="D19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:20">
       <c r="D20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:20">
       <c r="F21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -3386,28 +3385,28 @@
     </row>
     <row r="23" spans="1:20" s="4" customFormat="1">
       <c r="A23" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="E23" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="F23" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="G23" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="H23" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -3415,7 +3414,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C25" s="29"/>
       <c r="D25" s="29"/>
@@ -3441,74 +3440,74 @@
         <v>3</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="F26" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="H26" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="I26" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="I26" s="5" t="s">
+      <c r="J26" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:20">
       <c r="B27" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E27" t="s">
         <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="I27" t="s">
         <v>16</v>
       </c>
       <c r="J27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:20">
       <c r="B28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E28" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -3525,10 +3524,10 @@
     </row>
     <row r="29" spans="1:20">
       <c r="B29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
         <v>24</v>
@@ -3540,10 +3539,10 @@
         <v>27</v>
       </c>
       <c r="G29" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="H29" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="I29" t="s">
         <v>30</v>
@@ -3551,16 +3550,16 @@
     </row>
     <row r="30" spans="1:20">
       <c r="B30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E30" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F30" t="s">
         <v>34</v>
@@ -3572,15 +3571,15 @@
         <v>36</v>
       </c>
       <c r="I30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:20">
       <c r="B31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D31" t="s">
         <v>38</v>
@@ -3595,7 +3594,7 @@
         <v>33</v>
       </c>
       <c r="H31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I31" t="s">
         <v>42</v>
@@ -3603,7 +3602,7 @@
     </row>
     <row r="32" spans="1:20">
       <c r="B32" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C32" t="s">
         <v>40</v>
@@ -3612,50 +3611,50 @@
         <v>28</v>
       </c>
       <c r="E32" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H32" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="I32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="C33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D33" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E33" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H33" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="I33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="C34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E34" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H34" t="s">
         <v>29</v>
@@ -3666,7 +3665,7 @@
     </row>
     <row r="35" spans="1:10">
       <c r="C35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D35" t="s">
         <v>31</v>
@@ -3675,7 +3674,7 @@
         <v>25</v>
       </c>
       <c r="G35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H35" t="s">
         <v>41</v>
@@ -3683,13 +3682,13 @@
     </row>
     <row r="36" spans="1:10">
       <c r="C36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H36" t="s">
         <v>22</v>
@@ -3697,24 +3696,24 @@
     </row>
     <row r="37" spans="1:10">
       <c r="C37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D37" t="s">
         <v>35</v>
       </c>
       <c r="G37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="C38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
       </c>
       <c r="G38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -3725,7 +3724,7 @@
         <v>43</v>
       </c>
       <c r="G39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -3733,62 +3732,62 @@
         <v>44</v>
       </c>
       <c r="G40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="C41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G41" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="G42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="G43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="6" customFormat="1">
       <c r="A45" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -3796,7 +3795,7 @@
         <v>1</v>
       </c>
       <c r="B49" s="28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C49" s="28"/>
       <c r="D49" s="28"/>
@@ -3816,336 +3815,336 @@
         <v>3</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="E50" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="F50" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="G50" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="B51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C51" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D51" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E51" t="s">
+        <v>113</v>
+      </c>
+      <c r="F51" t="s">
         <v>114</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>115</v>
-      </c>
-      <c r="G51" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="B52" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C52" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D52" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E52" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F52" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G52" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="B53" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C53" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D53" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E53" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F53" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G53" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="B54" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D54" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E54" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F54" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G54" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="55" spans="1:14">
       <c r="B55" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C55" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D55" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E55" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F55" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G55" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="B56" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C56" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D56" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E56" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F56" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G56" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="57" spans="1:14">
       <c r="C57" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E57" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F57" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G57" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="58" spans="1:14">
       <c r="C58" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D58" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F58" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G58" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" spans="1:14">
       <c r="C59" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D59" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F59" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G59" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60" spans="1:14">
       <c r="C60" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D60" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F60" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G60" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="C61" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D61" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F61" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G61" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="62" spans="1:14">
       <c r="C62" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D62" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F62" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G62" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="C63" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D63" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F63" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="G63" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="64" spans="1:14">
       <c r="G64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="G65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="G66" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="G67" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="G68" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="G69" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="G70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="G71" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="G72" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="G73" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="G74" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="G75" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="G76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="G77" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:7" s="4" customFormat="1">
       <c r="A79" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B79" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="D79" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="E79" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="F79" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="E79" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>180</v>
-      </c>
       <c r="G79" s="4" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="81" spans="1:20">
@@ -4153,7 +4152,7 @@
         <v>1</v>
       </c>
       <c r="B81" s="29" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C81" s="29"/>
       <c r="D81" s="29"/>
@@ -4179,370 +4178,370 @@
         <v>3</v>
       </c>
       <c r="B82" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C82" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C82" s="6" t="s">
+      <c r="D82" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="D82" s="6" t="s">
+      <c r="E82" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="E82" s="6" t="s">
+      <c r="F82" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F82" s="6" t="s">
+      <c r="G82" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="G82" s="6" t="s">
+      <c r="H82" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="H82" s="6" t="s">
+      <c r="I82" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="I82" s="6" t="s">
+      <c r="J82" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="J82" s="6" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="83" spans="1:20">
       <c r="B83" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C83" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D83" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E83" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F83" t="s">
+        <v>190</v>
+      </c>
+      <c r="G83" t="s">
         <v>191</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
         <v>192</v>
       </c>
-      <c r="H83" t="s">
+      <c r="I83" t="s">
         <v>193</v>
       </c>
-      <c r="I83" t="s">
+      <c r="J83" t="s">
         <v>194</v>
-      </c>
-      <c r="J83" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="84" spans="1:20">
       <c r="B84" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C84" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D84" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E84" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F84" t="s">
+        <v>195</v>
+      </c>
+      <c r="G84" t="s">
         <v>196</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
         <v>197</v>
-      </c>
-      <c r="H84" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:20">
       <c r="B85" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C85" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D85" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E85" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:20">
       <c r="B86" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C86" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D86" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E86" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G86" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="87" spans="1:20">
       <c r="B87" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C87" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D87" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E87" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G87" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="88" spans="1:20">
       <c r="B88" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C88" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D88" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E88" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G88" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="89" spans="1:20">
       <c r="B89" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C89" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D89" t="s">
+        <v>200</v>
+      </c>
+      <c r="E89" t="s">
         <v>201</v>
       </c>
-      <c r="E89" t="s">
-        <v>202</v>
-      </c>
       <c r="G89" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="90" spans="1:20">
       <c r="B90" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C90" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D90" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E90" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="91" spans="1:20">
       <c r="B91" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C91" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E91" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="92" spans="1:20">
       <c r="B92" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C92" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E92" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="93" spans="1:20">
       <c r="B93" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C93" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E93" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="94" spans="1:20">
       <c r="B94" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C94" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E94" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="95" spans="1:20">
       <c r="B95" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C95" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E95" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="96" spans="1:20">
       <c r="B96" t="s">
+        <v>611</v>
+      </c>
+      <c r="C96" t="s">
+        <v>159</v>
+      </c>
+      <c r="E96" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14">
+      <c r="B97" t="s">
+        <v>612</v>
+      </c>
+      <c r="C97" t="s">
+        <v>639</v>
+      </c>
+      <c r="E97" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14">
+      <c r="B98" t="s">
         <v>613</v>
       </c>
-      <c r="C96" t="s">
-        <v>160</v>
-      </c>
-      <c r="E96" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15">
-      <c r="B97" t="s">
+      <c r="E98" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14">
+      <c r="B99" t="s">
         <v>614</v>
       </c>
-      <c r="C97" t="s">
-        <v>641</v>
-      </c>
-      <c r="E97" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15">
-      <c r="B98" t="s">
+      <c r="E99" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14">
+      <c r="B100" t="s">
         <v>615</v>
       </c>
-      <c r="E98" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15">
-      <c r="B99" t="s">
+      <c r="E100" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14">
+      <c r="B101" t="s">
         <v>616</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E101" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14">
+      <c r="B102" t="s">
+        <v>617</v>
+      </c>
+      <c r="E102" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14">
+      <c r="B103" t="s">
+        <v>618</v>
+      </c>
+      <c r="E103" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14">
+      <c r="E104" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14">
+      <c r="E105" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14">
+      <c r="B106" t="s">
+        <v>203</v>
+      </c>
+      <c r="E106" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="100" spans="1:15">
-      <c r="B100" t="s">
-        <v>617</v>
-      </c>
-      <c r="E100" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15">
-      <c r="B101" t="s">
-        <v>618</v>
-      </c>
-      <c r="E101" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15">
-      <c r="B102" t="s">
-        <v>619</v>
-      </c>
-      <c r="E102" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15">
-      <c r="B103" t="s">
-        <v>620</v>
-      </c>
-      <c r="E103" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15">
-      <c r="E104" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15">
-      <c r="E105" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15">
-      <c r="B106" t="s">
-        <v>204</v>
-      </c>
-      <c r="E106" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15" s="6" customFormat="1">
+    <row r="107" spans="1:14" s="6" customFormat="1">
       <c r="A107" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B107" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F107" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="G107" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="D107" s="6" t="s">
+      <c r="H107" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="E107" s="6" t="s">
+      <c r="I107" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="F107" s="6" t="s">
+      <c r="J107" s="6" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14">
+      <c r="A110" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="G107" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="H107" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="I107" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="J107" s="6" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15">
-      <c r="A110" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15">
+    </row>
+    <row r="111" spans="1:14">
       <c r="A111" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B111" s="28" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C111" s="28"/>
       <c r="D111" s="28"/>
@@ -4557,2622 +4556,2613 @@
       <c r="M111" s="28"/>
       <c r="N111" s="28"/>
     </row>
-    <row r="112" spans="1:15" s="3" customFormat="1">
+    <row r="112" spans="1:14" s="3" customFormat="1">
       <c r="A112" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B112" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C112" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="D112" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="D112" s="3" t="s">
+      <c r="E112" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="E112" s="3" t="s">
+      <c r="F112" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F112" s="3" t="s">
+      <c r="G112" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="G112" s="3" t="s">
+      <c r="H112" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="H112" s="3" t="s">
+      <c r="I112" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="I112" s="3" t="s">
+      <c r="J112" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="J112" s="3" t="s">
+      <c r="K112" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="K112" s="3" t="s">
+      <c r="L112" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="L112" s="3" t="s">
+      <c r="M112" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="M112" s="3" t="s">
+      <c r="N112" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="N112" s="3" t="s">
+    </row>
+    <row r="113" spans="2:14">
+      <c r="B113" t="s">
         <v>223</v>
       </c>
-      <c r="O112" s="3" t="s">
+      <c r="C113" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="113" spans="2:15">
-      <c r="B113" t="s">
+      <c r="D113" t="s">
         <v>225</v>
       </c>
-      <c r="C113" t="s">
+      <c r="E113" t="s">
         <v>226</v>
       </c>
-      <c r="D113" t="s">
+      <c r="F113" t="s">
         <v>227</v>
       </c>
-      <c r="E113" t="s">
-        <v>228</v>
-      </c>
-      <c r="F113" t="s">
+      <c r="G113" t="s">
         <v>229</v>
       </c>
-      <c r="G113" t="s">
+      <c r="H113" t="s">
         <v>230</v>
       </c>
-      <c r="H113" t="s">
+      <c r="I113" t="s">
         <v>231</v>
       </c>
-      <c r="I113" t="s">
+      <c r="J113" t="s">
         <v>232</v>
       </c>
-      <c r="J113" t="s">
+      <c r="K113" t="s">
         <v>233</v>
       </c>
-      <c r="K113" t="s">
+      <c r="L113" t="s">
         <v>234</v>
       </c>
-      <c r="L113" t="s">
+      <c r="M113" t="s">
         <v>235</v>
       </c>
-      <c r="M113" t="s">
+      <c r="N113" t="s">
         <v>236</v>
       </c>
-      <c r="N113" t="s">
+    </row>
+    <row r="114" spans="2:14">
+      <c r="B114" t="s">
         <v>237</v>
       </c>
-      <c r="O113" t="s">
+      <c r="C114" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="114" spans="2:15">
-      <c r="B114" t="s">
+      <c r="D114" t="s">
         <v>239</v>
       </c>
-      <c r="C114" t="s">
+      <c r="E114" t="s">
         <v>240</v>
       </c>
-      <c r="D114" t="s">
+      <c r="F114" t="s">
         <v>241</v>
       </c>
-      <c r="E114" t="s">
-        <v>242</v>
-      </c>
-      <c r="F114" t="s">
+      <c r="G114" t="s">
         <v>243</v>
       </c>
-      <c r="G114" t="s">
+      <c r="H114" t="s">
         <v>244</v>
       </c>
-      <c r="H114" t="s">
+      <c r="I114" t="s">
+        <v>231</v>
+      </c>
+      <c r="J114" t="s">
         <v>245</v>
       </c>
-      <c r="I114" t="s">
+      <c r="K114" t="s">
         <v>246</v>
       </c>
-      <c r="J114" t="s">
-        <v>233</v>
-      </c>
-      <c r="K114" t="s">
+      <c r="L114" t="s">
         <v>247</v>
       </c>
-      <c r="L114" t="s">
+      <c r="M114" t="s">
         <v>248</v>
       </c>
-      <c r="M114" t="s">
+      <c r="N114" t="s">
         <v>249</v>
       </c>
-      <c r="N114" t="s">
+    </row>
+    <row r="115" spans="2:14">
+      <c r="B115" t="s">
         <v>250</v>
       </c>
-      <c r="O114" t="s">
+      <c r="C115" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="115" spans="2:15">
-      <c r="B115" t="s">
+      <c r="D115" t="s">
         <v>252</v>
       </c>
-      <c r="C115" t="s">
+      <c r="E115" t="s">
         <v>253</v>
       </c>
-      <c r="D115" t="s">
+      <c r="F115" t="s">
         <v>254</v>
       </c>
-      <c r="E115" t="s">
-        <v>255</v>
-      </c>
-      <c r="F115" t="s">
+      <c r="H115" t="s">
         <v>256</v>
       </c>
-      <c r="G115" t="s">
+      <c r="I115" t="s">
         <v>257</v>
       </c>
-      <c r="I115" t="s">
+      <c r="J115" t="s">
         <v>258</v>
       </c>
-      <c r="J115" t="s">
+      <c r="K115" t="s">
         <v>259</v>
       </c>
-      <c r="K115" t="s">
+      <c r="L115" t="s">
         <v>260</v>
       </c>
-      <c r="L115" t="s">
+      <c r="M115" t="s">
         <v>261</v>
       </c>
-      <c r="M115" t="s">
+      <c r="N115" t="s">
         <v>262</v>
       </c>
-      <c r="N115" t="s">
+    </row>
+    <row r="116" spans="2:14">
+      <c r="B116" t="s">
         <v>263</v>
       </c>
-      <c r="O115" t="s">
+      <c r="C116" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="116" spans="2:15">
-      <c r="B116" t="s">
+      <c r="D116" t="s">
+        <v>94</v>
+      </c>
+      <c r="E116" t="s">
         <v>265</v>
       </c>
-      <c r="C116" t="s">
+      <c r="F116" t="s">
         <v>266</v>
       </c>
-      <c r="D116" t="s">
-        <v>95</v>
-      </c>
-      <c r="E116" t="s">
+      <c r="H116" t="s">
+        <v>268</v>
+      </c>
+      <c r="I116" t="s">
+        <v>269</v>
+      </c>
+      <c r="J116" t="s">
+        <v>270</v>
+      </c>
+      <c r="K116" t="s">
+        <v>271</v>
+      </c>
+      <c r="L116" t="s">
+        <v>272</v>
+      </c>
+      <c r="M116" t="s">
+        <v>273</v>
+      </c>
+      <c r="N116" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="117" spans="2:14">
+      <c r="B117" t="s">
+        <v>275</v>
+      </c>
+      <c r="C117" t="s">
+        <v>276</v>
+      </c>
+      <c r="D117" t="s">
+        <v>277</v>
+      </c>
+      <c r="E117" t="s">
+        <v>278</v>
+      </c>
+      <c r="F117" t="s">
+        <v>279</v>
+      </c>
+      <c r="H117" t="s">
+        <v>281</v>
+      </c>
+      <c r="I117" t="s">
+        <v>282</v>
+      </c>
+      <c r="J117" t="s">
+        <v>283</v>
+      </c>
+      <c r="K117" t="s">
+        <v>284</v>
+      </c>
+      <c r="L117" t="s">
+        <v>285</v>
+      </c>
+      <c r="N117" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="118" spans="2:14">
+      <c r="B118" t="s">
+        <v>287</v>
+      </c>
+      <c r="C118" t="s">
+        <v>288</v>
+      </c>
+      <c r="D118" t="s">
+        <v>289</v>
+      </c>
+      <c r="E118" t="s">
+        <v>290</v>
+      </c>
+      <c r="H118" t="s">
+        <v>292</v>
+      </c>
+      <c r="I118" t="s">
+        <v>293</v>
+      </c>
+      <c r="J118" t="s">
+        <v>294</v>
+      </c>
+      <c r="K118" t="s">
+        <v>295</v>
+      </c>
+      <c r="N118" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="119" spans="2:14">
+      <c r="B119" t="s">
+        <v>297</v>
+      </c>
+      <c r="C119" t="s">
+        <v>298</v>
+      </c>
+      <c r="D119" t="s">
+        <v>299</v>
+      </c>
+      <c r="E119" t="s">
+        <v>300</v>
+      </c>
+      <c r="H119" t="s">
+        <v>301</v>
+      </c>
+      <c r="I119" t="s">
+        <v>302</v>
+      </c>
+      <c r="J119" t="s">
+        <v>303</v>
+      </c>
+      <c r="K119" t="s">
+        <v>304</v>
+      </c>
+      <c r="N119" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="120" spans="2:14">
+      <c r="B120" t="s">
+        <v>306</v>
+      </c>
+      <c r="C120" t="s">
+        <v>307</v>
+      </c>
+      <c r="D120" t="s">
+        <v>308</v>
+      </c>
+      <c r="E120" t="s">
+        <v>309</v>
+      </c>
+      <c r="H120" t="s">
+        <v>310</v>
+      </c>
+      <c r="I120" t="s">
+        <v>366</v>
+      </c>
+      <c r="J120" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="121" spans="2:14">
+      <c r="B121" t="s">
+        <v>312</v>
+      </c>
+      <c r="C121" t="s">
+        <v>313</v>
+      </c>
+      <c r="D121" t="s">
+        <v>314</v>
+      </c>
+      <c r="E121" t="s">
+        <v>315</v>
+      </c>
+      <c r="J121" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="122" spans="2:14">
+      <c r="B122" t="s">
+        <v>317</v>
+      </c>
+      <c r="C122" t="s">
+        <v>318</v>
+      </c>
+      <c r="D122" t="s">
+        <v>319</v>
+      </c>
+      <c r="E122" t="s">
+        <v>240</v>
+      </c>
+      <c r="J122" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="123" spans="2:14">
+      <c r="B123" t="s">
+        <v>321</v>
+      </c>
+      <c r="C123" t="s">
+        <v>322</v>
+      </c>
+      <c r="E123" t="s">
+        <v>278</v>
+      </c>
+      <c r="J123" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="124" spans="2:14">
+      <c r="B124" t="s">
+        <v>324</v>
+      </c>
+      <c r="E124" t="s">
         <v>267</v>
       </c>
-      <c r="F116" t="s">
-        <v>268</v>
-      </c>
-      <c r="G116" t="s">
-        <v>269</v>
-      </c>
-      <c r="I116" t="s">
-        <v>270</v>
-      </c>
-      <c r="J116" t="s">
-        <v>271</v>
-      </c>
-      <c r="K116" t="s">
-        <v>272</v>
-      </c>
-      <c r="L116" t="s">
-        <v>273</v>
-      </c>
-      <c r="M116" t="s">
-        <v>274</v>
-      </c>
-      <c r="N116" t="s">
-        <v>275</v>
-      </c>
-      <c r="O116" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="117" spans="2:15">
-      <c r="B117" t="s">
-        <v>277</v>
-      </c>
-      <c r="C117" t="s">
-        <v>278</v>
-      </c>
-      <c r="D117" t="s">
-        <v>279</v>
-      </c>
-      <c r="E117" t="s">
+      <c r="J124" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="125" spans="2:14">
+      <c r="E125" t="s">
         <v>280</v>
       </c>
-      <c r="F117" t="s">
-        <v>281</v>
-      </c>
-      <c r="G117" t="s">
-        <v>282</v>
-      </c>
-      <c r="I117" t="s">
-        <v>283</v>
-      </c>
-      <c r="J117" t="s">
-        <v>284</v>
-      </c>
-      <c r="K117" t="s">
-        <v>285</v>
-      </c>
-      <c r="L117" t="s">
-        <v>286</v>
-      </c>
-      <c r="M117" t="s">
-        <v>287</v>
-      </c>
-      <c r="O117" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="118" spans="2:15">
-      <c r="B118" t="s">
-        <v>289</v>
-      </c>
-      <c r="C118" t="s">
-        <v>290</v>
-      </c>
-      <c r="D118" t="s">
+      <c r="J125" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="126" spans="2:14">
+      <c r="E126" t="s">
         <v>291</v>
       </c>
-      <c r="E118" t="s">
-        <v>292</v>
-      </c>
-      <c r="G118" t="s">
-        <v>293</v>
-      </c>
-      <c r="I118" t="s">
-        <v>294</v>
-      </c>
-      <c r="J118" t="s">
-        <v>295</v>
-      </c>
-      <c r="K118" t="s">
-        <v>296</v>
-      </c>
-      <c r="L118" t="s">
-        <v>297</v>
-      </c>
-      <c r="O118" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="119" spans="2:15">
-      <c r="B119" t="s">
-        <v>299</v>
-      </c>
-      <c r="C119" t="s">
-        <v>300</v>
-      </c>
-      <c r="D119" t="s">
-        <v>301</v>
-      </c>
-      <c r="E119" t="s">
-        <v>302</v>
-      </c>
-      <c r="I119" t="s">
-        <v>303</v>
-      </c>
-      <c r="J119" t="s">
-        <v>304</v>
-      </c>
-      <c r="K119" t="s">
-        <v>305</v>
-      </c>
-      <c r="L119" t="s">
-        <v>306</v>
-      </c>
-      <c r="O119" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="120" spans="2:15">
-      <c r="B120" t="s">
-        <v>308</v>
-      </c>
-      <c r="C120" t="s">
-        <v>309</v>
-      </c>
-      <c r="D120" t="s">
-        <v>310</v>
-      </c>
-      <c r="E120" t="s">
-        <v>311</v>
-      </c>
-      <c r="I120" t="s">
-        <v>312</v>
-      </c>
-      <c r="J120" t="s">
-        <v>368</v>
-      </c>
-      <c r="K120" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="121" spans="2:15">
-      <c r="B121" t="s">
-        <v>314</v>
-      </c>
-      <c r="C121" t="s">
-        <v>315</v>
-      </c>
-      <c r="D121" t="s">
-        <v>316</v>
-      </c>
-      <c r="E121" t="s">
-        <v>317</v>
-      </c>
-      <c r="K121" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="122" spans="2:15">
-      <c r="B122" t="s">
-        <v>319</v>
-      </c>
-      <c r="C122" t="s">
-        <v>320</v>
-      </c>
-      <c r="D122" t="s">
-        <v>321</v>
-      </c>
-      <c r="K122" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="123" spans="2:15">
-      <c r="B123" t="s">
-        <v>323</v>
-      </c>
-      <c r="C123" t="s">
-        <v>324</v>
-      </c>
-      <c r="K123" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="124" spans="2:15">
-      <c r="B124" t="s">
-        <v>326</v>
-      </c>
-      <c r="K124" t="s">
+      <c r="J126" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="125" spans="2:15">
-      <c r="K125" t="s">
+    <row r="127" spans="2:14">
+      <c r="J127" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="126" spans="2:15">
-      <c r="K126" t="s">
+    <row r="128" spans="2:14">
+      <c r="J128" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="127" spans="2:15">
-      <c r="K127" t="s">
+    <row r="134" spans="1:20" s="4" customFormat="1">
+      <c r="A134" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B134" s="4" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="128" spans="2:15">
-      <c r="K128" t="s">
+      <c r="C134" s="4" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="129" spans="1:20" s="4" customFormat="1">
-      <c r="A129" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B129" s="4" t="s">
+      <c r="D134" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="C129" s="4" t="s">
+      <c r="E134" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="D129" s="4" t="s">
+      <c r="F134" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="E129" s="4" t="s">
+      <c r="G134" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="H134" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="F129" s="4" t="s">
+      <c r="I134" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="G129" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="H129" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="I129" s="4" t="s">
+      <c r="J134" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="J129" s="4" t="s">
+      <c r="K134" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="K129" s="4" t="s">
+      <c r="L134" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="L129" s="4" t="s">
+      <c r="M134" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="M129" s="4" t="s">
+      <c r="N134" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="N129" s="4" t="s">
+    </row>
+    <row r="136" spans="1:20">
+      <c r="A136" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B136" s="29" t="s">
         <v>342</v>
       </c>
-      <c r="O129" s="4" t="s">
+      <c r="C136" s="29"/>
+      <c r="D136" s="29"/>
+      <c r="E136" s="29"/>
+      <c r="F136" s="29"/>
+      <c r="G136" s="29"/>
+      <c r="H136" s="29"/>
+      <c r="I136" s="30"/>
+      <c r="J136" s="30"/>
+      <c r="K136" s="30"/>
+      <c r="L136" s="30"/>
+      <c r="M136" s="30"/>
+      <c r="N136" s="30"/>
+      <c r="O136" s="30"/>
+      <c r="P136" s="30"/>
+      <c r="Q136" s="30"/>
+      <c r="R136" s="30"/>
+      <c r="S136" s="30"/>
+      <c r="T136" s="30"/>
+    </row>
+    <row r="137" spans="1:20" s="5" customFormat="1">
+      <c r="A137" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B137" s="5" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="131" spans="1:20">
-      <c r="A131" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B131" s="29" t="s">
+      <c r="C137" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="C131" s="29"/>
-      <c r="D131" s="29"/>
-      <c r="E131" s="29"/>
-      <c r="F131" s="29"/>
-      <c r="G131" s="29"/>
-      <c r="H131" s="29"/>
-      <c r="I131" s="30"/>
-      <c r="J131" s="30"/>
-      <c r="K131" s="30"/>
-      <c r="L131" s="30"/>
-      <c r="M131" s="30"/>
-      <c r="N131" s="30"/>
-      <c r="O131" s="30"/>
-      <c r="P131" s="30"/>
-      <c r="Q131" s="30"/>
-      <c r="R131" s="30"/>
-      <c r="S131" s="30"/>
-      <c r="T131" s="30"/>
-    </row>
-    <row r="132" spans="1:20" s="5" customFormat="1">
-      <c r="A132" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B132" s="5" t="s">
+      <c r="D137" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="C132" s="5" t="s">
+      <c r="E137" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="D132" s="5" t="s">
+      <c r="F137" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="E132" s="5" t="s">
+      <c r="G137" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="F132" s="5" t="s">
+      <c r="H137" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="G132" s="5" t="s">
+      <c r="I137" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="H132" s="5" t="s">
+      <c r="J137" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="I132" s="5" t="s">
+      <c r="K137" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="J132" s="5" t="s">
+      <c r="L137" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="K132" s="5" t="s">
+      <c r="M137" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="L132" s="5" t="s">
+      <c r="N137" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="M132" s="5" t="s">
+      <c r="O137" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="N132" s="5" t="s">
+      <c r="P137" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="O132" s="5" t="s">
+      <c r="Q137" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="P132" s="5" t="s">
+      <c r="R137" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="Q132" s="5" t="s">
+      <c r="S137" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="R132" s="5" t="s">
+      <c r="T137" s="5" t="s">
         <v>361</v>
-      </c>
-      <c r="S132" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="T132" s="5" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="133" spans="1:20">
-      <c r="B133" t="s">
-        <v>285</v>
-      </c>
-      <c r="C133" t="s">
-        <v>237</v>
-      </c>
-      <c r="D133" t="s">
-        <v>236</v>
-      </c>
-      <c r="E133" t="s">
-        <v>235</v>
-      </c>
-      <c r="F133" t="s">
-        <v>233</v>
-      </c>
-      <c r="G133" t="s">
-        <v>232</v>
-      </c>
-      <c r="H133" t="s">
-        <v>364</v>
-      </c>
-      <c r="I133" t="s">
-        <v>365</v>
-      </c>
-      <c r="J133" t="s">
-        <v>269</v>
-      </c>
-      <c r="K133" t="s">
-        <v>366</v>
-      </c>
-      <c r="L133" t="s">
-        <v>367</v>
-      </c>
-      <c r="M133" t="s">
-        <v>325</v>
-      </c>
-      <c r="N133" t="s">
-        <v>230</v>
-      </c>
-      <c r="O133" t="s">
-        <v>229</v>
-      </c>
-      <c r="P133" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q133" t="s">
-        <v>228</v>
-      </c>
-      <c r="R133" t="s">
-        <v>265</v>
-      </c>
-      <c r="S133" t="s">
-        <v>247</v>
-      </c>
-      <c r="T133" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="134" spans="1:20">
-      <c r="B134" t="s">
-        <v>225</v>
-      </c>
-      <c r="C134" t="s">
-        <v>250</v>
-      </c>
-      <c r="D134" t="s">
-        <v>249</v>
-      </c>
-      <c r="E134" t="s">
-        <v>248</v>
-      </c>
-      <c r="F134" t="s">
-        <v>368</v>
-      </c>
-      <c r="G134" t="s">
-        <v>246</v>
-      </c>
-      <c r="I134" t="s">
-        <v>369</v>
-      </c>
-      <c r="J134" t="s">
-        <v>282</v>
-      </c>
-      <c r="K134" t="s">
-        <v>370</v>
-      </c>
-      <c r="L134" t="s">
-        <v>371</v>
-      </c>
-      <c r="N134" t="s">
-        <v>244</v>
-      </c>
-      <c r="O134" t="s">
-        <v>243</v>
-      </c>
-      <c r="P134" t="s">
-        <v>307</v>
-      </c>
-      <c r="Q134" t="s">
-        <v>242</v>
-      </c>
-      <c r="R134" t="s">
-        <v>289</v>
-      </c>
-      <c r="S134" t="s">
-        <v>260</v>
-      </c>
-      <c r="T134" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="135" spans="1:20">
-      <c r="B135" t="s">
-        <v>239</v>
-      </c>
-      <c r="C135" t="s">
-        <v>263</v>
-      </c>
-      <c r="D135" t="s">
-        <v>262</v>
-      </c>
-      <c r="E135" t="s">
-        <v>261</v>
-      </c>
-      <c r="F135" t="s">
-        <v>259</v>
-      </c>
-      <c r="G135" t="s">
-        <v>258</v>
-      </c>
-      <c r="I135" t="s">
-        <v>372</v>
-      </c>
-      <c r="J135" t="s">
-        <v>293</v>
-      </c>
-      <c r="K135" t="s">
-        <v>373</v>
-      </c>
-      <c r="N135" t="s">
-        <v>257</v>
-      </c>
-      <c r="O135" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q135" t="s">
-        <v>255</v>
-      </c>
-      <c r="R135" t="s">
-        <v>253</v>
-      </c>
-      <c r="S135" t="s">
-        <v>272</v>
-      </c>
-      <c r="T135" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="136" spans="1:20">
-      <c r="B136" t="s">
-        <v>252</v>
-      </c>
-      <c r="C136" t="s">
-        <v>275</v>
-      </c>
-      <c r="D136" t="s">
-        <v>274</v>
-      </c>
-      <c r="E136" t="s">
-        <v>273</v>
-      </c>
-      <c r="F136" t="s">
-        <v>271</v>
-      </c>
-      <c r="G136" t="s">
-        <v>270</v>
-      </c>
-      <c r="O136" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q136" t="s">
-        <v>267</v>
-      </c>
-      <c r="R136" t="s">
-        <v>266</v>
-      </c>
-      <c r="S136" t="s">
-        <v>234</v>
-      </c>
-      <c r="T136" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="137" spans="1:20">
-      <c r="B137" t="s">
-        <v>323</v>
-      </c>
-      <c r="C137" t="s">
-        <v>231</v>
-      </c>
-      <c r="D137" t="s">
-        <v>287</v>
-      </c>
-      <c r="E137" t="s">
-        <v>286</v>
-      </c>
-      <c r="F137" t="s">
-        <v>284</v>
-      </c>
-      <c r="G137" t="s">
-        <v>283</v>
-      </c>
-      <c r="O137" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q137" t="s">
-        <v>280</v>
-      </c>
-      <c r="R137" t="s">
-        <v>299</v>
-      </c>
-      <c r="S137" t="s">
-        <v>296</v>
-      </c>
-      <c r="T137" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="138" spans="1:20">
       <c r="B138" t="s">
-        <v>374</v>
+        <v>283</v>
       </c>
       <c r="C138" t="s">
+        <v>235</v>
+      </c>
+      <c r="D138" t="s">
+        <v>234</v>
+      </c>
+      <c r="E138" t="s">
+        <v>233</v>
+      </c>
+      <c r="F138" t="s">
+        <v>231</v>
+      </c>
+      <c r="G138" t="s">
+        <v>230</v>
+      </c>
+      <c r="H138" t="s">
+        <v>362</v>
+      </c>
+      <c r="I138" t="s">
+        <v>363</v>
+      </c>
+      <c r="J138" t="s">
+        <v>267</v>
+      </c>
+      <c r="K138" t="s">
+        <v>364</v>
+      </c>
+      <c r="L138" t="s">
+        <v>365</v>
+      </c>
+      <c r="M138" t="s">
+        <v>323</v>
+      </c>
+      <c r="N138" t="s">
+        <v>228</v>
+      </c>
+      <c r="O138" t="s">
+        <v>227</v>
+      </c>
+      <c r="P138" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>226</v>
+      </c>
+      <c r="R138" t="s">
+        <v>263</v>
+      </c>
+      <c r="S138" t="s">
         <v>245</v>
       </c>
-      <c r="D138" t="s">
-        <v>238</v>
-      </c>
-      <c r="E138" t="s">
-        <v>297</v>
-      </c>
-      <c r="F138" t="s">
-        <v>295</v>
-      </c>
-      <c r="G138" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q138" t="s">
-        <v>292</v>
-      </c>
-      <c r="R138" t="s">
-        <v>308</v>
-      </c>
-      <c r="S138" t="s">
-        <v>226</v>
-      </c>
       <c r="T138" t="s">
-        <v>291</v>
+        <v>225</v>
       </c>
     </row>
     <row r="139" spans="1:20">
       <c r="B139" t="s">
-        <v>375</v>
+        <v>223</v>
+      </c>
+      <c r="C139" t="s">
+        <v>248</v>
       </c>
       <c r="D139" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E139" t="s">
-        <v>306</v>
+        <v>246</v>
       </c>
       <c r="F139" t="s">
-        <v>304</v>
+        <v>366</v>
       </c>
       <c r="G139" t="s">
-        <v>303</v>
+        <v>244</v>
+      </c>
+      <c r="I139" t="s">
+        <v>367</v>
+      </c>
+      <c r="J139" t="s">
+        <v>280</v>
+      </c>
+      <c r="K139" t="s">
+        <v>368</v>
+      </c>
+      <c r="L139" t="s">
+        <v>369</v>
+      </c>
+      <c r="N139" t="s">
+        <v>242</v>
+      </c>
+      <c r="O139" t="s">
+        <v>241</v>
+      </c>
+      <c r="P139" t="s">
+        <v>305</v>
       </c>
       <c r="Q139" t="s">
-        <v>302</v>
+        <v>240</v>
       </c>
       <c r="R139" t="s">
-        <v>319</v>
+        <v>287</v>
       </c>
       <c r="S139" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="T139" t="s">
-        <v>301</v>
+        <v>239</v>
       </c>
     </row>
     <row r="140" spans="1:20">
       <c r="B140" t="s">
-        <v>277</v>
+        <v>237</v>
+      </c>
+      <c r="C140" t="s">
+        <v>261</v>
       </c>
       <c r="D140" t="s">
-        <v>264</v>
+        <v>260</v>
+      </c>
+      <c r="E140" t="s">
+        <v>259</v>
+      </c>
+      <c r="F140" t="s">
+        <v>257</v>
       </c>
       <c r="G140" t="s">
-        <v>312</v>
+        <v>256</v>
+      </c>
+      <c r="I140" t="s">
+        <v>370</v>
+      </c>
+      <c r="J140" t="s">
+        <v>291</v>
+      </c>
+      <c r="K140" t="s">
+        <v>371</v>
+      </c>
+      <c r="N140" t="s">
+        <v>255</v>
+      </c>
+      <c r="O140" t="s">
+        <v>254</v>
       </c>
       <c r="Q140" t="s">
-        <v>311</v>
+        <v>253</v>
       </c>
       <c r="R140" t="s">
-        <v>314</v>
+        <v>251</v>
       </c>
       <c r="S140" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="T140" t="s">
-        <v>310</v>
+        <v>252</v>
       </c>
     </row>
     <row r="141" spans="1:20">
       <c r="B141" t="s">
-        <v>318</v>
+        <v>250</v>
+      </c>
+      <c r="C141" t="s">
+        <v>273</v>
       </c>
       <c r="D141" t="s">
-        <v>276</v>
+        <v>272</v>
+      </c>
+      <c r="E141" t="s">
+        <v>271</v>
+      </c>
+      <c r="F141" t="s">
+        <v>269</v>
+      </c>
+      <c r="G141" t="s">
+        <v>268</v>
+      </c>
+      <c r="O141" t="s">
+        <v>266</v>
       </c>
       <c r="Q141" t="s">
-        <v>317</v>
+        <v>265</v>
       </c>
       <c r="R141" t="s">
-        <v>324</v>
+        <v>264</v>
       </c>
       <c r="S141" t="s">
-        <v>290</v>
+        <v>232</v>
       </c>
       <c r="T141" t="s">
-        <v>321</v>
+        <v>94</v>
       </c>
     </row>
     <row r="142" spans="1:20">
       <c r="B142" t="s">
-        <v>322</v>
+        <v>321</v>
+      </c>
+      <c r="C142" t="s">
+        <v>229</v>
       </c>
       <c r="D142" t="s">
-        <v>288</v>
+        <v>285</v>
+      </c>
+      <c r="E142" t="s">
+        <v>284</v>
+      </c>
+      <c r="F142" t="s">
+        <v>282</v>
+      </c>
+      <c r="G142" t="s">
+        <v>281</v>
+      </c>
+      <c r="O142" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>278</v>
       </c>
       <c r="R142" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="S142" t="s">
-        <v>300</v>
+        <v>294</v>
+      </c>
+      <c r="T142" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="143" spans="1:20">
       <c r="B143" t="s">
-        <v>326</v>
+        <v>372</v>
+      </c>
+      <c r="C143" t="s">
+        <v>243</v>
+      </c>
+      <c r="D143" t="s">
+        <v>236</v>
+      </c>
+      <c r="E143" t="s">
+        <v>295</v>
+      </c>
+      <c r="F143" t="s">
+        <v>293</v>
+      </c>
+      <c r="G143" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>290</v>
       </c>
       <c r="R143" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="S143" t="s">
-        <v>309</v>
+        <v>224</v>
+      </c>
+      <c r="T143" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="144" spans="1:20">
       <c r="B144" t="s">
-        <v>327</v>
+        <v>373</v>
+      </c>
+      <c r="D144" t="s">
+        <v>249</v>
+      </c>
+      <c r="E144" t="s">
+        <v>304</v>
+      </c>
+      <c r="F144" t="s">
+        <v>302</v>
+      </c>
+      <c r="G144" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>300</v>
+      </c>
+      <c r="R144" t="s">
+        <v>317</v>
+      </c>
+      <c r="S144" t="s">
+        <v>238</v>
+      </c>
+      <c r="T144" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="145" spans="1:20">
       <c r="B145" t="s">
-        <v>328</v>
+        <v>275</v>
+      </c>
+      <c r="D145" t="s">
+        <v>262</v>
+      </c>
+      <c r="G145" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>309</v>
+      </c>
+      <c r="R145" t="s">
+        <v>312</v>
+      </c>
+      <c r="S145" t="s">
+        <v>276</v>
+      </c>
+      <c r="T145" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="146" spans="1:20">
       <c r="B146" t="s">
-        <v>329</v>
+        <v>316</v>
+      </c>
+      <c r="D146" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>315</v>
+      </c>
+      <c r="R146" t="s">
+        <v>322</v>
+      </c>
+      <c r="S146" t="s">
+        <v>288</v>
+      </c>
+      <c r="T146" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="147" spans="1:20">
       <c r="B147" t="s">
-        <v>330</v>
+        <v>320</v>
+      </c>
+      <c r="D147" t="s">
+        <v>286</v>
+      </c>
+      <c r="R147" t="s">
+        <v>313</v>
+      </c>
+      <c r="S147" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="148" spans="1:20">
       <c r="B148" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="149" spans="1:20" s="6" customFormat="1">
-      <c r="A149" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B149" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="R148" t="s">
+        <v>318</v>
+      </c>
+      <c r="S148" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="149" spans="1:20">
+      <c r="B149" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="150" spans="1:20">
+      <c r="B150" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="151" spans="1:20">
+      <c r="B151" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="152" spans="1:20">
+      <c r="B152" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="153" spans="1:20">
+      <c r="B153" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="154" spans="1:20" s="6" customFormat="1">
+      <c r="A154" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="G154" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H154" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="I154" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="J154" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="K154" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="L154" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="M154" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="N154" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="O154" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="P154" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q154" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="R154" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="S154" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="T154" s="6" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="157" spans="1:20">
+      <c r="A157" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="C149" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="D149" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="E149" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="F149" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="G149" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="H149" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="I149" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="J149" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="K149" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="L149" s="6" t="s">
+    </row>
+    <row r="158" spans="1:20">
+      <c r="A158" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B158" s="28" t="s">
         <v>377</v>
       </c>
-      <c r="M149" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="N149" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="O149" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="P149" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="Q149" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="R149" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="S149" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="T149" s="6" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="152" spans="1:20">
-      <c r="A152" s="7" t="s">
+      <c r="C158" s="28"/>
+      <c r="D158" s="28"/>
+      <c r="E158" s="28"/>
+      <c r="F158" s="28"/>
+      <c r="G158" s="28"/>
+      <c r="H158" s="28"/>
+      <c r="I158" s="28"/>
+      <c r="J158" s="28"/>
+      <c r="K158" s="28"/>
+      <c r="L158" s="28"/>
+      <c r="M158" s="28"/>
+      <c r="N158" s="28"/>
+    </row>
+    <row r="159" spans="1:20" s="12" customFormat="1">
+      <c r="A159" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B159" s="8" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="153" spans="1:20">
-      <c r="A153" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B153" s="28" t="s">
+      <c r="C159" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="C153" s="28"/>
-      <c r="D153" s="28"/>
-      <c r="E153" s="28"/>
-      <c r="F153" s="28"/>
-      <c r="G153" s="28"/>
-      <c r="H153" s="28"/>
-      <c r="I153" s="28"/>
-      <c r="J153" s="28"/>
-      <c r="K153" s="28"/>
-      <c r="L153" s="28"/>
-      <c r="M153" s="28"/>
-      <c r="N153" s="28"/>
-    </row>
-    <row r="154" spans="1:20" s="12" customFormat="1">
-      <c r="A154" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B154" s="8" t="s">
+      <c r="D159" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="C154" s="8" t="s">
+      <c r="E159" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="D154" s="8" t="s">
+      <c r="F159" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="E154" s="9" t="s">
+      <c r="G159" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="F154" s="10" t="s">
+      <c r="H159" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="G154" s="11" t="s">
+      <c r="I159" s="11" t="s">
         <v>385</v>
       </c>
-      <c r="H154" s="11" t="s">
+    </row>
+    <row r="160" spans="1:20" ht="30">
+      <c r="B160" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="I154" s="11" t="s">
+      <c r="C160" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="155" spans="1:20" ht="30">
-      <c r="B155" s="13" t="s">
+      <c r="D160" t="s">
         <v>388</v>
       </c>
-      <c r="C155" t="s">
+      <c r="E160" t="s">
         <v>389</v>
       </c>
-      <c r="D155" t="s">
+      <c r="F160" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="E155" t="s">
+      <c r="G160" t="s">
         <v>391</v>
       </c>
-      <c r="F155" s="14" t="s">
-        <v>392</v>
-      </c>
-      <c r="G155" t="s">
+      <c r="H160" t="s">
+        <v>406</v>
+      </c>
+      <c r="I160" s="15" t="s">
         <v>393</v>
-      </c>
-      <c r="H155" t="s">
-        <v>408</v>
-      </c>
-      <c r="I155" s="15" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="156" spans="1:20">
-      <c r="B156" t="s">
-        <v>396</v>
-      </c>
-      <c r="C156" t="s">
-        <v>397</v>
-      </c>
-      <c r="D156" t="s">
-        <v>398</v>
-      </c>
-      <c r="E156" t="s">
-        <v>391</v>
-      </c>
-      <c r="F156" t="s">
-        <v>406</v>
-      </c>
-      <c r="G156" t="s">
-        <v>399</v>
-      </c>
-      <c r="H156" t="s">
-        <v>416</v>
-      </c>
-      <c r="I156" s="15" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="157" spans="1:20" ht="30">
-      <c r="B157" s="16" t="s">
-        <v>402</v>
-      </c>
-      <c r="C157" s="16" t="s">
-        <v>403</v>
-      </c>
-      <c r="D157" t="s">
-        <v>404</v>
-      </c>
-      <c r="E157" t="s">
-        <v>405</v>
-      </c>
-      <c r="F157" s="14" t="s">
-        <v>414</v>
-      </c>
-      <c r="G157" t="s">
-        <v>407</v>
-      </c>
-      <c r="H157" t="s">
-        <v>422</v>
-      </c>
-      <c r="I157" s="17" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="158" spans="1:20">
-      <c r="B158" t="s">
-        <v>410</v>
-      </c>
-      <c r="C158" t="s">
-        <v>411</v>
-      </c>
-      <c r="D158" t="s">
-        <v>412</v>
-      </c>
-      <c r="E158" t="s">
-        <v>413</v>
-      </c>
-      <c r="F158" s="14" t="s">
-        <v>463</v>
-      </c>
-      <c r="G158" t="s">
-        <v>415</v>
-      </c>
-      <c r="H158" t="s">
-        <v>428</v>
-      </c>
-      <c r="I158" s="15" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="159" spans="1:20">
-      <c r="B159" t="s">
-        <v>418</v>
-      </c>
-      <c r="C159" t="s">
-        <v>419</v>
-      </c>
-      <c r="E159" t="s">
-        <v>420</v>
-      </c>
-      <c r="F159" t="s">
-        <v>465</v>
-      </c>
-      <c r="G159" t="s">
-        <v>421</v>
-      </c>
-      <c r="H159" t="s">
-        <v>434</v>
-      </c>
-      <c r="I159" s="15" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="160" spans="1:20">
-      <c r="B160" t="s">
-        <v>424</v>
-      </c>
-      <c r="C160" t="s">
-        <v>425</v>
-      </c>
-      <c r="E160" t="s">
-        <v>426</v>
-      </c>
-      <c r="F160" t="s">
-        <v>392</v>
-      </c>
-      <c r="G160" s="18"/>
-      <c r="I160" s="15" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="161" spans="2:9">
       <c r="B161" t="s">
-        <v>430</v>
+        <v>394</v>
       </c>
       <c r="C161" t="s">
-        <v>431</v>
+        <v>395</v>
+      </c>
+      <c r="D161" t="s">
+        <v>396</v>
       </c>
       <c r="E161" t="s">
-        <v>432</v>
+        <v>389</v>
       </c>
       <c r="F161" t="s">
-        <v>406</v>
-      </c>
-      <c r="I161" s="19" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="162" spans="2:9">
-      <c r="B162" t="s">
-        <v>396</v>
-      </c>
-      <c r="C162" t="s">
-        <v>436</v>
+        <v>404</v>
+      </c>
+      <c r="G161" t="s">
+        <v>397</v>
+      </c>
+      <c r="H161" t="s">
+        <v>414</v>
+      </c>
+      <c r="I161" s="15" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="162" spans="2:9" ht="30">
+      <c r="B162" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="C162" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="D162" t="s">
+        <v>402</v>
       </c>
       <c r="E162" t="s">
-        <v>437</v>
-      </c>
-      <c r="F162" t="s">
-        <v>470</v>
-      </c>
-      <c r="I162" s="19" t="s">
-        <v>640</v>
+        <v>403</v>
+      </c>
+      <c r="F162" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="G162" t="s">
+        <v>405</v>
+      </c>
+      <c r="H162" t="s">
+        <v>420</v>
+      </c>
+      <c r="I162" s="17" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="163" spans="2:9">
       <c r="B163" t="s">
-        <v>440</v>
+        <v>408</v>
       </c>
       <c r="C163" t="s">
-        <v>441</v>
+        <v>409</v>
+      </c>
+      <c r="D163" t="s">
+        <v>410</v>
       </c>
       <c r="E163" t="s">
-        <v>442</v>
-      </c>
-      <c r="F163" t="s">
-        <v>414</v>
+        <v>411</v>
+      </c>
+      <c r="F163" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="G163" t="s">
+        <v>413</v>
+      </c>
+      <c r="H163" t="s">
+        <v>426</v>
       </c>
       <c r="I163" s="15" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="164" spans="2:9" ht="30">
-      <c r="B164" s="14" t="s">
-        <v>445</v>
+        <v>415</v>
+      </c>
+    </row>
+    <row r="164" spans="2:9">
+      <c r="B164" t="s">
+        <v>416</v>
       </c>
       <c r="C164" t="s">
-        <v>446</v>
+        <v>417</v>
       </c>
       <c r="E164" t="s">
-        <v>447</v>
+        <v>418</v>
       </c>
       <c r="F164" t="s">
+        <v>463</v>
+      </c>
+      <c r="G164" t="s">
+        <v>419</v>
+      </c>
+      <c r="H164" t="s">
+        <v>432</v>
+      </c>
+      <c r="I164" s="15" t="s">
         <v>427</v>
-      </c>
-      <c r="I164" s="15" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="165" spans="2:9">
       <c r="B165" t="s">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="C165" t="s">
-        <v>431</v>
+        <v>423</v>
+      </c>
+      <c r="E165" t="s">
+        <v>424</v>
       </c>
       <c r="F165" t="s">
+        <v>390</v>
+      </c>
+      <c r="G165" s="18"/>
+      <c r="I165" s="15" t="s">
         <v>433</v>
-      </c>
-      <c r="I165" s="15" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="166" spans="2:9">
       <c r="B166" t="s">
-        <v>396</v>
+        <v>428</v>
       </c>
       <c r="C166" t="s">
-        <v>453</v>
+        <v>429</v>
+      </c>
+      <c r="E166" t="s">
+        <v>430</v>
       </c>
       <c r="F166" t="s">
-        <v>438</v>
-      </c>
-      <c r="I166" s="15" t="s">
-        <v>452</v>
+        <v>404</v>
+      </c>
+      <c r="I166" s="19" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="167" spans="2:9">
       <c r="B167" t="s">
-        <v>455</v>
+        <v>394</v>
       </c>
       <c r="C167" t="s">
-        <v>456</v>
+        <v>434</v>
+      </c>
+      <c r="E167" t="s">
+        <v>435</v>
       </c>
       <c r="F167" t="s">
-        <v>443</v>
-      </c>
-      <c r="I167" t="s">
-        <v>423</v>
+        <v>468</v>
+      </c>
+      <c r="I167" s="19" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="168" spans="2:9">
       <c r="B168" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="C168" t="s">
-        <v>459</v>
+        <v>439</v>
+      </c>
+      <c r="E168" t="s">
+        <v>440</v>
       </c>
       <c r="F168" t="s">
-        <v>448</v>
-      </c>
-      <c r="I168" s="27" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="169" spans="2:9">
-      <c r="B169" t="s">
-        <v>461</v>
+        <v>412</v>
+      </c>
+      <c r="I168" s="15" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="169" spans="2:9" ht="30">
+      <c r="B169" s="14" t="s">
+        <v>443</v>
       </c>
       <c r="C169" t="s">
-        <v>462</v>
+        <v>444</v>
+      </c>
+      <c r="E169" t="s">
+        <v>445</v>
       </c>
       <c r="F169" t="s">
-        <v>451</v>
-      </c>
-      <c r="I169" t="s">
-        <v>444</v>
+        <v>425</v>
+      </c>
+      <c r="I169" s="15" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="170" spans="2:9">
       <c r="B170" t="s">
-        <v>410</v>
+        <v>448</v>
       </c>
       <c r="C170" t="s">
-        <v>464</v>
+        <v>429</v>
       </c>
       <c r="F170" t="s">
-        <v>454</v>
-      </c>
-      <c r="I170" t="s">
-        <v>648</v>
+        <v>431</v>
+      </c>
+      <c r="I170" s="15" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="171" spans="2:9">
       <c r="B171" t="s">
-        <v>466</v>
+        <v>394</v>
       </c>
       <c r="C171" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="F171" t="s">
-        <v>457</v>
+        <v>436</v>
+      </c>
+      <c r="I171" s="15" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="172" spans="2:9">
       <c r="B172" t="s">
-        <v>468</v>
-      </c>
-      <c r="C172" s="20" t="s">
-        <v>469</v>
+        <v>453</v>
+      </c>
+      <c r="C172" t="s">
+        <v>454</v>
       </c>
       <c r="F172" t="s">
-        <v>460</v>
+        <v>441</v>
+      </c>
+      <c r="I172" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="173" spans="2:9">
       <c r="B173" t="s">
-        <v>418</v>
+        <v>456</v>
       </c>
       <c r="C173" t="s">
-        <v>491</v>
+        <v>457</v>
+      </c>
+      <c r="F173" t="s">
+        <v>446</v>
+      </c>
+      <c r="I173" s="27" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="174" spans="2:9">
       <c r="B174" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="C174" t="s">
-        <v>639</v>
+        <v>460</v>
+      </c>
+      <c r="F174" t="s">
+        <v>449</v>
+      </c>
+      <c r="I174" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="175" spans="2:9">
       <c r="B175" t="s">
-        <v>472</v>
+        <v>408</v>
+      </c>
+      <c r="C175" t="s">
+        <v>462</v>
+      </c>
+      <c r="F175" t="s">
+        <v>452</v>
+      </c>
+      <c r="I175" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="176" spans="2:9">
       <c r="B176" t="s">
-        <v>473</v>
+        <v>464</v>
+      </c>
+      <c r="C176" t="s">
+        <v>465</v>
+      </c>
+      <c r="F176" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="177" spans="1:20">
       <c r="B177" t="s">
+        <v>466</v>
+      </c>
+      <c r="C177" s="20" t="s">
+        <v>467</v>
+      </c>
+      <c r="F177" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="178" spans="1:20">
+      <c r="B178" t="s">
+        <v>416</v>
+      </c>
+      <c r="C178" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="179" spans="1:20">
+      <c r="B179" t="s">
+        <v>469</v>
+      </c>
+      <c r="C179" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="180" spans="1:20">
+      <c r="B180" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="181" spans="1:20">
+      <c r="B181" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="182" spans="1:20">
+      <c r="B182" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="183" spans="1:20">
+      <c r="B183" s="21" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="184" spans="1:20">
+      <c r="A184" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B184" s="22" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="178" spans="1:20">
-      <c r="B178" s="21" t="s">
+      <c r="C184" s="22" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="179" spans="1:20">
-      <c r="A179" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B179" s="22" t="s">
+      <c r="D184" s="22" t="s">
         <v>476</v>
       </c>
-      <c r="C179" s="22" t="s">
+      <c r="E184" s="23" t="s">
         <v>477</v>
       </c>
-      <c r="D179" s="22" t="s">
+      <c r="F184" s="24" t="s">
         <v>478</v>
       </c>
-      <c r="E179" s="23" t="s">
+      <c r="G184" s="22" t="s">
         <v>479</v>
       </c>
-      <c r="F179" s="24" t="s">
+      <c r="H184" s="22" t="s">
         <v>480</v>
       </c>
-      <c r="G179" s="22" t="s">
+      <c r="I184" s="22" t="s">
         <v>481</v>
       </c>
-      <c r="H179" s="22" t="s">
+    </row>
+    <row r="186" spans="1:20">
+      <c r="A186" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B186" s="29" t="s">
         <v>482</v>
       </c>
-      <c r="I179" s="22" t="s">
+      <c r="C186" s="29"/>
+      <c r="D186" s="29"/>
+      <c r="E186" s="29"/>
+      <c r="F186" s="29"/>
+      <c r="G186" s="29"/>
+      <c r="H186" s="29"/>
+      <c r="I186" s="30"/>
+      <c r="J186" s="30"/>
+      <c r="K186" s="30"/>
+      <c r="L186" s="30"/>
+      <c r="M186" s="30"/>
+      <c r="N186" s="30"/>
+      <c r="O186" s="30"/>
+      <c r="P186" s="30"/>
+      <c r="Q186" s="30"/>
+      <c r="R186" s="30"/>
+      <c r="S186" s="30"/>
+      <c r="T186" s="30"/>
+    </row>
+    <row r="187" spans="1:20" s="5" customFormat="1">
+      <c r="A187" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B187" s="5" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="181" spans="1:20">
-      <c r="A181" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B181" s="29" t="s">
+      <c r="C187" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="C181" s="29"/>
-      <c r="D181" s="29"/>
-      <c r="E181" s="29"/>
-      <c r="F181" s="29"/>
-      <c r="G181" s="29"/>
-      <c r="H181" s="29"/>
-      <c r="I181" s="30"/>
-      <c r="J181" s="30"/>
-      <c r="K181" s="30"/>
-      <c r="L181" s="30"/>
-      <c r="M181" s="30"/>
-      <c r="N181" s="30"/>
-      <c r="O181" s="30"/>
-      <c r="P181" s="30"/>
-      <c r="Q181" s="30"/>
-      <c r="R181" s="30"/>
-      <c r="S181" s="30"/>
-      <c r="T181" s="30"/>
-    </row>
-    <row r="182" spans="1:20" s="5" customFormat="1">
-      <c r="A182" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B182" s="5" t="s">
+      <c r="D187" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="C182" s="5" t="s">
+      <c r="E187" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="D182" s="5" t="s">
+      <c r="F187" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="G187" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="E182" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>621</v>
-      </c>
-      <c r="G182" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="H182" s="5" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="183" spans="1:20">
-      <c r="B183" t="s">
-        <v>389</v>
-      </c>
-      <c r="C183" t="s">
-        <v>388</v>
-      </c>
-      <c r="D183" t="s">
-        <v>390</v>
-      </c>
-      <c r="E183" t="s">
-        <v>393</v>
-      </c>
-      <c r="F183" t="s">
-        <v>392</v>
-      </c>
-      <c r="G183" t="s">
-        <v>400</v>
-      </c>
-      <c r="H183" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="184" spans="1:20">
-      <c r="B184" t="s">
-        <v>397</v>
-      </c>
-      <c r="C184" t="s">
-        <v>402</v>
-      </c>
-      <c r="D184" t="s">
-        <v>404</v>
-      </c>
-      <c r="E184" t="s">
-        <v>407</v>
-      </c>
-      <c r="F184" t="s">
-        <v>406</v>
-      </c>
-      <c r="G184" t="s">
-        <v>394</v>
-      </c>
-      <c r="H184" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="185" spans="1:20">
-      <c r="B185" t="s">
-        <v>403</v>
-      </c>
-      <c r="C185" t="s">
-        <v>410</v>
-      </c>
-      <c r="D185" t="s">
-        <v>490</v>
-      </c>
-      <c r="E185" t="s">
-        <v>399</v>
-      </c>
-      <c r="F185" t="s">
-        <v>414</v>
-      </c>
-      <c r="G185" t="s">
-        <v>408</v>
-      </c>
-      <c r="H185" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="186" spans="1:20">
-      <c r="B186" t="s">
-        <v>411</v>
-      </c>
-      <c r="C186" t="s">
-        <v>418</v>
-      </c>
-      <c r="D186" t="s">
-        <v>632</v>
-      </c>
-      <c r="E186" t="s">
-        <v>491</v>
-      </c>
-      <c r="F186" t="s">
-        <v>463</v>
-      </c>
-      <c r="G186" t="s">
-        <v>416</v>
-      </c>
-      <c r="H186" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="187" spans="1:20">
-      <c r="B187" t="s">
-        <v>419</v>
-      </c>
-      <c r="C187" t="s">
-        <v>424</v>
-      </c>
-      <c r="D187" t="s">
-        <v>631</v>
-      </c>
-      <c r="E187" t="s">
-        <v>421</v>
-      </c>
-      <c r="F187" t="s">
-        <v>465</v>
-      </c>
-      <c r="G187" t="s">
-        <v>422</v>
-      </c>
-      <c r="H187" t="s">
-        <v>415</v>
+      <c r="H187" s="5" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="188" spans="1:20">
       <c r="B188" t="s">
-        <v>425</v>
+        <v>387</v>
       </c>
       <c r="C188" t="s">
-        <v>430</v>
+        <v>386</v>
       </c>
       <c r="D188" t="s">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="E188" t="s">
-        <v>419</v>
+        <v>391</v>
       </c>
       <c r="F188" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G188" t="s">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="H188" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
     </row>
     <row r="189" spans="1:20">
       <c r="B189" t="s">
-        <v>431</v>
+        <v>395</v>
       </c>
       <c r="C189" t="s">
-        <v>440</v>
+        <v>400</v>
+      </c>
+      <c r="D189" t="s">
+        <v>402</v>
+      </c>
+      <c r="E189" t="s">
+        <v>405</v>
       </c>
       <c r="F189" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="G189" t="s">
-        <v>434</v>
+        <v>392</v>
       </c>
       <c r="H189" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
     </row>
     <row r="190" spans="1:20">
       <c r="B190" t="s">
-        <v>436</v>
+        <v>401</v>
       </c>
       <c r="C190" t="s">
-        <v>461</v>
+        <v>408</v>
+      </c>
+      <c r="D190" t="s">
+        <v>488</v>
+      </c>
+      <c r="E190" t="s">
+        <v>397</v>
       </c>
       <c r="F190" t="s">
-        <v>470</v>
+        <v>412</v>
+      </c>
+      <c r="G190" t="s">
+        <v>406</v>
       </c>
       <c r="H190" t="s">
-        <v>442</v>
+        <v>389</v>
       </c>
     </row>
     <row r="191" spans="1:20">
       <c r="B191" t="s">
-        <v>441</v>
+        <v>409</v>
       </c>
       <c r="C191" t="s">
-        <v>410</v>
+        <v>416</v>
+      </c>
+      <c r="D191" t="s">
+        <v>630</v>
+      </c>
+      <c r="E191" t="s">
+        <v>489</v>
       </c>
       <c r="F191" t="s">
+        <v>461</v>
+      </c>
+      <c r="G191" t="s">
         <v>414</v>
       </c>
       <c r="H191" t="s">
-        <v>432</v>
+        <v>403</v>
       </c>
     </row>
     <row r="192" spans="1:20">
       <c r="B192" t="s">
+        <v>417</v>
+      </c>
+      <c r="C192" t="s">
+        <v>422</v>
+      </c>
+      <c r="D192" t="s">
+        <v>629</v>
+      </c>
+      <c r="E192" t="s">
+        <v>419</v>
+      </c>
+      <c r="F192" t="s">
+        <v>463</v>
+      </c>
+      <c r="G192" t="s">
+        <v>420</v>
+      </c>
+      <c r="H192" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="193" spans="2:8">
+      <c r="B193" t="s">
+        <v>423</v>
+      </c>
+      <c r="C193" t="s">
+        <v>428</v>
+      </c>
+      <c r="D193" t="s">
+        <v>410</v>
+      </c>
+      <c r="E193" t="s">
+        <v>417</v>
+      </c>
+      <c r="F193" t="s">
+        <v>390</v>
+      </c>
+      <c r="G193" t="s">
+        <v>426</v>
+      </c>
+      <c r="H193" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="194" spans="2:8">
+      <c r="B194" t="s">
+        <v>429</v>
+      </c>
+      <c r="C194" t="s">
+        <v>438</v>
+      </c>
+      <c r="F194" t="s">
+        <v>404</v>
+      </c>
+      <c r="G194" t="s">
+        <v>432</v>
+      </c>
+      <c r="H194" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="195" spans="2:8">
+      <c r="B195" t="s">
+        <v>434</v>
+      </c>
+      <c r="C195" t="s">
+        <v>459</v>
+      </c>
+      <c r="F195" t="s">
+        <v>468</v>
+      </c>
+      <c r="H195" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="196" spans="2:8">
+      <c r="B196" t="s">
+        <v>439</v>
+      </c>
+      <c r="C196" t="s">
+        <v>408</v>
+      </c>
+      <c r="F196" t="s">
+        <v>412</v>
+      </c>
+      <c r="H196" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="197" spans="2:8">
+      <c r="B197" t="s">
+        <v>444</v>
+      </c>
+      <c r="C197" t="s">
+        <v>464</v>
+      </c>
+      <c r="F197" t="s">
+        <v>425</v>
+      </c>
+      <c r="H197" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="198" spans="2:8">
+      <c r="B198" t="s">
+        <v>429</v>
+      </c>
+      <c r="C198" t="s">
+        <v>466</v>
+      </c>
+      <c r="F198" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="199" spans="2:8">
+      <c r="B199" t="s">
+        <v>451</v>
+      </c>
+      <c r="C199" t="s">
+        <v>416</v>
+      </c>
+      <c r="F199" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="200" spans="2:8">
+      <c r="B200" t="s">
+        <v>465</v>
+      </c>
+      <c r="C200" t="s">
+        <v>469</v>
+      </c>
+      <c r="F200" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="201" spans="2:8">
+      <c r="B201" t="s">
+        <v>454</v>
+      </c>
+      <c r="C201" t="s">
+        <v>470</v>
+      </c>
+      <c r="F201" t="s">
         <v>446</v>
       </c>
-      <c r="C192" t="s">
-        <v>466</v>
-      </c>
-      <c r="F192" t="s">
+    </row>
+    <row r="202" spans="2:8">
+      <c r="B202" t="s">
+        <v>457</v>
+      </c>
+      <c r="C202" t="s">
+        <v>471</v>
+      </c>
+      <c r="F202" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="203" spans="2:8">
+      <c r="B203" t="s">
+        <v>460</v>
+      </c>
+      <c r="C203" t="s">
+        <v>472</v>
+      </c>
+      <c r="F203" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="204" spans="2:8">
+      <c r="B204" t="s">
+        <v>462</v>
+      </c>
+      <c r="C204" t="s">
+        <v>473</v>
+      </c>
+      <c r="F204" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="205" spans="2:8">
+      <c r="B205" t="s">
+        <v>467</v>
+      </c>
+      <c r="C205" t="s">
+        <v>410</v>
+      </c>
+      <c r="F205" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="206" spans="2:8">
+      <c r="B206" t="s">
+        <v>443</v>
+      </c>
+      <c r="C206" t="s">
+        <v>399</v>
+      </c>
+      <c r="F206" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="207" spans="2:8">
+      <c r="B207" t="s">
+        <v>448</v>
+      </c>
+      <c r="C207" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="208" spans="2:8">
+      <c r="B208" t="s">
+        <v>394</v>
+      </c>
+      <c r="C208" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14">
+      <c r="B209" t="s">
+        <v>453</v>
+      </c>
+      <c r="C209" t="s">
         <v>427</v>
       </c>
-      <c r="H192" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="193" spans="2:6">
-      <c r="B193" t="s">
-        <v>431</v>
-      </c>
-      <c r="C193" t="s">
-        <v>468</v>
-      </c>
-      <c r="F193" t="s">
+    </row>
+    <row r="210" spans="1:14">
+      <c r="B210" t="s">
+        <v>456</v>
+      </c>
+      <c r="C210" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="194" spans="2:6">
-      <c r="B194" t="s">
-        <v>453</v>
-      </c>
-      <c r="C194" t="s">
-        <v>418</v>
-      </c>
-      <c r="F194" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="195" spans="2:6">
-      <c r="B195" t="s">
-        <v>467</v>
-      </c>
-      <c r="C195" t="s">
-        <v>471</v>
-      </c>
-      <c r="F195" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="196" spans="2:6">
-      <c r="B196" t="s">
-        <v>456</v>
-      </c>
-      <c r="C196" t="s">
-        <v>472</v>
-      </c>
-      <c r="F196" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="197" spans="2:6">
-      <c r="B197" t="s">
-        <v>459</v>
-      </c>
-      <c r="C197" t="s">
-        <v>473</v>
-      </c>
-      <c r="F197" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="198" spans="2:6">
-      <c r="B198" t="s">
-        <v>462</v>
-      </c>
-      <c r="C198" t="s">
-        <v>474</v>
-      </c>
-      <c r="F198" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="199" spans="2:6">
-      <c r="B199" t="s">
-        <v>464</v>
-      </c>
-      <c r="C199" t="s">
-        <v>475</v>
-      </c>
-      <c r="F199" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="200" spans="2:6">
-      <c r="B200" t="s">
-        <v>469</v>
-      </c>
-      <c r="C200" t="s">
-        <v>412</v>
-      </c>
-      <c r="F200" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="201" spans="2:6">
-      <c r="B201" t="s">
-        <v>445</v>
-      </c>
-      <c r="C201" t="s">
-        <v>401</v>
-      </c>
-      <c r="F201" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="202" spans="2:6">
-      <c r="B202" t="s">
-        <v>450</v>
-      </c>
-      <c r="C202" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="203" spans="2:6">
-      <c r="B203" t="s">
-        <v>396</v>
-      </c>
-      <c r="C203" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="204" spans="2:6">
-      <c r="B204" t="s">
-        <v>455</v>
-      </c>
-      <c r="C204" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="205" spans="2:6">
-      <c r="B205" t="s">
-        <v>458</v>
-      </c>
-      <c r="C205" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="206" spans="2:6">
-      <c r="B206" t="s">
-        <v>396</v>
-      </c>
-      <c r="C206" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="207" spans="2:6">
-      <c r="C207" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="208" spans="2:6">
-      <c r="C208" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="209" spans="1:14">
-      <c r="C209" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="210" spans="1:14">
-      <c r="C210" t="s">
-        <v>452</v>
-      </c>
-    </row>
     <row r="211" spans="1:14">
+      <c r="B211" t="s">
+        <v>394</v>
+      </c>
       <c r="C211" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
     </row>
     <row r="212" spans="1:14">
       <c r="C212" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
     </row>
     <row r="213" spans="1:14">
       <c r="C213" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="214" spans="1:14">
       <c r="C214" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="215" spans="1:14" s="6" customFormat="1">
-      <c r="A215" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B215" s="6" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14">
+      <c r="C215" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14">
+      <c r="C216" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14">
+      <c r="C217" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14">
+      <c r="C218" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14">
+      <c r="C219" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" s="6" customFormat="1">
+      <c r="A220" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="D220" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="E220" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="F220" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="G220" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="H220" s="6" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14">
+      <c r="A222" s="7" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14">
+      <c r="A223" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B223" s="28" t="s">
+        <v>491</v>
+      </c>
+      <c r="C223" s="28"/>
+      <c r="D223" s="28"/>
+      <c r="E223" s="28"/>
+      <c r="F223" s="28"/>
+      <c r="G223" s="28"/>
+      <c r="H223" s="28"/>
+      <c r="I223" s="28"/>
+      <c r="J223" s="28"/>
+      <c r="K223" s="28"/>
+      <c r="L223" s="28"/>
+      <c r="M223" s="28"/>
+      <c r="N223" s="28"/>
+    </row>
+    <row r="224" spans="1:14" s="3" customFormat="1">
+      <c r="A224" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B224" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="C215" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="D215" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="E215" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="F215" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="G215" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="H215" s="6" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="217" spans="1:14">
-      <c r="A217" s="7" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="218" spans="1:14">
-      <c r="A218" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B218" s="28" t="s">
+      <c r="C224" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="C218" s="28"/>
-      <c r="D218" s="28"/>
-      <c r="E218" s="28"/>
-      <c r="F218" s="28"/>
-      <c r="G218" s="28"/>
-      <c r="H218" s="28"/>
-      <c r="I218" s="28"/>
-      <c r="J218" s="28"/>
-      <c r="K218" s="28"/>
-      <c r="L218" s="28"/>
-      <c r="M218" s="28"/>
-      <c r="N218" s="28"/>
-    </row>
-    <row r="219" spans="1:14" s="3" customFormat="1">
-      <c r="A219" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B219" s="3" t="s">
+      <c r="D224" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="C219" s="3" t="s">
+      <c r="E224" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="D219" s="3" t="s">
+      <c r="F224" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="E219" s="3" t="s">
+      <c r="G224" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="F219" s="3" t="s">
+      <c r="H224" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="G219" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="H219" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="I219" s="3" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="220" spans="1:14">
-      <c r="B220" t="s">
-        <v>553</v>
-      </c>
-      <c r="C220" t="s">
-        <v>507</v>
-      </c>
-      <c r="D220" t="s">
-        <v>536</v>
-      </c>
-      <c r="E220" t="s">
-        <v>545</v>
-      </c>
-      <c r="F220" t="s">
-        <v>504</v>
-      </c>
-      <c r="G220" t="s">
-        <v>505</v>
-      </c>
-      <c r="H220" s="20" t="s">
-        <v>511</v>
-      </c>
-      <c r="I220" t="s">
+      <c r="I224" s="3" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="221" spans="1:14">
-      <c r="B221" t="s">
-        <v>541</v>
-      </c>
-      <c r="C221" t="s">
-        <v>513</v>
-      </c>
-      <c r="D221" t="s">
-        <v>502</v>
-      </c>
-      <c r="E221" t="s">
-        <v>503</v>
-      </c>
-      <c r="G221" t="s">
-        <v>510</v>
-      </c>
-      <c r="H221" t="s">
-        <v>515</v>
-      </c>
-      <c r="I221" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="222" spans="1:14">
-      <c r="B222" t="s">
-        <v>623</v>
-      </c>
-      <c r="C222" t="s">
-        <v>517</v>
-      </c>
-      <c r="D222" t="s">
-        <v>625</v>
-      </c>
-      <c r="E222" t="s">
-        <v>626</v>
-      </c>
-      <c r="H222" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="223" spans="1:14">
-      <c r="B223" t="s">
-        <v>551</v>
-      </c>
-      <c r="C223" t="s">
-        <v>521</v>
-      </c>
-      <c r="D223" t="s">
-        <v>582</v>
-      </c>
-      <c r="E223" t="s">
-        <v>627</v>
-      </c>
-      <c r="H223" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="224" spans="1:14">
-      <c r="B224" t="s">
-        <v>516</v>
-      </c>
-      <c r="C224" t="s">
-        <v>525</v>
-      </c>
-      <c r="D224" t="s">
-        <v>508</v>
-      </c>
-      <c r="E224" t="s">
-        <v>514</v>
-      </c>
-      <c r="H224" t="s">
-        <v>533</v>
-      </c>
-      <c r="K224" s="26"/>
     </row>
     <row r="225" spans="2:11">
       <c r="B225" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C225" t="s">
-        <v>530</v>
+        <v>505</v>
       </c>
       <c r="D225" t="s">
-        <v>99</v>
+        <v>534</v>
       </c>
       <c r="E225" t="s">
-        <v>587</v>
-      </c>
-      <c r="H225" t="s">
-        <v>537</v>
-      </c>
-      <c r="K225" s="25"/>
+        <v>543</v>
+      </c>
+      <c r="F225" t="s">
+        <v>502</v>
+      </c>
+      <c r="G225" t="s">
+        <v>503</v>
+      </c>
+      <c r="H225" s="20" t="s">
+        <v>509</v>
+      </c>
+      <c r="I225" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="226" spans="2:11">
       <c r="B226" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="C226" t="s">
-        <v>535</v>
+        <v>511</v>
       </c>
       <c r="D226" t="s">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="E226" t="s">
-        <v>527</v>
+        <v>501</v>
+      </c>
+      <c r="G226" t="s">
+        <v>508</v>
       </c>
       <c r="H226" t="s">
-        <v>506</v>
-      </c>
-      <c r="K226" s="26"/>
+        <v>513</v>
+      </c>
+      <c r="I226" t="s">
+        <v>642</v>
+      </c>
     </row>
     <row r="227" spans="2:11">
       <c r="B227" t="s">
-        <v>571</v>
+        <v>621</v>
       </c>
       <c r="C227" t="s">
-        <v>539</v>
+        <v>515</v>
       </c>
       <c r="D227" t="s">
-        <v>526</v>
+        <v>623</v>
       </c>
       <c r="E227" t="s">
-        <v>532</v>
+        <v>624</v>
       </c>
       <c r="H227" t="s">
-        <v>589</v>
-      </c>
-      <c r="K227" s="25"/>
+        <v>518</v>
+      </c>
     </row>
     <row r="228" spans="2:11">
       <c r="B228" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C228" t="s">
-        <v>542</v>
+        <v>519</v>
       </c>
       <c r="D228" t="s">
-        <v>531</v>
+        <v>580</v>
       </c>
       <c r="E228" t="s">
-        <v>547</v>
+        <v>625</v>
       </c>
       <c r="H228" t="s">
-        <v>628</v>
-      </c>
-      <c r="K228" s="26"/>
+        <v>521</v>
+      </c>
     </row>
     <row r="229" spans="2:11">
       <c r="B229" t="s">
-        <v>546</v>
+        <v>514</v>
       </c>
       <c r="C229" t="s">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="D229" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="E229" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="H229" t="s">
-        <v>580</v>
-      </c>
-      <c r="K229" s="25"/>
+        <v>531</v>
+      </c>
+      <c r="K229" s="26"/>
     </row>
     <row r="230" spans="2:11">
       <c r="B230" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="C230" t="s">
-        <v>539</v>
+        <v>528</v>
+      </c>
+      <c r="D230" t="s">
+        <v>98</v>
       </c>
       <c r="E230" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="H230" t="s">
-        <v>528</v>
-      </c>
-      <c r="K230" s="26"/>
+        <v>535</v>
+      </c>
+      <c r="K230" s="25"/>
     </row>
     <row r="231" spans="2:11">
       <c r="B231" t="s">
-        <v>556</v>
+        <v>527</v>
       </c>
       <c r="C231" t="s">
-        <v>501</v>
+        <v>533</v>
+      </c>
+      <c r="D231" t="s">
+        <v>516</v>
       </c>
       <c r="E231" t="s">
-        <v>543</v>
-      </c>
-      <c r="K231" s="25"/>
+        <v>525</v>
+      </c>
+      <c r="H231" t="s">
+        <v>504</v>
+      </c>
+      <c r="K231" s="26"/>
     </row>
     <row r="232" spans="2:11">
       <c r="B232" t="s">
+        <v>569</v>
+      </c>
+      <c r="C232" t="s">
+        <v>537</v>
+      </c>
+      <c r="D232" t="s">
         <v>524</v>
       </c>
-      <c r="C232" t="s">
-        <v>624</v>
-      </c>
-      <c r="K232" s="26"/>
+      <c r="E232" t="s">
+        <v>530</v>
+      </c>
+      <c r="H232" t="s">
+        <v>587</v>
+      </c>
+      <c r="K232" s="25"/>
     </row>
     <row r="233" spans="2:11">
       <c r="B233" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="C233" t="s">
-        <v>575</v>
-      </c>
-      <c r="K233" s="25"/>
+        <v>540</v>
+      </c>
+      <c r="D233" t="s">
+        <v>529</v>
+      </c>
+      <c r="E233" t="s">
+        <v>545</v>
+      </c>
+      <c r="H233" t="s">
+        <v>626</v>
+      </c>
+      <c r="K233" s="26"/>
     </row>
     <row r="234" spans="2:11">
       <c r="B234" t="s">
-        <v>549</v>
-      </c>
-      <c r="K234" s="26"/>
+        <v>544</v>
+      </c>
+      <c r="C234" t="s">
+        <v>542</v>
+      </c>
+      <c r="D234" t="s">
+        <v>520</v>
+      </c>
+      <c r="E234" t="s">
+        <v>517</v>
+      </c>
+      <c r="H234" t="s">
+        <v>578</v>
+      </c>
+      <c r="K234" s="25"/>
     </row>
     <row r="235" spans="2:11">
       <c r="B235" t="s">
+        <v>532</v>
+      </c>
+      <c r="C235" t="s">
+        <v>537</v>
+      </c>
+      <c r="E235" t="s">
         <v>538</v>
       </c>
-      <c r="K235" s="25"/>
+      <c r="H235" t="s">
+        <v>526</v>
+      </c>
+      <c r="K235" s="26"/>
     </row>
     <row r="236" spans="2:11">
       <c r="B236" t="s">
-        <v>550</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="C236" t="s">
+        <v>499</v>
+      </c>
+      <c r="E236" t="s">
+        <v>541</v>
+      </c>
+      <c r="K236" s="25"/>
     </row>
     <row r="237" spans="2:11">
       <c r="B237" t="s">
-        <v>512</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="C237" t="s">
+        <v>622</v>
+      </c>
+      <c r="K237" s="26"/>
     </row>
     <row r="238" spans="2:11">
       <c r="B238" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="241" spans="1:20" s="4" customFormat="1">
-      <c r="A241" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B241" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="C238" t="s">
+        <v>573</v>
+      </c>
+      <c r="K238" s="25"/>
+    </row>
+    <row r="239" spans="2:11">
+      <c r="B239" t="s">
+        <v>547</v>
+      </c>
+      <c r="K239" s="26"/>
+    </row>
+    <row r="240" spans="2:11">
+      <c r="B240" t="s">
+        <v>536</v>
+      </c>
+      <c r="K240" s="25"/>
+    </row>
+    <row r="241" spans="1:20">
+      <c r="B241" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="242" spans="1:20">
+      <c r="B242" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="243" spans="1:20">
+      <c r="B243" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="246" spans="1:20" s="4" customFormat="1">
+      <c r="A246" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B246" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="D246" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="C241" s="4" t="s">
+      <c r="E246" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="D241" s="4" t="s">
+      <c r="F246" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="E241" s="4" t="s">
+      <c r="G246" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="F241" s="4" t="s">
+      <c r="H246" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="G241" s="4" t="s">
+    </row>
+    <row r="248" spans="1:20">
+      <c r="A248" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B248" s="29" t="s">
         <v>562</v>
       </c>
-      <c r="H241" s="4" t="s">
+      <c r="C248" s="29"/>
+      <c r="D248" s="29"/>
+      <c r="E248" s="29"/>
+      <c r="F248" s="29"/>
+      <c r="G248" s="29"/>
+      <c r="H248" s="29"/>
+      <c r="I248" s="30"/>
+      <c r="J248" s="30"/>
+      <c r="K248" s="30"/>
+      <c r="L248" s="30"/>
+      <c r="M248" s="30"/>
+      <c r="N248" s="30"/>
+      <c r="O248" s="30"/>
+      <c r="P248" s="30"/>
+      <c r="Q248" s="30"/>
+      <c r="R248" s="30"/>
+      <c r="S248" s="30"/>
+      <c r="T248" s="30"/>
+    </row>
+    <row r="249" spans="1:20" s="5" customFormat="1">
+      <c r="A249" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="C249" s="5" t="s">
         <v>563</v>
       </c>
-    </row>
-    <row r="243" spans="1:20">
-      <c r="A243" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B243" s="29" t="s">
-        <v>564</v>
-      </c>
-      <c r="C243" s="29"/>
-      <c r="D243" s="29"/>
-      <c r="E243" s="29"/>
-      <c r="F243" s="29"/>
-      <c r="G243" s="29"/>
-      <c r="H243" s="29"/>
-      <c r="I243" s="30"/>
-      <c r="J243" s="30"/>
-      <c r="K243" s="30"/>
-      <c r="L243" s="30"/>
-      <c r="M243" s="30"/>
-      <c r="N243" s="30"/>
-      <c r="O243" s="30"/>
-      <c r="P243" s="30"/>
-      <c r="Q243" s="30"/>
-      <c r="R243" s="30"/>
-      <c r="S243" s="30"/>
-      <c r="T243" s="30"/>
-    </row>
-    <row r="244" spans="1:20" s="5" customFormat="1">
-      <c r="A244" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B244" s="5" t="s">
+      <c r="D249" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="E249" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="C244" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="D244" s="5" t="s">
+      <c r="F249" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="E244" s="5" t="s">
+      <c r="G249" s="5" t="s">
         <v>568</v>
-      </c>
-      <c r="F244" s="5" t="s">
-        <v>569</v>
-      </c>
-      <c r="G244" s="5" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="245" spans="1:20">
-      <c r="B245" t="s">
-        <v>555</v>
-      </c>
-      <c r="C245" t="s">
-        <v>553</v>
-      </c>
-      <c r="D245" t="s">
-        <v>545</v>
-      </c>
-      <c r="E245" t="s">
-        <v>574</v>
-      </c>
-      <c r="F245" t="s">
-        <v>536</v>
-      </c>
-      <c r="G245" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="246" spans="1:20">
-      <c r="B246" t="s">
-        <v>635</v>
-      </c>
-      <c r="C246" t="s">
-        <v>541</v>
-      </c>
-      <c r="D246" t="s">
-        <v>576</v>
-      </c>
-      <c r="E246" t="s">
-        <v>577</v>
-      </c>
-      <c r="F246" t="s">
-        <v>502</v>
-      </c>
-      <c r="G246" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="247" spans="1:20">
-      <c r="B247" t="s">
-        <v>506</v>
-      </c>
-      <c r="C247" t="s">
-        <v>623</v>
-      </c>
-      <c r="D247" t="s">
-        <v>503</v>
-      </c>
-      <c r="E247" t="s">
-        <v>579</v>
-      </c>
-      <c r="F247" t="s">
-        <v>625</v>
-      </c>
-      <c r="G247" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="248" spans="1:20">
-      <c r="B248" t="s">
-        <v>589</v>
-      </c>
-      <c r="C248" t="s">
-        <v>551</v>
-      </c>
-      <c r="D248" t="s">
-        <v>573</v>
-      </c>
-      <c r="F248" t="s">
-        <v>582</v>
-      </c>
-      <c r="G248" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="249" spans="1:20">
-      <c r="B249" t="s">
-        <v>523</v>
-      </c>
-      <c r="C249" t="s">
-        <v>516</v>
-      </c>
-      <c r="D249" t="s">
-        <v>626</v>
-      </c>
-      <c r="F249" t="s">
-        <v>581</v>
-      </c>
-      <c r="G249" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="250" spans="1:20">
       <c r="B250" t="s">
-        <v>628</v>
+        <v>553</v>
       </c>
       <c r="C250" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D250" t="s">
-        <v>583</v>
+        <v>543</v>
+      </c>
+      <c r="E250" t="s">
+        <v>572</v>
       </c>
       <c r="F250" t="s">
-        <v>508</v>
+        <v>534</v>
       </c>
       <c r="G250" t="s">
-        <v>530</v>
+        <v>505</v>
       </c>
     </row>
     <row r="251" spans="1:20">
       <c r="B251" t="s">
-        <v>586</v>
+        <v>633</v>
       </c>
       <c r="C251" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="D251" t="s">
-        <v>627</v>
+        <v>574</v>
+      </c>
+      <c r="E251" t="s">
+        <v>575</v>
       </c>
       <c r="F251" t="s">
-        <v>99</v>
+        <v>500</v>
       </c>
       <c r="G251" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
     </row>
     <row r="252" spans="1:20">
       <c r="B252" t="s">
-        <v>572</v>
+        <v>504</v>
       </c>
       <c r="C252" t="s">
-        <v>571</v>
+        <v>621</v>
       </c>
       <c r="D252" t="s">
-        <v>629</v>
+        <v>501</v>
+      </c>
+      <c r="E252" t="s">
+        <v>577</v>
       </c>
       <c r="F252" t="s">
-        <v>518</v>
+        <v>623</v>
       </c>
       <c r="G252" t="s">
-        <v>544</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:20">
       <c r="B253" t="s">
-        <v>537</v>
+        <v>587</v>
       </c>
       <c r="C253" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D253" t="s">
-        <v>591</v>
+        <v>571</v>
       </c>
       <c r="F253" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G253" t="s">
-        <v>588</v>
+        <v>511</v>
       </c>
     </row>
     <row r="254" spans="1:20">
       <c r="B254" t="s">
-        <v>584</v>
+        <v>521</v>
       </c>
       <c r="C254" t="s">
-        <v>546</v>
+        <v>514</v>
       </c>
       <c r="D254" t="s">
-        <v>585</v>
+        <v>624</v>
       </c>
       <c r="F254" t="s">
-        <v>526</v>
+        <v>579</v>
       </c>
       <c r="G254" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
     </row>
     <row r="255" spans="1:20">
       <c r="B255" t="s">
-        <v>515</v>
+        <v>626</v>
       </c>
       <c r="C255" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="D255" t="s">
-        <v>514</v>
+        <v>581</v>
       </c>
       <c r="F255" t="s">
-        <v>531</v>
+        <v>506</v>
       </c>
       <c r="G255" t="s">
-        <v>624</v>
+        <v>528</v>
       </c>
     </row>
     <row r="256" spans="1:20">
       <c r="B256" t="s">
+        <v>584</v>
+      </c>
+      <c r="C256" t="s">
+        <v>527</v>
+      </c>
+      <c r="D256" t="s">
+        <v>625</v>
+      </c>
+      <c r="F256" t="s">
+        <v>98</v>
+      </c>
+      <c r="G256" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="257" spans="2:7">
+      <c r="B257" t="s">
+        <v>570</v>
+      </c>
+      <c r="C257" t="s">
+        <v>569</v>
+      </c>
+      <c r="D257" t="s">
+        <v>627</v>
+      </c>
+      <c r="F257" t="s">
+        <v>516</v>
+      </c>
+      <c r="G257" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="258" spans="2:7">
+      <c r="B258" t="s">
+        <v>535</v>
+      </c>
+      <c r="C258" t="s">
+        <v>546</v>
+      </c>
+      <c r="D258" t="s">
+        <v>589</v>
+      </c>
+      <c r="F258" t="s">
+        <v>576</v>
+      </c>
+      <c r="G258" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="259" spans="2:7">
+      <c r="B259" t="s">
+        <v>582</v>
+      </c>
+      <c r="C259" t="s">
+        <v>544</v>
+      </c>
+      <c r="D259" t="s">
+        <v>583</v>
+      </c>
+      <c r="F259" t="s">
+        <v>524</v>
+      </c>
+      <c r="G259" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="260" spans="2:7">
+      <c r="B260" t="s">
+        <v>513</v>
+      </c>
+      <c r="C260" t="s">
+        <v>532</v>
+      </c>
+      <c r="D260" t="s">
+        <v>512</v>
+      </c>
+      <c r="F260" t="s">
+        <v>529</v>
+      </c>
+      <c r="G260" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="261" spans="2:7">
+      <c r="B261" t="s">
+        <v>507</v>
+      </c>
+      <c r="C261" t="s">
+        <v>554</v>
+      </c>
+      <c r="D261" t="s">
+        <v>585</v>
+      </c>
+      <c r="F261" t="s">
+        <v>520</v>
+      </c>
+      <c r="G261" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="262" spans="2:7">
+      <c r="B262" t="s">
         <v>509</v>
       </c>
-      <c r="C256" t="s">
-        <v>556</v>
-      </c>
-      <c r="D256" t="s">
-        <v>587</v>
-      </c>
-      <c r="F256" t="s">
+      <c r="C262" t="s">
         <v>522</v>
       </c>
-      <c r="G256" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="257" spans="1:8">
-      <c r="B257" t="s">
-        <v>511</v>
-      </c>
-      <c r="C257" t="s">
-        <v>524</v>
-      </c>
-      <c r="D257" t="s">
-        <v>527</v>
-      </c>
-      <c r="G257" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="258" spans="1:8">
-      <c r="B258" t="s">
-        <v>520</v>
-      </c>
-      <c r="C258" t="s">
-        <v>552</v>
-      </c>
-      <c r="D258" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="259" spans="1:8">
-      <c r="B259" t="s">
-        <v>580</v>
-      </c>
-      <c r="C259" t="s">
-        <v>549</v>
-      </c>
-      <c r="D259" t="s">
+      <c r="D262" t="s">
+        <v>525</v>
+      </c>
+      <c r="G262" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="263" spans="2:7">
+      <c r="B263" t="s">
+        <v>518</v>
+      </c>
+      <c r="C263" t="s">
+        <v>550</v>
+      </c>
+      <c r="D263" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="264" spans="2:7">
+      <c r="B264" t="s">
+        <v>578</v>
+      </c>
+      <c r="C264" t="s">
+        <v>547</v>
+      </c>
+      <c r="D264" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="265" spans="2:7">
+      <c r="B265" t="s">
+        <v>526</v>
+      </c>
+      <c r="C265" t="s">
+        <v>536</v>
+      </c>
+      <c r="D265" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="266" spans="2:7">
+      <c r="C266" t="s">
+        <v>548</v>
+      </c>
+      <c r="D266" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="267" spans="2:7">
+      <c r="C267" t="s">
+        <v>510</v>
+      </c>
+      <c r="D267" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="268" spans="2:7">
+      <c r="D268" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="269" spans="2:7">
+      <c r="D269" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="270" spans="2:7">
+      <c r="D270" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="271" spans="2:7">
+      <c r="D271" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="272" spans="2:7">
+      <c r="D272" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" s="6" customFormat="1">
+      <c r="A273" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B273" s="6" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="260" spans="1:8">
-      <c r="B260" t="s">
-        <v>528</v>
-      </c>
-      <c r="C260" t="s">
-        <v>538</v>
-      </c>
-      <c r="D260" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="261" spans="1:8">
-      <c r="C261" t="s">
-        <v>550</v>
-      </c>
-      <c r="D261" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="262" spans="1:8">
-      <c r="C262" t="s">
-        <v>512</v>
-      </c>
-      <c r="D262" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="263" spans="1:8">
-      <c r="D263" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="264" spans="1:8">
-      <c r="D264" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="265" spans="1:8">
-      <c r="D265" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="266" spans="1:8">
-      <c r="D266" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="267" spans="1:8">
-      <c r="D267" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="268" spans="1:8" s="6" customFormat="1">
-      <c r="A268" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B268" s="6" t="s">
-        <v>592</v>
-      </c>
-      <c r="C268" s="6" t="s">
-        <v>592</v>
-      </c>
-      <c r="D268" s="6" t="s">
-        <v>592</v>
-      </c>
-      <c r="E268" s="6" t="s">
-        <v>592</v>
-      </c>
-      <c r="F268" s="6" t="s">
-        <v>592</v>
-      </c>
-      <c r="G268" s="6" t="s">
-        <v>592</v>
-      </c>
-      <c r="H268" s="6" t="s">
-        <v>592</v>
+      <c r="C273" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="D273" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="E273" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="F273" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="G273" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="H273" s="6" t="s">
+        <v>590</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B153:N153"/>
-    <mergeCell ref="B181:T181"/>
-    <mergeCell ref="B218:N218"/>
-    <mergeCell ref="B243:T243"/>
+    <mergeCell ref="B158:N158"/>
+    <mergeCell ref="B186:T186"/>
+    <mergeCell ref="B223:N223"/>
+    <mergeCell ref="B248:T248"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B25:T25"/>
     <mergeCell ref="B49:N49"/>
     <mergeCell ref="B81:T81"/>
     <mergeCell ref="B111:N111"/>
-    <mergeCell ref="B131:T131"/>
+    <mergeCell ref="B136:T136"/>
   </mergeCells>
-  <conditionalFormatting sqref="H221:H230">
+  <conditionalFormatting sqref="H226:H235">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="SBS-GADUNG-HW.MA5801-OLT-01">
-      <formula>NOT(ISERROR(SEARCH("SBS-GADUNG-HW.MA5801-OLT-01",H221)))</formula>
+      <formula>NOT(ISERROR(SEARCH("SBS-GADUNG-HW.MA5801-OLT-01",H226)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/data/List_Team_Region.xlsx
+++ b/public/data/List_Team_Region.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muham\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BCB72E-CDD4-486F-AF01-D5C1B79C9CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0587D559-D857-46F7-9EEC-4038ECF4544E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1560" windowWidth="14460" windowHeight="7320" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
+    <workbookView xWindow="555" yWindow="4200" windowWidth="12345" windowHeight="7320" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="656">
   <si>
     <t>JAMBI</t>
   </si>
@@ -1032,9 +1032,6 @@
     <t>ALDO</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC RETAIL	</t>
-  </si>
-  <si>
     <t>Malik</t>
   </si>
   <si>
@@ -1959,9 +1956,6 @@
     <t>SBS-BHMA.TANJUNG.RATU-FH.AN6001.G16-OLT-01</t>
   </si>
   <si>
-    <t xml:space="preserve"> SBS-BHMA.TANJUNG.GUNUNG-FH.AN6000.2-OLT-01</t>
-  </si>
-  <si>
     <t>BHMA PANGKAL</t>
   </si>
   <si>
@@ -1975,6 +1969,36 @@
   </si>
   <si>
     <t>SBS-SUNGAI.PENUH-HW.MA5801-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-BHMA.TOBOALI-FH.AN6001.G16-OLT-05</t>
+  </si>
+  <si>
+    <t>SBS-BHMA.AIRBARA-FH.AN6001.G16-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-BHMA.KULUR-FH.AN6000.2-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-BHMA.TAMBAKSARI-AN6000.2-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-BHMA.JELUTUNG-AN6000.2-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-BHMA.KOTABARU-AN6001-OLT-02</t>
+  </si>
+  <si>
+    <t>BHMA JAMBI</t>
+  </si>
+  <si>
+    <t>SBS-BHMA.SEKIP.JAYA-FH.AN6000.2-OLT-01</t>
+  </si>
+  <si>
+    <t>SBS-BHMA.KEMUNING-FH.AN6000.2-OLT-01</t>
+  </si>
+  <si>
+    <t>BHMA PALEMBANG</t>
   </si>
 </sst>
 </file>
@@ -2538,15 +2562,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}" name="Table919" displayName="Table919" ref="B3:H22" totalsRowShown="0" headerRowDxfId="12">
-  <autoFilter ref="B3:H22" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}" name="Table919" displayName="Table919" ref="B3:I22" totalsRowShown="0" headerRowDxfId="12">
+  <autoFilter ref="B3:I22" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{1E18F602-B85E-4C85-8C34-8684E3651598}" name="INTERNAL JAMBI"/>
     <tableColumn id="2" xr3:uid="{FB0AE047-7A54-41C3-8DE2-5FB87347FC5A}" name="TTM SAROLANGUN"/>
     <tableColumn id="3" xr3:uid="{A9B09C98-0448-4BFE-9FCC-534A4FFDCBB7}" name="TTM MERANGIN"/>
     <tableColumn id="4" xr3:uid="{54B8B45C-2FD6-4B38-83C8-85E5B4BDC6D9}" name="GSP MUARA BULIAN"/>
     <tableColumn id="5" xr3:uid="{CB18B3A9-79B8-4ED4-A869-445C0D0FFA3E}" name="GSP JAMBI 2"/>
     <tableColumn id="6" xr3:uid="{D9DCD84D-C9D6-4860-AE60-7A035270E21A}" name="GSP SUNGAI PENUH"/>
+    <tableColumn id="8" xr3:uid="{DDACFCB7-36E2-43BD-9D11-A74626303C39}" name="BHMA JAMBI"/>
     <tableColumn id="7" xr3:uid="{ED41A1AB-EDC7-4B03-A268-9EB9271D2B5D}" name="GSP TEBO"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2633,9 +2658,9 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}" name="Table1323" displayName="Table1323" ref="B112:N134" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="B112:N134" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}" name="Table1323" displayName="Table1323" ref="B112:O134" totalsRowShown="0" headerRowDxfId="8">
+  <autoFilter ref="B112:O134" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}"/>
+  <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{6FB6563D-399C-4506-8AF0-A312347E4888}" name="REG7 PALEMBANG 1"/>
     <tableColumn id="2" xr3:uid="{211D6500-28BD-4C9B-A588-576FE1D6FE10}" name="REG7 PALEMBANG 2"/>
     <tableColumn id="3" xr3:uid="{355E3A8F-21BA-4348-9564-2FAF305488B3}" name="REG7 PALEMBANG 3"/>
@@ -2649,6 +2674,7 @@
     <tableColumn id="12" xr3:uid="{3BF035D4-D0DE-4F99-8178-5942792867E9}" name="SIB PAGARALAM "/>
     <tableColumn id="13" xr3:uid="{DB140030-979E-44A0-B027-9374EEA27F7E}" name="SIB LAHAT"/>
     <tableColumn id="14" xr3:uid="{F37F02C6-FE10-4DC1-875F-57ABBB0AF623}" name="SIB EMPAT LAWANG"/>
+    <tableColumn id="6" xr3:uid="{85A4AA6D-A8EF-4A9B-8B83-7372439F408F}" name="BHMA PALEMBANG"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3108,6 +3134,9 @@
         <v>9</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3122,7 +3151,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
@@ -3131,6 +3160,9 @@
         <v>15</v>
       </c>
       <c r="H4" t="s">
+        <v>649</v>
+      </c>
+      <c r="I4" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3139,7 +3171,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -3154,6 +3186,9 @@
         <v>22</v>
       </c>
       <c r="H5" t="s">
+        <v>650</v>
+      </c>
+      <c r="I5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3165,7 +3200,7 @@
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E6" t="s">
         <v>27</v>
@@ -3177,6 +3212,9 @@
         <v>29</v>
       </c>
       <c r="H6" t="s">
+        <v>651</v>
+      </c>
+      <c r="I6" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3185,7 +3223,7 @@
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -3199,7 +3237,7 @@
       <c r="G7" t="s">
         <v>36</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3222,7 +3260,7 @@
       <c r="G8" t="s">
         <v>41</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -3231,7 +3269,7 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D9" t="s">
         <v>47</v>
@@ -3240,9 +3278,9 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>647</v>
-      </c>
-      <c r="H9" t="s">
+        <v>645</v>
+      </c>
+      <c r="I9" t="s">
         <v>45</v>
       </c>
     </row>
@@ -3251,7 +3289,7 @@
         <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D10" t="s">
         <v>51</v>
@@ -3262,16 +3300,16 @@
       <c r="G10" t="s">
         <v>49</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="B11" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C11" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D11" t="s">
         <v>54</v>
@@ -3280,7 +3318,7 @@
         <v>52</v>
       </c>
       <c r="G11" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -3297,7 +3335,7 @@
         <v>55</v>
       </c>
       <c r="G12" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -3311,7 +3349,7 @@
         <v>58</v>
       </c>
       <c r="G13" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -3388,7 +3426,7 @@
         <v>74</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>75</v>
@@ -3406,6 +3444,9 @@
         <v>79</v>
       </c>
       <c r="H23" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3469,7 +3510,7 @@
     </row>
     <row r="27" spans="1:20">
       <c r="B27" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C27" t="s">
         <v>62</v>
@@ -3487,7 +3528,7 @@
         <v>13</v>
       </c>
       <c r="H27" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="I27" t="s">
         <v>16</v>
@@ -3507,7 +3548,7 @@
         <v>46</v>
       </c>
       <c r="E28" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -3539,10 +3580,10 @@
         <v>27</v>
       </c>
       <c r="G29" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H29" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="I29" t="s">
         <v>30</v>
@@ -3559,7 +3600,7 @@
         <v>99</v>
       </c>
       <c r="E30" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F30" t="s">
         <v>34</v>
@@ -3602,7 +3643,7 @@
     </row>
     <row r="32" spans="1:20">
       <c r="B32" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C32" t="s">
         <v>40</v>
@@ -3611,13 +3652,13 @@
         <v>28</v>
       </c>
       <c r="E32" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G32" t="s">
         <v>47</v>
       </c>
       <c r="H32" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="I32" t="s">
         <v>45</v>
@@ -3628,16 +3669,16 @@
         <v>66</v>
       </c>
       <c r="D33" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E33" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G33" t="s">
         <v>51</v>
       </c>
       <c r="H33" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I33" t="s">
         <v>50</v>
@@ -3651,7 +3692,7 @@
         <v>72</v>
       </c>
       <c r="E34" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G34" t="s">
         <v>54</v>
@@ -3901,7 +3942,7 @@
         <v>135</v>
       </c>
       <c r="D54" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E54" t="s">
         <v>131</v>
@@ -3941,7 +3982,7 @@
         <v>146</v>
       </c>
       <c r="D56" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E56" t="s">
         <v>143</v>
@@ -3975,7 +4016,7 @@
         <v>154</v>
       </c>
       <c r="D58" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F58" t="s">
         <v>156</v>
@@ -4028,13 +4069,13 @@
     </row>
     <row r="62" spans="1:14">
       <c r="C62" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D62" t="s">
         <v>147</v>
       </c>
       <c r="F62" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G62" t="s">
         <v>162</v>
@@ -4042,13 +4083,13 @@
     </row>
     <row r="63" spans="1:14">
       <c r="C63" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D63" t="s">
         <v>151</v>
       </c>
       <c r="F63" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G63" t="s">
         <v>164</v>
@@ -4138,13 +4179,13 @@
         <v>178</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>179</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="81" spans="1:20">
@@ -4276,7 +4317,7 @@
     </row>
     <row r="86" spans="1:20">
       <c r="B86" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C86" t="s">
         <v>139</v>
@@ -4327,7 +4368,7 @@
     </row>
     <row r="89" spans="1:20">
       <c r="B89" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C89" t="s">
         <v>133</v>
@@ -4413,7 +4454,7 @@
     </row>
     <row r="96" spans="1:20">
       <c r="B96" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C96" t="s">
         <v>159</v>
@@ -4422,76 +4463,76 @@
         <v>123</v>
       </c>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:15">
       <c r="B97" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C97" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E97" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:15">
       <c r="B98" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E98" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:15">
       <c r="B99" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E99" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:15">
       <c r="B100" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E100" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:15">
       <c r="B101" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E101" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:15">
       <c r="B102" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E102" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:15">
       <c r="B103" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E103" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:15">
       <c r="E104" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
       <c r="E105" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:15">
       <c r="B106" t="s">
         <v>203</v>
       </c>
@@ -4499,7 +4540,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="107" spans="1:14" s="6" customFormat="1">
+    <row r="107" spans="1:15" s="6" customFormat="1">
       <c r="A107" s="6" t="s">
         <v>74</v>
       </c>
@@ -4528,15 +4569,15 @@
         <v>207</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
       <c r="A110" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:15">
       <c r="A111" s="2" t="s">
         <v>1</v>
       </c>
@@ -4556,7 +4597,7 @@
       <c r="M111" s="28"/>
       <c r="N111" s="28"/>
     </row>
-    <row r="112" spans="1:14" s="3" customFormat="1">
+    <row r="112" spans="1:15" s="3" customFormat="1">
       <c r="A112" s="3" t="s">
         <v>3</v>
       </c>
@@ -4599,8 +4640,11 @@
       <c r="N112" s="3" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="113" spans="2:14">
+      <c r="O112" s="3" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="113" spans="2:15">
       <c r="B113" t="s">
         <v>223</v>
       </c>
@@ -4640,8 +4684,11 @@
       <c r="N113" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="114" spans="2:14">
+      <c r="O113" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="114" spans="2:15">
       <c r="B114" t="s">
         <v>237</v>
       </c>
@@ -4681,8 +4728,11 @@
       <c r="N114" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="115" spans="2:14">
+      <c r="O114" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="115" spans="2:15">
       <c r="B115" t="s">
         <v>250</v>
       </c>
@@ -4720,7 +4770,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="116" spans="2:14">
+    <row r="116" spans="2:15">
       <c r="B116" t="s">
         <v>263</v>
       </c>
@@ -4758,7 +4808,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="117" spans="2:14">
+    <row r="117" spans="2:15">
       <c r="B117" t="s">
         <v>275</v>
       </c>
@@ -4793,7 +4843,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="118" spans="2:14">
+    <row r="118" spans="2:15">
       <c r="B118" t="s">
         <v>287</v>
       </c>
@@ -4822,7 +4872,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="119" spans="2:14">
+    <row r="119" spans="2:15">
       <c r="B119" t="s">
         <v>297</v>
       </c>
@@ -4851,7 +4901,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="120" spans="2:14">
+    <row r="120" spans="2:15">
       <c r="B120" t="s">
         <v>306</v>
       </c>
@@ -4868,13 +4918,13 @@
         <v>310</v>
       </c>
       <c r="I120" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J120" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="121" spans="2:14">
+    <row r="121" spans="2:15">
       <c r="B121" t="s">
         <v>312</v>
       </c>
@@ -4891,7 +4941,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="122" spans="2:14">
+    <row r="122" spans="2:15">
       <c r="B122" t="s">
         <v>317</v>
       </c>
@@ -4908,7 +4958,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="123" spans="2:14">
+    <row r="123" spans="2:15">
       <c r="B123" t="s">
         <v>321</v>
       </c>
@@ -4922,7 +4972,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="124" spans="2:14">
+    <row r="124" spans="2:15">
       <c r="B124" t="s">
         <v>324</v>
       </c>
@@ -4933,7 +4983,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="125" spans="2:14">
+    <row r="125" spans="2:15">
       <c r="E125" t="s">
         <v>280</v>
       </c>
@@ -4941,7 +4991,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="126" spans="2:14">
+    <row r="126" spans="2:15">
       <c r="E126" t="s">
         <v>291</v>
       </c>
@@ -4949,12 +4999,12 @@
         <v>327</v>
       </c>
     </row>
-    <row r="127" spans="2:14">
+    <row r="127" spans="2:15">
       <c r="J127" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="128" spans="2:14">
+    <row r="128" spans="2:15">
       <c r="J128" t="s">
         <v>329</v>
       </c>
@@ -4973,34 +5023,34 @@
         <v>332</v>
       </c>
       <c r="E134" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="F134" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="F134" s="4" t="s">
+      <c r="G134" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="H134" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="G134" s="4" t="s">
-        <v>635</v>
-      </c>
-      <c r="H134" s="4" t="s">
+      <c r="I134" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="I134" s="4" t="s">
+      <c r="J134" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="J134" s="4" t="s">
+      <c r="K134" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="K134" s="4" t="s">
+      <c r="L134" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="L134" s="4" t="s">
+      <c r="M134" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="M134" s="4" t="s">
+      <c r="N134" s="4" t="s">
         <v>340</v>
-      </c>
-      <c r="N134" s="4" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="136" spans="1:20">
@@ -5008,7 +5058,7 @@
         <v>1</v>
       </c>
       <c r="B136" s="29" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C136" s="29"/>
       <c r="D136" s="29"/>
@@ -5034,61 +5084,61 @@
         <v>3</v>
       </c>
       <c r="B137" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="C137" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="C137" s="5" t="s">
+      <c r="D137" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="D137" s="5" t="s">
+      <c r="E137" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="E137" s="5" t="s">
+      <c r="F137" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="F137" s="5" t="s">
+      <c r="G137" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="G137" s="5" t="s">
+      <c r="H137" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="H137" s="5" t="s">
+      <c r="I137" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="I137" s="5" t="s">
+      <c r="J137" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="J137" s="5" t="s">
+      <c r="K137" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="K137" s="5" t="s">
+      <c r="L137" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="L137" s="5" t="s">
+      <c r="M137" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="M137" s="5" t="s">
+      <c r="N137" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="N137" s="5" t="s">
+      <c r="O137" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="O137" s="5" t="s">
+      <c r="P137" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="P137" s="5" t="s">
+      <c r="Q137" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="Q137" s="5" t="s">
+      <c r="R137" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="R137" s="5" t="s">
+      <c r="S137" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="S137" s="5" t="s">
+      <c r="T137" s="5" t="s">
         <v>360</v>
-      </c>
-      <c r="T137" s="5" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="138" spans="1:20">
@@ -5111,19 +5161,19 @@
         <v>230</v>
       </c>
       <c r="H138" t="s">
+        <v>361</v>
+      </c>
+      <c r="I138" t="s">
         <v>362</v>
-      </c>
-      <c r="I138" t="s">
-        <v>363</v>
       </c>
       <c r="J138" t="s">
         <v>267</v>
       </c>
       <c r="K138" t="s">
+        <v>363</v>
+      </c>
+      <c r="L138" t="s">
         <v>364</v>
-      </c>
-      <c r="L138" t="s">
-        <v>365</v>
       </c>
       <c r="M138" t="s">
         <v>323</v>
@@ -5164,22 +5214,22 @@
         <v>246</v>
       </c>
       <c r="F139" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G139" t="s">
         <v>244</v>
       </c>
       <c r="I139" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J139" t="s">
         <v>280</v>
       </c>
       <c r="K139" t="s">
+        <v>367</v>
+      </c>
+      <c r="L139" t="s">
         <v>368</v>
-      </c>
-      <c r="L139" t="s">
-        <v>369</v>
       </c>
       <c r="N139" t="s">
         <v>242</v>
@@ -5223,13 +5273,13 @@
         <v>256</v>
       </c>
       <c r="I140" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="J140" t="s">
         <v>291</v>
       </c>
       <c r="K140" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="N140" t="s">
         <v>255</v>
@@ -5322,7 +5372,7 @@
     </row>
     <row r="143" spans="1:20">
       <c r="B143" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C143" t="s">
         <v>243</v>
@@ -5354,7 +5404,7 @@
     </row>
     <row r="144" spans="1:20">
       <c r="B144" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D144" t="s">
         <v>249</v>
@@ -5479,66 +5529,66 @@
         <v>74</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G154" s="6" t="s">
         <v>102</v>
       </c>
       <c r="H154" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="I154" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="J154" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="K154" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="L154" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="I154" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="J154" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="K154" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="L154" s="6" t="s">
-        <v>375</v>
-      </c>
       <c r="M154" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Q154" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="R154" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="S154" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="T154" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="157" spans="1:20">
       <c r="A157" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="158" spans="1:20">
@@ -5546,7 +5596,7 @@
         <v>1</v>
       </c>
       <c r="B158" s="28" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C158" s="28"/>
       <c r="D158" s="28"/>
@@ -5566,383 +5616,383 @@
         <v>3</v>
       </c>
       <c r="B159" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="C159" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="C159" s="8" t="s">
+      <c r="D159" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="D159" s="8" t="s">
+      <c r="E159" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="E159" s="9" t="s">
+      <c r="F159" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="F159" s="10" t="s">
+      <c r="G159" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="G159" s="11" t="s">
+      <c r="H159" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="H159" s="11" t="s">
+      <c r="I159" s="11" t="s">
         <v>384</v>
-      </c>
-      <c r="I159" s="11" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="160" spans="1:20" ht="30">
       <c r="B160" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="C160" t="s">
         <v>386</v>
       </c>
-      <c r="C160" t="s">
+      <c r="D160" t="s">
         <v>387</v>
       </c>
-      <c r="D160" t="s">
+      <c r="E160" t="s">
         <v>388</v>
       </c>
-      <c r="E160" t="s">
+      <c r="F160" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="F160" s="14" t="s">
+      <c r="G160" t="s">
         <v>390</v>
       </c>
-      <c r="G160" t="s">
-        <v>391</v>
-      </c>
       <c r="H160" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I160" s="15" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="161" spans="2:9">
       <c r="B161" t="s">
+        <v>393</v>
+      </c>
+      <c r="C161" t="s">
         <v>394</v>
       </c>
-      <c r="C161" t="s">
+      <c r="D161" t="s">
         <v>395</v>
       </c>
-      <c r="D161" t="s">
+      <c r="E161" t="s">
+        <v>388</v>
+      </c>
+      <c r="F161" t="s">
+        <v>403</v>
+      </c>
+      <c r="G161" t="s">
         <v>396</v>
       </c>
-      <c r="E161" t="s">
-        <v>389</v>
-      </c>
-      <c r="F161" t="s">
-        <v>404</v>
-      </c>
-      <c r="G161" t="s">
-        <v>397</v>
-      </c>
       <c r="H161" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I161" s="15" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="162" spans="2:9" ht="30">
       <c r="B162" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="C162" s="16" t="s">
         <v>400</v>
       </c>
-      <c r="C162" s="16" t="s">
+      <c r="D162" t="s">
         <v>401</v>
       </c>
-      <c r="D162" t="s">
+      <c r="E162" t="s">
         <v>402</v>
       </c>
-      <c r="E162" t="s">
-        <v>403</v>
-      </c>
       <c r="F162" s="14" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G162" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H162" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I162" s="17" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="163" spans="2:9">
       <c r="B163" t="s">
+        <v>407</v>
+      </c>
+      <c r="C163" t="s">
         <v>408</v>
       </c>
-      <c r="C163" t="s">
+      <c r="D163" t="s">
         <v>409</v>
       </c>
-      <c r="D163" t="s">
+      <c r="E163" t="s">
         <v>410</v>
       </c>
-      <c r="E163" t="s">
-        <v>411</v>
-      </c>
       <c r="F163" s="14" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G163" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H163" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I163" s="15" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="164" spans="2:9">
       <c r="B164" t="s">
+        <v>415</v>
+      </c>
+      <c r="C164" t="s">
         <v>416</v>
       </c>
-      <c r="C164" t="s">
+      <c r="E164" t="s">
         <v>417</v>
       </c>
-      <c r="E164" t="s">
+      <c r="F164" t="s">
+        <v>462</v>
+      </c>
+      <c r="G164" t="s">
         <v>418</v>
       </c>
-      <c r="F164" t="s">
-        <v>463</v>
-      </c>
-      <c r="G164" t="s">
-        <v>419</v>
-      </c>
       <c r="H164" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I164" s="15" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="165" spans="2:9">
       <c r="B165" t="s">
+        <v>421</v>
+      </c>
+      <c r="C165" t="s">
         <v>422</v>
       </c>
-      <c r="C165" t="s">
+      <c r="E165" t="s">
         <v>423</v>
       </c>
-      <c r="E165" t="s">
-        <v>424</v>
-      </c>
       <c r="F165" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G165" s="18"/>
       <c r="I165" s="15" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="166" spans="2:9">
       <c r="B166" t="s">
+        <v>427</v>
+      </c>
+      <c r="C166" t="s">
         <v>428</v>
       </c>
-      <c r="C166" t="s">
+      <c r="E166" t="s">
         <v>429</v>
       </c>
-      <c r="E166" t="s">
-        <v>430</v>
-      </c>
       <c r="F166" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I166" s="19" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="167" spans="2:9">
       <c r="B167" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C167" t="s">
+        <v>433</v>
+      </c>
+      <c r="E167" t="s">
         <v>434</v>
       </c>
-      <c r="E167" t="s">
-        <v>435</v>
-      </c>
       <c r="F167" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I167" s="19" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="168" spans="2:9">
       <c r="B168" t="s">
+        <v>437</v>
+      </c>
+      <c r="C168" t="s">
         <v>438</v>
       </c>
-      <c r="C168" t="s">
+      <c r="E168" t="s">
         <v>439</v>
       </c>
-      <c r="E168" t="s">
-        <v>440</v>
-      </c>
       <c r="F168" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I168" s="15" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="169" spans="2:9" ht="30">
       <c r="B169" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="C169" t="s">
         <v>443</v>
       </c>
-      <c r="C169" t="s">
+      <c r="E169" t="s">
         <v>444</v>
       </c>
-      <c r="E169" t="s">
-        <v>445</v>
-      </c>
       <c r="F169" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I169" s="15" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="170" spans="2:9">
       <c r="B170" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C170" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F170" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I170" s="15" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="171" spans="2:9">
       <c r="B171" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C171" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F171" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I171" s="15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="172" spans="2:9">
       <c r="B172" t="s">
+        <v>452</v>
+      </c>
+      <c r="C172" t="s">
         <v>453</v>
       </c>
-      <c r="C172" t="s">
-        <v>454</v>
-      </c>
       <c r="F172" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I172" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="173" spans="2:9">
       <c r="B173" t="s">
+        <v>455</v>
+      </c>
+      <c r="C173" t="s">
         <v>456</v>
       </c>
-      <c r="C173" t="s">
-        <v>457</v>
-      </c>
       <c r="F173" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I173" s="27" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="174" spans="2:9">
       <c r="B174" t="s">
+        <v>458</v>
+      </c>
+      <c r="C174" t="s">
         <v>459</v>
       </c>
-      <c r="C174" t="s">
-        <v>460</v>
-      </c>
       <c r="F174" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I174" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" spans="2:9">
       <c r="B175" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C175" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F175" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I175" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="176" spans="2:9">
       <c r="B176" t="s">
+        <v>463</v>
+      </c>
+      <c r="C176" t="s">
         <v>464</v>
       </c>
-      <c r="C176" t="s">
-        <v>465</v>
-      </c>
       <c r="F176" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="177" spans="1:20">
       <c r="B177" t="s">
+        <v>465</v>
+      </c>
+      <c r="C177" s="20" t="s">
         <v>466</v>
       </c>
-      <c r="C177" s="20" t="s">
-        <v>467</v>
-      </c>
       <c r="F177" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="178" spans="1:20">
       <c r="B178" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C178" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="179" spans="1:20">
       <c r="B179" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C179" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="180" spans="1:20">
       <c r="B180" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="181" spans="1:20">
       <c r="B181" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="182" spans="1:20">
       <c r="B182" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="183" spans="1:20">
       <c r="B183" s="21" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="184" spans="1:20">
@@ -5950,28 +6000,28 @@
         <v>74</v>
       </c>
       <c r="B184" s="22" t="s">
+        <v>473</v>
+      </c>
+      <c r="C184" s="22" t="s">
         <v>474</v>
       </c>
-      <c r="C184" s="22" t="s">
+      <c r="D184" s="22" t="s">
         <v>475</v>
       </c>
-      <c r="D184" s="22" t="s">
+      <c r="E184" s="23" t="s">
         <v>476</v>
       </c>
-      <c r="E184" s="23" t="s">
+      <c r="F184" s="24" t="s">
         <v>477</v>
       </c>
-      <c r="F184" s="24" t="s">
+      <c r="G184" s="22" t="s">
         <v>478</v>
       </c>
-      <c r="G184" s="22" t="s">
+      <c r="H184" s="22" t="s">
         <v>479</v>
       </c>
-      <c r="H184" s="22" t="s">
+      <c r="I184" s="22" t="s">
         <v>480</v>
-      </c>
-      <c r="I184" s="22" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="186" spans="1:20">
@@ -5979,7 +6029,7 @@
         <v>1</v>
       </c>
       <c r="B186" s="29" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C186" s="29"/>
       <c r="D186" s="29"/>
@@ -6005,401 +6055,401 @@
         <v>3</v>
       </c>
       <c r="B187" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="C187" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="C187" s="5" t="s">
+      <c r="D187" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="D187" s="5" t="s">
+      <c r="E187" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="E187" s="5" t="s">
+      <c r="F187" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="G187" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="F187" s="5" t="s">
+      <c r="H187" s="5" t="s">
         <v>619</v>
-      </c>
-      <c r="G187" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="H187" s="5" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="188" spans="1:20">
       <c r="B188" t="s">
+        <v>386</v>
+      </c>
+      <c r="C188" t="s">
+        <v>385</v>
+      </c>
+      <c r="D188" t="s">
         <v>387</v>
       </c>
-      <c r="C188" t="s">
-        <v>386</v>
-      </c>
-      <c r="D188" t="s">
-        <v>388</v>
-      </c>
       <c r="E188" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F188" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G188" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H188" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="189" spans="1:20">
       <c r="B189" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C189" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D189" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E189" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F189" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G189" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H189" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="190" spans="1:20">
       <c r="B190" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C190" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D190" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E190" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F190" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G190" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H190" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="191" spans="1:20">
       <c r="B191" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C191" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D191" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E191" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F191" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G191" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H191" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="192" spans="1:20">
       <c r="B192" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C192" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D192" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E192" t="s">
+        <v>418</v>
+      </c>
+      <c r="F192" t="s">
+        <v>462</v>
+      </c>
+      <c r="G192" t="s">
         <v>419</v>
       </c>
-      <c r="F192" t="s">
-        <v>463</v>
-      </c>
-      <c r="G192" t="s">
-        <v>420</v>
-      </c>
       <c r="H192" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="193" spans="2:8">
       <c r="B193" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C193" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D193" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E193" t="s">
+        <v>416</v>
+      </c>
+      <c r="F193" t="s">
+        <v>389</v>
+      </c>
+      <c r="G193" t="s">
+        <v>425</v>
+      </c>
+      <c r="H193" t="s">
         <v>417</v>
-      </c>
-      <c r="F193" t="s">
-        <v>390</v>
-      </c>
-      <c r="G193" t="s">
-        <v>426</v>
-      </c>
-      <c r="H193" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="194" spans="2:8">
       <c r="B194" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C194" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F194" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G194" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H194" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="195" spans="2:8">
       <c r="B195" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C195" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F195" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H195" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="196" spans="2:8">
       <c r="B196" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C196" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F196" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H196" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="197" spans="2:8">
       <c r="B197" t="s">
+        <v>443</v>
+      </c>
+      <c r="C197" t="s">
+        <v>463</v>
+      </c>
+      <c r="F197" t="s">
+        <v>424</v>
+      </c>
+      <c r="H197" t="s">
         <v>444</v>
-      </c>
-      <c r="C197" t="s">
-        <v>464</v>
-      </c>
-      <c r="F197" t="s">
-        <v>425</v>
-      </c>
-      <c r="H197" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="198" spans="2:8">
       <c r="B198" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C198" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F198" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="199" spans="2:8">
       <c r="B199" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C199" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F199" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="200" spans="2:8">
       <c r="B200" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C200" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F200" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="201" spans="2:8">
       <c r="B201" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C201" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F201" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="202" spans="2:8">
       <c r="B202" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C202" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F202" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="203" spans="2:8">
       <c r="B203" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C203" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F203" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="204" spans="2:8">
       <c r="B204" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C204" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F204" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="205" spans="2:8">
       <c r="B205" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C205" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F205" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="206" spans="2:8">
       <c r="B206" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C206" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F206" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="207" spans="2:8">
       <c r="B207" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C207" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="208" spans="2:8">
       <c r="B208" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C208" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="209" spans="1:14">
       <c r="B209" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C209" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="210" spans="1:14">
       <c r="B210" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C210" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="211" spans="1:14">
       <c r="B211" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C211" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="212" spans="1:14">
       <c r="C212" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="213" spans="1:14">
       <c r="C213" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="214" spans="1:14">
       <c r="C214" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="215" spans="1:14">
       <c r="C215" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="216" spans="1:14">
       <c r="C216" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="217" spans="1:14">
       <c r="C217" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="218" spans="1:14">
       <c r="C218" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="219" spans="1:14">
       <c r="C219" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="220" spans="1:14" s="6" customFormat="1">
@@ -6407,30 +6457,30 @@
         <v>74</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F220" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="222" spans="1:14">
       <c r="A222" s="7" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="223" spans="1:14">
@@ -6438,7 +6488,7 @@
         <v>1</v>
       </c>
       <c r="B223" s="28" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C223" s="28"/>
       <c r="D223" s="28"/>
@@ -6458,291 +6508,297 @@
         <v>3</v>
       </c>
       <c r="B224" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="C224" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="C224" s="3" t="s">
+      <c r="D224" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="D224" s="3" t="s">
+      <c r="E224" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="E224" s="3" t="s">
+      <c r="F224" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="F224" s="3" t="s">
+      <c r="G224" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="G224" s="3" t="s">
+      <c r="H224" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="H224" s="3" t="s">
-        <v>498</v>
-      </c>
       <c r="I224" s="3" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="225" spans="2:11">
       <c r="B225" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C225" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D225" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E225" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F225" t="s">
+        <v>501</v>
+      </c>
+      <c r="G225" t="s">
         <v>502</v>
       </c>
-      <c r="G225" t="s">
-        <v>503</v>
-      </c>
       <c r="H225" s="20" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="I225" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="226" spans="2:11">
       <c r="B226" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C226" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D226" t="s">
+        <v>499</v>
+      </c>
+      <c r="E226" t="s">
         <v>500</v>
       </c>
-      <c r="E226" t="s">
-        <v>501</v>
-      </c>
       <c r="G226" t="s">
-        <v>508</v>
+        <v>646</v>
       </c>
       <c r="H226" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="I226" t="s">
-        <v>642</v>
+        <v>507</v>
       </c>
     </row>
     <row r="227" spans="2:11">
       <c r="B227" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C227" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D227" t="s">
+        <v>622</v>
+      </c>
+      <c r="E227" t="s">
         <v>623</v>
       </c>
-      <c r="E227" t="s">
-        <v>624</v>
+      <c r="G227" t="s">
+        <v>647</v>
       </c>
       <c r="H227" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="228" spans="2:11">
       <c r="B228" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C228" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D228" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E228" t="s">
-        <v>625</v>
+        <v>624</v>
+      </c>
+      <c r="G228" t="s">
+        <v>648</v>
       </c>
       <c r="H228" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="229" spans="2:11">
       <c r="B229" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C229" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D229" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E229" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H229" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K229" s="26"/>
     </row>
     <row r="230" spans="2:11">
       <c r="B230" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C230" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D230" t="s">
         <v>98</v>
       </c>
       <c r="E230" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H230" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="K230" s="25"/>
     </row>
     <row r="231" spans="2:11">
       <c r="B231" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C231" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D231" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E231" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H231" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K231" s="26"/>
     </row>
     <row r="232" spans="2:11">
       <c r="B232" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C232" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D232" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E232" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H232" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="K232" s="25"/>
     </row>
     <row r="233" spans="2:11">
       <c r="B233" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C233" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D233" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E233" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H233" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K233" s="26"/>
     </row>
     <row r="234" spans="2:11">
       <c r="B234" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C234" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D234" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E234" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H234" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K234" s="25"/>
     </row>
     <row r="235" spans="2:11">
       <c r="B235" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C235" t="s">
+        <v>536</v>
+      </c>
+      <c r="E235" t="s">
         <v>537</v>
       </c>
-      <c r="E235" t="s">
-        <v>538</v>
-      </c>
       <c r="H235" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="K235" s="26"/>
     </row>
     <row r="236" spans="2:11">
       <c r="B236" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C236" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E236" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="K236" s="25"/>
     </row>
     <row r="237" spans="2:11">
       <c r="B237" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C237" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="K237" s="26"/>
     </row>
     <row r="238" spans="2:11">
       <c r="B238" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C238" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K238" s="25"/>
     </row>
     <row r="239" spans="2:11">
       <c r="B239" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="K239" s="26"/>
     </row>
     <row r="240" spans="2:11">
       <c r="B240" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="K240" s="25"/>
     </row>
     <row r="241" spans="1:20">
       <c r="B241" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="242" spans="1:20">
       <c r="B242" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:20">
       <c r="B243" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="246" spans="1:20" s="4" customFormat="1">
@@ -6750,25 +6806,28 @@
         <v>74</v>
       </c>
       <c r="B246" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="C246" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="C246" s="4" t="s">
+      <c r="D246" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="D246" s="4" t="s">
+      <c r="E246" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="E246" s="4" t="s">
+      <c r="F246" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="F246" s="4" t="s">
+      <c r="G246" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="G246" s="4" t="s">
+      <c r="H246" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="H246" s="4" t="s">
-        <v>561</v>
+      <c r="I246" s="4" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="248" spans="1:20">
@@ -6776,7 +6835,7 @@
         <v>1</v>
       </c>
       <c r="B248" s="29" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C248" s="29"/>
       <c r="D248" s="29"/>
@@ -6802,323 +6861,323 @@
         <v>3</v>
       </c>
       <c r="B249" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="D249" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="C249" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="D249" s="5" t="s">
+      <c r="E249" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="E249" s="5" t="s">
+      <c r="F249" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="F249" s="5" t="s">
+      <c r="G249" s="5" t="s">
         <v>567</v>
-      </c>
-      <c r="G249" s="5" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="250" spans="1:20">
       <c r="B250" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C250" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D250" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E250" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F250" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="G250" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="251" spans="1:20">
       <c r="B251" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C251" t="s">
+        <v>538</v>
+      </c>
+      <c r="D251" t="s">
+        <v>573</v>
+      </c>
+      <c r="E251" t="s">
+        <v>574</v>
+      </c>
+      <c r="F251" t="s">
+        <v>499</v>
+      </c>
+      <c r="G251" t="s">
         <v>539</v>
-      </c>
-      <c r="D251" t="s">
-        <v>574</v>
-      </c>
-      <c r="E251" t="s">
-        <v>575</v>
-      </c>
-      <c r="F251" t="s">
-        <v>500</v>
-      </c>
-      <c r="G251" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="252" spans="1:20">
       <c r="B252" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C252" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D252" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E252" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F252" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G252" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:20">
       <c r="B253" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C253" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D253" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F253" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G253" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="254" spans="1:20">
       <c r="B254" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C254" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D254" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F254" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G254" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="255" spans="1:20">
       <c r="B255" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C255" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D255" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F255" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G255" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="256" spans="1:20">
       <c r="B256" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C256" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D256" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F256" t="s">
         <v>98</v>
       </c>
       <c r="G256" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="257" spans="2:7">
       <c r="B257" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C257" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D257" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F257" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G257" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="258" spans="2:7">
       <c r="B258" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C258" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D258" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="F258" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G258" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="259" spans="2:7">
       <c r="B259" t="s">
+        <v>581</v>
+      </c>
+      <c r="C259" t="s">
+        <v>543</v>
+      </c>
+      <c r="D259" t="s">
         <v>582</v>
       </c>
-      <c r="C259" t="s">
-        <v>544</v>
-      </c>
-      <c r="D259" t="s">
-        <v>583</v>
-      </c>
       <c r="F259" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G259" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="260" spans="2:7">
       <c r="B260" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C260" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D260" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F260" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G260" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="261" spans="2:7">
       <c r="B261" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C261" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D261" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F261" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G261" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="262" spans="2:7">
       <c r="B262" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C262" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D262" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G262" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="263" spans="2:7">
       <c r="B263" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C263" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D263" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="264" spans="2:7">
       <c r="B264" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C264" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D264" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="265" spans="2:7">
       <c r="B265" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C265" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D265" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="266" spans="2:7">
       <c r="C266" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D266" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="267" spans="2:7">
       <c r="C267" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D267" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="268" spans="2:7">
       <c r="D268" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="269" spans="2:7">
       <c r="D269" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="270" spans="2:7">
       <c r="D270" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="271" spans="2:7">
       <c r="D271" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="272" spans="2:7">
       <c r="D272" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="273" spans="1:8" s="6" customFormat="1">
@@ -7126,25 +7185,25 @@
         <v>74</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D273" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E273" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F273" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G273" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H273" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/List_Team_Region.xlsx
+++ b/public/data/List_Team_Region.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muham\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0587D559-D857-46F7-9EEC-4038ECF4544E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE1B41F-D534-4449-9C71-7E1BE1D54C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="555" yWindow="4200" windowWidth="12345" windowHeight="7320" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
+    <workbookView xWindow="9435" yWindow="795" windowWidth="13905" windowHeight="14265" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="656">
   <si>
     <t>JAMBI</t>
   </si>
@@ -7167,17 +7167,7 @@
     </row>
     <row r="270" spans="2:7">
       <c r="D270" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="271" spans="2:7">
-      <c r="D271" t="s">
         <v>633</v>
-      </c>
-    </row>
-    <row r="272" spans="2:7">
-      <c r="D272" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="273" spans="1:8" s="6" customFormat="1">

--- a/public/data/List_Team_Region.xlsx
+++ b/public/data/List_Team_Region.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muham\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE1B41F-D534-4449-9C71-7E1BE1D54C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82CFDE1-B944-4733-BD8C-D5E02D984276}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9435" yWindow="795" windowWidth="13905" windowHeight="14265" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
+    <workbookView xWindow="9180" yWindow="1845" windowWidth="17655" windowHeight="12960" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="648">
   <si>
     <t>JAMBI</t>
   </si>
@@ -1032,6 +1032,9 @@
     <t>ALDO</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC RETAIL	</t>
+  </si>
+  <si>
     <t>Malik</t>
   </si>
   <si>
@@ -1956,6 +1959,9 @@
     <t>SBS-BHMA.TANJUNG.RATU-FH.AN6001.G16-OLT-01</t>
   </si>
   <si>
+    <t xml:space="preserve"> SBS-BHMA.TANJUNG.GUNUNG-FH.AN6000.2-OLT-01</t>
+  </si>
+  <si>
     <t>BHMA PANGKAL</t>
   </si>
   <si>
@@ -1969,36 +1975,6 @@
   </si>
   <si>
     <t>SBS-SUNGAI.PENUH-HW.MA5801-OLT-01</t>
-  </si>
-  <si>
-    <t>SBS-BHMA.TOBOALI-FH.AN6001.G16-OLT-05</t>
-  </si>
-  <si>
-    <t>SBS-BHMA.AIRBARA-FH.AN6001.G16-OLT-01</t>
-  </si>
-  <si>
-    <t>SBS-BHMA.KULUR-FH.AN6000.2-OLT-01</t>
-  </si>
-  <si>
-    <t>SBS-BHMA.TAMBAKSARI-AN6000.2-OLT-01</t>
-  </si>
-  <si>
-    <t>SBS-BHMA.JELUTUNG-AN6000.2-OLT-01</t>
-  </si>
-  <si>
-    <t>SBS-BHMA.KOTABARU-AN6001-OLT-02</t>
-  </si>
-  <si>
-    <t>BHMA JAMBI</t>
-  </si>
-  <si>
-    <t>SBS-BHMA.SEKIP.JAYA-FH.AN6000.2-OLT-01</t>
-  </si>
-  <si>
-    <t>SBS-BHMA.KEMUNING-FH.AN6000.2-OLT-01</t>
-  </si>
-  <si>
-    <t>BHMA PALEMBANG</t>
   </si>
 </sst>
 </file>
@@ -2562,16 +2538,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}" name="Table919" displayName="Table919" ref="B3:I22" totalsRowShown="0" headerRowDxfId="12">
-  <autoFilter ref="B3:I22" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}" name="Table919" displayName="Table919" ref="B3:H22" totalsRowShown="0" headerRowDxfId="12">
+  <autoFilter ref="B3:H22" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{1E18F602-B85E-4C85-8C34-8684E3651598}" name="INTERNAL JAMBI"/>
     <tableColumn id="2" xr3:uid="{FB0AE047-7A54-41C3-8DE2-5FB87347FC5A}" name="TTM SAROLANGUN"/>
     <tableColumn id="3" xr3:uid="{A9B09C98-0448-4BFE-9FCC-534A4FFDCBB7}" name="TTM MERANGIN"/>
     <tableColumn id="4" xr3:uid="{54B8B45C-2FD6-4B38-83C8-85E5B4BDC6D9}" name="GSP MUARA BULIAN"/>
     <tableColumn id="5" xr3:uid="{CB18B3A9-79B8-4ED4-A869-445C0D0FFA3E}" name="GSP JAMBI 2"/>
     <tableColumn id="6" xr3:uid="{D9DCD84D-C9D6-4860-AE60-7A035270E21A}" name="GSP SUNGAI PENUH"/>
-    <tableColumn id="8" xr3:uid="{DDACFCB7-36E2-43BD-9D11-A74626303C39}" name="BHMA JAMBI"/>
     <tableColumn id="7" xr3:uid="{ED41A1AB-EDC7-4B03-A268-9EB9271D2B5D}" name="GSP TEBO"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2658,9 +2633,9 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}" name="Table1323" displayName="Table1323" ref="B112:O134" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="B112:O134" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}" name="Table1323" displayName="Table1323" ref="B112:N134" totalsRowShown="0" headerRowDxfId="8">
+  <autoFilter ref="B112:N134" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}"/>
+  <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{6FB6563D-399C-4506-8AF0-A312347E4888}" name="REG7 PALEMBANG 1"/>
     <tableColumn id="2" xr3:uid="{211D6500-28BD-4C9B-A588-576FE1D6FE10}" name="REG7 PALEMBANG 2"/>
     <tableColumn id="3" xr3:uid="{355E3A8F-21BA-4348-9564-2FAF305488B3}" name="REG7 PALEMBANG 3"/>
@@ -2674,7 +2649,6 @@
     <tableColumn id="12" xr3:uid="{3BF035D4-D0DE-4F99-8178-5942792867E9}" name="SIB PAGARALAM "/>
     <tableColumn id="13" xr3:uid="{DB140030-979E-44A0-B027-9374EEA27F7E}" name="SIB LAHAT"/>
     <tableColumn id="14" xr3:uid="{F37F02C6-FE10-4DC1-875F-57ABBB0AF623}" name="SIB EMPAT LAWANG"/>
-    <tableColumn id="6" xr3:uid="{85A4AA6D-A8EF-4A9B-8B83-7372439F408F}" name="BHMA PALEMBANG"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2698,8 +2672,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}" name="Table1525" displayName="Table1525" ref="B187:H219" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="B187:H219" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}" name="Table1525" displayName="Table1525" ref="B187:H220" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="B187:H220" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{ACEB90AF-9CBB-4605-8377-2CF0EF299650}" name="SERPO SUKAMERINDU"/>
     <tableColumn id="2" xr3:uid="{351154A5-2DE7-411B-9044-B8641069B0BF}" name="SERPO BENGKULU KOTA"/>
@@ -2714,8 +2688,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}" name="Table1626" displayName="Table1626" ref="B224:I246" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="B224:I246" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}" name="Table1626" displayName="Table1626" ref="B225:I247" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="B225:I247" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{D0B3A41D-F35E-4B89-AC56-18717B9B04E5}" name="BANGKA REG 7"/>
     <tableColumn id="2" xr3:uid="{9C59FCCC-409F-4148-A8DC-48E653CEBBAA}" name="TTM SUNGAI LIAT"/>
@@ -2731,8 +2705,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}" name="Table1727" displayName="Table1727" ref="B249:G272" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="B249:G272" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}" name="Table1727" displayName="Table1727" ref="B250:G273" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="B250:G273" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{97E25E83-847F-4991-A885-21D98063A2DB}" name="SERPO KOBA"/>
     <tableColumn id="2" xr3:uid="{0AB964B5-883A-49C8-8DDA-C8EE93753519}" name="SERPO PANGKAL PINANG"/>
@@ -3062,31 +3036,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D0AF9EF-6686-405D-9473-604A5805FA6C}">
-  <dimension ref="A1:T273"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:T274"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="34.140625" customWidth="1"/>
+    <col min="2" max="2" width="34.125" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="27.7109375" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" customWidth="1"/>
-    <col min="6" max="6" width="27.5703125" customWidth="1"/>
-    <col min="7" max="7" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="27.75" customWidth="1"/>
+    <col min="5" max="5" width="26.625" customWidth="1"/>
+    <col min="6" max="6" width="27.625" customWidth="1"/>
+    <col min="7" max="7" width="22.875" customWidth="1"/>
     <col min="8" max="8" width="27" customWidth="1"/>
-    <col min="9" max="9" width="21.85546875" customWidth="1"/>
-    <col min="10" max="10" width="27.140625" customWidth="1"/>
-    <col min="11" max="11" width="24.7109375" customWidth="1"/>
-    <col min="12" max="12" width="27.5703125" customWidth="1"/>
-    <col min="13" max="13" width="21.85546875" customWidth="1"/>
+    <col min="9" max="9" width="21.875" customWidth="1"/>
+    <col min="10" max="10" width="27.125" customWidth="1"/>
+    <col min="11" max="11" width="24.75" customWidth="1"/>
+    <col min="12" max="12" width="27.625" customWidth="1"/>
+    <col min="13" max="13" width="21.875" customWidth="1"/>
     <col min="14" max="14" width="28" customWidth="1"/>
-    <col min="15" max="15" width="25.7109375" customWidth="1"/>
-    <col min="16" max="16" width="20.85546875" customWidth="1"/>
-    <col min="17" max="17" width="23.85546875" customWidth="1"/>
-    <col min="18" max="18" width="22.28515625" customWidth="1"/>
-    <col min="19" max="19" width="28.140625" customWidth="1"/>
-    <col min="20" max="20" width="27.28515625" customWidth="1"/>
+    <col min="15" max="15" width="25.75" customWidth="1"/>
+    <col min="16" max="16" width="20.875" customWidth="1"/>
+    <col min="17" max="17" width="23.875" customWidth="1"/>
+    <col min="18" max="18" width="22.25" customWidth="1"/>
+    <col min="19" max="19" width="28.125" customWidth="1"/>
+    <col min="20" max="20" width="27.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3134,9 +3108,6 @@
         <v>9</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="I3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3151,7 +3122,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
@@ -3160,9 +3131,6 @@
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>649</v>
-      </c>
-      <c r="I4" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3171,7 +3139,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -3186,9 +3154,6 @@
         <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>650</v>
-      </c>
-      <c r="I5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3200,7 +3165,7 @@
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E6" t="s">
         <v>27</v>
@@ -3212,9 +3177,6 @@
         <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>651</v>
-      </c>
-      <c r="I6" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3223,7 +3185,7 @@
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -3237,7 +3199,7 @@
       <c r="G7" t="s">
         <v>36</v>
       </c>
-      <c r="I7" t="s">
+      <c r="H7" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3260,7 +3222,7 @@
       <c r="G8" t="s">
         <v>41</v>
       </c>
-      <c r="I8" t="s">
+      <c r="H8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -3269,7 +3231,7 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D9" t="s">
         <v>47</v>
@@ -3278,9 +3240,9 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>645</v>
-      </c>
-      <c r="I9" t="s">
+        <v>647</v>
+      </c>
+      <c r="H9" t="s">
         <v>45</v>
       </c>
     </row>
@@ -3289,7 +3251,7 @@
         <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D10" t="s">
         <v>51</v>
@@ -3300,16 +3262,16 @@
       <c r="G10" t="s">
         <v>49</v>
       </c>
-      <c r="I10" t="s">
+      <c r="H10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="B11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D11" t="s">
         <v>54</v>
@@ -3318,7 +3280,7 @@
         <v>52</v>
       </c>
       <c r="G11" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -3335,7 +3297,7 @@
         <v>55</v>
       </c>
       <c r="G12" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -3349,7 +3311,7 @@
         <v>58</v>
       </c>
       <c r="G13" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -3426,7 +3388,7 @@
         <v>74</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>75</v>
@@ -3444,13 +3406,10 @@
         <v>79</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>634</v>
-      </c>
-      <c r="I23" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:20" ht="15">
       <c r="A25" s="2" t="s">
         <v>1</v>
       </c>
@@ -3510,7 +3469,7 @@
     </row>
     <row r="27" spans="1:20">
       <c r="B27" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C27" t="s">
         <v>62</v>
@@ -3528,7 +3487,7 @@
         <v>13</v>
       </c>
       <c r="H27" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="I27" t="s">
         <v>16</v>
@@ -3548,7 +3507,7 @@
         <v>46</v>
       </c>
       <c r="E28" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -3580,10 +3539,10 @@
         <v>27</v>
       </c>
       <c r="G29" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H29" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="I29" t="s">
         <v>30</v>
@@ -3600,7 +3559,7 @@
         <v>99</v>
       </c>
       <c r="E30" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F30" t="s">
         <v>34</v>
@@ -3643,7 +3602,7 @@
     </row>
     <row r="32" spans="1:20">
       <c r="B32" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C32" t="s">
         <v>40</v>
@@ -3652,13 +3611,13 @@
         <v>28</v>
       </c>
       <c r="E32" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G32" t="s">
         <v>47</v>
       </c>
       <c r="H32" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="I32" t="s">
         <v>45</v>
@@ -3669,16 +3628,16 @@
         <v>66</v>
       </c>
       <c r="D33" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E33" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G33" t="s">
         <v>51</v>
       </c>
       <c r="H33" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I33" t="s">
         <v>50</v>
@@ -3692,7 +3651,7 @@
         <v>72</v>
       </c>
       <c r="E34" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G34" t="s">
         <v>54</v>
@@ -3826,7 +3785,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" ht="15">
       <c r="A48" s="1" t="s">
         <v>103</v>
       </c>
@@ -3942,7 +3901,7 @@
         <v>135</v>
       </c>
       <c r="D54" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E54" t="s">
         <v>131</v>
@@ -3982,7 +3941,7 @@
         <v>146</v>
       </c>
       <c r="D56" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E56" t="s">
         <v>143</v>
@@ -4016,7 +3975,7 @@
         <v>154</v>
       </c>
       <c r="D58" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F58" t="s">
         <v>156</v>
@@ -4069,13 +4028,13 @@
     </row>
     <row r="62" spans="1:14">
       <c r="C62" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D62" t="s">
         <v>147</v>
       </c>
       <c r="F62" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G62" t="s">
         <v>162</v>
@@ -4083,13 +4042,13 @@
     </row>
     <row r="63" spans="1:14">
       <c r="C63" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D63" t="s">
         <v>151</v>
       </c>
       <c r="F63" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G63" t="s">
         <v>164</v>
@@ -4179,16 +4138,16 @@
         <v>178</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>179</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" ht="15">
       <c r="A81" s="2" t="s">
         <v>1</v>
       </c>
@@ -4317,7 +4276,7 @@
     </row>
     <row r="86" spans="1:20">
       <c r="B86" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C86" t="s">
         <v>139</v>
@@ -4368,7 +4327,7 @@
     </row>
     <row r="89" spans="1:20">
       <c r="B89" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C89" t="s">
         <v>133</v>
@@ -4454,7 +4413,7 @@
     </row>
     <row r="96" spans="1:20">
       <c r="B96" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C96" t="s">
         <v>159</v>
@@ -4463,76 +4422,76 @@
         <v>123</v>
       </c>
     </row>
-    <row r="97" spans="1:15">
+    <row r="97" spans="1:14">
       <c r="B97" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C97" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E97" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="98" spans="1:15">
+    <row r="98" spans="1:14">
       <c r="B98" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E98" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="99" spans="1:15">
+    <row r="99" spans="1:14">
       <c r="B99" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E99" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="100" spans="1:15">
+    <row r="100" spans="1:14">
       <c r="B100" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E100" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="101" spans="1:15">
+    <row r="101" spans="1:14">
       <c r="B101" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E101" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="102" spans="1:15">
+    <row r="102" spans="1:14">
       <c r="B102" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E102" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="103" spans="1:15">
+    <row r="103" spans="1:14">
       <c r="B103" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E103" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="104" spans="1:15">
+    <row r="104" spans="1:14">
       <c r="E104" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14">
       <c r="E105" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="106" spans="1:15">
+    <row r="106" spans="1:14">
       <c r="B106" t="s">
         <v>203</v>
       </c>
@@ -4540,7 +4499,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="107" spans="1:15" s="6" customFormat="1">
+    <row r="107" spans="1:14" s="6" customFormat="1">
       <c r="A107" s="6" t="s">
         <v>74</v>
       </c>
@@ -4569,15 +4528,15 @@
         <v>207</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" ht="15">
       <c r="A110" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="111" spans="1:15">
+    <row r="111" spans="1:14">
       <c r="A111" s="2" t="s">
         <v>1</v>
       </c>
@@ -4597,7 +4556,7 @@
       <c r="M111" s="28"/>
       <c r="N111" s="28"/>
     </row>
-    <row r="112" spans="1:15" s="3" customFormat="1">
+    <row r="112" spans="1:14" s="3" customFormat="1">
       <c r="A112" s="3" t="s">
         <v>3</v>
       </c>
@@ -4640,11 +4599,8 @@
       <c r="N112" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="O112" s="3" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="113" spans="2:15">
+    </row>
+    <row r="113" spans="2:14">
       <c r="B113" t="s">
         <v>223</v>
       </c>
@@ -4684,11 +4640,8 @@
       <c r="N113" t="s">
         <v>236</v>
       </c>
-      <c r="O113" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="114" spans="2:15">
+    </row>
+    <row r="114" spans="2:14">
       <c r="B114" t="s">
         <v>237</v>
       </c>
@@ -4728,11 +4681,8 @@
       <c r="N114" t="s">
         <v>249</v>
       </c>
-      <c r="O114" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="115" spans="2:15">
+    </row>
+    <row r="115" spans="2:14">
       <c r="B115" t="s">
         <v>250</v>
       </c>
@@ -4770,7 +4720,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="116" spans="2:15">
+    <row r="116" spans="2:14">
       <c r="B116" t="s">
         <v>263</v>
       </c>
@@ -4808,7 +4758,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="117" spans="2:15">
+    <row r="117" spans="2:14">
       <c r="B117" t="s">
         <v>275</v>
       </c>
@@ -4843,7 +4793,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="118" spans="2:15">
+    <row r="118" spans="2:14">
       <c r="B118" t="s">
         <v>287</v>
       </c>
@@ -4872,7 +4822,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="119" spans="2:15">
+    <row r="119" spans="2:14">
       <c r="B119" t="s">
         <v>297</v>
       </c>
@@ -4901,7 +4851,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="120" spans="2:15">
+    <row r="120" spans="2:14">
       <c r="B120" t="s">
         <v>306</v>
       </c>
@@ -4918,13 +4868,13 @@
         <v>310</v>
       </c>
       <c r="I120" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J120" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="121" spans="2:15">
+    <row r="121" spans="2:14">
       <c r="B121" t="s">
         <v>312</v>
       </c>
@@ -4941,7 +4891,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="122" spans="2:15">
+    <row r="122" spans="2:14">
       <c r="B122" t="s">
         <v>317</v>
       </c>
@@ -4958,7 +4908,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="123" spans="2:15">
+    <row r="123" spans="2:14">
       <c r="B123" t="s">
         <v>321</v>
       </c>
@@ -4972,7 +4922,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="124" spans="2:15">
+    <row r="124" spans="2:14">
       <c r="B124" t="s">
         <v>324</v>
       </c>
@@ -4983,7 +4933,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="125" spans="2:15">
+    <row r="125" spans="2:14">
       <c r="E125" t="s">
         <v>280</v>
       </c>
@@ -4991,7 +4941,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="126" spans="2:15">
+    <row r="126" spans="2:14">
       <c r="E126" t="s">
         <v>291</v>
       </c>
@@ -4999,12 +4949,12 @@
         <v>327</v>
       </c>
     </row>
-    <row r="127" spans="2:15">
+    <row r="127" spans="2:14">
       <c r="J127" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="128" spans="2:15">
+    <row r="128" spans="2:14">
       <c r="J128" t="s">
         <v>329</v>
       </c>
@@ -5023,42 +4973,42 @@
         <v>332</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>634</v>
+        <v>333</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M134" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N134" s="4" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="136" spans="1:20">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="136" spans="1:20" ht="15">
       <c r="A136" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B136" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C136" s="29"/>
       <c r="D136" s="29"/>
@@ -5084,61 +5034,61 @@
         <v>3</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I137" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J137" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K137" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L137" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M137" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N137" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O137" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P137" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q137" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="R137" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="S137" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="T137" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="138" spans="1:20">
@@ -5161,19 +5111,19 @@
         <v>230</v>
       </c>
       <c r="H138" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I138" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J138" t="s">
         <v>267</v>
       </c>
       <c r="K138" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L138" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M138" t="s">
         <v>323</v>
@@ -5214,22 +5164,22 @@
         <v>246</v>
       </c>
       <c r="F139" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G139" t="s">
         <v>244</v>
       </c>
       <c r="I139" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J139" t="s">
         <v>280</v>
       </c>
       <c r="K139" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L139" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N139" t="s">
         <v>242</v>
@@ -5273,13 +5223,13 @@
         <v>256</v>
       </c>
       <c r="I140" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J140" t="s">
         <v>291</v>
       </c>
       <c r="K140" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N140" t="s">
         <v>255</v>
@@ -5372,7 +5322,7 @@
     </row>
     <row r="143" spans="1:20">
       <c r="B143" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C143" t="s">
         <v>243</v>
@@ -5404,7 +5354,7 @@
     </row>
     <row r="144" spans="1:20">
       <c r="B144" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D144" t="s">
         <v>249</v>
@@ -5529,66 +5479,66 @@
         <v>74</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G154" s="6" t="s">
         <v>102</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J154" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K154" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L154" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="M154" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="M154" s="6" t="s">
-        <v>373</v>
-      </c>
       <c r="N154" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q154" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="R154" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="S154" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="T154" s="6" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="157" spans="1:20">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="157" spans="1:20" ht="15">
       <c r="A157" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="158" spans="1:20">
@@ -5596,7 +5546,7 @@
         <v>1</v>
       </c>
       <c r="B158" s="28" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C158" s="28"/>
       <c r="D158" s="28"/>
@@ -5611,425 +5561,425 @@
       <c r="M158" s="28"/>
       <c r="N158" s="28"/>
     </row>
-    <row r="159" spans="1:20" s="12" customFormat="1">
+    <row r="159" spans="1:20" s="12" customFormat="1" ht="15">
       <c r="A159" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F159" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G159" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H159" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I159" s="11" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="160" spans="1:20" ht="30">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="160" spans="1:20" ht="28.5">
       <c r="B160" s="13" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C160" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D160" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E160" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F160" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G160" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H160" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I160" s="15" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="161" spans="2:9">
       <c r="B161" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C161" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D161" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E161" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F161" t="s">
+        <v>404</v>
+      </c>
+      <c r="G161" t="s">
+        <v>397</v>
+      </c>
+      <c r="H161" t="s">
+        <v>414</v>
+      </c>
+      <c r="I161" s="15" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="162" spans="2:9" ht="28.5">
+      <c r="B162" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="C162" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="D162" t="s">
+        <v>402</v>
+      </c>
+      <c r="E162" t="s">
         <v>403</v>
       </c>
-      <c r="G161" t="s">
-        <v>396</v>
-      </c>
-      <c r="H161" t="s">
-        <v>413</v>
-      </c>
-      <c r="I161" s="15" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="162" spans="2:9" ht="30">
-      <c r="B162" s="16" t="s">
-        <v>399</v>
-      </c>
-      <c r="C162" s="16" t="s">
-        <v>400</v>
-      </c>
-      <c r="D162" t="s">
-        <v>401</v>
-      </c>
-      <c r="E162" t="s">
-        <v>402</v>
-      </c>
       <c r="F162" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G162" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H162" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I162" s="17" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="163" spans="2:9">
       <c r="B163" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C163" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D163" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E163" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F163" s="14" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G163" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I163" s="15" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="164" spans="2:9">
       <c r="B164" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C164" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E164" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F164" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G164" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H164" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I164" s="15" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="165" spans="2:9">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="165" spans="2:9" ht="15">
       <c r="B165" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C165" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E165" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F165" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G165" s="18"/>
       <c r="I165" s="15" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="166" spans="2:9">
       <c r="B166" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E166" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F166" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I166" s="19" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="167" spans="2:9">
       <c r="B167" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C167" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E167" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F167" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="I167" s="19" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="168" spans="2:9">
       <c r="B168" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C168" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E168" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F168" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I168" s="15" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="169" spans="2:9" ht="30">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="169" spans="2:9" ht="28.5">
       <c r="B169" s="14" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C169" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E169" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F169" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I169" s="15" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="170" spans="2:9">
       <c r="B170" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C170" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F170" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I170" s="15" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="171" spans="2:9">
       <c r="B171" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C171" t="s">
+        <v>451</v>
+      </c>
+      <c r="F171" t="s">
+        <v>436</v>
+      </c>
+      <c r="I171" s="15" t="s">
         <v>450</v>
-      </c>
-      <c r="F171" t="s">
-        <v>435</v>
-      </c>
-      <c r="I171" s="15" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="172" spans="2:9">
       <c r="B172" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C172" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F172" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I172" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="173" spans="2:9">
       <c r="B173" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C173" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F173" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I173" s="27" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="174" spans="2:9">
       <c r="B174" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C174" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F174" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I174" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="175" spans="2:9">
       <c r="B175" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C175" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F175" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I175" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="176" spans="2:9">
       <c r="B176" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C176" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F176" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="177" spans="1:20">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="177" spans="1:20" ht="15">
       <c r="B177" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C177" s="20" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F177" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="178" spans="1:20">
       <c r="B178" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C178" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="179" spans="1:20">
       <c r="B179" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C179" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="180" spans="1:20">
       <c r="B180" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="181" spans="1:20">
       <c r="B181" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="182" spans="1:20">
       <c r="B182" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="183" spans="1:20">
       <c r="B183" s="21" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="184" spans="1:20">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="184" spans="1:20" ht="15">
       <c r="A184" s="4" t="s">
         <v>74</v>
       </c>
       <c r="B184" s="22" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C184" s="22" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D184" s="22" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E184" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F184" s="24" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G184" s="22" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H184" s="22" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I184" s="22" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="186" spans="1:20">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="186" spans="1:20" ht="15">
       <c r="A186" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B186" s="29" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C186" s="29"/>
       <c r="D186" s="29"/>
@@ -6055,1153 +6005,1156 @@
         <v>3</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H187" s="5" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="188" spans="1:20">
       <c r="B188" t="s">
+        <v>387</v>
+      </c>
+      <c r="C188" t="s">
         <v>386</v>
       </c>
-      <c r="C188" t="s">
-        <v>385</v>
-      </c>
       <c r="D188" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E188" t="s">
+        <v>391</v>
+      </c>
+      <c r="F188" t="s">
         <v>390</v>
       </c>
-      <c r="F188" t="s">
-        <v>389</v>
-      </c>
       <c r="G188" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H188" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="189" spans="1:20">
       <c r="B189" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C189" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D189" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E189" t="s">
+        <v>405</v>
+      </c>
+      <c r="F189" t="s">
         <v>404</v>
       </c>
-      <c r="F189" t="s">
-        <v>403</v>
-      </c>
       <c r="G189" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H189" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="190" spans="1:20">
       <c r="B190" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C190" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D190" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E190" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F190" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G190" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H190" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="191" spans="1:20">
       <c r="B191" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C191" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D191" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E191" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F191" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G191" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H191" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="192" spans="1:20">
       <c r="B192" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C192" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D192" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E192" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F192" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G192" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H192" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="193" spans="2:8">
       <c r="B193" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C193" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D193" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E193" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F193" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G193" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H193" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="194" spans="2:8">
       <c r="B194" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C194" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F194" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G194" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H194" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="195" spans="2:8">
       <c r="B195" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C195" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F195" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H195" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="196" spans="2:8">
       <c r="B196" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C196" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F196" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H196" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="197" spans="2:8">
       <c r="B197" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C197" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F197" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H197" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="198" spans="2:8">
       <c r="B198" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C198" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F198" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="199" spans="2:8">
       <c r="B199" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C199" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F199" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="200" spans="2:8">
       <c r="B200" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C200" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F200" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="201" spans="2:8">
       <c r="B201" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C201" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F201" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="202" spans="2:8">
       <c r="B202" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C202" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F202" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="203" spans="2:8">
       <c r="B203" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C203" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F203" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="204" spans="2:8">
       <c r="B204" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C204" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F204" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="205" spans="2:8">
       <c r="B205" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C205" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F205" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="206" spans="2:8">
       <c r="B206" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C206" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F206" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="207" spans="2:8">
       <c r="B207" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C207" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="208" spans="2:8">
       <c r="B208" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C208" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="209" spans="1:14">
       <c r="B209" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C209" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="210" spans="1:14">
       <c r="B210" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C210" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="211" spans="1:14">
       <c r="B211" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C211" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="212" spans="1:14">
       <c r="C212" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="213" spans="1:14">
       <c r="C213" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="214" spans="1:14">
       <c r="C214" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="215" spans="1:14">
       <c r="C215" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="216" spans="1:14">
       <c r="C216" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="217" spans="1:14">
       <c r="C217" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="218" spans="1:14">
       <c r="C218" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="219" spans="1:14">
       <c r="C219" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="220" spans="1:14" s="6" customFormat="1">
-      <c r="A220" s="6" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14">
+      <c r="C220" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" s="6" customFormat="1">
+      <c r="A221" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B220" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="C220" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="D220" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="E220" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="F220" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="G220" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="H220" s="6" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="222" spans="1:14">
-      <c r="A222" s="7" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="223" spans="1:14">
-      <c r="A223" s="2" t="s">
+      <c r="B221" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="D221" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="E221" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="F221" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="G221" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="H221" s="6" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" ht="15">
+      <c r="A223" s="7" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14">
+      <c r="A224" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B223" s="28" t="s">
-        <v>490</v>
-      </c>
-      <c r="C223" s="28"/>
-      <c r="D223" s="28"/>
-      <c r="E223" s="28"/>
-      <c r="F223" s="28"/>
-      <c r="G223" s="28"/>
-      <c r="H223" s="28"/>
-      <c r="I223" s="28"/>
-      <c r="J223" s="28"/>
-      <c r="K223" s="28"/>
-      <c r="L223" s="28"/>
-      <c r="M223" s="28"/>
-      <c r="N223" s="28"/>
-    </row>
-    <row r="224" spans="1:14" s="3" customFormat="1">
-      <c r="A224" s="3" t="s">
+      <c r="B224" s="28" t="s">
+        <v>491</v>
+      </c>
+      <c r="C224" s="28"/>
+      <c r="D224" s="28"/>
+      <c r="E224" s="28"/>
+      <c r="F224" s="28"/>
+      <c r="G224" s="28"/>
+      <c r="H224" s="28"/>
+      <c r="I224" s="28"/>
+      <c r="J224" s="28"/>
+      <c r="K224" s="28"/>
+      <c r="L224" s="28"/>
+      <c r="M224" s="28"/>
+      <c r="N224" s="28"/>
+    </row>
+    <row r="225" spans="1:11" s="3" customFormat="1">
+      <c r="A225" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B224" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="C224" s="3" t="s">
+      <c r="B225" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="D224" s="3" t="s">
+      <c r="C225" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="E224" s="3" t="s">
+      <c r="D225" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="F224" s="3" t="s">
+      <c r="E225" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="G224" s="3" t="s">
+      <c r="F225" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="H224" s="3" t="s">
+      <c r="G225" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="I224" s="3" t="s">
+      <c r="H225" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="I225" s="3" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" ht="15">
+      <c r="B226" t="s">
+        <v>551</v>
+      </c>
+      <c r="C226" t="s">
+        <v>505</v>
+      </c>
+      <c r="D226" t="s">
+        <v>534</v>
+      </c>
+      <c r="E226" t="s">
+        <v>543</v>
+      </c>
+      <c r="F226" t="s">
+        <v>502</v>
+      </c>
+      <c r="G226" t="s">
+        <v>503</v>
+      </c>
+      <c r="H226" s="20" t="s">
+        <v>509</v>
+      </c>
+      <c r="I226" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="225" spans="2:11">
-      <c r="B225" t="s">
-        <v>550</v>
-      </c>
-      <c r="C225" t="s">
-        <v>504</v>
-      </c>
-      <c r="D225" t="s">
-        <v>533</v>
-      </c>
-      <c r="E225" t="s">
-        <v>542</v>
-      </c>
-      <c r="F225" t="s">
+    <row r="227" spans="1:11">
+      <c r="B227" t="s">
+        <v>539</v>
+      </c>
+      <c r="C227" t="s">
+        <v>511</v>
+      </c>
+      <c r="D227" t="s">
+        <v>500</v>
+      </c>
+      <c r="E227" t="s">
         <v>501</v>
       </c>
-      <c r="G225" t="s">
-        <v>502</v>
-      </c>
-      <c r="H225" s="20" t="s">
+      <c r="G227" t="s">
         <v>508</v>
       </c>
-      <c r="I225" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="226" spans="2:11">
-      <c r="B226" t="s">
-        <v>538</v>
-      </c>
-      <c r="C226" t="s">
-        <v>510</v>
-      </c>
-      <c r="D226" t="s">
-        <v>499</v>
-      </c>
-      <c r="E226" t="s">
-        <v>500</v>
-      </c>
-      <c r="G226" t="s">
-        <v>646</v>
-      </c>
-      <c r="H226" t="s">
-        <v>512</v>
-      </c>
-      <c r="I226" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="227" spans="2:11">
-      <c r="B227" t="s">
-        <v>620</v>
-      </c>
-      <c r="C227" t="s">
-        <v>514</v>
-      </c>
-      <c r="D227" t="s">
-        <v>622</v>
-      </c>
-      <c r="E227" t="s">
+      <c r="H227" t="s">
+        <v>513</v>
+      </c>
+      <c r="I227" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11">
+      <c r="B228" t="s">
+        <v>621</v>
+      </c>
+      <c r="C228" t="s">
+        <v>515</v>
+      </c>
+      <c r="D228" t="s">
         <v>623</v>
-      </c>
-      <c r="G227" t="s">
-        <v>647</v>
-      </c>
-      <c r="H227" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="228" spans="2:11">
-      <c r="B228" t="s">
-        <v>548</v>
-      </c>
-      <c r="C228" t="s">
-        <v>518</v>
-      </c>
-      <c r="D228" t="s">
-        <v>579</v>
       </c>
       <c r="E228" t="s">
         <v>624</v>
       </c>
-      <c r="G228" t="s">
-        <v>648</v>
-      </c>
       <c r="H228" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11">
+      <c r="B229" t="s">
+        <v>549</v>
+      </c>
+      <c r="C229" t="s">
+        <v>519</v>
+      </c>
+      <c r="D229" t="s">
+        <v>580</v>
+      </c>
+      <c r="E229" t="s">
+        <v>625</v>
+      </c>
+      <c r="H229" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11">
+      <c r="B230" t="s">
+        <v>514</v>
+      </c>
+      <c r="C230" t="s">
+        <v>523</v>
+      </c>
+      <c r="D230" t="s">
+        <v>506</v>
+      </c>
+      <c r="E230" t="s">
+        <v>512</v>
+      </c>
+      <c r="H230" t="s">
+        <v>531</v>
+      </c>
+      <c r="K230" s="26"/>
+    </row>
+    <row r="231" spans="1:11">
+      <c r="B231" t="s">
+        <v>552</v>
+      </c>
+      <c r="C231" t="s">
+        <v>528</v>
+      </c>
+      <c r="D231" t="s">
+        <v>98</v>
+      </c>
+      <c r="E231" t="s">
+        <v>525</v>
+      </c>
+      <c r="H231" t="s">
+        <v>535</v>
+      </c>
+      <c r="K231" s="25"/>
+    </row>
+    <row r="232" spans="1:11">
+      <c r="B232" t="s">
+        <v>527</v>
+      </c>
+      <c r="C232" t="s">
+        <v>533</v>
+      </c>
+      <c r="D232" t="s">
+        <v>516</v>
+      </c>
+      <c r="E232" t="s">
+        <v>530</v>
+      </c>
+      <c r="H232" t="s">
+        <v>504</v>
+      </c>
+      <c r="K232" s="26"/>
+    </row>
+    <row r="233" spans="1:11">
+      <c r="B233" t="s">
+        <v>569</v>
+      </c>
+      <c r="C233" t="s">
+        <v>537</v>
+      </c>
+      <c r="D233" t="s">
+        <v>524</v>
+      </c>
+      <c r="E233" t="s">
+        <v>545</v>
+      </c>
+      <c r="H233" t="s">
+        <v>587</v>
+      </c>
+      <c r="K233" s="25"/>
+    </row>
+    <row r="234" spans="1:11">
+      <c r="B234" t="s">
+        <v>546</v>
+      </c>
+      <c r="C234" t="s">
+        <v>540</v>
+      </c>
+      <c r="D234" t="s">
+        <v>529</v>
+      </c>
+      <c r="E234" t="s">
+        <v>517</v>
+      </c>
+      <c r="H234" t="s">
+        <v>626</v>
+      </c>
+      <c r="K234" s="26"/>
+    </row>
+    <row r="235" spans="1:11">
+      <c r="B235" t="s">
+        <v>544</v>
+      </c>
+      <c r="C235" t="s">
+        <v>542</v>
+      </c>
+      <c r="D235" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="229" spans="2:11">
-      <c r="B229" t="s">
-        <v>513</v>
-      </c>
-      <c r="C229" t="s">
+      <c r="E235" t="s">
+        <v>538</v>
+      </c>
+      <c r="H235" t="s">
+        <v>578</v>
+      </c>
+      <c r="K235" s="25"/>
+    </row>
+    <row r="236" spans="1:11">
+      <c r="B236" t="s">
+        <v>532</v>
+      </c>
+      <c r="C236" t="s">
+        <v>537</v>
+      </c>
+      <c r="E236" t="s">
+        <v>541</v>
+      </c>
+      <c r="H236" t="s">
+        <v>526</v>
+      </c>
+      <c r="K236" s="26"/>
+    </row>
+    <row r="237" spans="1:11">
+      <c r="B237" t="s">
+        <v>554</v>
+      </c>
+      <c r="C237" t="s">
+        <v>499</v>
+      </c>
+      <c r="K237" s="25"/>
+    </row>
+    <row r="238" spans="1:11">
+      <c r="B238" t="s">
         <v>522</v>
       </c>
-      <c r="D229" t="s">
-        <v>505</v>
-      </c>
-      <c r="E229" t="s">
-        <v>511</v>
-      </c>
-      <c r="H229" t="s">
-        <v>530</v>
-      </c>
-      <c r="K229" s="26"/>
-    </row>
-    <row r="230" spans="2:11">
-      <c r="B230" t="s">
-        <v>551</v>
-      </c>
-      <c r="C230" t="s">
-        <v>527</v>
-      </c>
-      <c r="D230" t="s">
-        <v>98</v>
-      </c>
-      <c r="E230" t="s">
-        <v>584</v>
-      </c>
-      <c r="H230" t="s">
-        <v>534</v>
-      </c>
-      <c r="K230" s="25"/>
-    </row>
-    <row r="231" spans="2:11">
-      <c r="B231" t="s">
-        <v>526</v>
-      </c>
-      <c r="C231" t="s">
-        <v>532</v>
-      </c>
-      <c r="D231" t="s">
-        <v>515</v>
-      </c>
-      <c r="E231" t="s">
-        <v>524</v>
-      </c>
-      <c r="H231" t="s">
-        <v>503</v>
-      </c>
-      <c r="K231" s="26"/>
-    </row>
-    <row r="232" spans="2:11">
-      <c r="B232" t="s">
-        <v>568</v>
-      </c>
-      <c r="C232" t="s">
-        <v>536</v>
-      </c>
-      <c r="D232" t="s">
-        <v>523</v>
-      </c>
-      <c r="E232" t="s">
-        <v>529</v>
-      </c>
-      <c r="H232" t="s">
-        <v>586</v>
-      </c>
-      <c r="K232" s="25"/>
-    </row>
-    <row r="233" spans="2:11">
-      <c r="B233" t="s">
-        <v>545</v>
-      </c>
-      <c r="C233" t="s">
-        <v>539</v>
-      </c>
-      <c r="D233" t="s">
-        <v>528</v>
-      </c>
-      <c r="E233" t="s">
-        <v>544</v>
-      </c>
-      <c r="H233" t="s">
-        <v>625</v>
-      </c>
-      <c r="K233" s="26"/>
-    </row>
-    <row r="234" spans="2:11">
-      <c r="B234" t="s">
-        <v>543</v>
-      </c>
-      <c r="C234" t="s">
-        <v>541</v>
-      </c>
-      <c r="D234" t="s">
-        <v>519</v>
-      </c>
-      <c r="E234" t="s">
-        <v>516</v>
-      </c>
-      <c r="H234" t="s">
-        <v>577</v>
-      </c>
-      <c r="K234" s="25"/>
-    </row>
-    <row r="235" spans="2:11">
-      <c r="B235" t="s">
-        <v>531</v>
-      </c>
-      <c r="C235" t="s">
-        <v>536</v>
-      </c>
-      <c r="E235" t="s">
-        <v>537</v>
-      </c>
-      <c r="H235" t="s">
-        <v>525</v>
-      </c>
-      <c r="K235" s="26"/>
-    </row>
-    <row r="236" spans="2:11">
-      <c r="B236" t="s">
-        <v>553</v>
-      </c>
-      <c r="C236" t="s">
-        <v>498</v>
-      </c>
-      <c r="E236" t="s">
-        <v>540</v>
-      </c>
-      <c r="K236" s="25"/>
-    </row>
-    <row r="237" spans="2:11">
-      <c r="B237" t="s">
-        <v>521</v>
-      </c>
-      <c r="C237" t="s">
-        <v>621</v>
-      </c>
-      <c r="K237" s="26"/>
-    </row>
-    <row r="238" spans="2:11">
-      <c r="B238" t="s">
-        <v>549</v>
-      </c>
       <c r="C238" t="s">
-        <v>572</v>
-      </c>
-      <c r="K238" s="25"/>
-    </row>
-    <row r="239" spans="2:11">
+        <v>622</v>
+      </c>
+      <c r="K238" s="26"/>
+    </row>
+    <row r="239" spans="1:11">
       <c r="B239" t="s">
-        <v>546</v>
-      </c>
-      <c r="K239" s="26"/>
-    </row>
-    <row r="240" spans="2:11">
+        <v>550</v>
+      </c>
+      <c r="C239" t="s">
+        <v>573</v>
+      </c>
+      <c r="K239" s="25"/>
+    </row>
+    <row r="240" spans="1:11">
       <c r="B240" t="s">
-        <v>535</v>
-      </c>
-      <c r="K240" s="25"/>
+        <v>547</v>
+      </c>
+      <c r="K240" s="26"/>
     </row>
     <row r="241" spans="1:20">
       <c r="B241" t="s">
-        <v>547</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="K241" s="25"/>
     </row>
     <row r="242" spans="1:20">
       <c r="B242" t="s">
-        <v>509</v>
+        <v>548</v>
       </c>
     </row>
     <row r="243" spans="1:20">
       <c r="B243" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="246" spans="1:20" s="4" customFormat="1">
-      <c r="A246" s="4" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="244" spans="1:20">
+      <c r="B244" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="247" spans="1:20" s="4" customFormat="1">
+      <c r="A247" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B246" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="C246" s="4" t="s">
+      <c r="B247" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="D246" s="4" t="s">
+      <c r="C247" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="E246" s="4" t="s">
+      <c r="D247" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="F246" s="4" t="s">
+      <c r="E247" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="G246" s="4" t="s">
+      <c r="F247" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="H246" s="4" t="s">
+      <c r="G247" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="I246" s="4" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="248" spans="1:20">
-      <c r="A248" s="2" t="s">
+      <c r="H247" s="4" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="249" spans="1:20" ht="15">
+      <c r="A249" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B248" s="29" t="s">
-        <v>561</v>
-      </c>
-      <c r="C248" s="29"/>
-      <c r="D248" s="29"/>
-      <c r="E248" s="29"/>
-      <c r="F248" s="29"/>
-      <c r="G248" s="29"/>
-      <c r="H248" s="29"/>
-      <c r="I248" s="30"/>
-      <c r="J248" s="30"/>
-      <c r="K248" s="30"/>
-      <c r="L248" s="30"/>
-      <c r="M248" s="30"/>
-      <c r="N248" s="30"/>
-      <c r="O248" s="30"/>
-      <c r="P248" s="30"/>
-      <c r="Q248" s="30"/>
-      <c r="R248" s="30"/>
-      <c r="S248" s="30"/>
-      <c r="T248" s="30"/>
-    </row>
-    <row r="249" spans="1:20" s="5" customFormat="1">
-      <c r="A249" s="5" t="s">
+      <c r="B249" s="29" t="s">
+        <v>562</v>
+      </c>
+      <c r="C249" s="29"/>
+      <c r="D249" s="29"/>
+      <c r="E249" s="29"/>
+      <c r="F249" s="29"/>
+      <c r="G249" s="29"/>
+      <c r="H249" s="29"/>
+      <c r="I249" s="30"/>
+      <c r="J249" s="30"/>
+      <c r="K249" s="30"/>
+      <c r="L249" s="30"/>
+      <c r="M249" s="30"/>
+      <c r="N249" s="30"/>
+      <c r="O249" s="30"/>
+      <c r="P249" s="30"/>
+      <c r="Q249" s="30"/>
+      <c r="R249" s="30"/>
+      <c r="S249" s="30"/>
+      <c r="T249" s="30"/>
+    </row>
+    <row r="250" spans="1:20" s="5" customFormat="1">
+      <c r="A250" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B249" s="5" t="s">
+      <c r="B250" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="C250" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="C249" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="D249" s="5" t="s">
-        <v>564</v>
-      </c>
-      <c r="E249" s="5" t="s">
+      <c r="D250" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="F249" s="5" t="s">
+      <c r="E250" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="G249" s="5" t="s">
+      <c r="F250" s="5" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="250" spans="1:20">
-      <c r="B250" t="s">
-        <v>552</v>
-      </c>
-      <c r="C250" t="s">
-        <v>550</v>
-      </c>
-      <c r="D250" t="s">
-        <v>542</v>
-      </c>
-      <c r="E250" t="s">
-        <v>571</v>
-      </c>
-      <c r="F250" t="s">
-        <v>533</v>
-      </c>
-      <c r="G250" t="s">
-        <v>504</v>
+      <c r="G250" s="5" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="251" spans="1:20">
       <c r="B251" t="s">
-        <v>632</v>
+        <v>553</v>
       </c>
       <c r="C251" t="s">
-        <v>538</v>
+        <v>551</v>
       </c>
       <c r="D251" t="s">
-        <v>573</v>
+        <v>543</v>
       </c>
       <c r="E251" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F251" t="s">
-        <v>499</v>
+        <v>534</v>
       </c>
       <c r="G251" t="s">
-        <v>539</v>
+        <v>505</v>
       </c>
     </row>
     <row r="252" spans="1:20">
       <c r="B252" t="s">
-        <v>503</v>
+        <v>633</v>
       </c>
       <c r="C252" t="s">
-        <v>620</v>
+        <v>539</v>
       </c>
       <c r="D252" t="s">
+        <v>574</v>
+      </c>
+      <c r="E252" t="s">
+        <v>575</v>
+      </c>
+      <c r="F252" t="s">
         <v>500</v>
       </c>
-      <c r="E252" t="s">
-        <v>576</v>
-      </c>
-      <c r="F252" t="s">
-        <v>622</v>
-      </c>
       <c r="G252" t="s">
-        <v>518</v>
+        <v>540</v>
       </c>
     </row>
     <row r="253" spans="1:20">
       <c r="B253" t="s">
-        <v>586</v>
+        <v>504</v>
       </c>
       <c r="C253" t="s">
-        <v>548</v>
+        <v>621</v>
       </c>
       <c r="D253" t="s">
-        <v>570</v>
+        <v>501</v>
+      </c>
+      <c r="E253" t="s">
+        <v>577</v>
       </c>
       <c r="F253" t="s">
-        <v>579</v>
+        <v>623</v>
       </c>
       <c r="G253" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:20">
       <c r="B254" t="s">
-        <v>520</v>
+        <v>587</v>
       </c>
       <c r="C254" t="s">
-        <v>513</v>
+        <v>549</v>
       </c>
       <c r="D254" t="s">
-        <v>623</v>
+        <v>571</v>
       </c>
       <c r="F254" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G254" t="s">
-        <v>536</v>
+        <v>511</v>
       </c>
     </row>
     <row r="255" spans="1:20">
       <c r="B255" t="s">
-        <v>625</v>
+        <v>521</v>
       </c>
       <c r="C255" t="s">
-        <v>551</v>
+        <v>514</v>
       </c>
       <c r="D255" t="s">
-        <v>580</v>
+        <v>624</v>
       </c>
       <c r="F255" t="s">
-        <v>505</v>
+        <v>579</v>
       </c>
       <c r="G255" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
     </row>
     <row r="256" spans="1:20">
       <c r="B256" t="s">
-        <v>583</v>
+        <v>626</v>
       </c>
       <c r="C256" t="s">
-        <v>526</v>
+        <v>552</v>
       </c>
       <c r="D256" t="s">
-        <v>624</v>
+        <v>581</v>
       </c>
       <c r="F256" t="s">
-        <v>98</v>
+        <v>506</v>
       </c>
       <c r="G256" t="s">
-        <v>545</v>
+        <v>528</v>
       </c>
     </row>
     <row r="257" spans="2:7">
       <c r="B257" t="s">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="C257" t="s">
-        <v>568</v>
+        <v>527</v>
       </c>
       <c r="D257" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F257" t="s">
-        <v>515</v>
+        <v>98</v>
       </c>
       <c r="G257" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="258" spans="2:7">
       <c r="B258" t="s">
-        <v>534</v>
+        <v>570</v>
       </c>
       <c r="C258" t="s">
-        <v>545</v>
+        <v>569</v>
       </c>
       <c r="D258" t="s">
-        <v>588</v>
+        <v>627</v>
       </c>
       <c r="F258" t="s">
-        <v>575</v>
+        <v>516</v>
       </c>
       <c r="G258" t="s">
-        <v>585</v>
+        <v>542</v>
       </c>
     </row>
     <row r="259" spans="2:7">
       <c r="B259" t="s">
-        <v>581</v>
+        <v>535</v>
       </c>
       <c r="C259" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D259" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="F259" t="s">
-        <v>523</v>
+        <v>576</v>
       </c>
       <c r="G259" t="s">
-        <v>498</v>
+        <v>586</v>
       </c>
     </row>
     <row r="260" spans="2:7">
       <c r="B260" t="s">
-        <v>512</v>
+        <v>582</v>
       </c>
       <c r="C260" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="D260" t="s">
-        <v>511</v>
+        <v>583</v>
       </c>
       <c r="F260" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="G260" t="s">
-        <v>621</v>
+        <v>499</v>
       </c>
     </row>
     <row r="261" spans="2:7">
       <c r="B261" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="C261" t="s">
-        <v>553</v>
+        <v>532</v>
       </c>
       <c r="D261" t="s">
-        <v>584</v>
+        <v>512</v>
       </c>
       <c r="F261" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="G261" t="s">
-        <v>572</v>
+        <v>622</v>
       </c>
     </row>
     <row r="262" spans="2:7">
       <c r="B262" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C262" t="s">
-        <v>521</v>
+        <v>554</v>
       </c>
       <c r="D262" t="s">
-        <v>524</v>
+        <v>585</v>
+      </c>
+      <c r="F262" t="s">
+        <v>520</v>
       </c>
       <c r="G262" t="s">
-        <v>532</v>
+        <v>573</v>
       </c>
     </row>
     <row r="263" spans="2:7">
       <c r="B263" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="C263" t="s">
-        <v>549</v>
+        <v>522</v>
       </c>
       <c r="D263" t="s">
-        <v>529</v>
+        <v>525</v>
+      </c>
+      <c r="G263" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="264" spans="2:7">
       <c r="B264" t="s">
-        <v>577</v>
+        <v>518</v>
       </c>
       <c r="C264" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="D264" t="s">
-        <v>587</v>
+        <v>530</v>
       </c>
     </row>
     <row r="265" spans="2:7">
       <c r="B265" t="s">
-        <v>525</v>
+        <v>578</v>
       </c>
       <c r="C265" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="D265" t="s">
-        <v>504</v>
+        <v>588</v>
       </c>
     </row>
     <row r="266" spans="2:7">
+      <c r="B266" t="s">
+        <v>526</v>
+      </c>
       <c r="C266" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="D266" t="s">
-        <v>544</v>
+        <v>505</v>
       </c>
     </row>
     <row r="267" spans="2:7">
       <c r="C267" t="s">
-        <v>509</v>
+        <v>548</v>
       </c>
       <c r="D267" t="s">
-        <v>516</v>
+        <v>545</v>
       </c>
     </row>
     <row r="268" spans="2:7">
+      <c r="C268" t="s">
+        <v>510</v>
+      </c>
       <c r="D268" t="s">
-        <v>537</v>
+        <v>517</v>
       </c>
     </row>
     <row r="269" spans="2:7">
       <c r="D269" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="270" spans="2:7">
       <c r="D270" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="273" spans="1:8" s="6" customFormat="1">
-      <c r="A273" s="6" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="271" spans="2:7">
+      <c r="D271" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="272" spans="2:7">
+      <c r="D272" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8">
+      <c r="D273" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" s="6" customFormat="1">
+      <c r="A274" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B273" s="6" t="s">
-        <v>589</v>
-      </c>
-      <c r="C273" s="6" t="s">
-        <v>589</v>
-      </c>
-      <c r="D273" s="6" t="s">
-        <v>589</v>
-      </c>
-      <c r="E273" s="6" t="s">
-        <v>589</v>
-      </c>
-      <c r="F273" s="6" t="s">
-        <v>589</v>
-      </c>
-      <c r="G273" s="6" t="s">
-        <v>589</v>
-      </c>
-      <c r="H273" s="6" t="s">
-        <v>589</v>
+      <c r="B274" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="C274" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="D274" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="E274" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="F274" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="G274" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="H274" s="6" t="s">
+        <v>590</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="B158:N158"/>
     <mergeCell ref="B186:T186"/>
-    <mergeCell ref="B223:N223"/>
-    <mergeCell ref="B248:T248"/>
+    <mergeCell ref="B224:N224"/>
+    <mergeCell ref="B249:T249"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B25:T25"/>
     <mergeCell ref="B49:N49"/>
@@ -7209,9 +7162,9 @@
     <mergeCell ref="B111:N111"/>
     <mergeCell ref="B136:T136"/>
   </mergeCells>
-  <conditionalFormatting sqref="H226:H235">
+  <conditionalFormatting sqref="H227:H236">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="SBS-GADUNG-HW.MA5801-OLT-01">
-      <formula>NOT(ISERROR(SEARCH("SBS-GADUNG-HW.MA5801-OLT-01",H226)))</formula>
+      <formula>NOT(ISERROR(SEARCH("SBS-GADUNG-HW.MA5801-OLT-01",H227)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/data/List_Team_Region.xlsx
+++ b/public/data/List_Team_Region.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yoss Work\App Retail SBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82CFDE1-B944-4733-BD8C-D5E02D984276}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D8F6C2-3D61-48A7-924D-5064703A18D6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9180" yWindow="1845" windowWidth="17655" windowHeight="12960" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
+    <workbookView xWindow="13110" yWindow="1245" windowWidth="13440" windowHeight="12105" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="648">
   <si>
     <t>JAMBI</t>
   </si>
@@ -2299,16 +2299,6 @@
   <dxfs count="13">
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2524,6 +2514,16 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2538,7 +2538,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}" name="Table919" displayName="Table919" ref="B3:H22" totalsRowShown="0" headerRowDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}" name="Table919" displayName="Table919" ref="B3:H22" totalsRowShown="0" headerRowDxfId="11">
   <autoFilter ref="B3:H22" xr:uid="{B8D378AF-22DA-4D49-804B-1D3F3F024508}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{1E18F602-B85E-4C85-8C34-8684E3651598}" name="INTERNAL JAMBI"/>
@@ -2554,8 +2554,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}" name="Table27" displayName="Table27" ref="B137:T154" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="B137:T154" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}" name="Table27" displayName="Table27" ref="B138:T155" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="B138:T155" xr:uid="{F7289F80-0BF7-4EFB-A73E-F098635B5A9F}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{F8A4E442-73AD-4EB9-BB0D-D55E87DA1888}" name="SERPO PALEMBANG KOTA"/>
     <tableColumn id="2" xr3:uid="{FDE83478-980D-467C-B140-58C1B9CDE4FE}" name="SERPO LAHAT"/>
@@ -2582,7 +2582,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57681EA6-18EF-4E05-B178-44A6E049B133}" name="Table1020" displayName="Table1020" ref="B26:J44" totalsRowShown="0" headerRowDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{57681EA6-18EF-4E05-B178-44A6E049B133}" name="Table1020" displayName="Table1020" ref="B26:J44" totalsRowShown="0" headerRowDxfId="10">
   <autoFilter ref="B26:J44" xr:uid="{57681EA6-18EF-4E05-B178-44A6E049B133}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{A8602C42-C67C-43B1-B2C0-728995582D93}" name="SERPO BUNGO"/>
@@ -2600,7 +2600,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C6FB933F-6103-42DE-BAEC-03E0FCFEB76C}" name="Table1121" displayName="Table1121" ref="B50:G78" totalsRowShown="0" headerRowDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C6FB933F-6103-42DE-BAEC-03E0FCFEB76C}" name="Table1121" displayName="Table1121" ref="B50:G78" totalsRowShown="0" headerRowDxfId="9">
   <autoFilter ref="B50:G78" xr:uid="{C6FB933F-6103-42DE-BAEC-03E0FCFEB76C}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{DCC806F7-D168-48B2-B03E-CCE7FD87EEA9}" name="SIB PESAWARAN"/>
@@ -2615,8 +2615,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6E2D26AE-ECD5-48A4-AC1D-1B4180A6F140}" name="Table1222" displayName="Table1222" ref="B82:J106" totalsRowShown="0" headerRowDxfId="9">
-  <autoFilter ref="B82:J106" xr:uid="{6E2D26AE-ECD5-48A4-AC1D-1B4180A6F140}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6E2D26AE-ECD5-48A4-AC1D-1B4180A6F140}" name="Table1222" displayName="Table1222" ref="B82:J107" totalsRowShown="0" headerRowDxfId="8">
+  <autoFilter ref="B82:J107" xr:uid="{6E2D26AE-ECD5-48A4-AC1D-1B4180A6F140}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{060484FA-EE1E-4DC8-9A74-A60AA9B20548}" name="SERPO TEGINENENG_x0009__x0009_"/>
     <tableColumn id="2" xr3:uid="{6EF60155-EEC6-4684-8887-3DAB1F16BBBB}" name="SERPO SUTAMI"/>
@@ -2633,8 +2633,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}" name="Table1323" displayName="Table1323" ref="B112:N134" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="B112:N134" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}" name="Table1323" displayName="Table1323" ref="B113:N135" totalsRowShown="0" headerRowDxfId="7">
+  <autoFilter ref="B113:N135" xr:uid="{5081E226-2B97-42EE-B012-B5A6E8CF26A7}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{6FB6563D-399C-4506-8AF0-A312347E4888}" name="REG7 PALEMBANG 1"/>
     <tableColumn id="2" xr3:uid="{211D6500-28BD-4C9B-A588-576FE1D6FE10}" name="REG7 PALEMBANG 2"/>
@@ -2655,8 +2655,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}" name="Table1424" displayName="Table1424" ref="B159:I183" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
-  <autoFilter ref="B159:I183" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}" name="Table1424" displayName="Table1424" ref="B160:I184" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
+  <autoFilter ref="B160:I184" xr:uid="{EFE951CF-5CC8-4ED8-9F4C-0525BF115D30}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{9BFFF82B-4674-404E-AC18-7772CF16890E}" name="GSP BENGKULU 1"/>
     <tableColumn id="2" xr3:uid="{BF3EB892-4094-4FE7-B983-B0CEE975CE16}" name="GSP BENGKULU 2"/>
@@ -2672,8 +2672,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}" name="Table1525" displayName="Table1525" ref="B187:H220" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="B187:H220" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}" name="Table1525" displayName="Table1525" ref="B188:H221" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="B188:H221" xr:uid="{60040C56-9D57-474C-9478-E7FFB4643928}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{ACEB90AF-9CBB-4605-8377-2CF0EF299650}" name="SERPO SUKAMERINDU"/>
     <tableColumn id="2" xr3:uid="{351154A5-2DE7-411B-9044-B8641069B0BF}" name="SERPO BENGKULU KOTA"/>
@@ -2688,8 +2688,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}" name="Table1626" displayName="Table1626" ref="B225:I247" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="B225:I247" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}" name="Table1626" displayName="Table1626" ref="B226:I248" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="B226:I248" xr:uid="{8D9A355B-F507-44B7-B123-2BB782ED8DA0}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{D0B3A41D-F35E-4B89-AC56-18717B9B04E5}" name="BANGKA REG 7"/>
     <tableColumn id="2" xr3:uid="{9C59FCCC-409F-4148-A8DC-48E653CEBBAA}" name="TTM SUNGAI LIAT"/>
@@ -2705,8 +2705,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}" name="Table1727" displayName="Table1727" ref="B250:G273" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="B250:G273" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}" name="Table1727" displayName="Table1727" ref="B251:G274" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="B251:G274" xr:uid="{7AD76894-333F-412E-BC73-56F8C214DE95}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{97E25E83-847F-4991-A885-21D98063A2DB}" name="SERPO KOBA"/>
     <tableColumn id="2" xr3:uid="{0AB964B5-883A-49C8-8DDA-C8EE93753519}" name="SERPO PANGKAL PINANG"/>
@@ -3036,7 +3036,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D0AF9EF-6686-405D-9473-604A5805FA6C}">
-  <dimension ref="A1:T274"/>
+  <dimension ref="A1:T275"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="34.125" customWidth="1"/>
@@ -3324,6 +3324,9 @@
       <c r="F14" t="s">
         <v>60</v>
       </c>
+      <c r="G14" t="s">
+        <v>601</v>
+      </c>
     </row>
     <row r="15" spans="1:14">
       <c r="D15" t="s">
@@ -4363,6 +4366,9 @@
       <c r="C91" t="s">
         <v>113</v>
       </c>
+      <c r="D91" t="s">
+        <v>165</v>
+      </c>
       <c r="E91" t="s">
         <v>118</v>
       </c>
@@ -4482,6 +4488,9 @@
       </c>
     </row>
     <row r="104" spans="1:14">
+      <c r="B104" t="s">
+        <v>203</v>
+      </c>
       <c r="E104" t="s">
         <v>606</v>
       </c>
@@ -4492,2679 +4501,2681 @@
       </c>
     </row>
     <row r="106" spans="1:14">
-      <c r="B106" t="s">
-        <v>203</v>
-      </c>
       <c r="E106" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="107" spans="1:14" s="6" customFormat="1">
-      <c r="A107" s="6" t="s">
+    <row r="107" spans="1:14">
+      <c r="E107" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" s="6" customFormat="1">
+      <c r="A108" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B107" s="6" t="s">
+      <c r="B108" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="C108" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="D107" s="6" t="s">
+      <c r="D108" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="E107" s="6" t="s">
+      <c r="E108" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="F107" s="6" t="s">
+      <c r="F108" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="G107" s="6" t="s">
+      <c r="G108" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="H107" s="6" t="s">
+      <c r="H108" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="I107" s="6" t="s">
+      <c r="I108" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="J107" s="6" t="s">
+      <c r="J108" s="6" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="110" spans="1:14" ht="15">
-      <c r="A110" s="1" t="s">
+    <row r="111" spans="1:14" ht="15">
+      <c r="A111" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="111" spans="1:14">
-      <c r="A111" s="2" t="s">
+    <row r="112" spans="1:14">
+      <c r="A112" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B111" s="28" t="s">
+      <c r="B112" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="C111" s="28"/>
-      <c r="D111" s="28"/>
-      <c r="E111" s="28"/>
-      <c r="F111" s="28"/>
-      <c r="G111" s="28"/>
-      <c r="H111" s="28"/>
-      <c r="I111" s="28"/>
-      <c r="J111" s="28"/>
-      <c r="K111" s="28"/>
-      <c r="L111" s="28"/>
-      <c r="M111" s="28"/>
-      <c r="N111" s="28"/>
-    </row>
-    <row r="112" spans="1:14" s="3" customFormat="1">
-      <c r="A112" s="3" t="s">
+      <c r="C112" s="28"/>
+      <c r="D112" s="28"/>
+      <c r="E112" s="28"/>
+      <c r="F112" s="28"/>
+      <c r="G112" s="28"/>
+      <c r="H112" s="28"/>
+      <c r="I112" s="28"/>
+      <c r="J112" s="28"/>
+      <c r="K112" s="28"/>
+      <c r="L112" s="28"/>
+      <c r="M112" s="28"/>
+      <c r="N112" s="28"/>
+    </row>
+    <row r="113" spans="1:14" s="3" customFormat="1">
+      <c r="A113" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B113" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="C113" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D112" s="3" t="s">
+      <c r="D113" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E112" s="3" t="s">
+      <c r="E113" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F112" s="3" t="s">
+      <c r="F113" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="G112" s="3" t="s">
+      <c r="G113" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="H112" s="3" t="s">
+      <c r="H113" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="I112" s="3" t="s">
+      <c r="I113" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="J112" s="3" t="s">
+      <c r="J113" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="K112" s="3" t="s">
+      <c r="K113" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="L112" s="3" t="s">
+      <c r="L113" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="M112" s="3" t="s">
+      <c r="M113" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="N112" s="3" t="s">
+      <c r="N113" s="3" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="113" spans="2:14">
-      <c r="B113" t="s">
+    <row r="114" spans="1:14">
+      <c r="B114" t="s">
         <v>223</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C114" t="s">
         <v>224</v>
       </c>
-      <c r="D113" t="s">
+      <c r="D114" t="s">
         <v>225</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E114" t="s">
         <v>226</v>
       </c>
-      <c r="F113" t="s">
+      <c r="F114" t="s">
         <v>227</v>
       </c>
-      <c r="G113" t="s">
+      <c r="G114" t="s">
         <v>229</v>
       </c>
-      <c r="H113" t="s">
+      <c r="H114" t="s">
         <v>230</v>
-      </c>
-      <c r="I113" t="s">
-        <v>231</v>
-      </c>
-      <c r="J113" t="s">
-        <v>232</v>
-      </c>
-      <c r="K113" t="s">
-        <v>233</v>
-      </c>
-      <c r="L113" t="s">
-        <v>234</v>
-      </c>
-      <c r="M113" t="s">
-        <v>235</v>
-      </c>
-      <c r="N113" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="114" spans="2:14">
-      <c r="B114" t="s">
-        <v>237</v>
-      </c>
-      <c r="C114" t="s">
-        <v>238</v>
-      </c>
-      <c r="D114" t="s">
-        <v>239</v>
-      </c>
-      <c r="E114" t="s">
-        <v>240</v>
-      </c>
-      <c r="F114" t="s">
-        <v>241</v>
-      </c>
-      <c r="G114" t="s">
-        <v>243</v>
-      </c>
-      <c r="H114" t="s">
-        <v>244</v>
       </c>
       <c r="I114" t="s">
         <v>231</v>
       </c>
       <c r="J114" t="s">
+        <v>232</v>
+      </c>
+      <c r="K114" t="s">
+        <v>233</v>
+      </c>
+      <c r="L114" t="s">
+        <v>234</v>
+      </c>
+      <c r="M114" t="s">
+        <v>235</v>
+      </c>
+      <c r="N114" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14">
+      <c r="B115" t="s">
+        <v>237</v>
+      </c>
+      <c r="C115" t="s">
+        <v>238</v>
+      </c>
+      <c r="D115" t="s">
+        <v>239</v>
+      </c>
+      <c r="E115" t="s">
+        <v>240</v>
+      </c>
+      <c r="F115" t="s">
+        <v>241</v>
+      </c>
+      <c r="G115" t="s">
+        <v>243</v>
+      </c>
+      <c r="H115" t="s">
+        <v>244</v>
+      </c>
+      <c r="I115" t="s">
+        <v>231</v>
+      </c>
+      <c r="J115" t="s">
         <v>245</v>
       </c>
-      <c r="K114" t="s">
+      <c r="K115" t="s">
         <v>246</v>
       </c>
-      <c r="L114" t="s">
+      <c r="L115" t="s">
         <v>247</v>
       </c>
-      <c r="M114" t="s">
+      <c r="M115" t="s">
         <v>248</v>
       </c>
-      <c r="N114" t="s">
+      <c r="N115" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="115" spans="2:14">
-      <c r="B115" t="s">
+    <row r="116" spans="1:14">
+      <c r="B116" t="s">
         <v>250</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C116" t="s">
         <v>251</v>
       </c>
-      <c r="D115" t="s">
+      <c r="D116" t="s">
         <v>252</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E116" t="s">
         <v>253</v>
       </c>
-      <c r="F115" t="s">
+      <c r="F116" t="s">
         <v>254</v>
       </c>
-      <c r="H115" t="s">
+      <c r="H116" t="s">
         <v>256</v>
       </c>
-      <c r="I115" t="s">
+      <c r="I116" t="s">
         <v>257</v>
       </c>
-      <c r="J115" t="s">
+      <c r="J116" t="s">
         <v>258</v>
       </c>
-      <c r="K115" t="s">
+      <c r="K116" t="s">
         <v>259</v>
       </c>
-      <c r="L115" t="s">
+      <c r="L116" t="s">
         <v>260</v>
       </c>
-      <c r="M115" t="s">
+      <c r="M116" t="s">
         <v>261</v>
       </c>
-      <c r="N115" t="s">
+      <c r="N116" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="116" spans="2:14">
-      <c r="B116" t="s">
+    <row r="117" spans="1:14">
+      <c r="B117" t="s">
         <v>263</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C117" t="s">
         <v>264</v>
       </c>
-      <c r="D116" t="s">
+      <c r="D117" t="s">
         <v>94</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E117" t="s">
         <v>265</v>
       </c>
-      <c r="F116" t="s">
+      <c r="F117" t="s">
         <v>266</v>
       </c>
-      <c r="H116" t="s">
+      <c r="H117" t="s">
         <v>268</v>
       </c>
-      <c r="I116" t="s">
+      <c r="I117" t="s">
         <v>269</v>
       </c>
-      <c r="J116" t="s">
+      <c r="J117" t="s">
         <v>270</v>
       </c>
-      <c r="K116" t="s">
+      <c r="K117" t="s">
         <v>271</v>
       </c>
-      <c r="L116" t="s">
+      <c r="L117" t="s">
         <v>272</v>
       </c>
-      <c r="M116" t="s">
+      <c r="M117" t="s">
         <v>273</v>
       </c>
-      <c r="N116" t="s">
+      <c r="N117" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="117" spans="2:14">
-      <c r="B117" t="s">
+    <row r="118" spans="1:14">
+      <c r="B118" t="s">
         <v>275</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C118" t="s">
         <v>276</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D118" t="s">
         <v>277</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E118" t="s">
         <v>278</v>
       </c>
-      <c r="F117" t="s">
+      <c r="F118" t="s">
         <v>279</v>
       </c>
-      <c r="H117" t="s">
+      <c r="H118" t="s">
         <v>281</v>
       </c>
-      <c r="I117" t="s">
+      <c r="I118" t="s">
         <v>282</v>
       </c>
-      <c r="J117" t="s">
+      <c r="J118" t="s">
         <v>283</v>
       </c>
-      <c r="K117" t="s">
+      <c r="K118" t="s">
         <v>284</v>
       </c>
-      <c r="L117" t="s">
+      <c r="L118" t="s">
         <v>285</v>
       </c>
-      <c r="N117" t="s">
+      <c r="N118" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="118" spans="2:14">
-      <c r="B118" t="s">
+    <row r="119" spans="1:14">
+      <c r="B119" t="s">
         <v>287</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C119" t="s">
         <v>288</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D119" t="s">
         <v>289</v>
       </c>
-      <c r="E118" t="s">
+      <c r="E119" t="s">
         <v>290</v>
       </c>
-      <c r="H118" t="s">
+      <c r="H119" t="s">
         <v>292</v>
       </c>
-      <c r="I118" t="s">
+      <c r="I119" t="s">
         <v>293</v>
       </c>
-      <c r="J118" t="s">
+      <c r="J119" t="s">
         <v>294</v>
       </c>
-      <c r="K118" t="s">
+      <c r="K119" t="s">
         <v>295</v>
       </c>
-      <c r="N118" t="s">
+      <c r="N119" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="119" spans="2:14">
-      <c r="B119" t="s">
+    <row r="120" spans="1:14">
+      <c r="B120" t="s">
         <v>297</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C120" t="s">
         <v>298</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D120" t="s">
         <v>299</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E120" t="s">
         <v>300</v>
       </c>
-      <c r="H119" t="s">
+      <c r="H120" t="s">
         <v>301</v>
       </c>
-      <c r="I119" t="s">
+      <c r="I120" t="s">
         <v>302</v>
       </c>
-      <c r="J119" t="s">
+      <c r="J120" t="s">
         <v>303</v>
       </c>
-      <c r="K119" t="s">
+      <c r="K120" t="s">
         <v>304</v>
       </c>
-      <c r="N119" t="s">
+      <c r="N120" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="120" spans="2:14">
-      <c r="B120" t="s">
+    <row r="121" spans="1:14">
+      <c r="B121" t="s">
         <v>306</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C121" t="s">
         <v>307</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D121" t="s">
         <v>308</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E121" t="s">
         <v>309</v>
       </c>
-      <c r="H120" t="s">
+      <c r="H121" t="s">
         <v>310</v>
       </c>
-      <c r="I120" t="s">
+      <c r="I121" t="s">
         <v>366</v>
       </c>
-      <c r="J120" t="s">
+      <c r="J121" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="121" spans="2:14">
-      <c r="B121" t="s">
+    <row r="122" spans="1:14">
+      <c r="B122" t="s">
         <v>312</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C122" t="s">
         <v>313</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D122" t="s">
         <v>314</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E122" t="s">
         <v>315</v>
       </c>
-      <c r="J121" t="s">
+      <c r="J122" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="122" spans="2:14">
-      <c r="B122" t="s">
+    <row r="123" spans="1:14">
+      <c r="B123" t="s">
         <v>317</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C123" t="s">
         <v>318</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D123" t="s">
         <v>319</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E123" t="s">
         <v>240</v>
       </c>
-      <c r="J122" t="s">
+      <c r="J123" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="123" spans="2:14">
-      <c r="B123" t="s">
+    <row r="124" spans="1:14">
+      <c r="B124" t="s">
         <v>321</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C124" t="s">
         <v>322</v>
       </c>
-      <c r="E123" t="s">
+      <c r="E124" t="s">
         <v>278</v>
       </c>
-      <c r="J123" t="s">
+      <c r="J124" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="124" spans="2:14">
-      <c r="B124" t="s">
+    <row r="125" spans="1:14">
+      <c r="B125" t="s">
         <v>324</v>
       </c>
-      <c r="E124" t="s">
+      <c r="E125" t="s">
         <v>267</v>
       </c>
-      <c r="J124" t="s">
+      <c r="J125" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="125" spans="2:14">
-      <c r="E125" t="s">
+    <row r="126" spans="1:14">
+      <c r="E126" t="s">
         <v>280</v>
       </c>
-      <c r="J125" t="s">
+      <c r="J126" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="126" spans="2:14">
-      <c r="E126" t="s">
+    <row r="127" spans="1:14">
+      <c r="E127" t="s">
         <v>291</v>
       </c>
-      <c r="J126" t="s">
+      <c r="J127" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="127" spans="2:14">
-      <c r="J127" t="s">
+    <row r="128" spans="1:14">
+      <c r="J128" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="128" spans="2:14">
-      <c r="J128" t="s">
+    <row r="129" spans="1:20">
+      <c r="J129" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="134" spans="1:20" s="4" customFormat="1">
-      <c r="A134" s="4" t="s">
+    <row r="135" spans="1:20" s="4" customFormat="1">
+      <c r="A135" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B135" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="C135" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="D134" s="4" t="s">
+      <c r="D135" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="E134" s="4" t="s">
+      <c r="E135" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="F134" s="4" t="s">
+      <c r="F135" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="G134" s="4" t="s">
+      <c r="G135" s="4" t="s">
         <v>635</v>
       </c>
-      <c r="H134" s="4" t="s">
+      <c r="H135" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="I134" s="4" t="s">
+      <c r="I135" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="J134" s="4" t="s">
+      <c r="J135" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="K134" s="4" t="s">
+      <c r="K135" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="L134" s="4" t="s">
+      <c r="L135" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="M134" s="4" t="s">
+      <c r="M135" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="N134" s="4" t="s">
+      <c r="N135" s="4" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="136" spans="1:20" ht="15">
-      <c r="A136" s="2" t="s">
+    <row r="137" spans="1:20" ht="15">
+      <c r="A137" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B136" s="29" t="s">
+      <c r="B137" s="29" t="s">
         <v>342</v>
       </c>
-      <c r="C136" s="29"/>
-      <c r="D136" s="29"/>
-      <c r="E136" s="29"/>
-      <c r="F136" s="29"/>
-      <c r="G136" s="29"/>
-      <c r="H136" s="29"/>
-      <c r="I136" s="30"/>
-      <c r="J136" s="30"/>
-      <c r="K136" s="30"/>
-      <c r="L136" s="30"/>
-      <c r="M136" s="30"/>
-      <c r="N136" s="30"/>
-      <c r="O136" s="30"/>
-      <c r="P136" s="30"/>
-      <c r="Q136" s="30"/>
-      <c r="R136" s="30"/>
-      <c r="S136" s="30"/>
-      <c r="T136" s="30"/>
-    </row>
-    <row r="137" spans="1:20" s="5" customFormat="1">
-      <c r="A137" s="5" t="s">
+      <c r="C137" s="29"/>
+      <c r="D137" s="29"/>
+      <c r="E137" s="29"/>
+      <c r="F137" s="29"/>
+      <c r="G137" s="29"/>
+      <c r="H137" s="29"/>
+      <c r="I137" s="30"/>
+      <c r="J137" s="30"/>
+      <c r="K137" s="30"/>
+      <c r="L137" s="30"/>
+      <c r="M137" s="30"/>
+      <c r="N137" s="30"/>
+      <c r="O137" s="30"/>
+      <c r="P137" s="30"/>
+      <c r="Q137" s="30"/>
+      <c r="R137" s="30"/>
+      <c r="S137" s="30"/>
+      <c r="T137" s="30"/>
+    </row>
+    <row r="138" spans="1:20" s="5" customFormat="1">
+      <c r="A138" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B137" s="5" t="s">
+      <c r="B138" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="C137" s="5" t="s">
+      <c r="C138" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="D137" s="5" t="s">
+      <c r="D138" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="E137" s="5" t="s">
+      <c r="E138" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="F137" s="5" t="s">
+      <c r="F138" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="G137" s="5" t="s">
+      <c r="G138" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="H137" s="5" t="s">
+      <c r="H138" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="I137" s="5" t="s">
+      <c r="I138" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="J137" s="5" t="s">
+      <c r="J138" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="K137" s="5" t="s">
+      <c r="K138" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="L137" s="5" t="s">
+      <c r="L138" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="M137" s="5" t="s">
+      <c r="M138" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="N137" s="5" t="s">
+      <c r="N138" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="O137" s="5" t="s">
+      <c r="O138" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="P137" s="5" t="s">
+      <c r="P138" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="Q137" s="5" t="s">
+      <c r="Q138" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="R137" s="5" t="s">
+      <c r="R138" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="S137" s="5" t="s">
+      <c r="S138" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="T137" s="5" t="s">
+      <c r="T138" s="5" t="s">
         <v>361</v>
-      </c>
-    </row>
-    <row r="138" spans="1:20">
-      <c r="B138" t="s">
-        <v>283</v>
-      </c>
-      <c r="C138" t="s">
-        <v>235</v>
-      </c>
-      <c r="D138" t="s">
-        <v>234</v>
-      </c>
-      <c r="E138" t="s">
-        <v>233</v>
-      </c>
-      <c r="F138" t="s">
-        <v>231</v>
-      </c>
-      <c r="G138" t="s">
-        <v>230</v>
-      </c>
-      <c r="H138" t="s">
-        <v>362</v>
-      </c>
-      <c r="I138" t="s">
-        <v>363</v>
-      </c>
-      <c r="J138" t="s">
-        <v>267</v>
-      </c>
-      <c r="K138" t="s">
-        <v>364</v>
-      </c>
-      <c r="L138" t="s">
-        <v>365</v>
-      </c>
-      <c r="M138" t="s">
-        <v>323</v>
-      </c>
-      <c r="N138" t="s">
-        <v>228</v>
-      </c>
-      <c r="O138" t="s">
-        <v>227</v>
-      </c>
-      <c r="P138" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q138" t="s">
-        <v>226</v>
-      </c>
-      <c r="R138" t="s">
-        <v>263</v>
-      </c>
-      <c r="S138" t="s">
-        <v>245</v>
-      </c>
-      <c r="T138" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="139" spans="1:20">
       <c r="B139" t="s">
-        <v>223</v>
+        <v>283</v>
       </c>
       <c r="C139" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D139" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="E139" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="F139" t="s">
-        <v>366</v>
+        <v>231</v>
       </c>
       <c r="G139" t="s">
-        <v>244</v>
+        <v>230</v>
+      </c>
+      <c r="H139" t="s">
+        <v>362</v>
       </c>
       <c r="I139" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="J139" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="K139" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="L139" t="s">
-        <v>369</v>
+        <v>365</v>
+      </c>
+      <c r="M139" t="s">
+        <v>323</v>
       </c>
       <c r="N139" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="O139" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="P139" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="Q139" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="R139" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="S139" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="T139" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
     </row>
     <row r="140" spans="1:20">
       <c r="B140" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="C140" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="D140" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="E140" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="F140" t="s">
-        <v>257</v>
+        <v>366</v>
       </c>
       <c r="G140" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="I140" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="J140" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="K140" t="s">
-        <v>371</v>
+        <v>368</v>
+      </c>
+      <c r="L140" t="s">
+        <v>369</v>
       </c>
       <c r="N140" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="O140" t="s">
-        <v>254</v>
+        <v>241</v>
+      </c>
+      <c r="P140" t="s">
+        <v>305</v>
       </c>
       <c r="Q140" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="R140" t="s">
-        <v>251</v>
+        <v>287</v>
       </c>
       <c r="S140" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="T140" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
     </row>
     <row r="141" spans="1:20">
       <c r="B141" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="C141" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="E141" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="F141" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="G141" t="s">
-        <v>268</v>
+        <v>256</v>
+      </c>
+      <c r="I141" t="s">
+        <v>370</v>
+      </c>
+      <c r="J141" t="s">
+        <v>291</v>
+      </c>
+      <c r="K141" t="s">
+        <v>371</v>
+      </c>
+      <c r="N141" t="s">
+        <v>255</v>
       </c>
       <c r="O141" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="Q141" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="R141" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="S141" t="s">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="T141" t="s">
-        <v>94</v>
+        <v>252</v>
       </c>
     </row>
     <row r="142" spans="1:20">
       <c r="B142" t="s">
-        <v>321</v>
+        <v>250</v>
       </c>
       <c r="C142" t="s">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="D142" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="E142" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="F142" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="G142" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="O142" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="Q142" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="R142" t="s">
-        <v>297</v>
+        <v>264</v>
       </c>
       <c r="S142" t="s">
-        <v>294</v>
+        <v>232</v>
       </c>
       <c r="T142" t="s">
-        <v>277</v>
+        <v>94</v>
       </c>
     </row>
     <row r="143" spans="1:20">
       <c r="B143" t="s">
-        <v>372</v>
+        <v>321</v>
       </c>
       <c r="C143" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="D143" t="s">
-        <v>236</v>
+        <v>285</v>
       </c>
       <c r="E143" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="F143" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="G143" t="s">
-        <v>292</v>
+        <v>281</v>
+      </c>
+      <c r="O143" t="s">
+        <v>279</v>
       </c>
       <c r="Q143" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="R143" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="S143" t="s">
-        <v>224</v>
+        <v>294</v>
       </c>
       <c r="T143" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="144" spans="1:20">
       <c r="B144" t="s">
-        <v>373</v>
+        <v>372</v>
+      </c>
+      <c r="C144" t="s">
+        <v>243</v>
       </c>
       <c r="D144" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="E144" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="F144" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="G144" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="Q144" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="R144" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="S144" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="T144" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
     </row>
     <row r="145" spans="1:20">
       <c r="B145" t="s">
-        <v>275</v>
+        <v>373</v>
       </c>
       <c r="D145" t="s">
-        <v>262</v>
+        <v>249</v>
+      </c>
+      <c r="E145" t="s">
+        <v>304</v>
+      </c>
+      <c r="F145" t="s">
+        <v>302</v>
       </c>
       <c r="G145" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="Q145" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="R145" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="S145" t="s">
-        <v>276</v>
+        <v>238</v>
       </c>
       <c r="T145" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
     </row>
     <row r="146" spans="1:20">
       <c r="B146" t="s">
-        <v>316</v>
+        <v>275</v>
       </c>
       <c r="D146" t="s">
-        <v>274</v>
+        <v>262</v>
+      </c>
+      <c r="G146" t="s">
+        <v>310</v>
       </c>
       <c r="Q146" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="R146" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="S146" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="T146" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
     </row>
     <row r="147" spans="1:20">
       <c r="B147" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D147" t="s">
-        <v>286</v>
+        <v>274</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>315</v>
       </c>
       <c r="R147" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="S147" t="s">
-        <v>298</v>
+        <v>288</v>
+      </c>
+      <c r="T147" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="148" spans="1:20">
       <c r="B148" t="s">
-        <v>324</v>
+        <v>320</v>
+      </c>
+      <c r="D148" t="s">
+        <v>286</v>
       </c>
       <c r="R148" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="S148" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
     </row>
     <row r="149" spans="1:20">
       <c r="B149" t="s">
-        <v>325</v>
+        <v>324</v>
+      </c>
+      <c r="R149" t="s">
+        <v>318</v>
+      </c>
+      <c r="S149" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="150" spans="1:20">
       <c r="B150" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="151" spans="1:20">
       <c r="B151" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="152" spans="1:20">
       <c r="B152" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="153" spans="1:20">
       <c r="B153" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="154" spans="1:20">
+      <c r="B154" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="154" spans="1:20" s="6" customFormat="1">
-      <c r="A154" s="6" t="s">
+    <row r="155" spans="1:20" s="6" customFormat="1">
+      <c r="A155" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B154" s="6" t="s">
+      <c r="B155" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="C154" s="6" t="s">
+      <c r="C155" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="D154" s="6" t="s">
+      <c r="D155" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="E154" s="6" t="s">
+      <c r="E155" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="F154" s="6" t="s">
+      <c r="F155" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="G154" s="6" t="s">
+      <c r="G155" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="H154" s="6" t="s">
+      <c r="H155" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="I154" s="6" t="s">
+      <c r="I155" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="J154" s="6" t="s">
+      <c r="J155" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="K154" s="6" t="s">
+      <c r="K155" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="L154" s="6" t="s">
+      <c r="L155" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="M154" s="6" t="s">
+      <c r="M155" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="N154" s="6" t="s">
+      <c r="N155" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="O154" s="6" t="s">
+      <c r="O155" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="P154" s="6" t="s">
+      <c r="P155" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="Q154" s="6" t="s">
+      <c r="Q155" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="R154" s="6" t="s">
+      <c r="R155" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="S154" s="6" t="s">
+      <c r="S155" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="T154" s="6" t="s">
+      <c r="T155" s="6" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="157" spans="1:20" ht="15">
-      <c r="A157" s="7" t="s">
+    <row r="158" spans="1:20" ht="15">
+      <c r="A158" s="7" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="158" spans="1:20">
-      <c r="A158" s="2" t="s">
+    <row r="159" spans="1:20">
+      <c r="A159" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B158" s="28" t="s">
+      <c r="B159" s="28" t="s">
         <v>377</v>
       </c>
-      <c r="C158" s="28"/>
-      <c r="D158" s="28"/>
-      <c r="E158" s="28"/>
-      <c r="F158" s="28"/>
-      <c r="G158" s="28"/>
-      <c r="H158" s="28"/>
-      <c r="I158" s="28"/>
-      <c r="J158" s="28"/>
-      <c r="K158" s="28"/>
-      <c r="L158" s="28"/>
-      <c r="M158" s="28"/>
-      <c r="N158" s="28"/>
-    </row>
-    <row r="159" spans="1:20" s="12" customFormat="1" ht="15">
-      <c r="A159" s="3" t="s">
+      <c r="C159" s="28"/>
+      <c r="D159" s="28"/>
+      <c r="E159" s="28"/>
+      <c r="F159" s="28"/>
+      <c r="G159" s="28"/>
+      <c r="H159" s="28"/>
+      <c r="I159" s="28"/>
+      <c r="J159" s="28"/>
+      <c r="K159" s="28"/>
+      <c r="L159" s="28"/>
+      <c r="M159" s="28"/>
+      <c r="N159" s="28"/>
+    </row>
+    <row r="160" spans="1:20" s="12" customFormat="1" ht="15">
+      <c r="A160" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B159" s="8" t="s">
+      <c r="B160" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="C159" s="8" t="s">
+      <c r="C160" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="D159" s="8" t="s">
+      <c r="D160" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="E159" s="9" t="s">
+      <c r="E160" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="F159" s="10" t="s">
+      <c r="F160" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="G159" s="11" t="s">
+      <c r="G160" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="H159" s="11" t="s">
+      <c r="H160" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="I159" s="11" t="s">
+      <c r="I160" s="11" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="160" spans="1:20" ht="28.5">
-      <c r="B160" s="13" t="s">
+    <row r="161" spans="2:9" ht="28.5">
+      <c r="B161" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="C160" t="s">
+      <c r="C161" t="s">
         <v>387</v>
       </c>
-      <c r="D160" t="s">
+      <c r="D161" t="s">
         <v>388</v>
-      </c>
-      <c r="E160" t="s">
-        <v>389</v>
-      </c>
-      <c r="F160" s="14" t="s">
-        <v>390</v>
-      </c>
-      <c r="G160" t="s">
-        <v>391</v>
-      </c>
-      <c r="H160" t="s">
-        <v>406</v>
-      </c>
-      <c r="I160" s="15" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="161" spans="2:9">
-      <c r="B161" t="s">
-        <v>394</v>
-      </c>
-      <c r="C161" t="s">
-        <v>395</v>
-      </c>
-      <c r="D161" t="s">
-        <v>396</v>
       </c>
       <c r="E161" t="s">
         <v>389</v>
       </c>
-      <c r="F161" t="s">
+      <c r="F161" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="G161" t="s">
+        <v>391</v>
+      </c>
+      <c r="H161" t="s">
+        <v>406</v>
+      </c>
+      <c r="I161" s="15" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="162" spans="2:9">
+      <c r="B162" t="s">
+        <v>394</v>
+      </c>
+      <c r="C162" t="s">
+        <v>395</v>
+      </c>
+      <c r="D162" t="s">
+        <v>396</v>
+      </c>
+      <c r="E162" t="s">
+        <v>389</v>
+      </c>
+      <c r="F162" t="s">
         <v>404</v>
       </c>
-      <c r="G161" t="s">
+      <c r="G162" t="s">
         <v>397</v>
       </c>
-      <c r="H161" t="s">
+      <c r="H162" t="s">
         <v>414</v>
       </c>
-      <c r="I161" s="15" t="s">
+      <c r="I162" s="15" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="162" spans="2:9" ht="28.5">
-      <c r="B162" s="16" t="s">
+    <row r="163" spans="2:9" ht="28.5">
+      <c r="B163" s="16" t="s">
         <v>400</v>
       </c>
-      <c r="C162" s="16" t="s">
+      <c r="C163" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="D162" t="s">
+      <c r="D163" t="s">
         <v>402</v>
       </c>
-      <c r="E162" t="s">
+      <c r="E163" t="s">
         <v>403</v>
       </c>
-      <c r="F162" s="14" t="s">
+      <c r="F163" s="14" t="s">
         <v>412</v>
       </c>
-      <c r="G162" t="s">
+      <c r="G163" t="s">
         <v>405</v>
       </c>
-      <c r="H162" t="s">
+      <c r="H163" t="s">
         <v>420</v>
       </c>
-      <c r="I162" s="17" t="s">
+      <c r="I163" s="17" t="s">
         <v>407</v>
-      </c>
-    </row>
-    <row r="163" spans="2:9">
-      <c r="B163" t="s">
-        <v>408</v>
-      </c>
-      <c r="C163" t="s">
-        <v>409</v>
-      </c>
-      <c r="D163" t="s">
-        <v>410</v>
-      </c>
-      <c r="E163" t="s">
-        <v>411</v>
-      </c>
-      <c r="F163" s="14" t="s">
-        <v>461</v>
-      </c>
-      <c r="G163" t="s">
-        <v>413</v>
-      </c>
-      <c r="H163" t="s">
-        <v>426</v>
-      </c>
-      <c r="I163" s="15" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="164" spans="2:9">
       <c r="B164" t="s">
+        <v>408</v>
+      </c>
+      <c r="C164" t="s">
+        <v>409</v>
+      </c>
+      <c r="D164" t="s">
+        <v>410</v>
+      </c>
+      <c r="E164" t="s">
+        <v>411</v>
+      </c>
+      <c r="F164" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="G164" t="s">
+        <v>413</v>
+      </c>
+      <c r="H164" t="s">
+        <v>426</v>
+      </c>
+      <c r="I164" s="15" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="165" spans="2:9">
+      <c r="B165" t="s">
         <v>416</v>
       </c>
-      <c r="C164" t="s">
+      <c r="C165" t="s">
         <v>417</v>
       </c>
-      <c r="E164" t="s">
+      <c r="E165" t="s">
         <v>418</v>
       </c>
-      <c r="F164" t="s">
+      <c r="F165" t="s">
         <v>463</v>
       </c>
-      <c r="G164" t="s">
+      <c r="G165" t="s">
         <v>419</v>
       </c>
-      <c r="H164" t="s">
+      <c r="H165" t="s">
         <v>432</v>
       </c>
-      <c r="I164" s="15" t="s">
+      <c r="I165" s="15" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="165" spans="2:9" ht="15">
-      <c r="B165" t="s">
+    <row r="166" spans="2:9" ht="15">
+      <c r="B166" t="s">
         <v>422</v>
       </c>
-      <c r="C165" t="s">
+      <c r="C166" t="s">
         <v>423</v>
       </c>
-      <c r="E165" t="s">
+      <c r="E166" t="s">
         <v>424</v>
       </c>
-      <c r="F165" t="s">
+      <c r="F166" t="s">
         <v>390</v>
       </c>
-      <c r="G165" s="18"/>
-      <c r="I165" s="15" t="s">
+      <c r="G166" s="18"/>
+      <c r="I166" s="15" t="s">
         <v>433</v>
-      </c>
-    </row>
-    <row r="166" spans="2:9">
-      <c r="B166" t="s">
-        <v>428</v>
-      </c>
-      <c r="C166" t="s">
-        <v>429</v>
-      </c>
-      <c r="E166" t="s">
-        <v>430</v>
-      </c>
-      <c r="F166" t="s">
-        <v>404</v>
-      </c>
-      <c r="I166" s="19" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="167" spans="2:9">
       <c r="B167" t="s">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="C167" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="E167" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F167" t="s">
-        <v>468</v>
+        <v>404</v>
       </c>
       <c r="I167" s="19" t="s">
-        <v>638</v>
+        <v>437</v>
       </c>
     </row>
     <row r="168" spans="2:9">
       <c r="B168" t="s">
+        <v>394</v>
+      </c>
+      <c r="C168" t="s">
+        <v>434</v>
+      </c>
+      <c r="E168" t="s">
+        <v>435</v>
+      </c>
+      <c r="F168" t="s">
+        <v>468</v>
+      </c>
+      <c r="I168" s="19" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="169" spans="2:9">
+      <c r="B169" t="s">
         <v>438</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C169" t="s">
         <v>439</v>
       </c>
-      <c r="E168" t="s">
+      <c r="E169" t="s">
         <v>440</v>
       </c>
-      <c r="F168" t="s">
+      <c r="F169" t="s">
         <v>412</v>
       </c>
-      <c r="I168" s="15" t="s">
+      <c r="I169" s="15" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="169" spans="2:9" ht="28.5">
-      <c r="B169" s="14" t="s">
+    <row r="170" spans="2:9" ht="28.5">
+      <c r="B170" s="14" t="s">
         <v>443</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C170" t="s">
         <v>444</v>
       </c>
-      <c r="E169" t="s">
+      <c r="E170" t="s">
         <v>445</v>
       </c>
-      <c r="F169" t="s">
+      <c r="F170" t="s">
         <v>425</v>
       </c>
-      <c r="I169" s="15" t="s">
+      <c r="I170" s="15" t="s">
         <v>447</v>
-      </c>
-    </row>
-    <row r="170" spans="2:9">
-      <c r="B170" t="s">
-        <v>448</v>
-      </c>
-      <c r="C170" t="s">
-        <v>429</v>
-      </c>
-      <c r="F170" t="s">
-        <v>431</v>
-      </c>
-      <c r="I170" s="15" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="171" spans="2:9">
       <c r="B171" t="s">
-        <v>394</v>
+        <v>448</v>
       </c>
       <c r="C171" t="s">
-        <v>451</v>
+        <v>429</v>
       </c>
       <c r="F171" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="I171" s="15" t="s">
-        <v>450</v>
+        <v>644</v>
       </c>
     </row>
     <row r="172" spans="2:9">
       <c r="B172" t="s">
-        <v>453</v>
+        <v>394</v>
       </c>
       <c r="C172" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F172" t="s">
-        <v>441</v>
-      </c>
-      <c r="I172" t="s">
-        <v>421</v>
+        <v>436</v>
+      </c>
+      <c r="I172" s="15" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="173" spans="2:9">
       <c r="B173" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C173" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F173" t="s">
-        <v>446</v>
-      </c>
-      <c r="I173" s="27" t="s">
-        <v>645</v>
+        <v>441</v>
+      </c>
+      <c r="I173" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="174" spans="2:9">
       <c r="B174" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C174" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F174" t="s">
-        <v>449</v>
-      </c>
-      <c r="I174" t="s">
-        <v>442</v>
+        <v>446</v>
+      </c>
+      <c r="I174" s="27" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="175" spans="2:9">
       <c r="B175" t="s">
-        <v>408</v>
+        <v>459</v>
       </c>
       <c r="C175" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F175" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I175" t="s">
-        <v>646</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="2:9">
       <c r="B176" t="s">
+        <v>408</v>
+      </c>
+      <c r="C176" t="s">
+        <v>462</v>
+      </c>
+      <c r="F176" t="s">
+        <v>452</v>
+      </c>
+      <c r="I176" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="177" spans="1:20">
+      <c r="B177" t="s">
         <v>464</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C177" t="s">
         <v>465</v>
       </c>
-      <c r="F176" t="s">
+      <c r="F177" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="177" spans="1:20" ht="15">
-      <c r="B177" t="s">
+    <row r="178" spans="1:20" ht="15">
+      <c r="B178" t="s">
         <v>466</v>
       </c>
-      <c r="C177" s="20" t="s">
+      <c r="C178" s="20" t="s">
         <v>467</v>
       </c>
-      <c r="F177" t="s">
+      <c r="F178" t="s">
         <v>458</v>
-      </c>
-    </row>
-    <row r="178" spans="1:20">
-      <c r="B178" t="s">
-        <v>416</v>
-      </c>
-      <c r="C178" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="179" spans="1:20">
       <c r="B179" t="s">
-        <v>469</v>
+        <v>416</v>
       </c>
       <c r="C179" t="s">
-        <v>637</v>
+        <v>489</v>
       </c>
     </row>
     <row r="180" spans="1:20">
       <c r="B180" t="s">
-        <v>470</v>
+        <v>469</v>
+      </c>
+      <c r="C180" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="181" spans="1:20">
       <c r="B181" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="182" spans="1:20">
       <c r="B182" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="183" spans="1:20">
+      <c r="B183" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="183" spans="1:20">
-      <c r="B183" s="21" t="s">
+    <row r="184" spans="1:20">
+      <c r="B184" s="21" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="184" spans="1:20" ht="15">
-      <c r="A184" s="4" t="s">
+    <row r="185" spans="1:20" ht="15">
+      <c r="A185" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B184" s="22" t="s">
+      <c r="B185" s="22" t="s">
         <v>474</v>
       </c>
-      <c r="C184" s="22" t="s">
+      <c r="C185" s="22" t="s">
         <v>475</v>
       </c>
-      <c r="D184" s="22" t="s">
+      <c r="D185" s="22" t="s">
         <v>476</v>
       </c>
-      <c r="E184" s="23" t="s">
+      <c r="E185" s="23" t="s">
         <v>477</v>
       </c>
-      <c r="F184" s="24" t="s">
+      <c r="F185" s="24" t="s">
         <v>478</v>
       </c>
-      <c r="G184" s="22" t="s">
+      <c r="G185" s="22" t="s">
         <v>479</v>
       </c>
-      <c r="H184" s="22" t="s">
+      <c r="H185" s="22" t="s">
         <v>480</v>
       </c>
-      <c r="I184" s="22" t="s">
+      <c r="I185" s="22" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="186" spans="1:20" ht="15">
-      <c r="A186" s="2" t="s">
+    <row r="187" spans="1:20" ht="15">
+      <c r="A187" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B186" s="29" t="s">
+      <c r="B187" s="29" t="s">
         <v>482</v>
       </c>
-      <c r="C186" s="29"/>
-      <c r="D186" s="29"/>
-      <c r="E186" s="29"/>
-      <c r="F186" s="29"/>
-      <c r="G186" s="29"/>
-      <c r="H186" s="29"/>
-      <c r="I186" s="30"/>
-      <c r="J186" s="30"/>
-      <c r="K186" s="30"/>
-      <c r="L186" s="30"/>
-      <c r="M186" s="30"/>
-      <c r="N186" s="30"/>
-      <c r="O186" s="30"/>
-      <c r="P186" s="30"/>
-      <c r="Q186" s="30"/>
-      <c r="R186" s="30"/>
-      <c r="S186" s="30"/>
-      <c r="T186" s="30"/>
-    </row>
-    <row r="187" spans="1:20" s="5" customFormat="1">
-      <c r="A187" s="5" t="s">
+      <c r="C187" s="29"/>
+      <c r="D187" s="29"/>
+      <c r="E187" s="29"/>
+      <c r="F187" s="29"/>
+      <c r="G187" s="29"/>
+      <c r="H187" s="29"/>
+      <c r="I187" s="30"/>
+      <c r="J187" s="30"/>
+      <c r="K187" s="30"/>
+      <c r="L187" s="30"/>
+      <c r="M187" s="30"/>
+      <c r="N187" s="30"/>
+      <c r="O187" s="30"/>
+      <c r="P187" s="30"/>
+      <c r="Q187" s="30"/>
+      <c r="R187" s="30"/>
+      <c r="S187" s="30"/>
+      <c r="T187" s="30"/>
+    </row>
+    <row r="188" spans="1:20" s="5" customFormat="1">
+      <c r="A188" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B187" s="5" t="s">
+      <c r="B188" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="C187" s="5" t="s">
+      <c r="C188" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="D187" s="5" t="s">
+      <c r="D188" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="E187" s="5" t="s">
+      <c r="E188" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="F187" s="5" t="s">
+      <c r="F188" s="5" t="s">
         <v>619</v>
       </c>
-      <c r="G187" s="5" t="s">
+      <c r="G188" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="H187" s="5" t="s">
+      <c r="H188" s="5" t="s">
         <v>620</v>
-      </c>
-    </row>
-    <row r="188" spans="1:20">
-      <c r="B188" t="s">
-        <v>387</v>
-      </c>
-      <c r="C188" t="s">
-        <v>386</v>
-      </c>
-      <c r="D188" t="s">
-        <v>388</v>
-      </c>
-      <c r="E188" t="s">
-        <v>391</v>
-      </c>
-      <c r="F188" t="s">
-        <v>390</v>
-      </c>
-      <c r="G188" t="s">
-        <v>398</v>
-      </c>
-      <c r="H188" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="189" spans="1:20">
       <c r="B189" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C189" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="D189" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="E189" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="F189" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="G189" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="H189" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
     </row>
     <row r="190" spans="1:20">
       <c r="B190" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C190" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="D190" t="s">
-        <v>488</v>
+        <v>402</v>
       </c>
       <c r="E190" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F190" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="G190" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="H190" t="s">
-        <v>389</v>
+        <v>424</v>
       </c>
     </row>
     <row r="191" spans="1:20">
       <c r="B191" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="C191" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="D191" t="s">
-        <v>630</v>
+        <v>488</v>
       </c>
       <c r="E191" t="s">
-        <v>489</v>
+        <v>397</v>
       </c>
       <c r="F191" t="s">
-        <v>461</v>
+        <v>412</v>
       </c>
       <c r="G191" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="H191" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
     </row>
     <row r="192" spans="1:20">
       <c r="B192" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C192" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D192" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E192" t="s">
-        <v>419</v>
+        <v>489</v>
       </c>
       <c r="F192" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G192" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="H192" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
     </row>
     <row r="193" spans="2:8">
       <c r="B193" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C193" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="D193" t="s">
-        <v>410</v>
+        <v>629</v>
       </c>
       <c r="E193" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F193" t="s">
-        <v>390</v>
+        <v>463</v>
       </c>
       <c r="G193" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="H193" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="194" spans="2:8">
       <c r="B194" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C194" t="s">
-        <v>438</v>
+        <v>428</v>
+      </c>
+      <c r="D194" t="s">
+        <v>410</v>
+      </c>
+      <c r="E194" t="s">
+        <v>417</v>
       </c>
       <c r="F194" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="G194" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="H194" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
     </row>
     <row r="195" spans="2:8">
       <c r="B195" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C195" t="s">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="F195" t="s">
-        <v>468</v>
+        <v>404</v>
+      </c>
+      <c r="G195" t="s">
+        <v>432</v>
       </c>
       <c r="H195" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="196" spans="2:8">
       <c r="B196" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C196" t="s">
-        <v>408</v>
+        <v>459</v>
       </c>
       <c r="F196" t="s">
-        <v>412</v>
+        <v>468</v>
       </c>
       <c r="H196" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
     </row>
     <row r="197" spans="2:8">
       <c r="B197" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C197" t="s">
-        <v>464</v>
+        <v>408</v>
       </c>
       <c r="F197" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="H197" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
     </row>
     <row r="198" spans="2:8">
       <c r="B198" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="C198" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F198" t="s">
-        <v>431</v>
+        <v>425</v>
+      </c>
+      <c r="H198" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="199" spans="2:8">
       <c r="B199" t="s">
-        <v>451</v>
+        <v>429</v>
       </c>
       <c r="C199" t="s">
-        <v>416</v>
+        <v>466</v>
       </c>
       <c r="F199" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="200" spans="2:8">
       <c r="B200" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="C200" t="s">
-        <v>469</v>
+        <v>416</v>
       </c>
       <c r="F200" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="201" spans="2:8">
       <c r="B201" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="C201" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F201" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="202" spans="2:8">
       <c r="B202" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C202" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F202" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="203" spans="2:8">
       <c r="B203" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C203" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F203" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="204" spans="2:8">
       <c r="B204" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C204" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F204" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="205" spans="2:8">
       <c r="B205" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C205" t="s">
-        <v>410</v>
+        <v>473</v>
       </c>
       <c r="F205" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="206" spans="2:8">
       <c r="B206" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="C206" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="F206" t="s">
-        <v>396</v>
+        <v>458</v>
       </c>
     </row>
     <row r="207" spans="2:8">
       <c r="B207" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C207" t="s">
-        <v>407</v>
+        <v>399</v>
+      </c>
+      <c r="F207" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="208" spans="2:8">
       <c r="B208" t="s">
+        <v>448</v>
+      </c>
+      <c r="C208" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8">
+      <c r="B209" t="s">
         <v>394</v>
       </c>
-      <c r="C208" t="s">
+      <c r="C209" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="209" spans="1:14">
-      <c r="B209" t="s">
+    <row r="210" spans="1:8">
+      <c r="B210" t="s">
         <v>453</v>
       </c>
-      <c r="C209" t="s">
+      <c r="C210" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="210" spans="1:14">
-      <c r="B210" t="s">
+    <row r="211" spans="1:8">
+      <c r="B211" t="s">
         <v>456</v>
       </c>
-      <c r="C210" t="s">
+      <c r="C211" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="211" spans="1:14">
-      <c r="B211" t="s">
+    <row r="212" spans="1:8">
+      <c r="B212" t="s">
         <v>394</v>
       </c>
-      <c r="C211" t="s">
+      <c r="C212" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="212" spans="1:14">
-      <c r="C212" t="s">
+    <row r="213" spans="1:8">
+      <c r="C213" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="213" spans="1:14">
-      <c r="C213" t="s">
+    <row r="214" spans="1:8">
+      <c r="C214" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="214" spans="1:14">
-      <c r="C214" t="s">
+    <row r="215" spans="1:8">
+      <c r="C215" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="215" spans="1:14">
-      <c r="C215" t="s">
+    <row r="216" spans="1:8">
+      <c r="C216" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="216" spans="1:14">
-      <c r="C216" t="s">
+    <row r="217" spans="1:8">
+      <c r="C217" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="217" spans="1:14">
-      <c r="C217" t="s">
+    <row r="218" spans="1:8">
+      <c r="C218" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="218" spans="1:14">
-      <c r="C218" t="s">
+    <row r="219" spans="1:8">
+      <c r="C219" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="219" spans="1:14">
-      <c r="C219" t="s">
+    <row r="220" spans="1:8">
+      <c r="C220" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="220" spans="1:14">
-      <c r="C220" t="s">
+    <row r="221" spans="1:8">
+      <c r="C221" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="221" spans="1:14" s="6" customFormat="1">
-      <c r="A221" s="6" t="s">
+    <row r="222" spans="1:8" s="6" customFormat="1">
+      <c r="A222" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B221" s="6" t="s">
+      <c r="B222" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="C221" s="6" t="s">
+      <c r="C222" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="D221" s="6" t="s">
+      <c r="D222" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="E221" s="6" t="s">
+      <c r="E222" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="F221" s="6" t="s">
+      <c r="F222" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="G221" s="6" t="s">
+      <c r="G222" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="H221" s="6" t="s">
+      <c r="H222" s="6" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="223" spans="1:14" ht="15">
-      <c r="A223" s="7" t="s">
+    <row r="224" spans="1:8" ht="15">
+      <c r="A224" s="7" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="224" spans="1:14">
-      <c r="A224" s="2" t="s">
+    <row r="225" spans="1:14">
+      <c r="A225" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B224" s="28" t="s">
+      <c r="B225" s="28" t="s">
         <v>491</v>
       </c>
-      <c r="C224" s="28"/>
-      <c r="D224" s="28"/>
-      <c r="E224" s="28"/>
-      <c r="F224" s="28"/>
-      <c r="G224" s="28"/>
-      <c r="H224" s="28"/>
-      <c r="I224" s="28"/>
-      <c r="J224" s="28"/>
-      <c r="K224" s="28"/>
-      <c r="L224" s="28"/>
-      <c r="M224" s="28"/>
-      <c r="N224" s="28"/>
-    </row>
-    <row r="225" spans="1:11" s="3" customFormat="1">
-      <c r="A225" s="3" t="s">
+      <c r="C225" s="28"/>
+      <c r="D225" s="28"/>
+      <c r="E225" s="28"/>
+      <c r="F225" s="28"/>
+      <c r="G225" s="28"/>
+      <c r="H225" s="28"/>
+      <c r="I225" s="28"/>
+      <c r="J225" s="28"/>
+      <c r="K225" s="28"/>
+      <c r="L225" s="28"/>
+      <c r="M225" s="28"/>
+      <c r="N225" s="28"/>
+    </row>
+    <row r="226" spans="1:14" s="3" customFormat="1">
+      <c r="A226" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B225" s="3" t="s">
+      <c r="B226" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="C225" s="3" t="s">
+      <c r="C226" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="D225" s="3" t="s">
+      <c r="D226" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="E225" s="3" t="s">
+      <c r="E226" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="F225" s="3" t="s">
+      <c r="F226" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="G225" s="3" t="s">
+      <c r="G226" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="H225" s="3" t="s">
+      <c r="H226" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="I225" s="3" t="s">
+      <c r="I226" s="3" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="226" spans="1:11" ht="15">
-      <c r="B226" t="s">
+    <row r="227" spans="1:14" ht="15">
+      <c r="B227" t="s">
         <v>551</v>
       </c>
-      <c r="C226" t="s">
+      <c r="C227" t="s">
         <v>505</v>
       </c>
-      <c r="D226" t="s">
+      <c r="D227" t="s">
         <v>534</v>
       </c>
-      <c r="E226" t="s">
+      <c r="E227" t="s">
         <v>543</v>
       </c>
-      <c r="F226" t="s">
+      <c r="F227" t="s">
         <v>502</v>
       </c>
-      <c r="G226" t="s">
+      <c r="G227" t="s">
         <v>503</v>
       </c>
-      <c r="H226" s="20" t="s">
+      <c r="H227" s="20" t="s">
         <v>509</v>
       </c>
-      <c r="I226" t="s">
+      <c r="I227" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="227" spans="1:11">
-      <c r="B227" t="s">
+    <row r="228" spans="1:14">
+      <c r="B228" t="s">
         <v>539</v>
       </c>
-      <c r="C227" t="s">
+      <c r="C228" t="s">
         <v>511</v>
       </c>
-      <c r="D227" t="s">
+      <c r="D228" t="s">
         <v>500</v>
       </c>
-      <c r="E227" t="s">
+      <c r="E228" t="s">
         <v>501</v>
       </c>
-      <c r="G227" t="s">
+      <c r="G228" t="s">
         <v>508</v>
       </c>
-      <c r="H227" t="s">
+      <c r="H228" t="s">
         <v>513</v>
       </c>
-      <c r="I227" t="s">
+      <c r="I228" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="228" spans="1:11">
-      <c r="B228" t="s">
+    <row r="229" spans="1:14">
+      <c r="B229" t="s">
         <v>621</v>
       </c>
-      <c r="C228" t="s">
+      <c r="C229" t="s">
         <v>515</v>
       </c>
-      <c r="D228" t="s">
+      <c r="D229" t="s">
         <v>623</v>
       </c>
-      <c r="E228" t="s">
+      <c r="E229" t="s">
         <v>624</v>
       </c>
-      <c r="H228" t="s">
+      <c r="H229" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="229" spans="1:11">
-      <c r="B229" t="s">
+    <row r="230" spans="1:14">
+      <c r="B230" t="s">
         <v>549</v>
       </c>
-      <c r="C229" t="s">
+      <c r="C230" t="s">
         <v>519</v>
       </c>
-      <c r="D229" t="s">
+      <c r="D230" t="s">
         <v>580</v>
       </c>
-      <c r="E229" t="s">
+      <c r="E230" t="s">
         <v>625</v>
       </c>
-      <c r="H229" t="s">
+      <c r="H230" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="230" spans="1:11">
-      <c r="B230" t="s">
+    <row r="231" spans="1:14">
+      <c r="B231" t="s">
         <v>514</v>
       </c>
-      <c r="C230" t="s">
+      <c r="C231" t="s">
         <v>523</v>
       </c>
-      <c r="D230" t="s">
+      <c r="D231" t="s">
         <v>506</v>
       </c>
-      <c r="E230" t="s">
+      <c r="E231" t="s">
         <v>512</v>
       </c>
-      <c r="H230" t="s">
+      <c r="H231" t="s">
         <v>531</v>
       </c>
-      <c r="K230" s="26"/>
-    </row>
-    <row r="231" spans="1:11">
-      <c r="B231" t="s">
+      <c r="K231" s="26"/>
+    </row>
+    <row r="232" spans="1:14">
+      <c r="B232" t="s">
         <v>552</v>
       </c>
-      <c r="C231" t="s">
+      <c r="C232" t="s">
         <v>528</v>
       </c>
-      <c r="D231" t="s">
+      <c r="D232" t="s">
         <v>98</v>
       </c>
-      <c r="E231" t="s">
+      <c r="E232" t="s">
         <v>525</v>
       </c>
-      <c r="H231" t="s">
+      <c r="H232" t="s">
         <v>535</v>
       </c>
-      <c r="K231" s="25"/>
-    </row>
-    <row r="232" spans="1:11">
-      <c r="B232" t="s">
+      <c r="K232" s="25"/>
+    </row>
+    <row r="233" spans="1:14">
+      <c r="B233" t="s">
         <v>527</v>
       </c>
-      <c r="C232" t="s">
+      <c r="C233" t="s">
         <v>533</v>
       </c>
-      <c r="D232" t="s">
+      <c r="D233" t="s">
         <v>516</v>
       </c>
-      <c r="E232" t="s">
+      <c r="E233" t="s">
         <v>530</v>
       </c>
-      <c r="H232" t="s">
+      <c r="H233" t="s">
         <v>504</v>
       </c>
-      <c r="K232" s="26"/>
-    </row>
-    <row r="233" spans="1:11">
-      <c r="B233" t="s">
+      <c r="K233" s="26"/>
+    </row>
+    <row r="234" spans="1:14">
+      <c r="B234" t="s">
         <v>569</v>
       </c>
-      <c r="C233" t="s">
+      <c r="C234" t="s">
         <v>537</v>
       </c>
-      <c r="D233" t="s">
+      <c r="D234" t="s">
         <v>524</v>
       </c>
-      <c r="E233" t="s">
+      <c r="E234" t="s">
         <v>545</v>
       </c>
-      <c r="H233" t="s">
+      <c r="H234" t="s">
         <v>587</v>
       </c>
-      <c r="K233" s="25"/>
-    </row>
-    <row r="234" spans="1:11">
-      <c r="B234" t="s">
+      <c r="K234" s="25"/>
+    </row>
+    <row r="235" spans="1:14">
+      <c r="B235" t="s">
         <v>546</v>
       </c>
-      <c r="C234" t="s">
+      <c r="C235" t="s">
         <v>540</v>
       </c>
-      <c r="D234" t="s">
+      <c r="D235" t="s">
         <v>529</v>
       </c>
-      <c r="E234" t="s">
+      <c r="E235" t="s">
         <v>517</v>
       </c>
-      <c r="H234" t="s">
+      <c r="H235" t="s">
         <v>626</v>
       </c>
-      <c r="K234" s="26"/>
-    </row>
-    <row r="235" spans="1:11">
-      <c r="B235" t="s">
+      <c r="K235" s="26"/>
+    </row>
+    <row r="236" spans="1:14">
+      <c r="B236" t="s">
         <v>544</v>
       </c>
-      <c r="C235" t="s">
+      <c r="C236" t="s">
         <v>542</v>
       </c>
-      <c r="D235" t="s">
+      <c r="D236" t="s">
         <v>520</v>
       </c>
-      <c r="E235" t="s">
+      <c r="E236" t="s">
         <v>538</v>
       </c>
-      <c r="H235" t="s">
+      <c r="H236" t="s">
         <v>578</v>
       </c>
-      <c r="K235" s="25"/>
-    </row>
-    <row r="236" spans="1:11">
-      <c r="B236" t="s">
+      <c r="K236" s="25"/>
+    </row>
+    <row r="237" spans="1:14">
+      <c r="B237" t="s">
         <v>532</v>
       </c>
-      <c r="C236" t="s">
+      <c r="C237" t="s">
         <v>537</v>
       </c>
-      <c r="E236" t="s">
+      <c r="E237" t="s">
         <v>541</v>
       </c>
-      <c r="H236" t="s">
+      <c r="H237" t="s">
         <v>526</v>
       </c>
-      <c r="K236" s="26"/>
-    </row>
-    <row r="237" spans="1:11">
-      <c r="B237" t="s">
+      <c r="K237" s="26"/>
+    </row>
+    <row r="238" spans="1:14">
+      <c r="B238" t="s">
         <v>554</v>
       </c>
-      <c r="C237" t="s">
+      <c r="C238" t="s">
         <v>499</v>
       </c>
-      <c r="K237" s="25"/>
-    </row>
-    <row r="238" spans="1:11">
-      <c r="B238" t="s">
+      <c r="K238" s="25"/>
+    </row>
+    <row r="239" spans="1:14">
+      <c r="B239" t="s">
         <v>522</v>
       </c>
-      <c r="C238" t="s">
+      <c r="C239" t="s">
         <v>622</v>
       </c>
-      <c r="K238" s="26"/>
-    </row>
-    <row r="239" spans="1:11">
-      <c r="B239" t="s">
+      <c r="K239" s="26"/>
+    </row>
+    <row r="240" spans="1:14">
+      <c r="B240" t="s">
         <v>550</v>
       </c>
-      <c r="C239" t="s">
+      <c r="C240" t="s">
         <v>573</v>
       </c>
-      <c r="K239" s="25"/>
-    </row>
-    <row r="240" spans="1:11">
-      <c r="B240" t="s">
-        <v>547</v>
-      </c>
-      <c r="K240" s="26"/>
+      <c r="K240" s="25"/>
     </row>
     <row r="241" spans="1:20">
       <c r="B241" t="s">
-        <v>536</v>
-      </c>
-      <c r="K241" s="25"/>
+        <v>547</v>
+      </c>
+      <c r="K241" s="26"/>
     </row>
     <row r="242" spans="1:20">
       <c r="B242" t="s">
-        <v>548</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="K242" s="25"/>
     </row>
     <row r="243" spans="1:20">
       <c r="B243" t="s">
-        <v>510</v>
+        <v>548</v>
       </c>
     </row>
     <row r="244" spans="1:20">
       <c r="B244" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="245" spans="1:20">
+      <c r="B245" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="247" spans="1:20" s="4" customFormat="1">
-      <c r="A247" s="4" t="s">
+    <row r="248" spans="1:20" s="4" customFormat="1">
+      <c r="A248" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B247" s="4" t="s">
+      <c r="B248" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="C247" s="4" t="s">
+      <c r="C248" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="D247" s="4" t="s">
+      <c r="D248" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="E247" s="4" t="s">
+      <c r="E248" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="F247" s="4" t="s">
+      <c r="F248" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="G247" s="4" t="s">
+      <c r="G248" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="H247" s="4" t="s">
+      <c r="H248" s="4" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="249" spans="1:20" ht="15">
-      <c r="A249" s="2" t="s">
+    <row r="250" spans="1:20" ht="15">
+      <c r="A250" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B249" s="29" t="s">
+      <c r="B250" s="29" t="s">
         <v>562</v>
       </c>
-      <c r="C249" s="29"/>
-      <c r="D249" s="29"/>
-      <c r="E249" s="29"/>
-      <c r="F249" s="29"/>
-      <c r="G249" s="29"/>
-      <c r="H249" s="29"/>
-      <c r="I249" s="30"/>
-      <c r="J249" s="30"/>
-      <c r="K249" s="30"/>
-      <c r="L249" s="30"/>
-      <c r="M249" s="30"/>
-      <c r="N249" s="30"/>
-      <c r="O249" s="30"/>
-      <c r="P249" s="30"/>
-      <c r="Q249" s="30"/>
-      <c r="R249" s="30"/>
-      <c r="S249" s="30"/>
-      <c r="T249" s="30"/>
-    </row>
-    <row r="250" spans="1:20" s="5" customFormat="1">
-      <c r="A250" s="5" t="s">
+      <c r="C250" s="29"/>
+      <c r="D250" s="29"/>
+      <c r="E250" s="29"/>
+      <c r="F250" s="29"/>
+      <c r="G250" s="29"/>
+      <c r="H250" s="29"/>
+      <c r="I250" s="30"/>
+      <c r="J250" s="30"/>
+      <c r="K250" s="30"/>
+      <c r="L250" s="30"/>
+      <c r="M250" s="30"/>
+      <c r="N250" s="30"/>
+      <c r="O250" s="30"/>
+      <c r="P250" s="30"/>
+      <c r="Q250" s="30"/>
+      <c r="R250" s="30"/>
+      <c r="S250" s="30"/>
+      <c r="T250" s="30"/>
+    </row>
+    <row r="251" spans="1:20" s="5" customFormat="1">
+      <c r="A251" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B250" s="5" t="s">
+      <c r="B251" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="C250" s="5" t="s">
+      <c r="C251" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="D250" s="5" t="s">
+      <c r="D251" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="E250" s="5" t="s">
+      <c r="E251" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="F250" s="5" t="s">
+      <c r="F251" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="G250" s="5" t="s">
+      <c r="G251" s="5" t="s">
         <v>568</v>
-      </c>
-    </row>
-    <row r="251" spans="1:20">
-      <c r="B251" t="s">
-        <v>553</v>
-      </c>
-      <c r="C251" t="s">
-        <v>551</v>
-      </c>
-      <c r="D251" t="s">
-        <v>543</v>
-      </c>
-      <c r="E251" t="s">
-        <v>572</v>
-      </c>
-      <c r="F251" t="s">
-        <v>534</v>
-      </c>
-      <c r="G251" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="252" spans="1:20">
       <c r="B252" t="s">
-        <v>633</v>
+        <v>553</v>
       </c>
       <c r="C252" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="D252" t="s">
-        <v>574</v>
+        <v>543</v>
       </c>
       <c r="E252" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="F252" t="s">
-        <v>500</v>
+        <v>534</v>
       </c>
       <c r="G252" t="s">
-        <v>540</v>
+        <v>505</v>
       </c>
     </row>
     <row r="253" spans="1:20">
       <c r="B253" t="s">
-        <v>504</v>
+        <v>633</v>
       </c>
       <c r="C253" t="s">
-        <v>621</v>
+        <v>539</v>
       </c>
       <c r="D253" t="s">
-        <v>501</v>
+        <v>574</v>
       </c>
       <c r="E253" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="F253" t="s">
-        <v>623</v>
+        <v>500</v>
       </c>
       <c r="G253" t="s">
-        <v>519</v>
+        <v>540</v>
       </c>
     </row>
     <row r="254" spans="1:20">
       <c r="B254" t="s">
-        <v>587</v>
+        <v>504</v>
       </c>
       <c r="C254" t="s">
-        <v>549</v>
+        <v>621</v>
       </c>
       <c r="D254" t="s">
-        <v>571</v>
+        <v>501</v>
+      </c>
+      <c r="E254" t="s">
+        <v>577</v>
       </c>
       <c r="F254" t="s">
-        <v>580</v>
+        <v>623</v>
       </c>
       <c r="G254" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:20">
       <c r="B255" t="s">
-        <v>521</v>
+        <v>587</v>
       </c>
       <c r="C255" t="s">
-        <v>514</v>
+        <v>549</v>
       </c>
       <c r="D255" t="s">
-        <v>624</v>
+        <v>571</v>
       </c>
       <c r="F255" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G255" t="s">
-        <v>537</v>
+        <v>511</v>
       </c>
     </row>
     <row r="256" spans="1:20">
       <c r="B256" t="s">
-        <v>626</v>
+        <v>521</v>
       </c>
       <c r="C256" t="s">
-        <v>552</v>
+        <v>514</v>
       </c>
       <c r="D256" t="s">
-        <v>581</v>
+        <v>624</v>
       </c>
       <c r="F256" t="s">
-        <v>506</v>
+        <v>579</v>
       </c>
       <c r="G256" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
     </row>
     <row r="257" spans="2:7">
       <c r="B257" t="s">
-        <v>584</v>
+        <v>626</v>
       </c>
       <c r="C257" t="s">
-        <v>527</v>
+        <v>552</v>
       </c>
       <c r="D257" t="s">
-        <v>625</v>
+        <v>581</v>
       </c>
       <c r="F257" t="s">
-        <v>98</v>
+        <v>506</v>
       </c>
       <c r="G257" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
     </row>
     <row r="258" spans="2:7">
       <c r="B258" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="C258" t="s">
-        <v>569</v>
+        <v>527</v>
       </c>
       <c r="D258" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="F258" t="s">
-        <v>516</v>
+        <v>98</v>
       </c>
       <c r="G258" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="259" spans="2:7">
       <c r="B259" t="s">
-        <v>535</v>
+        <v>570</v>
       </c>
       <c r="C259" t="s">
-        <v>546</v>
+        <v>569</v>
       </c>
       <c r="D259" t="s">
-        <v>589</v>
+        <v>627</v>
       </c>
       <c r="F259" t="s">
-        <v>576</v>
+        <v>516</v>
       </c>
       <c r="G259" t="s">
-        <v>586</v>
+        <v>542</v>
       </c>
     </row>
     <row r="260" spans="2:7">
       <c r="B260" t="s">
-        <v>582</v>
+        <v>535</v>
       </c>
       <c r="C260" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D260" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="F260" t="s">
-        <v>524</v>
+        <v>576</v>
       </c>
       <c r="G260" t="s">
-        <v>499</v>
+        <v>586</v>
       </c>
     </row>
     <row r="261" spans="2:7">
       <c r="B261" t="s">
-        <v>513</v>
+        <v>582</v>
       </c>
       <c r="C261" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="D261" t="s">
-        <v>512</v>
+        <v>583</v>
       </c>
       <c r="F261" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="G261" t="s">
-        <v>622</v>
+        <v>499</v>
       </c>
     </row>
     <row r="262" spans="2:7">
       <c r="B262" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C262" t="s">
-        <v>554</v>
+        <v>532</v>
       </c>
       <c r="D262" t="s">
-        <v>585</v>
+        <v>512</v>
       </c>
       <c r="F262" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="G262" t="s">
-        <v>573</v>
+        <v>622</v>
       </c>
     </row>
     <row r="263" spans="2:7">
       <c r="B263" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C263" t="s">
-        <v>522</v>
+        <v>554</v>
       </c>
       <c r="D263" t="s">
-        <v>525</v>
+        <v>585</v>
+      </c>
+      <c r="F263" t="s">
+        <v>520</v>
       </c>
       <c r="G263" t="s">
-        <v>533</v>
+        <v>573</v>
       </c>
     </row>
     <row r="264" spans="2:7">
       <c r="B264" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="C264" t="s">
-        <v>550</v>
+        <v>522</v>
       </c>
       <c r="D264" t="s">
-        <v>530</v>
+        <v>525</v>
+      </c>
+      <c r="G264" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="265" spans="2:7">
       <c r="B265" t="s">
-        <v>578</v>
+        <v>518</v>
       </c>
       <c r="C265" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D265" t="s">
-        <v>588</v>
+        <v>530</v>
       </c>
     </row>
     <row r="266" spans="2:7">
       <c r="B266" t="s">
+        <v>578</v>
+      </c>
+      <c r="C266" t="s">
+        <v>547</v>
+      </c>
+      <c r="D266" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="267" spans="2:7">
+      <c r="B267" t="s">
         <v>526</v>
       </c>
-      <c r="C266" t="s">
+      <c r="C267" t="s">
         <v>536</v>
       </c>
-      <c r="D266" t="s">
+      <c r="D267" t="s">
         <v>505</v>
-      </c>
-    </row>
-    <row r="267" spans="2:7">
-      <c r="C267" t="s">
-        <v>548</v>
-      </c>
-      <c r="D267" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="268" spans="2:7">
       <c r="C268" t="s">
+        <v>548</v>
+      </c>
+      <c r="D268" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="269" spans="2:7">
+      <c r="C269" t="s">
         <v>510</v>
       </c>
-      <c r="D268" t="s">
+      <c r="D269" t="s">
         <v>517</v>
-      </c>
-    </row>
-    <row r="269" spans="2:7">
-      <c r="D269" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="270" spans="2:7">
       <c r="D270" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="271" spans="2:7">
       <c r="D271" t="s">
-        <v>586</v>
+        <v>541</v>
       </c>
     </row>
     <row r="272" spans="2:7">
       <c r="D272" t="s">
-        <v>634</v>
+        <v>586</v>
       </c>
     </row>
     <row r="273" spans="1:8">
       <c r="D273" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8">
+      <c r="D274" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="274" spans="1:8" s="6" customFormat="1">
-      <c r="A274" s="6" t="s">
+    <row r="275" spans="1:8" s="6" customFormat="1">
+      <c r="A275" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B274" s="6" t="s">
+      <c r="B275" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="C274" s="6" t="s">
+      <c r="C275" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="D274" s="6" t="s">
+      <c r="D275" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="E274" s="6" t="s">
+      <c r="E275" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="F274" s="6" t="s">
+      <c r="F275" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="G274" s="6" t="s">
+      <c r="G275" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="H274" s="6" t="s">
+      <c r="H275" s="6" t="s">
         <v>590</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B158:N158"/>
-    <mergeCell ref="B186:T186"/>
-    <mergeCell ref="B224:N224"/>
-    <mergeCell ref="B249:T249"/>
+    <mergeCell ref="B159:N159"/>
+    <mergeCell ref="B187:T187"/>
+    <mergeCell ref="B225:N225"/>
+    <mergeCell ref="B250:T250"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B25:T25"/>
     <mergeCell ref="B49:N49"/>
     <mergeCell ref="B81:T81"/>
-    <mergeCell ref="B111:N111"/>
-    <mergeCell ref="B136:T136"/>
+    <mergeCell ref="B112:N112"/>
+    <mergeCell ref="B137:T137"/>
   </mergeCells>
-  <conditionalFormatting sqref="H227:H236">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="SBS-GADUNG-HW.MA5801-OLT-01">
-      <formula>NOT(ISERROR(SEARCH("SBS-GADUNG-HW.MA5801-OLT-01",H227)))</formula>
+  <conditionalFormatting sqref="H228:H237">
+    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="SBS-GADUNG-HW.MA5801-OLT-01">
+      <formula>NOT(ISERROR(SEARCH("SBS-GADUNG-HW.MA5801-OLT-01",H228)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/data/List_Team_Region.xlsx
+++ b/public/data/List_Team_Region.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yoss Work\App Retail SBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D8F6C2-3D61-48A7-924D-5064703A18D6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A93982-BCD2-4E03-BDE3-A0B12C2C0B70}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13110" yWindow="1245" windowWidth="13440" windowHeight="12105" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
+    <workbookView xWindow="13455" yWindow="1590" windowWidth="13440" windowHeight="12105" xr2:uid="{898F8E57-BF61-46D5-A697-E09D3664FD8A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="List Team Region" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
